--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,117 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
+    <t>02:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Minnesota Utd</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Phoenix Rising FC</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Rayo Vallecano</t>
+  </si>
+  <si>
+    <t>St Louis City SC</t>
+  </si>
+  <si>
+    <t>Criciuma</t>
+  </si>
+  <si>
+    <t>Cruzeiro MG</t>
+  </si>
+  <si>
+    <t>Atlanta Utd</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Austin FC</t>
+  </si>
+  <si>
+    <t>Colorado Switchbacks FC</t>
+  </si>
+  <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes</t>
+  </si>
+  <si>
+    <t>Alaves</t>
+  </si>
+  <si>
+    <t>2026-08-18 00:31:35</t>
   </si>
 </sst>
 </file>
@@ -585,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +941,2910 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2">
+        <v>3.55</v>
+      </c>
+      <c r="G2">
+        <v>3.7</v>
+      </c>
+      <c r="H2">
+        <v>2.02</v>
+      </c>
+      <c r="I2">
+        <v>2.08</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>4.3</v>
+      </c>
+      <c r="L2">
+        <v>1.27</v>
+      </c>
+      <c r="M2">
+        <v>1.03</v>
+      </c>
+      <c r="N2">
+        <v>6</v>
+      </c>
+      <c r="O2">
+        <v>1.18</v>
+      </c>
+      <c r="P2">
+        <v>2.68</v>
+      </c>
+      <c r="Q2">
+        <v>1.56</v>
+      </c>
+      <c r="R2">
+        <v>1.68</v>
+      </c>
+      <c r="S2">
+        <v>2.38</v>
+      </c>
+      <c r="T2">
+        <v>1.53</v>
+      </c>
+      <c r="U2">
+        <v>2.66</v>
+      </c>
+      <c r="V2">
+        <v>1.92</v>
+      </c>
+      <c r="W2">
+        <v>1.37</v>
+      </c>
+      <c r="X2">
+        <v>48</v>
+      </c>
+      <c r="Y2">
+        <v>16</v>
+      </c>
+      <c r="Z2">
+        <v>17</v>
+      </c>
+      <c r="AA2">
+        <v>38</v>
+      </c>
+      <c r="AB2">
+        <v>22</v>
+      </c>
+      <c r="AC2">
+        <v>11</v>
+      </c>
+      <c r="AD2">
+        <v>11.5</v>
+      </c>
+      <c r="AE2">
+        <v>18.5</v>
+      </c>
+      <c r="AF2">
+        <v>50</v>
+      </c>
+      <c r="AG2">
+        <v>16</v>
+      </c>
+      <c r="AH2">
+        <v>15.5</v>
+      </c>
+      <c r="AI2">
+        <v>40</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>65</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>300</v>
+      </c>
+      <c r="AN2">
+        <v>25</v>
+      </c>
+      <c r="AO2">
+        <v>9.6</v>
+      </c>
+      <c r="AP2">
+        <v>21</v>
+      </c>
+      <c r="AQ2">
+        <v>12</v>
+      </c>
+      <c r="AR2">
+        <v>12.5</v>
+      </c>
+      <c r="AS2">
+        <v>17.5</v>
+      </c>
+      <c r="AT2">
+        <v>15</v>
+      </c>
+      <c r="AU2">
+        <v>8.4</v>
+      </c>
+      <c r="AV2">
+        <v>9</v>
+      </c>
+      <c r="AW2">
+        <v>13.5</v>
+      </c>
+      <c r="AX2">
+        <v>24</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>12</v>
+      </c>
+      <c r="BA2">
+        <v>19.5</v>
+      </c>
+      <c r="BB2">
+        <v>42</v>
+      </c>
+      <c r="BC2">
+        <v>25</v>
+      </c>
+      <c r="BD2">
+        <v>25</v>
+      </c>
+      <c r="BE2">
+        <v>40</v>
+      </c>
+      <c r="BF2">
+        <v>16.5</v>
+      </c>
+      <c r="BG2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.1</v>
+      </c>
+      <c r="BJ2">
+        <v>11.5</v>
+      </c>
+      <c r="BK2">
+        <v>1.77</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>2.06</v>
+      </c>
+      <c r="BN2">
+        <v>10</v>
+      </c>
+      <c r="BO2">
+        <v>4.9</v>
+      </c>
+      <c r="BP2">
+        <v>34</v>
+      </c>
+      <c r="BQ2">
+        <v>1.98</v>
+      </c>
+      <c r="BR2">
+        <v>40</v>
+      </c>
+      <c r="BS2">
+        <v>1.99</v>
+      </c>
+      <c r="BT2">
+        <v>7.4</v>
+      </c>
+      <c r="BU2">
+        <v>3.8</v>
+      </c>
+      <c r="BV2">
+        <v>18.5</v>
+      </c>
+      <c r="BW2">
+        <v>1.88</v>
+      </c>
+      <c r="BX2">
+        <v>30</v>
+      </c>
+      <c r="BY2">
+        <v>1.96</v>
+      </c>
+      <c r="BZ2">
+        <v>20</v>
+      </c>
+      <c r="CA2">
+        <v>1.9</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3">
+        <v>2.26</v>
+      </c>
+      <c r="G3">
+        <v>110</v>
+      </c>
+      <c r="H3">
+        <v>2.88</v>
+      </c>
+      <c r="I3">
+        <v>990</v>
+      </c>
+      <c r="J3">
+        <v>1.55</v>
+      </c>
+      <c r="K3">
+        <v>950</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.42</v>
+      </c>
+      <c r="O3">
+        <v>1.56</v>
+      </c>
+      <c r="P3">
+        <v>1.43</v>
+      </c>
+      <c r="Q3">
+        <v>2.68</v>
+      </c>
+      <c r="R3">
+        <v>1.08</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <v>2.02</v>
+      </c>
+      <c r="U3">
+        <v>1.72</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+      <c r="W3">
+        <v>1.42</v>
+      </c>
+      <c r="X3">
+        <v>9.6</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.12</v>
+      </c>
+      <c r="AR3">
+        <v>1.12</v>
+      </c>
+      <c r="AS3">
+        <v>1.12</v>
+      </c>
+      <c r="AT3">
+        <v>1.12</v>
+      </c>
+      <c r="AU3">
+        <v>1.12</v>
+      </c>
+      <c r="AV3">
+        <v>1.12</v>
+      </c>
+      <c r="AW3">
+        <v>1.12</v>
+      </c>
+      <c r="AX3">
+        <v>1.12</v>
+      </c>
+      <c r="AY3">
+        <v>1.12</v>
+      </c>
+      <c r="AZ3">
+        <v>1.12</v>
+      </c>
+      <c r="BA3">
+        <v>1.12</v>
+      </c>
+      <c r="BB3">
+        <v>1.12</v>
+      </c>
+      <c r="BC3">
+        <v>1.12</v>
+      </c>
+      <c r="BD3">
+        <v>1.12</v>
+      </c>
+      <c r="BE3">
+        <v>1.12</v>
+      </c>
+      <c r="BF3">
+        <v>1.12</v>
+      </c>
+      <c r="BG3">
+        <v>1.12</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.04</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.04</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4">
+        <v>1.71</v>
+      </c>
+      <c r="G4">
+        <v>1.78</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
+      </c>
+      <c r="I4">
+        <v>6.6</v>
+      </c>
+      <c r="J4">
+        <v>3.75</v>
+      </c>
+      <c r="K4">
+        <v>4.1</v>
+      </c>
+      <c r="L4">
+        <v>1.32</v>
+      </c>
+      <c r="M4">
+        <v>1.07</v>
+      </c>
+      <c r="N4">
+        <v>3.4</v>
+      </c>
+      <c r="O4">
+        <v>1.33</v>
+      </c>
+      <c r="P4">
+        <v>1.8</v>
+      </c>
+      <c r="Q4">
+        <v>2.02</v>
+      </c>
+      <c r="R4">
+        <v>1.31</v>
+      </c>
+      <c r="S4">
+        <v>3.6</v>
+      </c>
+      <c r="T4">
+        <v>1.94</v>
+      </c>
+      <c r="U4">
+        <v>1.87</v>
+      </c>
+      <c r="V4">
+        <v>1.17</v>
+      </c>
+      <c r="W4">
+        <v>2.28</v>
+      </c>
+      <c r="X4">
+        <v>13.5</v>
+      </c>
+      <c r="Y4">
+        <v>19.5</v>
+      </c>
+      <c r="Z4">
+        <v>50</v>
+      </c>
+      <c r="AA4">
+        <v>190</v>
+      </c>
+      <c r="AB4">
+        <v>8</v>
+      </c>
+      <c r="AC4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>24</v>
+      </c>
+      <c r="AE4">
+        <v>100</v>
+      </c>
+      <c r="AF4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>23</v>
+      </c>
+      <c r="AI4">
+        <v>100</v>
+      </c>
+      <c r="AJ4">
+        <v>17.5</v>
+      </c>
+      <c r="AK4">
+        <v>19.5</v>
+      </c>
+      <c r="AL4">
+        <v>42</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
+        <v>12.5</v>
+      </c>
+      <c r="AO4">
+        <v>130</v>
+      </c>
+      <c r="AP4">
+        <v>11</v>
+      </c>
+      <c r="AQ4">
+        <v>16</v>
+      </c>
+      <c r="AR4">
+        <v>34</v>
+      </c>
+      <c r="AS4">
+        <v>11</v>
+      </c>
+      <c r="AT4">
+        <v>6.8</v>
+      </c>
+      <c r="AU4">
+        <v>7.6</v>
+      </c>
+      <c r="AV4">
+        <v>20</v>
+      </c>
+      <c r="AW4">
+        <v>10.5</v>
+      </c>
+      <c r="AX4">
+        <v>8.4</v>
+      </c>
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>19.5</v>
+      </c>
+      <c r="BA4">
+        <v>10.5</v>
+      </c>
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>16.5</v>
+      </c>
+      <c r="BD4">
+        <v>34</v>
+      </c>
+      <c r="BE4">
+        <v>11</v>
+      </c>
+      <c r="BF4">
+        <v>10</v>
+      </c>
+      <c r="BG4">
+        <v>11</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.94</v>
+      </c>
+      <c r="BJ4">
+        <v>14.5</v>
+      </c>
+      <c r="BK4">
+        <v>7.4</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.94</v>
+      </c>
+      <c r="BN4">
+        <v>5.3</v>
+      </c>
+      <c r="BO4">
+        <v>3</v>
+      </c>
+      <c r="BP4">
+        <v>15.5</v>
+      </c>
+      <c r="BQ4">
+        <v>7.8</v>
+      </c>
+      <c r="BR4">
+        <v>38</v>
+      </c>
+      <c r="BS4">
+        <v>1.85</v>
+      </c>
+      <c r="BT4">
+        <v>12.5</v>
+      </c>
+      <c r="BU4">
+        <v>6.4</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.89</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.9</v>
+      </c>
+      <c r="BZ4">
+        <v>32</v>
+      </c>
+      <c r="CA4">
+        <v>1.83</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5">
+        <v>1.83</v>
+      </c>
+      <c r="G5">
+        <v>1.88</v>
+      </c>
+      <c r="H5">
+        <v>4.3</v>
+      </c>
+      <c r="I5">
+        <v>4.8</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4.3</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.05</v>
+      </c>
+      <c r="N5">
+        <v>4.6</v>
+      </c>
+      <c r="O5">
+        <v>1.22</v>
+      </c>
+      <c r="P5">
+        <v>2.22</v>
+      </c>
+      <c r="Q5">
+        <v>1.74</v>
+      </c>
+      <c r="R5">
+        <v>1.5</v>
+      </c>
+      <c r="S5">
+        <v>2.8</v>
+      </c>
+      <c r="T5">
+        <v>1.7</v>
+      </c>
+      <c r="U5">
+        <v>2.28</v>
+      </c>
+      <c r="V5">
+        <v>1.27</v>
+      </c>
+      <c r="W5">
+        <v>2.12</v>
+      </c>
+      <c r="X5">
+        <v>27</v>
+      </c>
+      <c r="Y5">
+        <v>21</v>
+      </c>
+      <c r="Z5">
+        <v>38</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>11.5</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>19.5</v>
+      </c>
+      <c r="AE5">
+        <v>180</v>
+      </c>
+      <c r="AF5">
+        <v>13.5</v>
+      </c>
+      <c r="AG5">
+        <v>11</v>
+      </c>
+      <c r="AH5">
+        <v>18.5</v>
+      </c>
+      <c r="AI5">
+        <v>260</v>
+      </c>
+      <c r="AJ5">
+        <v>22</v>
+      </c>
+      <c r="AK5">
+        <v>19.5</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>10.5</v>
+      </c>
+      <c r="AO5">
+        <v>160</v>
+      </c>
+      <c r="AP5">
+        <v>14.5</v>
+      </c>
+      <c r="AQ5">
+        <v>14</v>
+      </c>
+      <c r="AR5">
+        <v>21</v>
+      </c>
+      <c r="AS5">
+        <v>36</v>
+      </c>
+      <c r="AT5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>13.5</v>
+      </c>
+      <c r="AW5">
+        <v>27</v>
+      </c>
+      <c r="AX5">
+        <v>10</v>
+      </c>
+      <c r="AY5">
+        <v>8.6</v>
+      </c>
+      <c r="AZ5">
+        <v>13.5</v>
+      </c>
+      <c r="BA5">
+        <v>28</v>
+      </c>
+      <c r="BB5">
+        <v>16.5</v>
+      </c>
+      <c r="BC5">
+        <v>13.5</v>
+      </c>
+      <c r="BD5">
+        <v>20</v>
+      </c>
+      <c r="BE5">
+        <v>42</v>
+      </c>
+      <c r="BF5">
+        <v>8.4</v>
+      </c>
+      <c r="BG5">
+        <v>26</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>2.8</v>
+      </c>
+      <c r="BJ5">
+        <v>13</v>
+      </c>
+      <c r="BK5">
+        <v>1.71</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.97</v>
+      </c>
+      <c r="BN5">
+        <v>6.4</v>
+      </c>
+      <c r="BO5">
+        <v>3.3</v>
+      </c>
+      <c r="BP5">
+        <v>17</v>
+      </c>
+      <c r="BQ5">
+        <v>1.77</v>
+      </c>
+      <c r="BR5">
+        <v>32</v>
+      </c>
+      <c r="BS5">
+        <v>1.86</v>
+      </c>
+      <c r="BT5">
+        <v>11</v>
+      </c>
+      <c r="BU5">
+        <v>5.3</v>
+      </c>
+      <c r="BV5">
+        <v>48</v>
+      </c>
+      <c r="BW5">
+        <v>1.9</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.91</v>
+      </c>
+      <c r="BZ5">
+        <v>25</v>
+      </c>
+      <c r="CA5">
+        <v>1.83</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6">
+        <v>1.94</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4.1</v>
+      </c>
+      <c r="J6">
+        <v>3.9</v>
+      </c>
+      <c r="K6">
+        <v>4.3</v>
+      </c>
+      <c r="L6">
+        <v>1.28</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>5.7</v>
+      </c>
+      <c r="O6">
+        <v>1.18</v>
+      </c>
+      <c r="P6">
+        <v>2.56</v>
+      </c>
+      <c r="Q6">
+        <v>1.56</v>
+      </c>
+      <c r="R6">
+        <v>1.67</v>
+      </c>
+      <c r="S6">
+        <v>2.36</v>
+      </c>
+      <c r="T6">
+        <v>1.54</v>
+      </c>
+      <c r="U6">
+        <v>2.68</v>
+      </c>
+      <c r="V6">
+        <v>1.32</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>29</v>
+      </c>
+      <c r="Y6">
+        <v>24</v>
+      </c>
+      <c r="Z6">
+        <v>65</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>14</v>
+      </c>
+      <c r="AC6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>18</v>
+      </c>
+      <c r="AE6">
+        <v>90</v>
+      </c>
+      <c r="AF6">
+        <v>16</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>15</v>
+      </c>
+      <c r="AI6">
+        <v>95</v>
+      </c>
+      <c r="AJ6">
+        <v>25</v>
+      </c>
+      <c r="AK6">
+        <v>18</v>
+      </c>
+      <c r="AL6">
+        <v>27</v>
+      </c>
+      <c r="AM6">
+        <v>260</v>
+      </c>
+      <c r="AN6">
+        <v>9</v>
+      </c>
+      <c r="AO6">
+        <v>30</v>
+      </c>
+      <c r="AP6">
+        <v>22</v>
+      </c>
+      <c r="AQ6">
+        <v>16</v>
+      </c>
+      <c r="AR6">
+        <v>22</v>
+      </c>
+      <c r="AS6">
+        <v>34</v>
+      </c>
+      <c r="AT6">
+        <v>12.5</v>
+      </c>
+      <c r="AU6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV6">
+        <v>15</v>
+      </c>
+      <c r="AW6">
+        <v>23</v>
+      </c>
+      <c r="AX6">
+        <v>13.5</v>
+      </c>
+      <c r="AY6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>13</v>
+      </c>
+      <c r="BA6">
+        <v>24</v>
+      </c>
+      <c r="BB6">
+        <v>16.5</v>
+      </c>
+      <c r="BC6">
+        <v>15.5</v>
+      </c>
+      <c r="BD6">
+        <v>18.5</v>
+      </c>
+      <c r="BE6">
+        <v>38</v>
+      </c>
+      <c r="BF6">
+        <v>7.8</v>
+      </c>
+      <c r="BG6">
+        <v>19.5</v>
+      </c>
+      <c r="BH6">
+        <v>4.5</v>
+      </c>
+      <c r="BI6">
+        <v>3.5</v>
+      </c>
+      <c r="BJ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK6">
+        <v>1.04</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.04</v>
+      </c>
+      <c r="BN6">
+        <v>5.2</v>
+      </c>
+      <c r="BO6">
+        <v>3.95</v>
+      </c>
+      <c r="BP6">
+        <v>13</v>
+      </c>
+      <c r="BQ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR6">
+        <v>30</v>
+      </c>
+      <c r="BS6">
+        <v>13</v>
+      </c>
+      <c r="BT6">
+        <v>7.8</v>
+      </c>
+      <c r="BU6">
+        <v>5.7</v>
+      </c>
+      <c r="BV6">
+        <v>27</v>
+      </c>
+      <c r="BW6">
+        <v>1.04</v>
+      </c>
+      <c r="BX6">
+        <v>32</v>
+      </c>
+      <c r="BY6">
+        <v>1.04</v>
+      </c>
+      <c r="BZ6">
+        <v>15</v>
+      </c>
+      <c r="CA6">
+        <v>10.5</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7">
+        <v>2.82</v>
+      </c>
+      <c r="G7">
+        <v>2.98</v>
+      </c>
+      <c r="H7">
+        <v>2.48</v>
+      </c>
+      <c r="I7">
+        <v>2.62</v>
+      </c>
+      <c r="J7">
+        <v>3.7</v>
+      </c>
+      <c r="K7">
+        <v>3.95</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.05</v>
+      </c>
+      <c r="N7">
+        <v>4.7</v>
+      </c>
+      <c r="O7">
+        <v>1.22</v>
+      </c>
+      <c r="P7">
+        <v>2.28</v>
+      </c>
+      <c r="Q7">
+        <v>1.71</v>
+      </c>
+      <c r="R7">
+        <v>1.49</v>
+      </c>
+      <c r="S7">
+        <v>2.66</v>
+      </c>
+      <c r="T7">
+        <v>1.58</v>
+      </c>
+      <c r="U7">
+        <v>2.46</v>
+      </c>
+      <c r="V7">
+        <v>1.62</v>
+      </c>
+      <c r="W7">
+        <v>1.51</v>
+      </c>
+      <c r="X7">
+        <v>28</v>
+      </c>
+      <c r="Y7">
+        <v>17</v>
+      </c>
+      <c r="Z7">
+        <v>24</v>
+      </c>
+      <c r="AA7">
+        <v>75</v>
+      </c>
+      <c r="AB7">
+        <v>18.5</v>
+      </c>
+      <c r="AC7">
+        <v>9.4</v>
+      </c>
+      <c r="AD7">
+        <v>14</v>
+      </c>
+      <c r="AE7">
+        <v>34</v>
+      </c>
+      <c r="AF7">
+        <v>30</v>
+      </c>
+      <c r="AG7">
+        <v>15.5</v>
+      </c>
+      <c r="AH7">
+        <v>18.5</v>
+      </c>
+      <c r="AI7">
+        <v>60</v>
+      </c>
+      <c r="AJ7">
+        <v>140</v>
+      </c>
+      <c r="AK7">
+        <v>44</v>
+      </c>
+      <c r="AL7">
+        <v>70</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>27</v>
+      </c>
+      <c r="AO7">
+        <v>20</v>
+      </c>
+      <c r="AP7">
+        <v>15</v>
+      </c>
+      <c r="AQ7">
+        <v>11</v>
+      </c>
+      <c r="AR7">
+        <v>14</v>
+      </c>
+      <c r="AS7">
+        <v>26</v>
+      </c>
+      <c r="AT7">
+        <v>12</v>
+      </c>
+      <c r="AU7">
+        <v>7.4</v>
+      </c>
+      <c r="AV7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW7">
+        <v>16.5</v>
+      </c>
+      <c r="AX7">
+        <v>15.5</v>
+      </c>
+      <c r="AY7">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7">
+        <v>12</v>
+      </c>
+      <c r="BA7">
+        <v>21</v>
+      </c>
+      <c r="BB7">
+        <v>30</v>
+      </c>
+      <c r="BC7">
+        <v>18.5</v>
+      </c>
+      <c r="BD7">
+        <v>22</v>
+      </c>
+      <c r="BE7">
+        <v>42</v>
+      </c>
+      <c r="BF7">
+        <v>15</v>
+      </c>
+      <c r="BG7">
+        <v>12.5</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.04</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.04</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.04</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.04</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.04</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.04</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.04</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8">
+        <v>1.68</v>
+      </c>
+      <c r="G8">
+        <v>1.71</v>
+      </c>
+      <c r="H8">
+        <v>5.1</v>
+      </c>
+      <c r="I8">
+        <v>5.4</v>
+      </c>
+      <c r="J8">
+        <v>4.5</v>
+      </c>
+      <c r="K8">
+        <v>4.7</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
+        <v>5.7</v>
+      </c>
+      <c r="O8">
+        <v>1.17</v>
+      </c>
+      <c r="P8">
+        <v>2.62</v>
+      </c>
+      <c r="Q8">
+        <v>1.57</v>
+      </c>
+      <c r="R8">
+        <v>1.65</v>
+      </c>
+      <c r="S8">
+        <v>2.36</v>
+      </c>
+      <c r="T8">
+        <v>1.63</v>
+      </c>
+      <c r="U8">
+        <v>2.44</v>
+      </c>
+      <c r="V8">
+        <v>1.23</v>
+      </c>
+      <c r="W8">
+        <v>2.4</v>
+      </c>
+      <c r="X8">
+        <v>28</v>
+      </c>
+      <c r="Y8">
+        <v>28</v>
+      </c>
+      <c r="Z8">
+        <v>55</v>
+      </c>
+      <c r="AA8">
+        <v>140</v>
+      </c>
+      <c r="AB8">
+        <v>13.5</v>
+      </c>
+      <c r="AC8">
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <v>21</v>
+      </c>
+      <c r="AE8">
+        <v>65</v>
+      </c>
+      <c r="AF8">
+        <v>14</v>
+      </c>
+      <c r="AG8">
+        <v>10.5</v>
+      </c>
+      <c r="AH8">
+        <v>18.5</v>
+      </c>
+      <c r="AI8">
+        <v>60</v>
+      </c>
+      <c r="AJ8">
+        <v>18</v>
+      </c>
+      <c r="AK8">
+        <v>15.5</v>
+      </c>
+      <c r="AL8">
+        <v>29</v>
+      </c>
+      <c r="AM8">
+        <v>80</v>
+      </c>
+      <c r="AN8">
+        <v>6.8</v>
+      </c>
+      <c r="AO8">
+        <v>50</v>
+      </c>
+      <c r="AP8">
+        <v>22</v>
+      </c>
+      <c r="AQ8">
+        <v>21</v>
+      </c>
+      <c r="AR8">
+        <v>36</v>
+      </c>
+      <c r="AS8">
+        <v>40</v>
+      </c>
+      <c r="AT8">
+        <v>11.5</v>
+      </c>
+      <c r="AU8">
+        <v>9.6</v>
+      </c>
+      <c r="AV8">
+        <v>18</v>
+      </c>
+      <c r="AW8">
+        <v>29</v>
+      </c>
+      <c r="AX8">
+        <v>11</v>
+      </c>
+      <c r="AY8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8">
+        <v>15</v>
+      </c>
+      <c r="BA8">
+        <v>40</v>
+      </c>
+      <c r="BB8">
+        <v>15</v>
+      </c>
+      <c r="BC8">
+        <v>13</v>
+      </c>
+      <c r="BD8">
+        <v>22</v>
+      </c>
+      <c r="BE8">
+        <v>32</v>
+      </c>
+      <c r="BF8">
+        <v>6.2</v>
+      </c>
+      <c r="BG8">
+        <v>36</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.04</v>
+      </c>
+      <c r="BJ8">
+        <v>13</v>
+      </c>
+      <c r="BK8">
+        <v>1.04</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.04</v>
+      </c>
+      <c r="BN8">
+        <v>6.6</v>
+      </c>
+      <c r="BO8">
+        <v>3.2</v>
+      </c>
+      <c r="BP8">
+        <v>15</v>
+      </c>
+      <c r="BQ8">
+        <v>1.04</v>
+      </c>
+      <c r="BR8">
+        <v>29</v>
+      </c>
+      <c r="BS8">
+        <v>1.04</v>
+      </c>
+      <c r="BT8">
+        <v>13</v>
+      </c>
+      <c r="BU8">
+        <v>1.04</v>
+      </c>
+      <c r="BV8">
+        <v>50</v>
+      </c>
+      <c r="BW8">
+        <v>1.04</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.04</v>
+      </c>
+      <c r="BZ8">
+        <v>19</v>
+      </c>
+      <c r="CA8">
+        <v>1.04</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9">
+        <v>2.64</v>
+      </c>
+      <c r="G9">
+        <v>3.05</v>
+      </c>
+      <c r="H9">
+        <v>2.62</v>
+      </c>
+      <c r="I9">
+        <v>2.88</v>
+      </c>
+      <c r="J9">
+        <v>3.45</v>
+      </c>
+      <c r="K9">
+        <v>4.2</v>
+      </c>
+      <c r="L9">
+        <v>1.3</v>
+      </c>
+      <c r="M9">
+        <v>1.06</v>
+      </c>
+      <c r="N9">
+        <v>3.65</v>
+      </c>
+      <c r="O9">
+        <v>1.29</v>
+      </c>
+      <c r="P9">
+        <v>1.91</v>
+      </c>
+      <c r="Q9">
+        <v>1.86</v>
+      </c>
+      <c r="R9">
+        <v>1.34</v>
+      </c>
+      <c r="S9">
+        <v>2.86</v>
+      </c>
+      <c r="T9">
+        <v>1.11</v>
+      </c>
+      <c r="U9">
+        <v>1.11</v>
+      </c>
+      <c r="V9">
+        <v>1.53</v>
+      </c>
+      <c r="W9">
+        <v>1.52</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>2.78</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10">
+        <v>2.14</v>
+      </c>
+      <c r="G10">
+        <v>2.22</v>
+      </c>
+      <c r="H10">
+        <v>3.1</v>
+      </c>
+      <c r="I10">
+        <v>3.3</v>
+      </c>
+      <c r="J10">
+        <v>4.2</v>
+      </c>
+      <c r="K10">
+        <v>4.6</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.02</v>
+      </c>
+      <c r="N10">
+        <v>7.2</v>
+      </c>
+      <c r="O10">
+        <v>1.13</v>
+      </c>
+      <c r="P10">
+        <v>3.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.39</v>
+      </c>
+      <c r="R10">
+        <v>1.91</v>
+      </c>
+      <c r="S10">
+        <v>2</v>
+      </c>
+      <c r="T10">
+        <v>1.42</v>
+      </c>
+      <c r="U10">
+        <v>3.15</v>
+      </c>
+      <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.81</v>
+      </c>
+      <c r="X10">
+        <v>38</v>
+      </c>
+      <c r="Y10">
+        <v>26</v>
+      </c>
+      <c r="Z10">
+        <v>34</v>
+      </c>
+      <c r="AA10">
+        <v>380</v>
+      </c>
+      <c r="AB10">
+        <v>20</v>
+      </c>
+      <c r="AC10">
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <v>15.5</v>
+      </c>
+      <c r="AE10">
+        <v>30</v>
+      </c>
+      <c r="AF10">
+        <v>22</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>14.5</v>
+      </c>
+      <c r="AI10">
+        <v>30</v>
+      </c>
+      <c r="AJ10">
+        <v>32</v>
+      </c>
+      <c r="AK10">
+        <v>20</v>
+      </c>
+      <c r="AL10">
+        <v>24</v>
+      </c>
+      <c r="AM10">
+        <v>44</v>
+      </c>
+      <c r="AN10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO10">
+        <v>16</v>
+      </c>
+      <c r="AP10">
+        <v>28</v>
+      </c>
+      <c r="AQ10">
+        <v>21</v>
+      </c>
+      <c r="AR10">
+        <v>19.5</v>
+      </c>
+      <c r="AS10">
+        <v>29</v>
+      </c>
+      <c r="AT10">
+        <v>16</v>
+      </c>
+      <c r="AU10">
+        <v>10</v>
+      </c>
+      <c r="AV10">
+        <v>13.5</v>
+      </c>
+      <c r="AW10">
+        <v>18.5</v>
+      </c>
+      <c r="AX10">
+        <v>17.5</v>
+      </c>
+      <c r="AY10">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10">
+        <v>12</v>
+      </c>
+      <c r="BA10">
+        <v>18.5</v>
+      </c>
+      <c r="BB10">
+        <v>20</v>
+      </c>
+      <c r="BC10">
+        <v>16.5</v>
+      </c>
+      <c r="BD10">
+        <v>18.5</v>
+      </c>
+      <c r="BE10">
+        <v>27</v>
+      </c>
+      <c r="BF10">
+        <v>7.4</v>
+      </c>
+      <c r="BG10">
+        <v>13</v>
+      </c>
+      <c r="BH10">
+        <v>6.4</v>
+      </c>
+      <c r="BI10">
+        <v>3.65</v>
+      </c>
+      <c r="BJ10">
+        <v>11</v>
+      </c>
+      <c r="BK10">
+        <v>5.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>3.25</v>
+      </c>
+      <c r="BN10">
+        <v>8</v>
+      </c>
+      <c r="BO10">
+        <v>4.1</v>
+      </c>
+      <c r="BP10">
+        <v>19</v>
+      </c>
+      <c r="BQ10">
+        <v>2.88</v>
+      </c>
+      <c r="BR10">
+        <v>26</v>
+      </c>
+      <c r="BS10">
+        <v>3</v>
+      </c>
+      <c r="BT10">
+        <v>10</v>
+      </c>
+      <c r="BU10">
+        <v>4.9</v>
+      </c>
+      <c r="BV10">
+        <v>29</v>
+      </c>
+      <c r="BW10">
+        <v>3.05</v>
+      </c>
+      <c r="BX10">
+        <v>32</v>
+      </c>
+      <c r="BY10">
+        <v>3.05</v>
+      </c>
+      <c r="BZ10">
+        <v>15.5</v>
+      </c>
+      <c r="CA10">
+        <v>2.78</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11">
+        <v>1.58</v>
+      </c>
+      <c r="G11">
+        <v>1.6</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>6.4</v>
+      </c>
+      <c r="J11">
+        <v>4.7</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.02</v>
+      </c>
+      <c r="N11">
+        <v>5.2</v>
+      </c>
+      <c r="O11">
+        <v>1.17</v>
+      </c>
+      <c r="P11">
+        <v>2.52</v>
+      </c>
+      <c r="Q11">
+        <v>1.58</v>
+      </c>
+      <c r="R11">
+        <v>1.62</v>
+      </c>
+      <c r="S11">
+        <v>2.4</v>
+      </c>
+      <c r="T11">
+        <v>1.7</v>
+      </c>
+      <c r="U11">
+        <v>2.3</v>
+      </c>
+      <c r="V11">
+        <v>1.19</v>
+      </c>
+      <c r="W11">
+        <v>2.64</v>
+      </c>
+      <c r="X11">
+        <v>42</v>
+      </c>
+      <c r="Y11">
+        <v>40</v>
+      </c>
+      <c r="Z11">
+        <v>200</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>13.5</v>
+      </c>
+      <c r="AC11">
+        <v>12.5</v>
+      </c>
+      <c r="AD11">
+        <v>32</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>12.5</v>
+      </c>
+      <c r="AG11">
+        <v>11</v>
+      </c>
+      <c r="AH11">
+        <v>26</v>
+      </c>
+      <c r="AI11">
+        <v>810</v>
+      </c>
+      <c r="AJ11">
+        <v>19.5</v>
+      </c>
+      <c r="AK11">
+        <v>17.5</v>
+      </c>
+      <c r="AL11">
+        <v>44</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>6.8</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>18</v>
+      </c>
+      <c r="AQ11">
+        <v>18</v>
+      </c>
+      <c r="AR11">
+        <v>27</v>
+      </c>
+      <c r="AS11">
+        <v>42</v>
+      </c>
+      <c r="AT11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU11">
+        <v>9.6</v>
+      </c>
+      <c r="AV11">
+        <v>16</v>
+      </c>
+      <c r="AW11">
+        <v>32</v>
+      </c>
+      <c r="AX11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11">
+        <v>8.4</v>
+      </c>
+      <c r="AZ11">
+        <v>14.5</v>
+      </c>
+      <c r="BA11">
+        <v>40</v>
+      </c>
+      <c r="BB11">
+        <v>12.5</v>
+      </c>
+      <c r="BC11">
+        <v>11.5</v>
+      </c>
+      <c r="BD11">
+        <v>18.5</v>
+      </c>
+      <c r="BE11">
+        <v>42</v>
+      </c>
+      <c r="BF11">
+        <v>5.7</v>
+      </c>
+      <c r="BG11">
+        <v>30</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>2.06</v>
+      </c>
+      <c r="BJ11">
+        <v>13.5</v>
+      </c>
+      <c r="BK11">
+        <v>1.79</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>2.06</v>
+      </c>
+      <c r="BN11">
+        <v>5.9</v>
+      </c>
+      <c r="BO11">
+        <v>3.1</v>
+      </c>
+      <c r="BP11">
+        <v>13</v>
+      </c>
+      <c r="BQ11">
+        <v>1.78</v>
+      </c>
+      <c r="BR11">
+        <v>29</v>
+      </c>
+      <c r="BS11">
+        <v>1.93</v>
+      </c>
+      <c r="BT11">
+        <v>13.5</v>
+      </c>
+      <c r="BU11">
+        <v>1.79</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>2</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>2</v>
+      </c>
+      <c r="BZ11">
+        <v>18</v>
+      </c>
+      <c r="CA11">
+        <v>1.85</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12">
+        <v>2.32</v>
+      </c>
+      <c r="G12">
+        <v>2.42</v>
+      </c>
+      <c r="H12">
+        <v>2.86</v>
+      </c>
+      <c r="I12">
+        <v>3.05</v>
+      </c>
+      <c r="J12">
+        <v>4.1</v>
+      </c>
+      <c r="K12">
+        <v>4.4</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>6.4</v>
+      </c>
+      <c r="O12">
+        <v>1.16</v>
+      </c>
+      <c r="P12">
+        <v>2.9</v>
+      </c>
+      <c r="Q12">
+        <v>1.48</v>
+      </c>
+      <c r="R12">
+        <v>1.78</v>
+      </c>
+      <c r="S12">
+        <v>2.2</v>
+      </c>
+      <c r="T12">
+        <v>1.47</v>
+      </c>
+      <c r="U12">
+        <v>2.9</v>
+      </c>
+      <c r="V12">
+        <v>1.5</v>
+      </c>
+      <c r="W12">
+        <v>1.71</v>
+      </c>
+      <c r="X12">
+        <v>32</v>
+      </c>
+      <c r="Y12">
+        <v>22</v>
+      </c>
+      <c r="Z12">
+        <v>28</v>
+      </c>
+      <c r="AA12">
+        <v>190</v>
+      </c>
+      <c r="AB12">
+        <v>19</v>
+      </c>
+      <c r="AC12">
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <v>14.5</v>
+      </c>
+      <c r="AE12">
+        <v>30</v>
+      </c>
+      <c r="AF12">
+        <v>21</v>
+      </c>
+      <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <v>14.5</v>
+      </c>
+      <c r="AI12">
+        <v>32</v>
+      </c>
+      <c r="AJ12">
+        <v>60</v>
+      </c>
+      <c r="AK12">
+        <v>21</v>
+      </c>
+      <c r="AL12">
+        <v>29</v>
+      </c>
+      <c r="AM12">
+        <v>140</v>
+      </c>
+      <c r="AN12">
+        <v>10.5</v>
+      </c>
+      <c r="AO12">
+        <v>15.5</v>
+      </c>
+      <c r="AP12">
+        <v>25</v>
+      </c>
+      <c r="AQ12">
+        <v>17.5</v>
+      </c>
+      <c r="AR12">
+        <v>21</v>
+      </c>
+      <c r="AS12">
+        <v>36</v>
+      </c>
+      <c r="AT12">
+        <v>15.5</v>
+      </c>
+      <c r="AU12">
+        <v>9.4</v>
+      </c>
+      <c r="AV12">
+        <v>12</v>
+      </c>
+      <c r="AW12">
+        <v>17.5</v>
+      </c>
+      <c r="AX12">
+        <v>17.5</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>12.5</v>
+      </c>
+      <c r="BA12">
+        <v>22</v>
+      </c>
+      <c r="BB12">
+        <v>25</v>
+      </c>
+      <c r="BC12">
+        <v>17.5</v>
+      </c>
+      <c r="BD12">
+        <v>21</v>
+      </c>
+      <c r="BE12">
+        <v>34</v>
+      </c>
+      <c r="BF12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG12">
+        <v>13</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>3.3</v>
+      </c>
+      <c r="BJ12">
+        <v>12</v>
+      </c>
+      <c r="BK12">
+        <v>5.3</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2</v>
+      </c>
+      <c r="BN12">
+        <v>8.6</v>
+      </c>
+      <c r="BO12">
+        <v>3.85</v>
+      </c>
+      <c r="BP12">
+        <v>21</v>
+      </c>
+      <c r="BQ12">
+        <v>1.86</v>
+      </c>
+      <c r="BR12">
+        <v>30</v>
+      </c>
+      <c r="BS12">
+        <v>1.91</v>
+      </c>
+      <c r="BT12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU12">
+        <v>4.4</v>
+      </c>
+      <c r="BV12">
+        <v>29</v>
+      </c>
+      <c r="BW12">
+        <v>1.91</v>
+      </c>
+      <c r="BX12">
+        <v>34</v>
+      </c>
+      <c r="BY12">
+        <v>1.93</v>
+      </c>
+      <c r="BZ12">
+        <v>19</v>
+      </c>
+      <c r="CA12">
+        <v>1.84</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13">
+        <v>2.3</v>
+      </c>
+      <c r="G13">
+        <v>2.34</v>
+      </c>
+      <c r="H13">
+        <v>3.9</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>3.1</v>
+      </c>
+      <c r="K13">
+        <v>3.15</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.13</v>
+      </c>
+      <c r="N13">
+        <v>2.6</v>
+      </c>
+      <c r="O13">
+        <v>1.59</v>
+      </c>
+      <c r="P13">
+        <v>1.53</v>
+      </c>
+      <c r="Q13">
+        <v>2.74</v>
+      </c>
+      <c r="R13">
+        <v>1.19</v>
+      </c>
+      <c r="S13">
+        <v>5.9</v>
+      </c>
+      <c r="T13">
+        <v>2.24</v>
+      </c>
+      <c r="U13">
+        <v>1.74</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>8.4</v>
+      </c>
+      <c r="Y13">
+        <v>10</v>
+      </c>
+      <c r="Z13">
+        <v>26</v>
+      </c>
+      <c r="AA13">
+        <v>110</v>
+      </c>
+      <c r="AB13">
+        <v>7</v>
+      </c>
+      <c r="AC13">
+        <v>7</v>
+      </c>
+      <c r="AD13">
+        <v>17.5</v>
+      </c>
+      <c r="AE13">
+        <v>80</v>
+      </c>
+      <c r="AF13">
+        <v>12.5</v>
+      </c>
+      <c r="AG13">
+        <v>12.5</v>
+      </c>
+      <c r="AH13">
+        <v>26</v>
+      </c>
+      <c r="AI13">
+        <v>110</v>
+      </c>
+      <c r="AJ13">
+        <v>34</v>
+      </c>
+      <c r="AK13">
+        <v>34</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>36</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>7.6</v>
+      </c>
+      <c r="AQ13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR13">
+        <v>17</v>
+      </c>
+      <c r="AS13">
+        <v>36</v>
+      </c>
+      <c r="AT13">
+        <v>6.4</v>
+      </c>
+      <c r="AU13">
+        <v>6.6</v>
+      </c>
+      <c r="AV13">
+        <v>16</v>
+      </c>
+      <c r="AW13">
+        <v>32</v>
+      </c>
+      <c r="AX13">
+        <v>11.5</v>
+      </c>
+      <c r="AY13">
+        <v>11</v>
+      </c>
+      <c r="AZ13">
+        <v>22</v>
+      </c>
+      <c r="BA13">
+        <v>38</v>
+      </c>
+      <c r="BB13">
+        <v>21</v>
+      </c>
+      <c r="BC13">
+        <v>21</v>
+      </c>
+      <c r="BD13">
+        <v>32</v>
+      </c>
+      <c r="BE13">
+        <v>48</v>
+      </c>
+      <c r="BF13">
+        <v>21</v>
+      </c>
+      <c r="BG13">
+        <v>36</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -364,7 +364,7 @@
     <t>Alaves</t>
   </si>
   <si>
-    <t>2026-08-18 00:31:35</t>
+    <t>2026-08-18 02:39:46</t>
   </si>
 </sst>
 </file>
@@ -970,7 +970,7 @@
         <v>2.08</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -1006,7 +1006,7 @@
         <v>2.66</v>
       </c>
       <c r="V2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W2">
         <v>1.37</v>
@@ -1027,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
@@ -1057,13 +1057,13 @@
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN2">
         <v>25</v>
       </c>
       <c r="AO2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AP2">
         <v>21</v>
@@ -1081,10 +1081,10 @@
         <v>15</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
         <v>13.5</v>
@@ -1159,7 +1159,7 @@
         <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BV2">
         <v>18.5</v>
@@ -1200,22 +1200,22 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
         <v>2.88</v>
       </c>
       <c r="I3">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1227,10 +1227,10 @@
         <v>2.42</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q3">
         <v>2.68</v>
@@ -1239,7 +1239,7 @@
         <v>1.08</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="T3">
         <v>2.02</v>
@@ -1466,28 +1466,28 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.17</v>
@@ -1505,10 +1505,10 @@
         <v>50</v>
       </c>
       <c r="AA4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
@@ -1517,10 +1517,10 @@
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1550,7 +1550,7 @@
         <v>130</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
         <v>16</v>
@@ -1559,7 +1559,7 @@
         <v>34</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
@@ -1571,7 +1571,7 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1583,7 +1583,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1595,13 +1595,13 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1613,7 +1613,7 @@
         <v>14.5</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1684,7 +1684,7 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G5">
         <v>1.88</v>
@@ -1693,7 +1693,7 @@
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1702,28 +1702,28 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q5">
         <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
         <v>1.7</v>
@@ -1744,7 +1744,7 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1759,7 +1759,7 @@
         <v>19.5</v>
       </c>
       <c r="AE5">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
@@ -1771,7 +1771,7 @@
         <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AJ5">
         <v>22</v>
@@ -1810,7 +1810,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
         <v>27</v>
@@ -1831,7 +1831,7 @@
         <v>16.5</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD5">
         <v>20</v>
@@ -1849,7 +1849,7 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="BJ5">
         <v>13</v>
@@ -1935,37 +1935,37 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J6">
         <v>3.9</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.28</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q6">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R6">
         <v>1.67</v>
       </c>
       <c r="S6">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T6">
         <v>1.54</v>
@@ -1974,7 +1974,7 @@
         <v>2.68</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
         <v>2</v>
@@ -1995,13 +1995,13 @@
         <v>14</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
         <v>18</v>
       </c>
       <c r="AE6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF6">
         <v>16</v>
@@ -2025,10 +2025,10 @@
         <v>27</v>
       </c>
       <c r="AM6">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO6">
         <v>30</v>
@@ -2067,7 +2067,7 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB6">
         <v>16.5</v>
@@ -2079,7 +2079,7 @@
         <v>18.5</v>
       </c>
       <c r="BE6">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BF6">
         <v>7.8</v>
@@ -2088,7 +2088,7 @@
         <v>19.5</v>
       </c>
       <c r="BH6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI6">
         <v>3.5</v>
@@ -2106,19 +2106,19 @@
         <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
         <v>13</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BS6">
         <v>13</v>
@@ -2145,7 +2145,7 @@
         <v>15</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2168,16 +2168,16 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G7">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H7">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I7">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J7">
         <v>3.7</v>
@@ -2186,28 +2186,28 @@
         <v>3.95</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
         <v>1.58</v>
@@ -2410,16 +2410,16 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G8">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -2428,103 +2428,103 @@
         <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
         <v>1.57</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S8">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
         <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z8">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA8">
         <v>140</v>
       </c>
       <c r="AB8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
         <v>21</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>390</v>
       </c>
       <c r="AF8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK8">
         <v>15.5</v>
       </c>
       <c r="AL8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM8">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN8">
         <v>6.8</v>
       </c>
       <c r="AO8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP8">
         <v>22</v>
       </c>
       <c r="AQ8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS8">
         <v>40</v>
@@ -2539,31 +2539,31 @@
         <v>18</v>
       </c>
       <c r="AW8">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AX8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY8">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8">
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD8">
         <v>22</v>
       </c>
       <c r="BE8">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF8">
         <v>6.2</v>
@@ -2575,19 +2575,19 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BJ8">
         <v>13</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BN8">
         <v>6.6</v>
@@ -2599,37 +2599,37 @@
         <v>15</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BR8">
         <v>29</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BT8">
         <v>13</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BV8">
         <v>50</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BZ8">
         <v>19</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="CB8" t="s">
         <v>116</v>
@@ -2652,10 +2652,10 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G9">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H9">
         <v>2.62</v>
@@ -2673,13 +2673,13 @@
         <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
         <v>3.65</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
         <v>1.91</v>
@@ -2691,7 +2691,7 @@
         <v>1.34</v>
       </c>
       <c r="S9">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2703,7 +2703,7 @@
         <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2897,10 +2897,10 @@
         <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
         <v>3.3</v>
@@ -2909,31 +2909,31 @@
         <v>4.2</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M10">
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R10">
         <v>1.91</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T10">
         <v>1.42</v>
@@ -2942,10 +2942,10 @@
         <v>3.15</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X10">
         <v>38</v>
@@ -2957,7 +2957,7 @@
         <v>34</v>
       </c>
       <c r="AA10">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AB10">
         <v>20</v>
@@ -2969,10 +2969,10 @@
         <v>15.5</v>
       </c>
       <c r="AE10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -2990,7 +2990,7 @@
         <v>20</v>
       </c>
       <c r="AL10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM10">
         <v>44</v>
@@ -2999,10 +2999,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP10">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AQ10">
         <v>21</v>
@@ -3014,7 +3014,7 @@
         <v>29</v>
       </c>
       <c r="AT10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>18.5</v>
       </c>
       <c r="BB10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC10">
         <v>16.5</v>
@@ -3047,7 +3047,7 @@
         <v>18.5</v>
       </c>
       <c r="BE10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BF10">
         <v>7.4</v>
@@ -3056,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="BH10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
         <v>3.65</v>
@@ -3071,25 +3071,25 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>3.25</v>
+        <v>2.16</v>
       </c>
       <c r="BN10">
         <v>8</v>
       </c>
       <c r="BO10">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
         <v>19</v>
       </c>
       <c r="BQ10">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="BR10">
         <v>26</v>
       </c>
       <c r="BS10">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="BT10">
         <v>10</v>
@@ -3101,19 +3101,19 @@
         <v>29</v>
       </c>
       <c r="BW10">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="BX10">
         <v>32</v>
       </c>
       <c r="BY10">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="BZ10">
         <v>15.5</v>
       </c>
       <c r="CA10">
-        <v>2.78</v>
+        <v>1.94</v>
       </c>
       <c r="CB10" t="s">
         <v>116</v>
@@ -3142,7 +3142,7 @@
         <v>1.6</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I11">
         <v>6.4</v>
@@ -3154,40 +3154,40 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S11">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T11">
         <v>1.7</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
         <v>1.19</v>
       </c>
       <c r="W11">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X11">
         <v>42</v>
@@ -3223,7 +3223,7 @@
         <v>26</v>
       </c>
       <c r="AI11">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="AJ11">
         <v>19.5</v>
@@ -3250,7 +3250,7 @@
         <v>18</v>
       </c>
       <c r="AR11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AS11">
         <v>42</v>
@@ -3289,7 +3289,7 @@
         <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BF11">
         <v>5.7</v>
@@ -3304,7 +3304,7 @@
         <v>2.06</v>
       </c>
       <c r="BJ11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK11">
         <v>1.79</v>
@@ -3313,31 +3313,31 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BN11">
         <v>5.9</v>
       </c>
       <c r="BO11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP11">
         <v>13</v>
       </c>
       <c r="BQ11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BR11">
         <v>29</v>
       </c>
       <c r="BS11">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3355,7 +3355,7 @@
         <v>18</v>
       </c>
       <c r="CA11">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>
@@ -3378,52 +3378,52 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H12">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="I12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O12">
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R12">
         <v>1.78</v>
       </c>
       <c r="S12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T12">
         <v>1.47</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="V12">
         <v>1.5</v>
@@ -3438,10 +3438,10 @@
         <v>22</v>
       </c>
       <c r="Z12">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AB12">
         <v>19</v>
@@ -3450,13 +3450,13 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE12">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AF12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG12">
         <v>12.5</v>
@@ -3465,16 +3465,16 @@
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AL12">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AM12">
         <v>140</v>
@@ -3483,19 +3483,19 @@
         <v>10.5</v>
       </c>
       <c r="AO12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
+        <v>15</v>
+      </c>
+      <c r="AR12">
         <v>17.5</v>
       </c>
-      <c r="AR12">
-        <v>21</v>
-      </c>
       <c r="AS12">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AT12">
         <v>15.5</v>
@@ -3507,7 +3507,7 @@
         <v>12</v>
       </c>
       <c r="AW12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX12">
         <v>17.5</v>
@@ -3519,10 +3519,10 @@
         <v>12.5</v>
       </c>
       <c r="BA12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BB12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BC12">
         <v>17.5</v>
@@ -3543,10 +3543,10 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.3</v>
+        <v>2.06</v>
       </c>
       <c r="BJ12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
         <v>5.3</v>
@@ -3555,49 +3555,49 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BN12">
         <v>8.6</v>
       </c>
       <c r="BO12">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ12">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BR12">
         <v>30</v>
       </c>
       <c r="BS12">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BT12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU12">
         <v>4.4</v>
       </c>
       <c r="BV12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BX12">
         <v>34</v>
       </c>
       <c r="BY12">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BZ12">
         <v>19</v>
       </c>
       <c r="CA12">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CB12" t="s">
         <v>116</v>
@@ -3644,28 +3644,28 @@
         <v>1.13</v>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O13">
         <v>1.59</v>
       </c>
       <c r="P13">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q13">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
         <v>5.9</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3695,10 +3695,10 @@
         <v>17.5</v>
       </c>
       <c r="AE13">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
@@ -3716,13 +3716,13 @@
         <v>34</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM13">
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3746,7 +3746,7 @@
         <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW13">
         <v>32</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -364,7 +364,7 @@
     <t>Alaves</t>
   </si>
   <si>
-    <t>2026-08-18 02:39:46</t>
+    <t>2026-08-18 04:47:25</t>
   </si>
 </sst>
 </file>
@@ -958,10 +958,10 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H2">
         <v>2.02</v>
@@ -979,7 +979,7 @@
         <v>1.27</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>6</v>
@@ -1000,7 +1000,7 @@
         <v>2.38</v>
       </c>
       <c r="T2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U2">
         <v>2.66</v>
@@ -1009,25 +1009,25 @@
         <v>1.93</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
@@ -1036,7 +1036,7 @@
         <v>18.5</v>
       </c>
       <c r="AF2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AG2">
         <v>16</v>
@@ -1045,76 +1045,76 @@
         <v>15.5</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2">
+        <v>9</v>
+      </c>
+      <c r="AP2">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2">
+        <v>13</v>
+      </c>
+      <c r="AR2">
+        <v>13.5</v>
+      </c>
+      <c r="AS2">
+        <v>21</v>
+      </c>
+      <c r="AT2">
+        <v>18.5</v>
+      </c>
+      <c r="AU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2">
         <v>10</v>
       </c>
-      <c r="AP2">
+      <c r="AW2">
+        <v>15.5</v>
+      </c>
+      <c r="AX2">
+        <v>19.5</v>
+      </c>
+      <c r="AY2">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2">
+        <v>13</v>
+      </c>
+      <c r="BA2">
+        <v>17.5</v>
+      </c>
+      <c r="BB2">
+        <v>32</v>
+      </c>
+      <c r="BC2">
         <v>21</v>
       </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
-        <v>12.5</v>
-      </c>
-      <c r="AS2">
-        <v>17.5</v>
-      </c>
-      <c r="AT2">
-        <v>15</v>
-      </c>
-      <c r="AU2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2">
-        <v>9.4</v>
-      </c>
-      <c r="AW2">
-        <v>13.5</v>
-      </c>
-      <c r="AX2">
-        <v>24</v>
-      </c>
-      <c r="AY2">
-        <v>12</v>
-      </c>
-      <c r="AZ2">
-        <v>12</v>
-      </c>
-      <c r="BA2">
-        <v>19.5</v>
-      </c>
-      <c r="BB2">
-        <v>42</v>
-      </c>
-      <c r="BC2">
-        <v>25</v>
-      </c>
       <c r="BD2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BF2">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BG2">
         <v>8.199999999999999</v>
@@ -1123,19 +1123,19 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BN2">
         <v>10</v>
@@ -1147,37 +1147,37 @@
         <v>34</v>
       </c>
       <c r="BQ2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU2">
         <v>3.9</v>
       </c>
       <c r="BV2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW2">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="BX2">
         <v>30</v>
       </c>
       <c r="BY2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BZ2">
         <v>20</v>
       </c>
       <c r="CA2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CB2" t="s">
         <v>116</v>
@@ -1200,166 +1200,166 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="O3">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Q3">
         <v>2.68</v>
       </c>
       <c r="R3">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
         <v>9.6</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>1.12</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="AT3">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
-        <v>1.12</v>
+        <v>5.5</v>
       </c>
       <c r="AV3">
-        <v>1.12</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="AX3">
-        <v>1.12</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>1.12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="BA3">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="BB3">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="BC3">
-        <v>1.12</v>
+        <v>4.6</v>
       </c>
       <c r="BD3">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="BE3">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="BF3">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="BG3">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1445,10 +1445,10 @@
         <v>1.71</v>
       </c>
       <c r="G4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>6.6</v>
@@ -1457,22 +1457,22 @@
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1.32</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
@@ -1481,19 +1481,19 @@
         <v>1.32</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1505,10 +1505,10 @@
         <v>50</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
@@ -1520,7 +1520,7 @@
         <v>95</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1559,7 +1559,7 @@
         <v>34</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
@@ -1571,7 +1571,7 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1583,7 +1583,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1595,13 +1595,13 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF4">
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1613,7 +1613,7 @@
         <v>14.5</v>
       </c>
       <c r="BK4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1625,7 +1625,7 @@
         <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP4">
         <v>15.5</v>
@@ -1643,7 +1643,7 @@
         <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1687,7 +1687,7 @@
         <v>1.84</v>
       </c>
       <c r="G5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H5">
         <v>4.3</v>
@@ -1714,7 +1714,7 @@
         <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q5">
         <v>1.74</v>
@@ -1726,124 +1726,124 @@
         <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>270</v>
       </c>
       <c r="AJ5">
+        <v>21</v>
+      </c>
+      <c r="AK5">
+        <v>18</v>
+      </c>
+      <c r="AL5">
+        <v>32</v>
+      </c>
+      <c r="AM5">
+        <v>90</v>
+      </c>
+      <c r="AN5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO5">
+        <v>55</v>
+      </c>
+      <c r="AP5">
+        <v>17.5</v>
+      </c>
+      <c r="AQ5">
+        <v>16</v>
+      </c>
+      <c r="AR5">
         <v>22</v>
-      </c>
-      <c r="AK5">
-        <v>19.5</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>10.5</v>
-      </c>
-      <c r="AO5">
-        <v>160</v>
-      </c>
-      <c r="AP5">
-        <v>14.5</v>
-      </c>
-      <c r="AQ5">
-        <v>14</v>
-      </c>
-      <c r="AR5">
-        <v>21</v>
       </c>
       <c r="AS5">
         <v>36</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA5">
         <v>28</v>
       </c>
       <c r="BB5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD5">
         <v>20</v>
       </c>
       <c r="BE5">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BF5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1926,7 +1926,7 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1971,7 +1971,7 @@
         <v>1.54</v>
       </c>
       <c r="U6">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
         <v>1.31</v>
@@ -2025,22 +2025,22 @@
         <v>27</v>
       </c>
       <c r="AM6">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO6">
         <v>30</v>
       </c>
       <c r="AP6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
         <v>16</v>
       </c>
       <c r="AR6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS6">
         <v>34</v>
@@ -2049,7 +2049,7 @@
         <v>12.5</v>
       </c>
       <c r="AU6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV6">
         <v>15</v>
@@ -2061,13 +2061,13 @@
         <v>13.5</v>
       </c>
       <c r="AY6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB6">
         <v>16.5</v>
@@ -2088,7 +2088,7 @@
         <v>19.5</v>
       </c>
       <c r="BH6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI6">
         <v>3.5</v>
@@ -2106,10 +2106,10 @@
         <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO6">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP6">
         <v>13</v>
@@ -2118,7 +2118,7 @@
         <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BS6">
         <v>13</v>
@@ -2168,7 +2168,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G7">
         <v>2.96</v>
@@ -2204,16 +2204,16 @@
         <v>1.72</v>
       </c>
       <c r="R7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
         <v>2.8</v>
       </c>
       <c r="T7">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U7">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
         <v>1.62</v>
@@ -2222,37 +2222,37 @@
         <v>1.51</v>
       </c>
       <c r="X7">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Z7">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AA7">
         <v>75</v>
       </c>
       <c r="AB7">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AF7">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AG7">
+        <v>13.5</v>
+      </c>
+      <c r="AH7">
         <v>15.5</v>
-      </c>
-      <c r="AH7">
-        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>60</v>
@@ -2270,43 +2270,43 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AO7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP7">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS7">
         <v>26</v>
       </c>
       <c r="AT7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX7">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA7">
         <v>21</v>
@@ -2324,10 +2324,10 @@
         <v>42</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG7">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2419,7 +2419,7 @@
         <v>5.2</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -2434,25 +2434,25 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q8">
         <v>1.57</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S8">
         <v>2.42</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U8">
         <v>2.44</v>
@@ -2470,7 +2470,7 @@
         <v>26</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA8">
         <v>140</v>
@@ -2485,7 +2485,7 @@
         <v>21</v>
       </c>
       <c r="AE8">
-        <v>390</v>
+        <v>60</v>
       </c>
       <c r="AF8">
         <v>12.5</v>
@@ -2494,7 +2494,7 @@
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI8">
         <v>55</v>
@@ -2515,10 +2515,10 @@
         <v>6.8</v>
       </c>
       <c r="AO8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
         <v>23</v>
@@ -2551,7 +2551,7 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB8">
         <v>16</v>
@@ -2560,7 +2560,7 @@
         <v>14</v>
       </c>
       <c r="BD8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE8">
         <v>55</v>
@@ -2900,7 +2900,7 @@
         <v>2.2</v>
       </c>
       <c r="H10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I10">
         <v>3.3</v>
@@ -2912,7 +2912,7 @@
         <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M10">
         <v>1.02</v>
@@ -2921,46 +2921,46 @@
         <v>7.6</v>
       </c>
       <c r="O10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R10">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T10">
         <v>1.42</v>
       </c>
       <c r="U10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V10">
         <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X10">
         <v>38</v>
       </c>
       <c r="Y10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z10">
         <v>34</v>
       </c>
       <c r="AA10">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC10">
         <v>12</v>
@@ -2975,7 +2975,7 @@
         <v>21</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
         <v>14.5</v>
@@ -3032,10 +3032,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB10">
         <v>19.5</v>
@@ -3148,10 +3148,10 @@
         <v>6.4</v>
       </c>
       <c r="J11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
         <v>1.29</v>
@@ -3172,16 +3172,16 @@
         <v>1.59</v>
       </c>
       <c r="R11">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S11">
         <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U11">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V11">
         <v>1.19</v>
@@ -3190,22 +3190,22 @@
         <v>2.66</v>
       </c>
       <c r="X11">
+        <v>27</v>
+      </c>
+      <c r="Y11">
         <v>42</v>
       </c>
-      <c r="Y11">
-        <v>40</v>
-      </c>
       <c r="Z11">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD11">
         <v>32</v>
@@ -3214,22 +3214,22 @@
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>830</v>
+        <v>760</v>
       </c>
       <c r="AJ11">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AK11">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL11">
         <v>44</v>
@@ -3238,10 +3238,10 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="AP11">
         <v>18</v>
@@ -3250,40 +3250,40 @@
         <v>18</v>
       </c>
       <c r="AR11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AS11">
         <v>42</v>
       </c>
       <c r="AT11">
+        <v>10.5</v>
+      </c>
+      <c r="AU11">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU11">
-        <v>9.6</v>
-      </c>
       <c r="AV11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW11">
         <v>32</v>
       </c>
       <c r="AX11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY11">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BB11">
+        <v>13.5</v>
+      </c>
+      <c r="BC11">
         <v>12.5</v>
-      </c>
-      <c r="BC11">
-        <v>11.5</v>
       </c>
       <c r="BD11">
         <v>18.5</v>
@@ -3378,16 +3378,16 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G12">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H12">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J12">
         <v>4.1</v>
@@ -3408,7 +3408,7 @@
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q12">
         <v>1.49</v>
@@ -3423,25 +3423,25 @@
         <v>1.47</v>
       </c>
       <c r="U12">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
         <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X12">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Y12">
         <v>22</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA12">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB12">
         <v>19</v>
@@ -3456,7 +3456,7 @@
         <v>40</v>
       </c>
       <c r="AF12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG12">
         <v>12.5</v>
@@ -3465,19 +3465,19 @@
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AJ12">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN12">
         <v>10.5</v>
@@ -3498,7 +3498,7 @@
         <v>26</v>
       </c>
       <c r="AT12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU12">
         <v>9.4</v>
@@ -3513,7 +3513,7 @@
         <v>17.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
         <v>12.5</v>
@@ -3626,10 +3626,10 @@
         <v>2.34</v>
       </c>
       <c r="H13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J13">
         <v>3.1</v>
@@ -3641,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
         <v>1.59</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -3713,7 +3713,7 @@
         <v>34</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL13">
         <v>70</v>
@@ -3722,7 +3722,7 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3761,7 +3761,7 @@
         <v>22</v>
       </c>
       <c r="BA13">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BB13">
         <v>21</v>
@@ -3782,64 +3782,64 @@
         <v>36</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB13" t="s">
         <v>116</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -364,7 +364,7 @@
     <t>Alaves</t>
   </si>
   <si>
-    <t>2026-08-18 04:47:25</t>
+    <t>2026-08-18 06:55:43</t>
   </si>
 </sst>
 </file>
@@ -979,7 +979,7 @@
         <v>1.27</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
         <v>6</v>
@@ -1200,7 +1200,7 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1224,13 +1224,13 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
         <v>2.68</v>
@@ -1242,7 +1242,7 @@
         <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
         <v>1.78</v>
@@ -1296,7 +1296,7 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM3">
         <v>220</v>
@@ -1317,13 +1317,13 @@
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
         <v>11</v>
@@ -1332,7 +1332,7 @@
         <v>4.7</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1347,7 +1347,7 @@
         <v>4.7</v>
       </c>
       <c r="BC3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD3">
         <v>4.8</v>
@@ -1359,7 +1359,7 @@
         <v>4.7</v>
       </c>
       <c r="BG3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1771,7 +1771,7 @@
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
         <v>21</v>
@@ -1822,7 +1822,7 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
         <v>28</v>
@@ -1941,31 +1941,31 @@
         <v>3.9</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.28</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
         <v>6</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P6">
         <v>2.64</v>
       </c>
       <c r="Q6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
         <v>1.67</v>
       </c>
       <c r="S6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
         <v>1.54</v>
@@ -2168,7 +2168,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G7">
         <v>2.96</v>
@@ -2177,13 +2177,13 @@
         <v>2.52</v>
       </c>
       <c r="I7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>1.33</v>
@@ -2204,7 +2204,7 @@
         <v>1.72</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S7">
         <v>2.8</v>
@@ -2216,7 +2216,7 @@
         <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
         <v>1.51</v>
@@ -2228,13 +2228,13 @@
         <v>14.5</v>
       </c>
       <c r="Z7">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AA7">
         <v>75</v>
       </c>
       <c r="AB7">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AC7">
         <v>8.6</v>
@@ -2252,7 +2252,7 @@
         <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>60</v>
@@ -2264,7 +2264,7 @@
         <v>44</v>
       </c>
       <c r="AL7">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2273,7 +2273,7 @@
         <v>21</v>
       </c>
       <c r="AO7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP7">
         <v>17.5</v>
@@ -2285,10 +2285,10 @@
         <v>16</v>
       </c>
       <c r="AS7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
         <v>7.8</v>
@@ -2306,13 +2306,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA7">
         <v>21</v>
       </c>
       <c r="BB7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BC7">
         <v>18.5</v>
@@ -2321,7 +2321,7 @@
         <v>22</v>
       </c>
       <c r="BE7">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BF7">
         <v>17.5</v>
@@ -2333,61 +2333,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2413,13 +2413,13 @@
         <v>1.67</v>
       </c>
       <c r="G8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H8">
         <v>5.2</v>
       </c>
       <c r="I8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -2431,28 +2431,28 @@
         <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
         <v>1.57</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S8">
         <v>2.42</v>
       </c>
       <c r="T8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
         <v>2.44</v>
@@ -2461,7 +2461,7 @@
         <v>1.22</v>
       </c>
       <c r="W8">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X8">
         <v>25</v>
@@ -2515,10 +2515,10 @@
         <v>6.8</v>
       </c>
       <c r="AO8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8">
         <v>23</v>
@@ -2545,13 +2545,13 @@
         <v>11.5</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8">
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB8">
         <v>16</v>
@@ -2679,10 +2679,10 @@
         <v>3.65</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q9">
         <v>1.86</v>
@@ -2945,7 +2945,7 @@
         <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X10">
         <v>38</v>
@@ -3038,7 +3038,7 @@
         <v>19</v>
       </c>
       <c r="BB10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC10">
         <v>16.5</v>
@@ -3136,7 +3136,7 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G11">
         <v>1.6</v>
@@ -3151,7 +3151,7 @@
         <v>4.6</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>1.29</v>
@@ -3160,19 +3160,19 @@
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S11">
         <v>2.5</v>
@@ -3193,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="Y11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z11">
         <v>210</v>
@@ -3223,7 +3223,7 @@
         <v>21</v>
       </c>
       <c r="AI11">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="AJ11">
         <v>16</v>
@@ -3241,7 +3241,7 @@
         <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="AP11">
         <v>18</v>
@@ -3259,7 +3259,7 @@
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV11">
         <v>20</v>
@@ -3292,7 +3292,7 @@
         <v>34</v>
       </c>
       <c r="BF11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG11">
         <v>30</v>
@@ -3378,7 +3378,7 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G12">
         <v>2.44</v>
@@ -3393,7 +3393,7 @@
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.25</v>
@@ -3429,7 +3429,7 @@
         <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X12">
         <v>55</v>
@@ -3438,25 +3438,25 @@
         <v>22</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB12">
         <v>19</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
         <v>14</v>
       </c>
       <c r="AE12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG12">
         <v>12.5</v>
@@ -3465,13 +3465,13 @@
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ12">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL12">
         <v>40</v>
@@ -3495,10 +3495,10 @@
         <v>17.5</v>
       </c>
       <c r="AS12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU12">
         <v>9.4</v>
@@ -3534,7 +3534,7 @@
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG12">
         <v>13</v>
@@ -3623,7 +3623,7 @@
         <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
         <v>3.95</v>
@@ -3659,7 +3659,7 @@
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>2.26</v>
@@ -3689,7 +3689,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD13">
         <v>17.5</v>
@@ -3722,13 +3722,13 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13">
         <v>9.199999999999999</v>
@@ -3776,10 +3776,10 @@
         <v>48</v>
       </c>
       <c r="BF13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BG13">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="BH13">
         <v>2.9</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -364,7 +364,7 @@
     <t>Alaves</t>
   </si>
   <si>
-    <t>2026-08-18 06:55:43</t>
+    <t>2026-08-18 09:04:10</t>
   </si>
 </sst>
 </file>
@@ -961,7 +961,7 @@
         <v>3.6</v>
       </c>
       <c r="G2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H2">
         <v>2.02</v>
@@ -970,22 +970,22 @@
         <v>2.08</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>6</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
         <v>2.68</v>
@@ -1003,7 +1003,7 @@
         <v>1.54</v>
       </c>
       <c r="U2">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.93</v>
@@ -1024,10 +1024,10 @@
         <v>26</v>
       </c>
       <c r="AB2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
@@ -1039,10 +1039,10 @@
         <v>32</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2">
         <v>27</v>
@@ -1057,22 +1057,22 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>9</v>
       </c>
       <c r="AP2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ2">
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
         <v>21</v>
@@ -1090,7 +1090,7 @@
         <v>15.5</v>
       </c>
       <c r="AX2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY2">
         <v>13.5</v>
@@ -1105,19 +1105,19 @@
         <v>32</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF2">
         <v>20</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1138,7 +1138,7 @@
         <v>2.1</v>
       </c>
       <c r="BN2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO2">
         <v>4.9</v>
@@ -1159,7 +1159,7 @@
         <v>7</v>
       </c>
       <c r="BU2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
         <v>18</v>
@@ -1174,10 +1174,10 @@
         <v>2</v>
       </c>
       <c r="BZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CB2" t="s">
         <v>116</v>
@@ -1200,16 +1200,16 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H3">
         <v>2.98</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>2.92</v>
@@ -1248,10 +1248,10 @@
         <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
         <v>9.6</v>
@@ -1269,22 +1269,22 @@
         <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE3">
         <v>60</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI3">
         <v>90</v>
@@ -1317,7 +1317,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1329,7 +1329,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1338,28 +1338,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA3">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BC3">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD3">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BF3">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1442,22 +1442,22 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="G4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.32</v>
@@ -1472,7 +1472,7 @@
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
@@ -1490,28 +1490,28 @@
         <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
         <v>24</v>
@@ -1520,16 +1520,16 @@
         <v>95</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
@@ -1541,7 +1541,7 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN4">
         <v>12.5</v>
@@ -1550,19 +1550,19 @@
         <v>130</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
         <v>16</v>
       </c>
       <c r="AR4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU4">
         <v>7.6</v>
@@ -1571,7 +1571,7 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1583,7 +1583,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1595,13 +1595,13 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1684,52 +1684,52 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
         <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U5">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
         <v>1.27</v>
@@ -1789,25 +1789,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR5">
         <v>22</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT5">
         <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
         <v>15.5</v>
@@ -1816,13 +1816,13 @@
         <v>36</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA5">
         <v>28</v>
@@ -1834,13 +1834,13 @@
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE5">
         <v>34</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG5">
         <v>36</v>
@@ -1849,37 +1849,37 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BJ5">
         <v>13</v>
       </c>
       <c r="BK5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BN5">
         <v>6.4</v>
       </c>
       <c r="BO5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP5">
         <v>17</v>
       </c>
       <c r="BQ5">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BT5">
         <v>11</v>
@@ -1888,13 +1888,13 @@
         <v>5.3</v>
       </c>
       <c r="BV5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW5">
         <v>1.9</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY5">
         <v>1.91</v>
@@ -1903,7 +1903,7 @@
         <v>25</v>
       </c>
       <c r="CA5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CB5" t="s">
         <v>116</v>
@@ -1926,22 +1926,22 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.28</v>
@@ -1959,7 +1959,7 @@
         <v>2.64</v>
       </c>
       <c r="Q6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R6">
         <v>1.67</v>
@@ -1983,7 +1983,7 @@
         <v>29</v>
       </c>
       <c r="Y6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Z6">
         <v>65</v>
@@ -1995,16 +1995,16 @@
         <v>14</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE6">
         <v>85</v>
       </c>
       <c r="AF6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG6">
         <v>11</v>
@@ -2013,16 +2013,16 @@
         <v>15</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AK6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL6">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AM6">
         <v>260</v>
@@ -2031,7 +2031,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO6">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AP6">
         <v>21</v>
@@ -2040,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS6">
         <v>34</v>
@@ -2171,31 +2171,31 @@
         <v>2.84</v>
       </c>
       <c r="G7">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H7">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I7">
         <v>2.58</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
         <v>3.9</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
         <v>2.3</v>
@@ -2207,13 +2207,13 @@
         <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
         <v>1.6</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V7">
         <v>1.63</v>
@@ -2225,16 +2225,16 @@
         <v>21</v>
       </c>
       <c r="Y7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC7">
         <v>8.6</v>
@@ -2249,7 +2249,7 @@
         <v>23</v>
       </c>
       <c r="AG7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH7">
         <v>18.5</v>
@@ -2258,7 +2258,7 @@
         <v>60</v>
       </c>
       <c r="AJ7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK7">
         <v>44</v>
@@ -2276,10 +2276,10 @@
         <v>20</v>
       </c>
       <c r="AP7">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR7">
         <v>16</v>
@@ -2288,7 +2288,7 @@
         <v>22</v>
       </c>
       <c r="AT7">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU7">
         <v>7.8</v>
@@ -2324,70 +2324,70 @@
         <v>30</v>
       </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG7">
         <v>14</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK7">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.98</v>
+        <v>9.4</v>
       </c>
       <c r="BN7">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
+        <v>21</v>
+      </c>
+      <c r="BQ7">
+        <v>7</v>
+      </c>
+      <c r="BR7">
+        <v>30</v>
+      </c>
+      <c r="BS7">
+        <v>7.6</v>
+      </c>
+      <c r="BT7">
+        <v>6</v>
+      </c>
+      <c r="BU7">
+        <v>4.6</v>
+      </c>
+      <c r="BV7">
+        <v>18.5</v>
+      </c>
+      <c r="BW7">
+        <v>6.6</v>
+      </c>
+      <c r="BX7">
         <v>28</v>
       </c>
-      <c r="BQ7">
-        <v>1.86</v>
-      </c>
-      <c r="BR7">
-        <v>40</v>
-      </c>
-      <c r="BS7">
-        <v>1.89</v>
-      </c>
-      <c r="BT7">
-        <v>7.8</v>
-      </c>
-      <c r="BU7">
-        <v>3.95</v>
-      </c>
-      <c r="BV7">
-        <v>25</v>
-      </c>
-      <c r="BW7">
-        <v>1.84</v>
-      </c>
-      <c r="BX7">
-        <v>38</v>
-      </c>
       <c r="BY7">
-        <v>1.89</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="CA7">
-        <v>1.86</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2410,46 +2410,46 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="G8">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="H8">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="T8">
         <v>1.64</v>
@@ -2458,52 +2458,52 @@
         <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="X8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA8">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
+        <v>12</v>
+      </c>
+      <c r="AC8">
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <v>19.5</v>
+      </c>
+      <c r="AE8">
+        <v>55</v>
+      </c>
+      <c r="AF8">
         <v>13</v>
       </c>
-      <c r="AC8">
-        <v>10.5</v>
-      </c>
-      <c r="AD8">
-        <v>21</v>
-      </c>
-      <c r="AE8">
-        <v>60</v>
-      </c>
-      <c r="AF8">
-        <v>12.5</v>
-      </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL8">
         <v>26</v>
@@ -2512,52 +2512,52 @@
         <v>70</v>
       </c>
       <c r="AN8">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS8">
         <v>40</v>
       </c>
       <c r="AT8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW8">
         <v>48</v>
       </c>
       <c r="AX8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB8">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD8">
         <v>23</v>
@@ -2566,70 +2566,70 @@
         <v>55</v>
       </c>
       <c r="BF8">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG8">
         <v>36</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO8">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="BP8">
+        <v>11</v>
+      </c>
+      <c r="BQ8">
+        <v>8</v>
+      </c>
+      <c r="BR8">
+        <v>21</v>
+      </c>
+      <c r="BS8">
+        <v>9.4</v>
+      </c>
+      <c r="BT8">
+        <v>8.6</v>
+      </c>
+      <c r="BU8">
+        <v>6.4</v>
+      </c>
+      <c r="BV8">
+        <v>36</v>
+      </c>
+      <c r="BW8">
+        <v>11.5</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>11.5</v>
+      </c>
+      <c r="BZ8">
         <v>15</v>
       </c>
-      <c r="BQ8">
-        <v>1.76</v>
-      </c>
-      <c r="BR8">
-        <v>29</v>
-      </c>
-      <c r="BS8">
-        <v>1.86</v>
-      </c>
-      <c r="BT8">
-        <v>13</v>
-      </c>
-      <c r="BU8">
-        <v>1.73</v>
-      </c>
-      <c r="BV8">
-        <v>50</v>
-      </c>
-      <c r="BW8">
-        <v>1.92</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>1.92</v>
-      </c>
-      <c r="BZ8">
-        <v>19</v>
-      </c>
       <c r="CA8">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>116</v>
@@ -2676,19 +2676,19 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q9">
         <v>1.86</v>
       </c>
       <c r="R9">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
         <v>3</v>
@@ -2912,7 +2912,7 @@
         <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M10">
         <v>1.02</v>
@@ -2924,16 +2924,16 @@
         <v>1.13</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R10">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T10">
         <v>1.42</v>
@@ -3136,7 +3136,7 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G11">
         <v>1.6</v>
@@ -3196,7 +3196,7 @@
         <v>40</v>
       </c>
       <c r="Z11">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>12</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11">
         <v>32</v>
@@ -3220,10 +3220,10 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11">
-        <v>770</v>
+        <v>940</v>
       </c>
       <c r="AJ11">
         <v>16</v>
@@ -3241,10 +3241,10 @@
         <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11">
         <v>18</v>
@@ -3280,7 +3280,7 @@
         <v>30</v>
       </c>
       <c r="BB11">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BC11">
         <v>12.5</v>
@@ -3292,7 +3292,7 @@
         <v>34</v>
       </c>
       <c r="BF11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG11">
         <v>30</v>
@@ -3393,13 +3393,13 @@
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.25</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>6.6</v>
@@ -3408,7 +3408,7 @@
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q12">
         <v>1.49</v>
@@ -3423,7 +3423,7 @@
         <v>1.47</v>
       </c>
       <c r="U12">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V12">
         <v>1.5</v>
@@ -3453,10 +3453,10 @@
         <v>14</v>
       </c>
       <c r="AE12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG12">
         <v>12.5</v>
@@ -3471,7 +3471,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL12">
         <v>40</v>
@@ -3486,7 +3486,7 @@
         <v>15</v>
       </c>
       <c r="AP12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ12">
         <v>15</v>
@@ -3534,7 +3534,7 @@
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG12">
         <v>13</v>
@@ -3623,7 +3623,7 @@
         <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H13">
         <v>3.95</v>
@@ -3656,10 +3656,10 @@
         <v>2.76</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T13">
         <v>2.26</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -3692,13 +3692,13 @@
         <v>6.8</v>
       </c>
       <c r="AD13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE13">
         <v>70</v>
       </c>
       <c r="AF13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
@@ -3707,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="AI13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ13">
         <v>34</v>
       </c>
       <c r="AK13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL13">
         <v>70</v>
@@ -3728,16 +3728,16 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR13">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AS13">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AT13">
         <v>6.4</v>
@@ -3749,7 +3749,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AX13">
         <v>11.5</v>
@@ -3758,19 +3758,19 @@
         <v>11</v>
       </c>
       <c r="AZ13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA13">
         <v>80</v>
       </c>
       <c r="BB13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BC13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BD13">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BE13">
         <v>48</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="124">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>US United Soccer League</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>01:10:00</t>
+  </si>
+  <si>
     <t>01:30:00</t>
   </si>
   <si>
@@ -292,6 +298,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>Kansas City</t>
   </si>
   <si>
@@ -304,6 +313,9 @@
     <t>Minnesota Utd</t>
   </si>
   <si>
+    <t>Boyaca Patriotas</t>
+  </si>
+  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
@@ -328,6 +340,9 @@
     <t>Rayo Vallecano</t>
   </si>
   <si>
+    <t>Real Santander</t>
+  </si>
+  <si>
     <t>St Louis City SC</t>
   </si>
   <si>
@@ -340,6 +355,9 @@
     <t>Atlanta Utd</t>
   </si>
   <si>
+    <t>Orsomarso</t>
+  </si>
+  <si>
     <t>FC Dallas</t>
   </si>
   <si>
@@ -364,7 +382,10 @@
     <t>Alaves</t>
   </si>
   <si>
-    <t>2026-08-18 09:04:10</t>
+    <t>Barranquilla</t>
+  </si>
+  <si>
+    <t>2026-08-18 11:12:28</t>
   </si>
 </sst>
 </file>
@@ -696,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -946,16 +967,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F2">
         <v>3.6</v>
@@ -979,13 +1000,13 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
         <v>6</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
         <v>2.68</v>
@@ -1003,7 +1024,7 @@
         <v>1.54</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V2">
         <v>1.93</v>
@@ -1015,7 +1036,7 @@
         <v>27</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>16.5</v>
@@ -1057,7 +1078,7 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN2">
         <v>25</v>
@@ -1087,13 +1108,13 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX2">
         <v>20</v>
       </c>
       <c r="AY2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2">
         <v>13</v>
@@ -1117,70 +1138,70 @@
         <v>20</v>
       </c>
       <c r="BG2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH2">
+        <v>5.1</v>
+      </c>
+      <c r="BI2">
+        <v>3.65</v>
+      </c>
+      <c r="BJ2">
+        <v>9</v>
+      </c>
+      <c r="BK2">
+        <v>3.65</v>
+      </c>
+      <c r="BL2">
+        <v>85</v>
+      </c>
+      <c r="BM2">
+        <v>5.7</v>
+      </c>
+      <c r="BN2">
         <v>8.4</v>
       </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>2.14</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>1.8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>2.1</v>
-      </c>
-      <c r="BN2">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP2">
+        <v>29</v>
+      </c>
+      <c r="BQ2">
+        <v>5</v>
+      </c>
+      <c r="BR2">
         <v>34</v>
       </c>
-      <c r="BQ2">
-        <v>2</v>
-      </c>
-      <c r="BR2">
-        <v>40</v>
-      </c>
       <c r="BS2">
-        <v>2.02</v>
+        <v>5.2</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BU2">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BV2">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BY2">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CA2">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1188,16 +1209,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F3">
         <v>2.78</v>
@@ -1218,7 +1239,7 @@
         <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
         <v>1.13</v>
@@ -1260,7 +1281,7 @@
         <v>10</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>70</v>
@@ -1275,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>18.5</v>
@@ -1311,13 +1332,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1329,7 +1350,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1338,7 +1359,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA3">
         <v>6.2</v>
@@ -1353,76 +1374,76 @@
         <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
         <v>6.2</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1430,22 +1451,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H4">
         <v>5.9</v>
@@ -1454,13 +1475,13 @@
         <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.08</v>
@@ -1469,10 +1490,10 @@
         <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
@@ -1487,7 +1508,7 @@
         <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.19</v>
@@ -1499,28 +1520,28 @@
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z4">
         <v>46</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB4">
         <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1550,7 +1571,7 @@
         <v>130</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
         <v>16</v>
@@ -1559,22 +1580,22 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT4">
         <v>7.4</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX4">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY4">
         <v>9</v>
@@ -1583,7 +1604,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1604,67 +1625,67 @@
         <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="BN4">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BS4">
-        <v>1.85</v>
+        <v>8</v>
       </c>
       <c r="BT4">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BU4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW4">
-        <v>1.89</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY4">
-        <v>1.9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1672,34 +1693,34 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F5">
         <v>1.82</v>
       </c>
       <c r="G5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H5">
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1708,25 +1729,25 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q5">
+        <v>1.75</v>
+      </c>
+      <c r="R5">
+        <v>1.5</v>
+      </c>
+      <c r="S5">
+        <v>2.92</v>
+      </c>
+      <c r="T5">
         <v>1.71</v>
-      </c>
-      <c r="R5">
-        <v>1.52</v>
-      </c>
-      <c r="S5">
-        <v>2.8</v>
-      </c>
-      <c r="T5">
-        <v>1.68</v>
       </c>
       <c r="U5">
         <v>2.3</v>
@@ -1738,7 +1759,7 @@
         <v>2.14</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y5">
         <v>20</v>
@@ -1762,7 +1783,7 @@
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -1771,7 +1792,7 @@
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="AJ5">
         <v>21</v>
@@ -1789,10 +1810,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
         <v>17</v>
@@ -1804,7 +1825,7 @@
         <v>38</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU5">
         <v>8.4</v>
@@ -1813,16 +1834,16 @@
         <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX5">
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
         <v>28</v>
@@ -1834,7 +1855,7 @@
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE5">
         <v>34</v>
@@ -1843,312 +1864,312 @@
         <v>8.6</v>
       </c>
       <c r="BG5">
+        <v>26</v>
+      </c>
+      <c r="BH5">
+        <v>4.1</v>
+      </c>
+      <c r="BI5">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5">
+        <v>9.6</v>
+      </c>
+      <c r="BK5">
+        <v>5.1</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>10</v>
+      </c>
+      <c r="BN5">
+        <v>4.9</v>
+      </c>
+      <c r="BO5">
+        <v>4.1</v>
+      </c>
+      <c r="BP5">
+        <v>12.5</v>
+      </c>
+      <c r="BQ5">
+        <v>5.9</v>
+      </c>
+      <c r="BR5">
+        <v>24</v>
+      </c>
+      <c r="BS5">
+        <v>7.6</v>
+      </c>
+      <c r="BT5">
+        <v>8.4</v>
+      </c>
+      <c r="BU5">
+        <v>4.8</v>
+      </c>
+      <c r="BV5">
         <v>36</v>
       </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.98</v>
-      </c>
-      <c r="BJ5">
-        <v>13</v>
-      </c>
-      <c r="BK5">
-        <v>1.72</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.98</v>
-      </c>
-      <c r="BN5">
-        <v>6.4</v>
-      </c>
-      <c r="BO5">
-        <v>3.35</v>
-      </c>
-      <c r="BP5">
-        <v>17</v>
-      </c>
-      <c r="BQ5">
-        <v>1.78</v>
-      </c>
-      <c r="BR5">
-        <v>32</v>
-      </c>
-      <c r="BS5">
-        <v>1.87</v>
-      </c>
-      <c r="BT5">
-        <v>11</v>
-      </c>
-      <c r="BU5">
-        <v>5.3</v>
-      </c>
-      <c r="BV5">
-        <v>46</v>
-      </c>
       <c r="BW5">
-        <v>1.9</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>1.91</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CA5">
-        <v>1.84</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F6">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1.99</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>1.09</v>
       </c>
       <c r="O6">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>2.64</v>
+        <v>1.08</v>
       </c>
       <c r="Q6">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="R6">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2156,241 +2177,241 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F7">
-        <v>2.84</v>
+        <v>1.94</v>
       </c>
       <c r="G7">
-        <v>2.98</v>
+        <v>1.99</v>
       </c>
       <c r="H7">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="O7">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="T7">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U7">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="X7">
+        <v>40</v>
+      </c>
+      <c r="Y7">
+        <v>23</v>
+      </c>
+      <c r="Z7">
+        <v>60</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>14</v>
+      </c>
+      <c r="AC7">
+        <v>9.6</v>
+      </c>
+      <c r="AD7">
+        <v>17.5</v>
+      </c>
+      <c r="AE7">
+        <v>95</v>
+      </c>
+      <c r="AF7">
+        <v>16</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>15</v>
+      </c>
+      <c r="AI7">
+        <v>110</v>
+      </c>
+      <c r="AJ7">
+        <v>32</v>
+      </c>
+      <c r="AK7">
+        <v>23</v>
+      </c>
+      <c r="AL7">
+        <v>42</v>
+      </c>
+      <c r="AM7">
+        <v>270</v>
+      </c>
+      <c r="AN7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO7">
+        <v>48</v>
+      </c>
+      <c r="AP7">
         <v>21</v>
       </c>
-      <c r="Y7">
-        <v>14</v>
-      </c>
-      <c r="Z7">
-        <v>25</v>
-      </c>
-      <c r="AA7">
-        <v>70</v>
-      </c>
-      <c r="AB7">
+      <c r="AQ7">
+        <v>16</v>
+      </c>
+      <c r="AR7">
+        <v>21</v>
+      </c>
+      <c r="AS7">
+        <v>38</v>
+      </c>
+      <c r="AT7">
+        <v>12.5</v>
+      </c>
+      <c r="AU7">
+        <v>8.6</v>
+      </c>
+      <c r="AV7">
+        <v>15</v>
+      </c>
+      <c r="AW7">
+        <v>24</v>
+      </c>
+      <c r="AX7">
+        <v>13.5</v>
+      </c>
+      <c r="AY7">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7">
+        <v>13</v>
+      </c>
+      <c r="BA7">
+        <v>24</v>
+      </c>
+      <c r="BB7">
+        <v>17.5</v>
+      </c>
+      <c r="BC7">
+        <v>15.5</v>
+      </c>
+      <c r="BD7">
         <v>18.5</v>
-      </c>
-      <c r="AC7">
-        <v>8.6</v>
-      </c>
-      <c r="AD7">
-        <v>12.5</v>
-      </c>
-      <c r="AE7">
-        <v>26</v>
-      </c>
-      <c r="AF7">
-        <v>23</v>
-      </c>
-      <c r="AG7">
-        <v>13</v>
-      </c>
-      <c r="AH7">
-        <v>18.5</v>
-      </c>
-      <c r="AI7">
-        <v>60</v>
-      </c>
-      <c r="AJ7">
-        <v>130</v>
-      </c>
-      <c r="AK7">
-        <v>44</v>
-      </c>
-      <c r="AL7">
-        <v>38</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>21</v>
-      </c>
-      <c r="AO7">
-        <v>20</v>
-      </c>
-      <c r="AP7">
-        <v>15</v>
-      </c>
-      <c r="AQ7">
-        <v>12.5</v>
-      </c>
-      <c r="AR7">
-        <v>16</v>
-      </c>
-      <c r="AS7">
-        <v>22</v>
-      </c>
-      <c r="AT7">
-        <v>13</v>
-      </c>
-      <c r="AU7">
-        <v>7.8</v>
-      </c>
-      <c r="AV7">
-        <v>10.5</v>
-      </c>
-      <c r="AW7">
-        <v>20</v>
-      </c>
-      <c r="AX7">
-        <v>18.5</v>
-      </c>
-      <c r="AY7">
-        <v>11.5</v>
-      </c>
-      <c r="AZ7">
-        <v>12</v>
-      </c>
-      <c r="BA7">
-        <v>21</v>
-      </c>
-      <c r="BB7">
-        <v>36</v>
-      </c>
-      <c r="BC7">
-        <v>18.5</v>
-      </c>
-      <c r="BD7">
-        <v>22</v>
       </c>
       <c r="BE7">
         <v>30</v>
       </c>
       <c r="BF7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BG7">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BH7">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
         <v>30</v>
       </c>
       <c r="BS7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BU7">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV7">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BW7">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BY7">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="CA7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2398,725 +2419,725 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F8">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="H8">
+        <v>2.5</v>
+      </c>
+      <c r="I8">
+        <v>2.58</v>
+      </c>
+      <c r="J8">
+        <v>3.75</v>
+      </c>
+      <c r="K8">
+        <v>3.9</v>
+      </c>
+      <c r="L8">
+        <v>1.34</v>
+      </c>
+      <c r="M8">
+        <v>1.05</v>
+      </c>
+      <c r="N8">
         <v>4.8</v>
       </c>
-      <c r="I8">
-        <v>5.1</v>
-      </c>
-      <c r="J8">
-        <v>4.3</v>
-      </c>
-      <c r="K8">
-        <v>4.4</v>
-      </c>
-      <c r="L8">
-        <v>1.3</v>
-      </c>
-      <c r="M8">
-        <v>1.03</v>
-      </c>
-      <c r="N8">
-        <v>5.5</v>
-      </c>
       <c r="O8">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="R8">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="S8">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="X8">
+        <v>21</v>
+      </c>
+      <c r="Y8">
+        <v>14</v>
+      </c>
+      <c r="Z8">
+        <v>25</v>
+      </c>
+      <c r="AA8">
+        <v>70</v>
+      </c>
+      <c r="AB8">
+        <v>18.5</v>
+      </c>
+      <c r="AC8">
+        <v>8.6</v>
+      </c>
+      <c r="AD8">
+        <v>12.5</v>
+      </c>
+      <c r="AE8">
+        <v>26</v>
+      </c>
+      <c r="AF8">
         <v>23</v>
       </c>
-      <c r="Y8">
-        <v>23</v>
-      </c>
-      <c r="Z8">
+      <c r="AG8">
+        <v>13</v>
+      </c>
+      <c r="AH8">
+        <v>18.5</v>
+      </c>
+      <c r="AI8">
+        <v>60</v>
+      </c>
+      <c r="AJ8">
+        <v>130</v>
+      </c>
+      <c r="AK8">
         <v>44</v>
       </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
+      <c r="AL8">
+        <v>38</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>21</v>
+      </c>
+      <c r="AO8">
+        <v>20</v>
+      </c>
+      <c r="AP8">
+        <v>15</v>
+      </c>
+      <c r="AQ8">
+        <v>12.5</v>
+      </c>
+      <c r="AR8">
+        <v>16</v>
+      </c>
+      <c r="AS8">
+        <v>22</v>
+      </c>
+      <c r="AT8">
+        <v>13</v>
+      </c>
+      <c r="AU8">
+        <v>7.8</v>
+      </c>
+      <c r="AV8">
+        <v>10.5</v>
+      </c>
+      <c r="AW8">
+        <v>20</v>
+      </c>
+      <c r="AX8">
+        <v>18.5</v>
+      </c>
+      <c r="AY8">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8">
         <v>12</v>
       </c>
-      <c r="AC8">
-        <v>10</v>
-      </c>
-      <c r="AD8">
-        <v>19.5</v>
-      </c>
-      <c r="AE8">
-        <v>55</v>
-      </c>
-      <c r="AF8">
-        <v>13</v>
-      </c>
-      <c r="AG8">
-        <v>10</v>
-      </c>
-      <c r="AH8">
-        <v>16.5</v>
-      </c>
-      <c r="AI8">
-        <v>55</v>
-      </c>
-      <c r="AJ8">
-        <v>19</v>
-      </c>
-      <c r="AK8">
-        <v>16.5</v>
-      </c>
-      <c r="AL8">
-        <v>26</v>
-      </c>
-      <c r="AM8">
-        <v>70</v>
-      </c>
-      <c r="AN8">
-        <v>7.6</v>
-      </c>
-      <c r="AO8">
-        <v>44</v>
-      </c>
-      <c r="AP8">
+      <c r="BA8">
         <v>21</v>
       </c>
-      <c r="AQ8">
-        <v>21</v>
-      </c>
-      <c r="AR8">
-        <v>38</v>
-      </c>
-      <c r="AS8">
-        <v>40</v>
-      </c>
-      <c r="AT8">
-        <v>11</v>
-      </c>
-      <c r="AU8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV8">
-        <v>17.5</v>
-      </c>
-      <c r="AW8">
-        <v>48</v>
-      </c>
-      <c r="AX8">
-        <v>12</v>
-      </c>
-      <c r="AY8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8">
-        <v>15.5</v>
-      </c>
-      <c r="BA8">
-        <v>44</v>
-      </c>
       <c r="BB8">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BG8">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="BH8">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI8">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
+        <v>30</v>
+      </c>
+      <c r="BS8">
+        <v>7.2</v>
+      </c>
+      <c r="BT8">
+        <v>6</v>
+      </c>
+      <c r="BU8">
+        <v>4.5</v>
+      </c>
+      <c r="BV8">
+        <v>18.5</v>
+      </c>
+      <c r="BW8">
+        <v>6.4</v>
+      </c>
+      <c r="BX8">
+        <v>28</v>
+      </c>
+      <c r="BY8">
+        <v>7.2</v>
+      </c>
+      <c r="BZ8">
         <v>21</v>
       </c>
-      <c r="BS8">
-        <v>9.4</v>
-      </c>
-      <c r="BT8">
-        <v>8.6</v>
-      </c>
-      <c r="BU8">
-        <v>6.4</v>
-      </c>
-      <c r="BV8">
-        <v>36</v>
-      </c>
-      <c r="BW8">
-        <v>11.5</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>11.5</v>
-      </c>
-      <c r="BZ8">
-        <v>15</v>
-      </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="CB8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F9">
-        <v>2.66</v>
+        <v>1.73</v>
       </c>
       <c r="G9">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>2.62</v>
+        <v>4.9</v>
       </c>
       <c r="I9">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
         <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="O9">
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="Q9">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI9">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10">
+        <v>2.66</v>
+      </c>
+      <c r="G10">
+        <v>2.94</v>
+      </c>
+      <c r="H10">
+        <v>2.62</v>
+      </c>
+      <c r="I10">
+        <v>2.88</v>
+      </c>
+      <c r="J10">
+        <v>3.45</v>
+      </c>
+      <c r="K10">
+        <v>4.2</v>
+      </c>
+      <c r="L10">
+        <v>1.38</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>3.95</v>
+      </c>
+      <c r="O10">
+        <v>1.28</v>
+      </c>
+      <c r="P10">
+        <v>2.02</v>
+      </c>
+      <c r="Q10">
+        <v>1.86</v>
+      </c>
+      <c r="R10">
+        <v>1.4</v>
+      </c>
+      <c r="S10">
+        <v>3.1</v>
+      </c>
+      <c r="T10">
+        <v>1.68</v>
+      </c>
+      <c r="U10">
+        <v>2.26</v>
+      </c>
+      <c r="V10">
+        <v>1.53</v>
+      </c>
+      <c r="W10">
+        <v>1.52</v>
+      </c>
+      <c r="X10">
+        <v>19</v>
+      </c>
+      <c r="Y10">
+        <v>14.5</v>
+      </c>
+      <c r="Z10">
+        <v>22</v>
+      </c>
+      <c r="AA10">
+        <v>48</v>
+      </c>
+      <c r="AB10">
+        <v>14.5</v>
+      </c>
+      <c r="AC10">
+        <v>9.6</v>
+      </c>
+      <c r="AD10">
+        <v>14.5</v>
+      </c>
+      <c r="AE10">
+        <v>34</v>
+      </c>
+      <c r="AF10">
+        <v>23</v>
+      </c>
+      <c r="AG10">
+        <v>14.5</v>
+      </c>
+      <c r="AH10">
+        <v>19</v>
+      </c>
+      <c r="AI10">
+        <v>44</v>
+      </c>
+      <c r="AJ10">
+        <v>48</v>
+      </c>
+      <c r="AK10">
+        <v>34</v>
+      </c>
+      <c r="AL10">
+        <v>46</v>
+      </c>
+      <c r="AM10">
         <v>90</v>
       </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10">
-        <v>2.14</v>
-      </c>
-      <c r="G10">
-        <v>2.2</v>
-      </c>
-      <c r="H10">
-        <v>3.15</v>
-      </c>
-      <c r="I10">
-        <v>3.3</v>
-      </c>
-      <c r="J10">
-        <v>4.2</v>
-      </c>
-      <c r="K10">
-        <v>4.5</v>
-      </c>
-      <c r="L10">
-        <v>1.22</v>
-      </c>
-      <c r="M10">
-        <v>1.02</v>
-      </c>
-      <c r="N10">
-        <v>7.6</v>
-      </c>
-      <c r="O10">
-        <v>1.13</v>
-      </c>
-      <c r="P10">
-        <v>3.25</v>
-      </c>
-      <c r="Q10">
-        <v>1.41</v>
-      </c>
-      <c r="R10">
-        <v>1.92</v>
-      </c>
-      <c r="S10">
-        <v>2.02</v>
-      </c>
-      <c r="T10">
-        <v>1.42</v>
-      </c>
-      <c r="U10">
-        <v>3.1</v>
-      </c>
-      <c r="V10">
-        <v>1.43</v>
-      </c>
-      <c r="W10">
-        <v>1.83</v>
-      </c>
-      <c r="X10">
-        <v>38</v>
-      </c>
-      <c r="Y10">
-        <v>25</v>
-      </c>
-      <c r="Z10">
-        <v>34</v>
-      </c>
-      <c r="AA10">
-        <v>380</v>
-      </c>
-      <c r="AB10">
-        <v>19.5</v>
-      </c>
-      <c r="AC10">
-        <v>12</v>
-      </c>
-      <c r="AD10">
-        <v>15.5</v>
-      </c>
-      <c r="AE10">
-        <v>32</v>
-      </c>
-      <c r="AF10">
-        <v>21</v>
-      </c>
-      <c r="AG10">
-        <v>12</v>
-      </c>
-      <c r="AH10">
+      <c r="AN10">
+        <v>27</v>
+      </c>
+      <c r="AO10">
+        <v>26</v>
+      </c>
+      <c r="AP10">
+        <v>12.5</v>
+      </c>
+      <c r="AQ10">
+        <v>9.6</v>
+      </c>
+      <c r="AR10">
         <v>14.5</v>
       </c>
-      <c r="AI10">
-        <v>30</v>
-      </c>
-      <c r="AJ10">
-        <v>32</v>
-      </c>
-      <c r="AK10">
-        <v>20</v>
-      </c>
-      <c r="AL10">
-        <v>23</v>
-      </c>
-      <c r="AM10">
-        <v>44</v>
-      </c>
-      <c r="AN10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO10">
-        <v>15.5</v>
-      </c>
-      <c r="AP10">
-        <v>24</v>
-      </c>
-      <c r="AQ10">
-        <v>21</v>
-      </c>
-      <c r="AR10">
-        <v>19.5</v>
-      </c>
       <c r="AS10">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="BG10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI10">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.16</v>
+        <v>12.5</v>
       </c>
       <c r="BN10">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BO10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BQ10">
-        <v>1.99</v>
+        <v>8.4</v>
       </c>
       <c r="BR10">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>2.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT10">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="BU10">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BW10">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BX10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>2.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3124,241 +3145,241 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F11">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="G11">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H11">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="I11">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="Q11">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="R11">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="T11">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="V11">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
-        <v>2.66</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Z11">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB11">
+        <v>19.5</v>
+      </c>
+      <c r="AC11">
         <v>12</v>
       </c>
-      <c r="AC11">
-        <v>11</v>
-      </c>
       <c r="AD11">
+        <v>15.5</v>
+      </c>
+      <c r="AE11">
         <v>32</v>
       </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
       <c r="AF11">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH11">
+        <v>14.5</v>
+      </c>
+      <c r="AI11">
+        <v>30</v>
+      </c>
+      <c r="AJ11">
+        <v>32</v>
+      </c>
+      <c r="AK11">
         <v>20</v>
       </c>
-      <c r="AI11">
-        <v>940</v>
-      </c>
-      <c r="AJ11">
-        <v>16</v>
-      </c>
-      <c r="AK11">
+      <c r="AL11">
+        <v>23</v>
+      </c>
+      <c r="AM11">
+        <v>44</v>
+      </c>
+      <c r="AN11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO11">
         <v>15.5</v>
       </c>
-      <c r="AL11">
-        <v>44</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>6.4</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
       <c r="AP11">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AQ11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR11">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AS11">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU11">
         <v>10</v>
       </c>
       <c r="AV11">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
+        <v>12.5</v>
+      </c>
+      <c r="BA11">
+        <v>19</v>
+      </c>
+      <c r="BB11">
+        <v>19</v>
+      </c>
+      <c r="BC11">
         <v>16.5</v>
-      </c>
-      <c r="BA11">
-        <v>30</v>
-      </c>
-      <c r="BB11">
-        <v>12</v>
-      </c>
-      <c r="BC11">
-        <v>12.5</v>
       </c>
       <c r="BD11">
         <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BF11">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BG11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BK11">
-        <v>1.79</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM11">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BN11">
+        <v>6.2</v>
+      </c>
+      <c r="BO11">
+        <v>5.1</v>
+      </c>
+      <c r="BP11">
+        <v>14</v>
+      </c>
+      <c r="BQ11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR11">
+        <v>19.5</v>
+      </c>
+      <c r="BS11">
         <v>5.9</v>
       </c>
-      <c r="BO11">
-        <v>3.15</v>
-      </c>
-      <c r="BP11">
-        <v>13</v>
-      </c>
-      <c r="BQ11">
-        <v>1.79</v>
-      </c>
-      <c r="BR11">
-        <v>29</v>
-      </c>
-      <c r="BS11">
-        <v>1.94</v>
-      </c>
       <c r="BT11">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY11">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="CA11">
-        <v>1.86</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB11" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3366,483 +3387,967 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F12">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
       <c r="G12">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>2.88</v>
+        <v>5.9</v>
       </c>
       <c r="I12">
-        <v>2.98</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="O12">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="R12">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="S12">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="T12">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="U12">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>1.69</v>
+        <v>2.66</v>
       </c>
       <c r="X12">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="Y12">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="AA12">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AC12">
         <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AE12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
+        <v>11.5</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+      <c r="AH12">
+        <v>26</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>16</v>
+      </c>
+      <c r="AK12">
+        <v>15.5</v>
+      </c>
+      <c r="AL12">
+        <v>44</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>6.4</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>18</v>
+      </c>
+      <c r="AQ12">
+        <v>18</v>
+      </c>
+      <c r="AR12">
         <v>28</v>
       </c>
-      <c r="AG12">
+      <c r="AS12">
+        <v>44</v>
+      </c>
+      <c r="AT12">
+        <v>10.5</v>
+      </c>
+      <c r="AU12">
+        <v>10</v>
+      </c>
+      <c r="AV12">
+        <v>20</v>
+      </c>
+      <c r="AW12">
+        <v>32</v>
+      </c>
+      <c r="AX12">
+        <v>10</v>
+      </c>
+      <c r="AY12">
+        <v>9</v>
+      </c>
+      <c r="AZ12">
+        <v>16.5</v>
+      </c>
+      <c r="BA12">
+        <v>30</v>
+      </c>
+      <c r="BB12">
+        <v>12</v>
+      </c>
+      <c r="BC12">
         <v>12.5</v>
       </c>
-      <c r="AH12">
-        <v>14.5</v>
-      </c>
-      <c r="AI12">
-        <v>48</v>
-      </c>
-      <c r="AJ12">
-        <v>60</v>
-      </c>
-      <c r="AK12">
-        <v>29</v>
-      </c>
-      <c r="AL12">
-        <v>40</v>
-      </c>
-      <c r="AM12">
-        <v>130</v>
-      </c>
-      <c r="AN12">
-        <v>10.5</v>
-      </c>
-      <c r="AO12">
-        <v>15</v>
-      </c>
-      <c r="AP12">
-        <v>20</v>
-      </c>
-      <c r="AQ12">
-        <v>15</v>
-      </c>
-      <c r="AR12">
-        <v>17.5</v>
-      </c>
-      <c r="AS12">
-        <v>25</v>
-      </c>
-      <c r="AT12">
-        <v>14</v>
-      </c>
-      <c r="AU12">
-        <v>9.4</v>
-      </c>
-      <c r="AV12">
-        <v>12</v>
-      </c>
-      <c r="AW12">
+      <c r="BD12">
         <v>18</v>
-      </c>
-      <c r="AX12">
-        <v>17.5</v>
-      </c>
-      <c r="AY12">
-        <v>11</v>
-      </c>
-      <c r="AZ12">
-        <v>12.5</v>
-      </c>
-      <c r="BA12">
-        <v>19</v>
-      </c>
-      <c r="BB12">
-        <v>21</v>
-      </c>
-      <c r="BC12">
-        <v>17.5</v>
-      </c>
-      <c r="BD12">
-        <v>21</v>
       </c>
       <c r="BE12">
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG12">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI12">
-        <v>2.06</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="BO12">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ12">
+        <v>4.9</v>
+      </c>
+      <c r="BR12">
         <v>22</v>
       </c>
-      <c r="BQ12">
-        <v>1.88</v>
-      </c>
-      <c r="BR12">
-        <v>30</v>
-      </c>
       <c r="BS12">
-        <v>1.93</v>
+        <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU12">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BV12">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.92</v>
+        <v>8</v>
       </c>
       <c r="BX12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.94</v>
+        <v>8</v>
       </c>
       <c r="BZ12">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="CA12">
-        <v>1.86</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="H13">
+        <v>2.9</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
         <v>3.95</v>
       </c>
-      <c r="I13">
-        <v>4.1</v>
-      </c>
-      <c r="J13">
-        <v>3.1</v>
-      </c>
       <c r="K13">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M13">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="O13">
-        <v>1.59</v>
+        <v>1.16</v>
       </c>
       <c r="P13">
-        <v>1.52</v>
+        <v>2.92</v>
       </c>
       <c r="Q13">
-        <v>2.76</v>
+        <v>1.49</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.78</v>
       </c>
       <c r="S13">
-        <v>5.9</v>
+        <v>2.22</v>
       </c>
       <c r="T13">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="U13">
-        <v>1.75</v>
+        <v>2.94</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Z13">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AA13">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AC13">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE13">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AF13">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL13">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN13">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="AQ13">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AR13">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AS13">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AT13">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AU13">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV13">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AW13">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="AX13">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY13">
         <v>11</v>
       </c>
       <c r="AZ13">
+        <v>12</v>
+      </c>
+      <c r="BA13">
+        <v>19</v>
+      </c>
+      <c r="BB13">
+        <v>21</v>
+      </c>
+      <c r="BC13">
+        <v>17.5</v>
+      </c>
+      <c r="BD13">
+        <v>21</v>
+      </c>
+      <c r="BE13">
+        <v>25</v>
+      </c>
+      <c r="BF13">
+        <v>9.6</v>
+      </c>
+      <c r="BG13">
+        <v>13</v>
+      </c>
+      <c r="BH13">
+        <v>5.1</v>
+      </c>
+      <c r="BI13">
+        <v>3.8</v>
+      </c>
+      <c r="BJ13">
+        <v>8.6</v>
+      </c>
+      <c r="BK13">
+        <v>4.6</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>8.6</v>
+      </c>
+      <c r="BN13">
+        <v>6.4</v>
+      </c>
+      <c r="BO13">
+        <v>4.6</v>
+      </c>
+      <c r="BP13">
+        <v>16</v>
+      </c>
+      <c r="BQ13">
+        <v>6</v>
+      </c>
+      <c r="BR13">
+        <v>22</v>
+      </c>
+      <c r="BS13">
+        <v>6.8</v>
+      </c>
+      <c r="BT13">
+        <v>7</v>
+      </c>
+      <c r="BU13">
+        <v>5.1</v>
+      </c>
+      <c r="BV13">
+        <v>19.5</v>
+      </c>
+      <c r="BW13">
+        <v>6.6</v>
+      </c>
+      <c r="BX13">
+        <v>25</v>
+      </c>
+      <c r="BY13">
+        <v>7</v>
+      </c>
+      <c r="BZ13">
+        <v>13.5</v>
+      </c>
+      <c r="CA13">
+        <v>5.7</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14">
+        <v>2.34</v>
+      </c>
+      <c r="G14">
+        <v>2.38</v>
+      </c>
+      <c r="H14">
+        <v>3.9</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>3.1</v>
+      </c>
+      <c r="K14">
+        <v>3.15</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.14</v>
+      </c>
+      <c r="N14">
+        <v>2.6</v>
+      </c>
+      <c r="O14">
+        <v>1.59</v>
+      </c>
+      <c r="P14">
+        <v>1.53</v>
+      </c>
+      <c r="Q14">
+        <v>2.76</v>
+      </c>
+      <c r="R14">
+        <v>1.19</v>
+      </c>
+      <c r="S14">
+        <v>5.9</v>
+      </c>
+      <c r="T14">
+        <v>2.26</v>
+      </c>
+      <c r="U14">
+        <v>1.76</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>10</v>
+      </c>
+      <c r="Z14">
+        <v>26</v>
+      </c>
+      <c r="AA14">
+        <v>110</v>
+      </c>
+      <c r="AB14">
+        <v>7</v>
+      </c>
+      <c r="AC14">
+        <v>6.8</v>
+      </c>
+      <c r="AD14">
+        <v>18</v>
+      </c>
+      <c r="AE14">
+        <v>70</v>
+      </c>
+      <c r="AF14">
+        <v>12.5</v>
+      </c>
+      <c r="AG14">
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <v>26</v>
+      </c>
+      <c r="AI14">
+        <v>120</v>
+      </c>
+      <c r="AJ14">
+        <v>34</v>
+      </c>
+      <c r="AK14">
+        <v>36</v>
+      </c>
+      <c r="AL14">
+        <v>70</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>38</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>7.6</v>
+      </c>
+      <c r="AQ14">
+        <v>9.4</v>
+      </c>
+      <c r="AR14">
         <v>23</v>
       </c>
-      <c r="BA13">
+      <c r="AS14">
+        <v>55</v>
+      </c>
+      <c r="AT14">
+        <v>6.4</v>
+      </c>
+      <c r="AU14">
+        <v>6.6</v>
+      </c>
+      <c r="AV14">
+        <v>15.5</v>
+      </c>
+      <c r="AW14">
+        <v>50</v>
+      </c>
+      <c r="AX14">
+        <v>11.5</v>
+      </c>
+      <c r="AY14">
+        <v>11</v>
+      </c>
+      <c r="AZ14">
+        <v>23</v>
+      </c>
+      <c r="BA14">
         <v>80</v>
       </c>
-      <c r="BB13">
+      <c r="BB14">
         <v>30</v>
       </c>
-      <c r="BC13">
+      <c r="BC14">
         <v>30</v>
       </c>
-      <c r="BD13">
+      <c r="BD14">
+        <v>48</v>
+      </c>
+      <c r="BE14">
+        <v>48</v>
+      </c>
+      <c r="BF14">
+        <v>30</v>
+      </c>
+      <c r="BG14">
+        <v>85</v>
+      </c>
+      <c r="BH14">
+        <v>2.9</v>
+      </c>
+      <c r="BI14">
+        <v>2.24</v>
+      </c>
+      <c r="BJ14">
+        <v>13.5</v>
+      </c>
+      <c r="BK14">
+        <v>4.3</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>6.2</v>
+      </c>
+      <c r="BN14">
+        <v>5.5</v>
+      </c>
+      <c r="BO14">
+        <v>3.95</v>
+      </c>
+      <c r="BP14">
+        <v>24</v>
+      </c>
+      <c r="BQ14">
+        <v>5</v>
+      </c>
+      <c r="BR14">
         <v>55</v>
       </c>
-      <c r="BE13">
-        <v>48</v>
-      </c>
-      <c r="BF13">
-        <v>30</v>
-      </c>
-      <c r="BG13">
-        <v>85</v>
-      </c>
-      <c r="BH13">
-        <v>2.9</v>
-      </c>
-      <c r="BI13">
-        <v>2.24</v>
-      </c>
-      <c r="BJ13">
-        <v>13.5</v>
-      </c>
-      <c r="BK13">
-        <v>4.3</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>6.2</v>
-      </c>
-      <c r="BN13">
-        <v>5.5</v>
-      </c>
-      <c r="BO13">
-        <v>3.95</v>
-      </c>
-      <c r="BP13">
-        <v>24</v>
-      </c>
-      <c r="BQ13">
-        <v>5</v>
-      </c>
-      <c r="BR13">
-        <v>55</v>
-      </c>
-      <c r="BS13">
+      <c r="BS14">
         <v>5.7</v>
       </c>
-      <c r="BT13">
+      <c r="BT14">
         <v>7.8</v>
       </c>
-      <c r="BU13">
+      <c r="BU14">
         <v>5.4</v>
       </c>
-      <c r="BV13">
+      <c r="BV14">
         <v>46</v>
       </c>
-      <c r="BW13">
+      <c r="BW14">
         <v>5.6</v>
       </c>
-      <c r="BX13">
+      <c r="BX14">
         <v>75</v>
       </c>
-      <c r="BY13">
+      <c r="BY14">
         <v>5.9</v>
       </c>
-      <c r="BZ13">
+      <c r="BZ14">
         <v>60</v>
       </c>
-      <c r="CA13">
+      <c r="CA14">
         <v>5.8</v>
       </c>
-      <c r="CB13" t="s">
-        <v>116</v>
+      <c r="CB14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15">
+        <v>1.04</v>
+      </c>
+      <c r="G15">
+        <v>600</v>
+      </c>
+      <c r="H15">
+        <v>1.04</v>
+      </c>
+      <c r="I15">
+        <v>870</v>
+      </c>
+      <c r="J15">
+        <v>1.03</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.24</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>US United Soccer League</t>
   </si>
   <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>02:30:00</t>
   </si>
   <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -337,6 +343,9 @@
     <t>LA Galaxy</t>
   </si>
   <si>
+    <t>Al-Wakra</t>
+  </si>
+  <si>
     <t>Rayo Vallecano</t>
   </si>
   <si>
@@ -379,13 +388,16 @@
     <t>San Jose Earthquakes</t>
   </si>
   <si>
+    <t>Qatar SC</t>
+  </si>
+  <si>
     <t>Alaves</t>
   </si>
   <si>
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-18 11:12:28</t>
+    <t>2026-08-18 13:20:51</t>
   </si>
 </sst>
 </file>
@@ -717,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -967,16 +979,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F2">
         <v>3.6</v>
@@ -1018,7 +1030,7 @@
         <v>1.68</v>
       </c>
       <c r="S2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T2">
         <v>1.54</v>
@@ -1036,7 +1048,7 @@
         <v>27</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
         <v>16.5</v>
@@ -1147,16 +1159,16 @@
         <v>3.65</v>
       </c>
       <c r="BJ2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK2">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BL2">
         <v>85</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BN2">
         <v>8.4</v>
@@ -1168,40 +1180,40 @@
         <v>29</v>
       </c>
       <c r="BQ2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BT2">
         <v>6</v>
       </c>
       <c r="BU2">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV2">
         <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BX2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BZ2">
         <v>17</v>
       </c>
       <c r="CA2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1209,19 +1221,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
         <v>2.96</v>
@@ -1251,7 +1263,7 @@
         <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
         <v>2.68</v>
@@ -1266,7 +1278,7 @@
         <v>2.12</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
         <v>1.45</v>
@@ -1275,10 +1287,10 @@
         <v>1.51</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
         <v>22</v>
@@ -1287,13 +1299,13 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
         <v>55</v>
@@ -1326,7 +1338,7 @@
         <v>65</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
@@ -1338,7 +1350,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1350,7 +1362,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1359,28 +1371,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BA3">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BD3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH3">
         <v>2.66</v>
@@ -1443,7 +1455,7 @@
         <v>12.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1451,22 +1463,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F4">
         <v>1.76</v>
       </c>
       <c r="G4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
         <v>5.9</v>
@@ -1481,16 +1493,16 @@
         <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
         <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
         <v>1.85</v>
@@ -1511,13 +1523,13 @@
         <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>2.28</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
         <v>18</v>
@@ -1532,13 +1544,13 @@
         <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF4">
         <v>10</v>
@@ -1547,10 +1559,10 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
@@ -1589,13 +1601,13 @@
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4">
         <v>9</v>
@@ -1604,7 +1616,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1616,7 +1628,7 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF4">
         <v>10</v>
@@ -1625,67 +1637,67 @@
         <v>11.5</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>8</v>
+        <v>1.58</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>1.77</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>1.35</v>
       </c>
       <c r="BP4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="BR4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8</v>
+        <v>1.69</v>
       </c>
       <c r="BT4">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>7</v>
+        <v>1.56</v>
       </c>
       <c r="BV4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="BX4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.4</v>
+        <v>1.74</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>7.6</v>
+        <v>1.68</v>
       </c>
       <c r="CB4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1693,16 +1705,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F5">
         <v>1.82</v>
@@ -1711,7 +1723,7 @@
         <v>1.87</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
         <v>4.7</v>
@@ -1732,13 +1744,13 @@
         <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
         <v>1.5</v>
@@ -1747,10 +1759,10 @@
         <v>2.92</v>
       </c>
       <c r="T5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
         <v>1.27</v>
@@ -1759,10 +1771,10 @@
         <v>2.14</v>
       </c>
       <c r="X5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
         <v>38</v>
@@ -1771,7 +1783,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
@@ -1780,7 +1792,7 @@
         <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF5">
         <v>12</v>
@@ -1792,7 +1804,7 @@
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>21</v>
@@ -1804,19 +1816,19 @@
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO5">
         <v>55</v>
       </c>
       <c r="AP5">
+        <v>17</v>
+      </c>
+      <c r="AQ5">
         <v>16.5</v>
-      </c>
-      <c r="AQ5">
-        <v>17</v>
       </c>
       <c r="AR5">
         <v>22</v>
@@ -1825,10 +1837,10 @@
         <v>38</v>
       </c>
       <c r="AT5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
         <v>15.5</v>
@@ -1837,13 +1849,13 @@
         <v>38</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5">
         <v>28</v>
@@ -1858,34 +1870,34 @@
         <v>20</v>
       </c>
       <c r="BE5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG5">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BI5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
         <v>4.1</v>
@@ -1894,40 +1906,40 @@
         <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT5">
         <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
         <v>36</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1935,70 +1947,70 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="Q6">
         <v>1.43</v>
       </c>
       <c r="R6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2112,55 +2124,55 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2169,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2177,22 +2189,22 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F7">
         <v>1.94</v>
       </c>
       <c r="G7">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -2201,10 +2213,10 @@
         <v>4.3</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2219,16 +2231,16 @@
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q7">
         <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S7">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T7">
         <v>1.55</v>
@@ -2237,25 +2249,25 @@
         <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y7">
         <v>23</v>
       </c>
       <c r="Z7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
@@ -2264,46 +2276,46 @@
         <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>15</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK7">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM7">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AN7">
         <v>8.800000000000001</v>
       </c>
       <c r="AO7">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AP7">
         <v>21</v>
       </c>
       <c r="AQ7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS7">
         <v>38</v>
@@ -2327,13 +2339,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
         <v>24</v>
       </c>
       <c r="BB7">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC7">
         <v>15.5</v>
@@ -2372,7 +2384,7 @@
         <v>5.2</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP7">
         <v>12.5</v>
@@ -2381,7 +2393,7 @@
         <v>6.8</v>
       </c>
       <c r="BR7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
         <v>8.800000000000001</v>
@@ -2411,7 +2423,7 @@
         <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2419,34 +2431,34 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="G8">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="I8">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.34</v>
@@ -2458,97 +2470,97 @@
         <v>4.8</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
         <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W8">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z8">
+        <v>18</v>
+      </c>
+      <c r="AA8">
+        <v>60</v>
+      </c>
+      <c r="AB8">
+        <v>15</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>12</v>
+      </c>
+      <c r="AE8">
         <v>25</v>
-      </c>
-      <c r="AA8">
-        <v>70</v>
-      </c>
-      <c r="AB8">
-        <v>18.5</v>
-      </c>
-      <c r="AC8">
-        <v>8.6</v>
-      </c>
-      <c r="AD8">
-        <v>12.5</v>
-      </c>
-      <c r="AE8">
-        <v>26</v>
       </c>
       <c r="AF8">
         <v>23</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI8">
         <v>60</v>
       </c>
       <c r="AJ8">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK8">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AL8">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AP8">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT8">
         <v>13</v>
@@ -2569,7 +2581,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA8">
         <v>21</v>
@@ -2578,64 +2590,64 @@
         <v>36</v>
       </c>
       <c r="BC8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE8">
         <v>32</v>
       </c>
       <c r="BF8">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
         <v>4.1</v>
       </c>
       <c r="BI8">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
         <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW8">
         <v>6.4</v>
@@ -2644,16 +2656,16 @@
         <v>28</v>
       </c>
       <c r="BY8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8">
         <v>21</v>
       </c>
       <c r="CA8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2661,19 +2673,19 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G9">
         <v>1.76</v>
@@ -2682,7 +2694,7 @@
         <v>4.9</v>
       </c>
       <c r="I9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9">
         <v>4.3</v>
@@ -2697,25 +2709,25 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
+        <v>1.62</v>
+      </c>
+      <c r="R9">
         <v>1.61</v>
       </c>
-      <c r="R9">
-        <v>1.62</v>
-      </c>
       <c r="S9">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U9">
         <v>2.44</v>
@@ -2736,7 +2748,7 @@
         <v>44</v>
       </c>
       <c r="AA9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
         <v>12</v>
@@ -2754,10 +2766,10 @@
         <v>13</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
         <v>55</v>
@@ -2802,13 +2814,13 @@
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
         <v>15.5</v>
@@ -2817,7 +2829,7 @@
         <v>44</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC9">
         <v>14.5</v>
@@ -2832,7 +2844,7 @@
         <v>7</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -2844,7 +2856,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2895,7 +2907,7 @@
         <v>7.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2903,22 +2915,22 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F10">
         <v>2.66</v>
       </c>
       <c r="G10">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H10">
         <v>2.62</v>
@@ -2933,7 +2945,7 @@
         <v>4.2</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M10">
         <v>1.06</v>
@@ -2945,13 +2957,13 @@
         <v>1.28</v>
       </c>
       <c r="P10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
         <v>1.86</v>
       </c>
       <c r="R10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
         <v>3.1</v>
@@ -2978,7 +2990,7 @@
         <v>22</v>
       </c>
       <c r="AA10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB10">
         <v>14.5</v>
@@ -3011,16 +3023,16 @@
         <v>34</v>
       </c>
       <c r="AL10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10">
         <v>90</v>
       </c>
       <c r="AN10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP10">
         <v>12.5</v>
@@ -3080,7 +3092,7 @@
         <v>3.65</v>
       </c>
       <c r="BI10">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ10">
         <v>9.199999999999999</v>
@@ -3137,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3145,16 +3157,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F11">
         <v>2.14</v>
@@ -3169,7 +3181,7 @@
         <v>3.3</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
         <v>4.5</v>
@@ -3187,16 +3199,16 @@
         <v>1.13</v>
       </c>
       <c r="P11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R11">
         <v>1.91</v>
       </c>
       <c r="S11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T11">
         <v>1.43</v>
@@ -3250,7 +3262,7 @@
         <v>32</v>
       </c>
       <c r="AK11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL11">
         <v>23</v>
@@ -3277,7 +3289,7 @@
         <v>29</v>
       </c>
       <c r="AT11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU11">
         <v>10</v>
@@ -3322,19 +3334,19 @@
         <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BJ11">
         <v>8.6</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
         <v>60</v>
       </c>
       <c r="BM11">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN11">
         <v>6.2</v>
@@ -3343,43 +3355,43 @@
         <v>5.1</v>
       </c>
       <c r="BP11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BQ11">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BR11">
         <v>19.5</v>
       </c>
       <c r="BS11">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
         <v>21</v>
       </c>
       <c r="BW11">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BX11">
         <v>24</v>
       </c>
       <c r="BY11">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CA11">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="CB11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3387,40 +3399,40 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G12">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>6.6</v>
       </c>
       <c r="J12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L12">
         <v>1.29</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
         <v>5.6</v>
@@ -3429,37 +3441,37 @@
         <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q12">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R12">
         <v>1.63</v>
       </c>
       <c r="S12">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U12">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V12">
         <v>1.18</v>
       </c>
       <c r="W12">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X12">
         <v>27</v>
       </c>
       <c r="Y12">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="Z12">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3471,7 +3483,7 @@
         <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE12">
         <v>1000</v>
@@ -3480,28 +3492,28 @@
         <v>11.5</v>
       </c>
       <c r="AG12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI12">
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK12">
         <v>15.5</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AM12">
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO12">
         <v>1000</v>
@@ -3510,7 +3522,7 @@
         <v>18</v>
       </c>
       <c r="AQ12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR12">
         <v>28</v>
@@ -3534,31 +3546,31 @@
         <v>10</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE12">
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH12">
         <v>4.6</v>
@@ -3621,7 +3633,7 @@
         <v>5.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3629,28 +3641,28 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H13">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J13">
         <v>3.95</v>
@@ -3659,7 +3671,7 @@
         <v>4.3</v>
       </c>
       <c r="L13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -3671,7 +3683,7 @@
         <v>1.16</v>
       </c>
       <c r="P13">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q13">
         <v>1.49</v>
@@ -3680,19 +3692,19 @@
         <v>1.78</v>
       </c>
       <c r="S13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T13">
         <v>1.47</v>
       </c>
       <c r="U13">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="V13">
         <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X13">
         <v>55</v>
@@ -3701,7 +3713,7 @@
         <v>22</v>
       </c>
       <c r="Z13">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA13">
         <v>130</v>
@@ -3710,16 +3722,16 @@
         <v>19</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AF13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
@@ -3728,31 +3740,31 @@
         <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AJ13">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AK13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL13">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO13">
         <v>15</v>
       </c>
       <c r="AP13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AQ13">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR13">
         <v>17.5</v>
@@ -3761,7 +3773,7 @@
         <v>25</v>
       </c>
       <c r="AT13">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AU13">
         <v>9.4</v>
@@ -3785,10 +3797,10 @@
         <v>19</v>
       </c>
       <c r="BB13">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD13">
         <v>21</v>
@@ -3812,13 +3824,13 @@
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN13">
         <v>6.4</v>
@@ -3827,7 +3839,7 @@
         <v>4.6</v>
       </c>
       <c r="BP13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ13">
         <v>6</v>
@@ -3836,34 +3848,34 @@
         <v>22</v>
       </c>
       <c r="BS13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT13">
         <v>7</v>
       </c>
       <c r="BU13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV13">
         <v>19.5</v>
       </c>
       <c r="BW13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA13">
         <v>5.7</v>
       </c>
       <c r="CB13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3871,483 +3883,725 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F14">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="G14">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H14">
+        <v>2.98</v>
+      </c>
+      <c r="I14">
+        <v>3.5</v>
+      </c>
+      <c r="J14">
+        <v>3.6</v>
+      </c>
+      <c r="K14">
+        <v>4.3</v>
+      </c>
+      <c r="L14">
+        <v>1.31</v>
+      </c>
+      <c r="M14">
+        <v>1.04</v>
+      </c>
+      <c r="N14">
+        <v>4.6</v>
+      </c>
+      <c r="O14">
+        <v>1.21</v>
+      </c>
+      <c r="P14">
+        <v>2.22</v>
+      </c>
+      <c r="Q14">
+        <v>1.64</v>
+      </c>
+      <c r="R14">
+        <v>1.49</v>
+      </c>
+      <c r="S14">
+        <v>2.6</v>
+      </c>
+      <c r="T14">
+        <v>1.58</v>
+      </c>
+      <c r="U14">
+        <v>2.36</v>
+      </c>
+      <c r="V14">
+        <v>1.4</v>
+      </c>
+      <c r="W14">
+        <v>1.68</v>
+      </c>
+      <c r="X14">
+        <v>25</v>
+      </c>
+      <c r="Y14">
+        <v>19.5</v>
+      </c>
+      <c r="Z14">
+        <v>30</v>
+      </c>
+      <c r="AA14">
+        <v>65</v>
+      </c>
+      <c r="AB14">
+        <v>16</v>
+      </c>
+      <c r="AC14">
+        <v>11</v>
+      </c>
+      <c r="AD14">
+        <v>17</v>
+      </c>
+      <c r="AE14">
+        <v>40</v>
+      </c>
+      <c r="AF14">
+        <v>21</v>
+      </c>
+      <c r="AG14">
+        <v>14</v>
+      </c>
+      <c r="AH14">
+        <v>19</v>
+      </c>
+      <c r="AI14">
+        <v>46</v>
+      </c>
+      <c r="AJ14">
+        <v>36</v>
+      </c>
+      <c r="AK14">
+        <v>27</v>
+      </c>
+      <c r="AL14">
+        <v>38</v>
+      </c>
+      <c r="AM14">
+        <v>80</v>
+      </c>
+      <c r="AN14">
+        <v>16.5</v>
+      </c>
+      <c r="AO14">
+        <v>29</v>
+      </c>
+      <c r="AP14">
+        <v>15</v>
+      </c>
+      <c r="AQ14">
+        <v>11.5</v>
+      </c>
+      <c r="AR14">
+        <v>18</v>
+      </c>
+      <c r="AS14">
+        <v>4</v>
+      </c>
+      <c r="AT14">
+        <v>9.6</v>
+      </c>
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
+        <v>10</v>
+      </c>
+      <c r="AW14">
         <v>3.9</v>
       </c>
-      <c r="I14">
-        <v>4</v>
-      </c>
-      <c r="J14">
-        <v>3.1</v>
-      </c>
-      <c r="K14">
+      <c r="AX14">
+        <v>12</v>
+      </c>
+      <c r="AY14">
+        <v>8.4</v>
+      </c>
+      <c r="AZ14">
+        <v>11</v>
+      </c>
+      <c r="BA14">
+        <v>3.95</v>
+      </c>
+      <c r="BB14">
+        <v>21</v>
+      </c>
+      <c r="BC14">
+        <v>16</v>
+      </c>
+      <c r="BD14">
+        <v>3.9</v>
+      </c>
+      <c r="BE14">
+        <v>4.1</v>
+      </c>
+      <c r="BF14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG14">
+        <v>17</v>
+      </c>
+      <c r="BH14">
+        <v>4.2</v>
+      </c>
+      <c r="BI14">
         <v>3.15</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>1.14</v>
-      </c>
-      <c r="N14">
-        <v>2.6</v>
-      </c>
-      <c r="O14">
-        <v>1.59</v>
-      </c>
-      <c r="P14">
-        <v>1.53</v>
-      </c>
-      <c r="Q14">
-        <v>2.76</v>
-      </c>
-      <c r="R14">
-        <v>1.19</v>
-      </c>
-      <c r="S14">
-        <v>5.9</v>
-      </c>
-      <c r="T14">
-        <v>2.26</v>
-      </c>
-      <c r="U14">
-        <v>1.76</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>8</v>
-      </c>
-      <c r="Y14">
-        <v>10</v>
-      </c>
-      <c r="Z14">
-        <v>26</v>
-      </c>
-      <c r="AA14">
-        <v>110</v>
-      </c>
-      <c r="AB14">
+      <c r="BJ14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14">
+        <v>4.7</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN14">
+        <v>5.7</v>
+      </c>
+      <c r="BO14">
+        <v>4.2</v>
+      </c>
+      <c r="BP14">
+        <v>16.5</v>
+      </c>
+      <c r="BQ14">
+        <v>6.2</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
         <v>7</v>
       </c>
-      <c r="AC14">
-        <v>6.8</v>
-      </c>
-      <c r="AD14">
-        <v>18</v>
-      </c>
-      <c r="AE14">
-        <v>70</v>
-      </c>
-      <c r="AF14">
-        <v>12.5</v>
-      </c>
-      <c r="AG14">
-        <v>12.5</v>
-      </c>
-      <c r="AH14">
-        <v>26</v>
-      </c>
-      <c r="AI14">
-        <v>120</v>
-      </c>
-      <c r="AJ14">
-        <v>34</v>
-      </c>
-      <c r="AK14">
-        <v>36</v>
-      </c>
-      <c r="AL14">
-        <v>70</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>38</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>7.6</v>
-      </c>
-      <c r="AQ14">
-        <v>9.4</v>
-      </c>
-      <c r="AR14">
-        <v>23</v>
-      </c>
-      <c r="AS14">
-        <v>55</v>
-      </c>
-      <c r="AT14">
+      <c r="BT14">
+        <v>7</v>
+      </c>
+      <c r="BU14">
+        <v>5</v>
+      </c>
+      <c r="BV14">
+        <v>24</v>
+      </c>
+      <c r="BW14">
+        <v>7</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>7.4</v>
+      </c>
+      <c r="BZ14">
+        <v>19.5</v>
+      </c>
+      <c r="CA14">
         <v>6.4</v>
       </c>
-      <c r="AU14">
-        <v>6.6</v>
-      </c>
-      <c r="AV14">
-        <v>15.5</v>
-      </c>
-      <c r="AW14">
-        <v>50</v>
-      </c>
-      <c r="AX14">
-        <v>11.5</v>
-      </c>
-      <c r="AY14">
-        <v>11</v>
-      </c>
-      <c r="AZ14">
-        <v>23</v>
-      </c>
-      <c r="BA14">
-        <v>80</v>
-      </c>
-      <c r="BB14">
-        <v>30</v>
-      </c>
-      <c r="BC14">
-        <v>30</v>
-      </c>
-      <c r="BD14">
-        <v>48</v>
-      </c>
-      <c r="BE14">
-        <v>48</v>
-      </c>
-      <c r="BF14">
-        <v>30</v>
-      </c>
-      <c r="BG14">
-        <v>85</v>
-      </c>
-      <c r="BH14">
-        <v>2.9</v>
-      </c>
-      <c r="BI14">
-        <v>2.24</v>
-      </c>
-      <c r="BJ14">
-        <v>13.5</v>
-      </c>
-      <c r="BK14">
-        <v>4.3</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>6.2</v>
-      </c>
-      <c r="BN14">
-        <v>5.5</v>
-      </c>
-      <c r="BO14">
-        <v>3.95</v>
-      </c>
-      <c r="BP14">
-        <v>24</v>
-      </c>
-      <c r="BQ14">
-        <v>5</v>
-      </c>
-      <c r="BR14">
-        <v>55</v>
-      </c>
-      <c r="BS14">
-        <v>5.7</v>
-      </c>
-      <c r="BT14">
-        <v>7.8</v>
-      </c>
-      <c r="BU14">
-        <v>5.4</v>
-      </c>
-      <c r="BV14">
-        <v>46</v>
-      </c>
-      <c r="BW14">
-        <v>5.6</v>
-      </c>
-      <c r="BX14">
-        <v>75</v>
-      </c>
-      <c r="BY14">
-        <v>5.9</v>
-      </c>
-      <c r="BZ14">
-        <v>60</v>
-      </c>
-      <c r="CA14">
-        <v>5.8</v>
-      </c>
       <c r="CB14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <v>2.38</v>
+      </c>
+      <c r="G15">
+        <v>2.4</v>
+      </c>
+      <c r="H15">
+        <v>3.85</v>
+      </c>
+      <c r="I15">
+        <v>3.9</v>
+      </c>
+      <c r="J15">
+        <v>3.1</v>
+      </c>
+      <c r="K15">
+        <v>3.15</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.14</v>
+      </c>
+      <c r="N15">
+        <v>2.6</v>
+      </c>
+      <c r="O15">
+        <v>1.59</v>
+      </c>
+      <c r="P15">
+        <v>1.52</v>
+      </c>
+      <c r="Q15">
+        <v>2.76</v>
+      </c>
+      <c r="R15">
+        <v>1.18</v>
+      </c>
+      <c r="S15">
+        <v>6</v>
+      </c>
+      <c r="T15">
+        <v>2.24</v>
+      </c>
+      <c r="U15">
+        <v>1.76</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>8</v>
+      </c>
+      <c r="Y15">
+        <v>10</v>
+      </c>
+      <c r="Z15">
+        <v>26</v>
+      </c>
+      <c r="AA15">
+        <v>110</v>
+      </c>
+      <c r="AB15">
+        <v>7</v>
+      </c>
+      <c r="AC15">
+        <v>6.8</v>
+      </c>
+      <c r="AD15">
+        <v>18</v>
+      </c>
+      <c r="AE15">
+        <v>70</v>
+      </c>
+      <c r="AF15">
+        <v>13</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>26</v>
+      </c>
+      <c r="AI15">
+        <v>110</v>
+      </c>
+      <c r="AJ15">
+        <v>34</v>
+      </c>
+      <c r="AK15">
+        <v>36</v>
+      </c>
+      <c r="AL15">
+        <v>70</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>36</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15">
+        <v>9.4</v>
+      </c>
+      <c r="AR15">
+        <v>23</v>
+      </c>
+      <c r="AS15">
+        <v>55</v>
+      </c>
+      <c r="AT15">
+        <v>6.4</v>
+      </c>
+      <c r="AU15">
+        <v>6.6</v>
+      </c>
+      <c r="AV15">
+        <v>15.5</v>
+      </c>
+      <c r="AW15">
+        <v>50</v>
+      </c>
+      <c r="AX15">
+        <v>11.5</v>
+      </c>
+      <c r="AY15">
+        <v>11</v>
+      </c>
+      <c r="AZ15">
+        <v>23</v>
+      </c>
+      <c r="BA15">
+        <v>80</v>
+      </c>
+      <c r="BB15">
+        <v>30</v>
+      </c>
+      <c r="BC15">
+        <v>30</v>
+      </c>
+      <c r="BD15">
+        <v>50</v>
+      </c>
+      <c r="BE15">
+        <v>48</v>
+      </c>
+      <c r="BF15">
+        <v>30</v>
+      </c>
+      <c r="BG15">
+        <v>85</v>
+      </c>
+      <c r="BH15">
+        <v>2.9</v>
+      </c>
+      <c r="BI15">
+        <v>2.22</v>
+      </c>
+      <c r="BJ15">
+        <v>13.5</v>
+      </c>
+      <c r="BK15">
+        <v>4.2</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>6</v>
+      </c>
+      <c r="BN15">
+        <v>5.6</v>
+      </c>
+      <c r="BO15">
+        <v>3.95</v>
+      </c>
+      <c r="BP15">
+        <v>24</v>
+      </c>
+      <c r="BQ15">
+        <v>4.9</v>
+      </c>
+      <c r="BR15">
+        <v>55</v>
+      </c>
+      <c r="BS15">
+        <v>5.5</v>
+      </c>
+      <c r="BT15">
+        <v>8</v>
+      </c>
+      <c r="BU15">
+        <v>5.4</v>
+      </c>
+      <c r="BV15">
+        <v>46</v>
+      </c>
+      <c r="BW15">
+        <v>5.4</v>
+      </c>
+      <c r="BX15">
+        <v>75</v>
+      </c>
+      <c r="BY15">
+        <v>5.6</v>
+      </c>
+      <c r="BZ15">
+        <v>60</v>
+      </c>
+      <c r="CA15">
+        <v>5.5</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
         <v>83</v>
       </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15">
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16">
         <v>1.04</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>600</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>1.04</v>
       </c>
-      <c r="I15">
+      <c r="I16">
         <v>870</v>
       </c>
-      <c r="J15">
+      <c r="J16">
         <v>1.03</v>
       </c>
-      <c r="K15">
+      <c r="K16">
         <v>950</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>1.24</v>
       </c>
-      <c r="Q15">
+      <c r="Q16">
         <v>1.01</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>0</v>
-      </c>
-      <c r="BC15">
-        <v>0</v>
-      </c>
-      <c r="BD15">
-        <v>0</v>
-      </c>
-      <c r="BE15">
-        <v>0</v>
-      </c>
-      <c r="BF15">
-        <v>0</v>
-      </c>
-      <c r="BG15">
-        <v>0</v>
-      </c>
-      <c r="BH15">
-        <v>0</v>
-      </c>
-      <c r="BI15">
-        <v>0</v>
-      </c>
-      <c r="BJ15">
-        <v>0</v>
-      </c>
-      <c r="BK15">
-        <v>0</v>
-      </c>
-      <c r="BL15">
-        <v>0</v>
-      </c>
-      <c r="BM15">
-        <v>0</v>
-      </c>
-      <c r="BN15">
-        <v>0</v>
-      </c>
-      <c r="BO15">
-        <v>0</v>
-      </c>
-      <c r="BP15">
-        <v>0</v>
-      </c>
-      <c r="BQ15">
-        <v>0</v>
-      </c>
-      <c r="BR15">
-        <v>0</v>
-      </c>
-      <c r="BS15">
-        <v>0</v>
-      </c>
-      <c r="BT15">
-        <v>0</v>
-      </c>
-      <c r="BU15">
-        <v>0</v>
-      </c>
-      <c r="BV15">
-        <v>0</v>
-      </c>
-      <c r="BW15">
-        <v>0</v>
-      </c>
-      <c r="BX15">
-        <v>0</v>
-      </c>
-      <c r="BY15">
-        <v>0</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>123</v>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="136">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,12 @@
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -301,6 +307,12 @@
     <t>14:15:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -346,6 +358,12 @@
     <t>Al-Wakra</t>
   </si>
   <si>
+    <t>Vendsyssel FF</t>
+  </si>
+  <si>
+    <t>Al-Feiha</t>
+  </si>
+  <si>
     <t>Rayo Vallecano</t>
   </si>
   <si>
@@ -391,13 +409,19 @@
     <t>Qatar SC</t>
   </si>
   <si>
+    <t>Hillerod Fodbold</t>
+  </si>
+  <si>
+    <t>Al-Hilal</t>
+  </si>
+  <si>
     <t>Alaves</t>
   </si>
   <si>
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-18 13:20:51</t>
+    <t>2026-08-18 15:29:02</t>
   </si>
 </sst>
 </file>
@@ -729,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -979,16 +1003,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F2">
         <v>3.6</v>
@@ -997,13 +1021,13 @@
         <v>3.8</v>
       </c>
       <c r="H2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2.08</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -1039,16 +1063,16 @@
         <v>2.74</v>
       </c>
       <c r="V2">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
         <v>27</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>16.5</v>
@@ -1063,16 +1087,16 @@
         <v>10</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF2">
         <v>32</v>
       </c>
       <c r="AG2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH2">
         <v>15</v>
@@ -1090,7 +1114,7 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="AN2">
         <v>25</v>
@@ -1099,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="AP2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2">
         <v>13</v>
@@ -1144,7 +1168,7 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF2">
         <v>20</v>
@@ -1213,7 +1237,7 @@
         <v>4.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1221,16 +1245,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F3">
         <v>2.82</v>
@@ -1257,19 +1281,19 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O3">
         <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q3">
         <v>2.68</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>5.7</v>
@@ -1311,13 +1335,13 @@
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI3">
         <v>90</v>
@@ -1347,10 +1371,10 @@
         <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1362,7 +1386,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1371,34 +1395,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH3">
         <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1410,10 +1434,10 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BN3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
         <v>4.5</v>
@@ -1422,13 +1446,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
         <v>5.9</v>
@@ -1440,22 +1464,22 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1463,34 +1487,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F4">
+        <v>1.72</v>
+      </c>
+      <c r="G4">
         <v>1.76</v>
       </c>
-      <c r="G4">
-        <v>1.77</v>
-      </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1499,22 +1523,22 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
         <v>1.96</v>
@@ -1523,10 +1547,10 @@
         <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1544,13 +1568,13 @@
         <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF4">
         <v>10</v>
@@ -1562,7 +1586,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
@@ -1574,10 +1598,10 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO4">
         <v>130</v>
@@ -1592,7 +1616,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>7.4</v>
@@ -1604,7 +1628,7 @@
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1616,7 +1640,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1628,13 +1652,13 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1658,7 +1682,7 @@
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1688,7 +1712,7 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1697,7 +1721,7 @@
         <v>1.68</v>
       </c>
       <c r="CB4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1705,16 +1729,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F5">
         <v>1.82</v>
@@ -1723,10 +1747,10 @@
         <v>1.87</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1744,7 +1768,7 @@
         <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
         <v>2.26</v>
@@ -1753,7 +1777,7 @@
         <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S5">
         <v>2.92</v>
@@ -1771,7 +1795,7 @@
         <v>2.14</v>
       </c>
       <c r="X5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y5">
         <v>19.5</v>
@@ -1795,7 +1819,7 @@
         <v>60</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -1840,7 +1864,7 @@
         <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
         <v>15.5</v>
@@ -1855,7 +1879,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
         <v>28</v>
@@ -1888,13 +1912,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -1906,40 +1930,40 @@
         <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR5">
         <v>25</v>
       </c>
       <c r="BS5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5">
         <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>36</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA5">
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1947,16 +1971,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F6">
         <v>1.71</v>
@@ -1980,31 +2004,31 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O6">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q6">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
         <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V6">
         <v>1.16</v>
@@ -2181,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2189,19 +2213,19 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G7">
         <v>1.97</v>
@@ -2210,7 +2234,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2231,13 +2255,13 @@
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q7">
         <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S7">
         <v>2.44</v>
@@ -2246,16 +2270,16 @@
         <v>1.55</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
         <v>2.02</v>
       </c>
       <c r="X7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y7">
         <v>23</v>
@@ -2276,22 +2300,22 @@
         <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>15</v>
       </c>
       <c r="AI7">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK7">
         <v>18.5</v>
@@ -2300,7 +2324,7 @@
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AN7">
         <v>8.800000000000001</v>
@@ -2315,7 +2339,7 @@
         <v>19</v>
       </c>
       <c r="AR7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS7">
         <v>38</v>
@@ -2339,7 +2363,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA7">
         <v>24</v>
@@ -2354,7 +2378,7 @@
         <v>18.5</v>
       </c>
       <c r="BE7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BF7">
         <v>8</v>
@@ -2366,19 +2390,19 @@
         <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN7">
         <v>5.2</v>
@@ -2387,7 +2411,7 @@
         <v>4.6</v>
       </c>
       <c r="BP7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ7">
         <v>6.8</v>
@@ -2396,19 +2420,19 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT7">
         <v>7.8</v>
       </c>
       <c r="BU7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV7">
         <v>27</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
         <v>32</v>
@@ -2417,13 +2441,13 @@
         <v>10</v>
       </c>
       <c r="BZ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA7">
         <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2431,28 +2455,28 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F8">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="G8">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="H8">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="I8">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="J8">
         <v>3.75</v>
@@ -2461,151 +2485,151 @@
         <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O8">
         <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T8">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
         <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W8">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y8">
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA8">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AB8">
         <v>15</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AF8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="AK8">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS8">
+        <v>29</v>
+      </c>
+      <c r="AT8">
+        <v>13.5</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>11</v>
+      </c>
+      <c r="AW8">
         <v>21</v>
       </c>
-      <c r="AT8">
-        <v>13</v>
-      </c>
-      <c r="AU8">
-        <v>7.8</v>
-      </c>
-      <c r="AV8">
-        <v>10.5</v>
-      </c>
-      <c r="AW8">
-        <v>20</v>
-      </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA8">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BB8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BC8">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF8">
         <v>19.5</v>
       </c>
       <c r="BG8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI8">
         <v>3.15</v>
@@ -2620,25 +2644,25 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN8">
         <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP8">
         <v>23</v>
       </c>
       <c r="BQ8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT8">
         <v>5.8</v>
@@ -2647,25 +2671,25 @@
         <v>4.4</v>
       </c>
       <c r="BV8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
         <v>28</v>
       </c>
       <c r="BY8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2673,25 +2697,25 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F9">
         <v>1.75</v>
       </c>
       <c r="G9">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
         <v>5.1</v>
@@ -2712,7 +2736,7 @@
         <v>5.4</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
         <v>2.52</v>
@@ -2733,10 +2757,10 @@
         <v>2.44</v>
       </c>
       <c r="V9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X9">
         <v>23</v>
@@ -2745,7 +2769,7 @@
         <v>23</v>
       </c>
       <c r="Z9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2808,7 +2832,7 @@
         <v>11</v>
       </c>
       <c r="AU9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV9">
         <v>17.5</v>
@@ -2820,7 +2844,7 @@
         <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
         <v>15.5</v>
@@ -2829,7 +2853,7 @@
         <v>44</v>
       </c>
       <c r="BB9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
         <v>14.5</v>
@@ -2841,16 +2865,16 @@
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
       </c>
       <c r="BI9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
@@ -2862,52 +2886,52 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
         <v>3.7</v>
       </c>
       <c r="BP9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT9">
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
         <v>36</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
         <v>15</v>
       </c>
       <c r="CA9">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2915,16 +2939,16 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F10">
         <v>2.66</v>
@@ -2945,31 +2969,31 @@
         <v>4.2</v>
       </c>
       <c r="L10">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q10">
         <v>1.86</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="T10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U10">
         <v>2.26</v>
@@ -3092,7 +3116,7 @@
         <v>3.65</v>
       </c>
       <c r="BI10">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10">
         <v>9.199999999999999</v>
@@ -3149,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3157,16 +3181,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F11">
         <v>2.14</v>
@@ -3214,7 +3238,7 @@
         <v>1.43</v>
       </c>
       <c r="U11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V11">
         <v>1.43</v>
@@ -3391,7 +3415,7 @@
         <v>7.2</v>
       </c>
       <c r="CB11" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3399,19 +3423,19 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G12">
         <v>1.59</v>
@@ -3441,16 +3465,16 @@
         <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R12">
         <v>1.63</v>
       </c>
       <c r="S12">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T12">
         <v>1.72</v>
@@ -3471,7 +3495,7 @@
         <v>29</v>
       </c>
       <c r="Z12">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3480,22 +3504,22 @@
         <v>12</v>
       </c>
       <c r="AC12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE12">
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI12">
         <v>1000</v>
@@ -3519,10 +3543,10 @@
         <v>1000</v>
       </c>
       <c r="AP12">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12">
         <v>18</v>
-      </c>
-      <c r="AQ12">
-        <v>18.5</v>
       </c>
       <c r="AR12">
         <v>28</v>
@@ -3546,7 +3570,7 @@
         <v>10</v>
       </c>
       <c r="AY12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
         <v>17</v>
@@ -3561,13 +3585,13 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG12">
         <v>32</v>
@@ -3633,7 +3657,7 @@
         <v>5.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3641,73 +3665,73 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G13">
         <v>2.46</v>
       </c>
       <c r="H13">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I13">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>4.3</v>
       </c>
       <c r="L13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M13">
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O13">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Q13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R13">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U13">
         <v>2.98</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
         <v>1.68</v>
       </c>
       <c r="X13">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="Y13">
         <v>22</v>
@@ -3728,10 +3752,10 @@
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
@@ -3740,25 +3764,25 @@
         <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK13">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AL13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM13">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN13">
         <v>11</v>
       </c>
       <c r="AO13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP13">
         <v>20</v>
@@ -3773,19 +3797,19 @@
         <v>25</v>
       </c>
       <c r="AT13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU13">
         <v>9.4</v>
       </c>
       <c r="AV13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY13">
         <v>11</v>
@@ -3794,10 +3818,10 @@
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BC13">
         <v>18.5</v>
@@ -3812,70 +3836,70 @@
         <v>9.6</v>
       </c>
       <c r="BG13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
         <v>5.1</v>
       </c>
       <c r="BI13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13">
         <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR13">
         <v>22</v>
       </c>
       <c r="BS13">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU13">
         <v>5</v>
       </c>
       <c r="BV13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW13">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3883,31 +3907,31 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F14">
         <v>2.18</v>
       </c>
       <c r="G14">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H14">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I14">
         <v>3.5</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
         <v>4.3</v>
@@ -3943,10 +3967,10 @@
         <v>2.36</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W14">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X14">
         <v>25</v>
@@ -4117,7 +4141,7 @@
         <v>6.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4125,483 +4149,967 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G15">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="H15">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="I15">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="J15">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="O15">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="Q15">
-        <v>2.76</v>
+        <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S15">
-        <v>6</v>
+        <v>2.32</v>
       </c>
       <c r="T15">
-        <v>2.24</v>
+        <v>1.44</v>
       </c>
       <c r="U15">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16">
+        <v>12.5</v>
+      </c>
+      <c r="G16">
+        <v>17</v>
+      </c>
+      <c r="H16">
+        <v>1.23</v>
+      </c>
+      <c r="I16">
+        <v>1.29</v>
+      </c>
+      <c r="J16">
+        <v>6.6</v>
+      </c>
+      <c r="K16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L16">
+        <v>1.19</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>3.15</v>
+      </c>
+      <c r="O16">
+        <v>1.16</v>
+      </c>
+      <c r="P16">
+        <v>2.74</v>
+      </c>
+      <c r="Q16">
+        <v>1.46</v>
+      </c>
+      <c r="R16">
+        <v>1.7</v>
+      </c>
+      <c r="S16">
+        <v>2.16</v>
+      </c>
+      <c r="T16">
+        <v>1.96</v>
+      </c>
+      <c r="U16">
+        <v>1.82</v>
+      </c>
+      <c r="V16">
+        <v>4.4</v>
+      </c>
+      <c r="W16">
+        <v>1.06</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>10</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.11</v>
+      </c>
+      <c r="AQ16">
+        <v>9</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.11</v>
+      </c>
+      <c r="AT16">
+        <v>1.11</v>
+      </c>
+      <c r="AU16">
+        <v>1.11</v>
+      </c>
+      <c r="AV16">
+        <v>1.11</v>
+      </c>
+      <c r="AW16">
+        <v>1.11</v>
+      </c>
+      <c r="AX16">
+        <v>1.11</v>
+      </c>
+      <c r="AY16">
+        <v>1.11</v>
+      </c>
+      <c r="AZ16">
+        <v>1.11</v>
+      </c>
+      <c r="BA16">
+        <v>1.11</v>
+      </c>
+      <c r="BB16">
+        <v>1.11</v>
+      </c>
+      <c r="BC16">
+        <v>1.11</v>
+      </c>
+      <c r="BD16">
+        <v>1.11</v>
+      </c>
+      <c r="BE16">
+        <v>1.11</v>
+      </c>
+      <c r="BF16">
+        <v>1.11</v>
+      </c>
+      <c r="BG16">
+        <v>1.11</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>17</v>
+      </c>
+      <c r="BK16">
+        <v>7.8</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>21</v>
+      </c>
+      <c r="BN16">
+        <v>20</v>
+      </c>
+      <c r="BO16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>21</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>21</v>
+      </c>
+      <c r="BT16">
+        <v>5.1</v>
+      </c>
+      <c r="BU16">
+        <v>2.8</v>
+      </c>
+      <c r="BV16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BW16">
+        <v>4.8</v>
+      </c>
+      <c r="BX16">
+        <v>29</v>
+      </c>
+      <c r="BY16">
+        <v>13.5</v>
+      </c>
+      <c r="BZ16">
+        <v>13</v>
+      </c>
+      <c r="CA16">
+        <v>6.2</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17">
+        <v>2.4</v>
+      </c>
+      <c r="G17">
+        <v>2.44</v>
+      </c>
+      <c r="H17">
+        <v>3.7</v>
+      </c>
+      <c r="I17">
+        <v>3.8</v>
+      </c>
+      <c r="J17">
+        <v>3.1</v>
+      </c>
+      <c r="K17">
+        <v>3.15</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1.14</v>
+      </c>
+      <c r="N17">
+        <v>2.6</v>
+      </c>
+      <c r="O17">
+        <v>1.59</v>
+      </c>
+      <c r="P17">
+        <v>1.52</v>
+      </c>
+      <c r="Q17">
+        <v>2.78</v>
+      </c>
+      <c r="R17">
+        <v>1.18</v>
+      </c>
+      <c r="S17">
+        <v>6</v>
+      </c>
+      <c r="T17">
+        <v>2.24</v>
+      </c>
+      <c r="U17">
+        <v>1.76</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>8</v>
+      </c>
+      <c r="Y17">
+        <v>9.6</v>
+      </c>
+      <c r="Z17">
+        <v>25</v>
+      </c>
+      <c r="AA17">
+        <v>110</v>
+      </c>
+      <c r="AB17">
+        <v>7</v>
+      </c>
+      <c r="AC17">
+        <v>6.8</v>
+      </c>
+      <c r="AD17">
+        <v>17.5</v>
+      </c>
+      <c r="AE17">
+        <v>70</v>
+      </c>
+      <c r="AF17">
+        <v>13</v>
+      </c>
+      <c r="AG17">
+        <v>12.5</v>
+      </c>
+      <c r="AH17">
+        <v>26</v>
+      </c>
+      <c r="AI17">
+        <v>110</v>
+      </c>
+      <c r="AJ17">
+        <v>36</v>
+      </c>
+      <c r="AK17">
+        <v>36</v>
+      </c>
+      <c r="AL17">
+        <v>70</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>38</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>7.6</v>
+      </c>
+      <c r="AQ17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR17">
+        <v>22</v>
+      </c>
+      <c r="AS17">
+        <v>55</v>
+      </c>
+      <c r="AT17">
+        <v>6.4</v>
+      </c>
+      <c r="AU17">
+        <v>6.6</v>
+      </c>
+      <c r="AV17">
+        <v>15.5</v>
+      </c>
+      <c r="AW17">
+        <v>50</v>
+      </c>
+      <c r="AX17">
+        <v>11.5</v>
+      </c>
+      <c r="AY17">
+        <v>11</v>
+      </c>
+      <c r="AZ17">
+        <v>23</v>
+      </c>
+      <c r="BA17">
+        <v>80</v>
+      </c>
+      <c r="BB17">
+        <v>30</v>
+      </c>
+      <c r="BC17">
+        <v>30</v>
+      </c>
+      <c r="BD17">
+        <v>50</v>
+      </c>
+      <c r="BE17">
+        <v>48</v>
+      </c>
+      <c r="BF17">
+        <v>30</v>
+      </c>
+      <c r="BG17">
+        <v>85</v>
+      </c>
+      <c r="BH17">
+        <v>2.88</v>
+      </c>
+      <c r="BI17">
+        <v>2.22</v>
+      </c>
+      <c r="BJ17">
+        <v>13.5</v>
+      </c>
+      <c r="BK17">
+        <v>4.2</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>6</v>
+      </c>
+      <c r="BN17">
+        <v>5.6</v>
+      </c>
+      <c r="BO17">
+        <v>3.95</v>
+      </c>
+      <c r="BP17">
+        <v>25</v>
+      </c>
+      <c r="BQ17">
+        <v>5</v>
+      </c>
+      <c r="BR17">
+        <v>55</v>
+      </c>
+      <c r="BS17">
+        <v>5.6</v>
+      </c>
+      <c r="BT17">
+        <v>7.8</v>
+      </c>
+      <c r="BU17">
+        <v>5.4</v>
+      </c>
+      <c r="BV17">
+        <v>46</v>
+      </c>
+      <c r="BW17">
+        <v>5.5</v>
+      </c>
+      <c r="BX17">
+        <v>75</v>
+      </c>
+      <c r="BY17">
+        <v>5.7</v>
+      </c>
+      <c r="BZ17">
+        <v>65</v>
+      </c>
+      <c r="CA17">
+        <v>5.7</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
         <v>83</v>
       </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16">
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18">
         <v>1.04</v>
       </c>
-      <c r="G16">
+      <c r="G18">
         <v>600</v>
       </c>
-      <c r="H16">
+      <c r="H18">
         <v>1.04</v>
       </c>
-      <c r="I16">
+      <c r="I18">
         <v>870</v>
       </c>
-      <c r="J16">
+      <c r="J18">
         <v>1.03</v>
       </c>
-      <c r="K16">
+      <c r="K18">
         <v>950</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
         <v>1.24</v>
       </c>
-      <c r="Q16">
+      <c r="Q18">
         <v>1.01</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16">
-        <v>0</v>
-      </c>
-      <c r="BE16">
-        <v>0</v>
-      </c>
-      <c r="BF16">
-        <v>0</v>
-      </c>
-      <c r="BG16">
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
-      </c>
-      <c r="BJ16">
-        <v>0</v>
-      </c>
-      <c r="BK16">
-        <v>0</v>
-      </c>
-      <c r="BL16">
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <v>0</v>
-      </c>
-      <c r="BN16">
-        <v>0</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16">
-        <v>0</v>
-      </c>
-      <c r="BS16">
-        <v>0</v>
-      </c>
-      <c r="BT16">
-        <v>0</v>
-      </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>0</v>
-      </c>
-      <c r="BX16">
-        <v>0</v>
-      </c>
-      <c r="BY16">
-        <v>0</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>127</v>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,9 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>English Sky Bet League 1</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -364,6 +367,9 @@
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>Sheff Wed</t>
+  </si>
+  <si>
     <t>Rayo Vallecano</t>
   </si>
   <si>
@@ -415,13 +421,16 @@
     <t>Al-Hilal</t>
   </si>
   <si>
+    <t>Bradford</t>
+  </si>
+  <si>
     <t>Alaves</t>
   </si>
   <si>
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-18 15:29:02</t>
+    <t>2026-08-18 17:37:54</t>
   </si>
 </sst>
 </file>
@@ -753,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1003,16 +1012,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>3.6</v>
@@ -1024,10 +1033,10 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -1045,7 +1054,7 @@
         <v>1.18</v>
       </c>
       <c r="P2">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q2">
         <v>1.56</v>
@@ -1054,25 +1063,25 @@
         <v>1.68</v>
       </c>
       <c r="S2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T2">
         <v>1.54</v>
       </c>
       <c r="U2">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V2">
         <v>1.94</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
         <v>27</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
         <v>16.5</v>
@@ -1087,10 +1096,10 @@
         <v>10</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF2">
         <v>32</v>
@@ -1114,7 +1123,7 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AN2">
         <v>25</v>
@@ -1168,7 +1177,7 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF2">
         <v>20</v>
@@ -1183,7 +1192,7 @@
         <v>3.65</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2">
         <v>3.55</v>
@@ -1198,7 +1207,7 @@
         <v>8.4</v>
       </c>
       <c r="BO2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP2">
         <v>29</v>
@@ -1210,19 +1219,19 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU2">
         <v>4.2</v>
       </c>
       <c r="BV2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BX2">
         <v>25</v>
@@ -1231,13 +1240,13 @@
         <v>4.5</v>
       </c>
       <c r="BZ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1245,16 +1254,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F3">
         <v>2.82</v>
@@ -1293,7 +1302,7 @@
         <v>2.68</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
         <v>5.7</v>
@@ -1479,7 +1488,7 @@
         <v>13</v>
       </c>
       <c r="CB3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1487,25 +1496,25 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G4">
         <v>1.76</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
         <v>6.2</v>
@@ -1535,7 +1544,7 @@
         <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
         <v>3.5</v>
@@ -1682,7 +1691,7 @@
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1712,7 +1721,7 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1721,7 +1730,7 @@
         <v>1.68</v>
       </c>
       <c r="CB4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1729,22 +1738,22 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F5">
         <v>1.82</v>
       </c>
       <c r="G5">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H5">
         <v>4.5</v>
@@ -1756,7 +1765,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1771,7 +1780,7 @@
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
         <v>1.76</v>
@@ -1792,7 +1801,7 @@
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
         <v>20</v>
@@ -1963,7 +1972,7 @@
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1971,70 +1980,70 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>990</v>
       </c>
       <c r="H6">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>990</v>
       </c>
       <c r="J6">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2205,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2213,22 +2222,22 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -2240,7 +2249,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2252,7 +2261,7 @@
         <v>5.8</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P7">
         <v>2.62</v>
@@ -2270,7 +2279,7 @@
         <v>1.55</v>
       </c>
       <c r="U7">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
         <v>1.31</v>
@@ -2339,10 +2348,10 @@
         <v>19</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT7">
         <v>12.5</v>
@@ -2366,7 +2375,7 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB7">
         <v>20</v>
@@ -2447,7 +2456,7 @@
         <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2455,22 +2464,22 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F8">
         <v>2.9</v>
       </c>
       <c r="G8">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H8">
         <v>2.54</v>
@@ -2482,7 +2491,7 @@
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2497,7 +2506,7 @@
         <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
         <v>1.75</v>
@@ -2506,10 +2515,10 @@
         <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U8">
         <v>2.46</v>
@@ -2518,7 +2527,7 @@
         <v>1.64</v>
       </c>
       <c r="W8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X8">
         <v>19</v>
@@ -2527,22 +2536,22 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
         <v>36</v>
       </c>
       <c r="AB8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF8">
         <v>22</v>
@@ -2560,7 +2569,7 @@
         <v>46</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL8">
         <v>75</v>
@@ -2614,13 +2623,13 @@
         <v>40</v>
       </c>
       <c r="BC8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD8">
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF8">
         <v>19.5</v>
@@ -2644,52 +2653,52 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN8">
         <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2697,16 +2706,16 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>1.75</v>
@@ -2739,7 +2748,7 @@
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
         <v>1.62</v>
@@ -2811,7 +2820,7 @@
         <v>75</v>
       </c>
       <c r="AN9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO9">
         <v>44</v>
@@ -2823,7 +2832,7 @@
         <v>21</v>
       </c>
       <c r="AR9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AS9">
         <v>40</v>
@@ -2838,7 +2847,7 @@
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2865,10 +2874,10 @@
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -2898,7 +2907,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9">
         <v>22</v>
@@ -2931,7 +2940,7 @@
         <v>10.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2939,46 +2948,46 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G10">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H10">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="I10">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="P10">
         <v>1.91</v>
@@ -2990,19 +2999,19 @@
         <v>1.34</v>
       </c>
       <c r="S10">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U10">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W10">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
         <v>19</v>
@@ -3113,58 +3122,58 @@
         <v>17</v>
       </c>
       <c r="BH10">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5.6</v>
+        <v>1.31</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12.5</v>
+        <v>1.31</v>
       </c>
       <c r="BN10">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4.6</v>
+        <v>1.31</v>
       </c>
       <c r="BP10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>8.4</v>
+        <v>1.31</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.800000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="BT10">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.6</v>
+        <v>1.31</v>
       </c>
       <c r="BV10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.4</v>
+        <v>1.31</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.800000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3173,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3181,16 +3190,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11">
         <v>2.14</v>
@@ -3199,7 +3208,7 @@
         <v>2.2</v>
       </c>
       <c r="H11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I11">
         <v>3.3</v>
@@ -3223,16 +3232,16 @@
         <v>1.13</v>
       </c>
       <c r="P11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q11">
         <v>1.42</v>
       </c>
       <c r="R11">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T11">
         <v>1.43</v>
@@ -3295,7 +3304,7 @@
         <v>44</v>
       </c>
       <c r="AN11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO11">
         <v>15.5</v>
@@ -3415,7 +3424,7 @@
         <v>7.2</v>
       </c>
       <c r="CB11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3423,16 +3432,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F12">
         <v>1.56</v>
@@ -3459,13 +3468,13 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O12">
         <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q12">
         <v>1.6</v>
@@ -3585,13 +3594,13 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BE12">
         <v>36</v>
       </c>
       <c r="BF12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG12">
         <v>32</v>
@@ -3657,7 +3666,7 @@
         <v>5.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3665,19 +3674,19 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G13">
         <v>2.46</v>
@@ -3686,13 +3695,13 @@
         <v>2.84</v>
       </c>
       <c r="I13">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J13">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.25</v>
@@ -3725,22 +3734,22 @@
         <v>2.98</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
         <v>1.68</v>
       </c>
       <c r="X13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y13">
         <v>22</v>
       </c>
       <c r="Z13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB13">
         <v>19</v>
@@ -3752,10 +3761,10 @@
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG13">
         <v>12.5</v>
@@ -3764,7 +3773,7 @@
         <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ13">
         <v>40</v>
@@ -3779,7 +3788,7 @@
         <v>110</v>
       </c>
       <c r="AN13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO13">
         <v>14</v>
@@ -3791,7 +3800,7 @@
         <v>17.5</v>
       </c>
       <c r="AR13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS13">
         <v>25</v>
@@ -3806,7 +3815,7 @@
         <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX13">
         <v>18.5</v>
@@ -3830,7 +3839,7 @@
         <v>21</v>
       </c>
       <c r="BE13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BF13">
         <v>9.6</v>
@@ -3848,7 +3857,7 @@
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3860,7 +3869,7 @@
         <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP13">
         <v>16</v>
@@ -3878,7 +3887,7 @@
         <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV13">
         <v>19</v>
@@ -3896,10 +3905,10 @@
         <v>13.5</v>
       </c>
       <c r="CA13">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="CB13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3907,31 +3916,31 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F14">
         <v>2.18</v>
       </c>
       <c r="G14">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H14">
         <v>3.05</v>
       </c>
       <c r="I14">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
         <v>4.3</v>
@@ -3946,7 +3955,7 @@
         <v>4.6</v>
       </c>
       <c r="O14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
         <v>2.22</v>
@@ -3970,7 +3979,7 @@
         <v>1.37</v>
       </c>
       <c r="W14">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X14">
         <v>25</v>
@@ -4141,7 +4150,7 @@
         <v>6.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4149,34 +4158,34 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F15">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G15">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="H15">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
         <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4209,10 +4218,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4383,7 +4392,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4391,22 +4400,22 @@
         <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F16">
         <v>12.5</v>
       </c>
       <c r="G16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16">
         <v>1.23</v>
@@ -4427,7 +4436,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4439,16 +4448,16 @@
         <v>1.46</v>
       </c>
       <c r="R16">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S16">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T16">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U16">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V16">
         <v>4.4</v>
@@ -4457,148 +4466,148 @@
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z16">
+        <v>9</v>
+      </c>
+      <c r="AA16">
+        <v>11.5</v>
+      </c>
+      <c r="AB16">
+        <v>60</v>
+      </c>
+      <c r="AC16">
+        <v>19.5</v>
+      </c>
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16">
+        <v>15</v>
+      </c>
+      <c r="AF16">
+        <v>150</v>
+      </c>
+      <c r="AG16">
+        <v>60</v>
+      </c>
+      <c r="AH16">
+        <v>38</v>
+      </c>
+      <c r="AI16">
+        <v>44</v>
+      </c>
+      <c r="AJ16">
+        <v>560</v>
+      </c>
+      <c r="AK16">
+        <v>230</v>
+      </c>
+      <c r="AL16">
+        <v>170</v>
+      </c>
+      <c r="AM16">
+        <v>180</v>
+      </c>
+      <c r="AN16">
+        <v>270</v>
+      </c>
+      <c r="AO16">
+        <v>4.4</v>
+      </c>
+      <c r="AP16">
+        <v>4.9</v>
+      </c>
+      <c r="AQ16">
         <v>10</v>
       </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.11</v>
-      </c>
-      <c r="AQ16">
-        <v>9</v>
-      </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS16">
-        <v>1.11</v>
+        <v>8.4</v>
       </c>
       <c r="AT16">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="AU16">
-        <v>1.11</v>
+        <v>14</v>
       </c>
       <c r="AV16">
-        <v>1.11</v>
+        <v>10</v>
       </c>
       <c r="AW16">
-        <v>1.11</v>
+        <v>11</v>
       </c>
       <c r="AX16">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="AY16">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="AZ16">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="BA16">
-        <v>1.11</v>
+        <v>5</v>
       </c>
       <c r="BB16">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BC16">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="BD16">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="BE16">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="BF16">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BG16">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ16">
         <v>17</v>
       </c>
       <c r="BK16">
-        <v>7.8</v>
+        <v>1.89</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>21</v>
+        <v>2.12</v>
       </c>
       <c r="BN16">
         <v>20</v>
       </c>
       <c r="BO16">
-        <v>9.199999999999999</v>
+        <v>1.92</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>21</v>
+        <v>2.12</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>21</v>
+        <v>2.08</v>
       </c>
       <c r="BT16">
         <v>5.1</v>
@@ -4616,16 +4625,16 @@
         <v>29</v>
       </c>
       <c r="BY16">
-        <v>13.5</v>
+        <v>1.98</v>
       </c>
       <c r="BZ16">
         <v>13</v>
       </c>
       <c r="CA16">
-        <v>6.2</v>
+        <v>1.83</v>
       </c>
       <c r="CB16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4633,187 +4642,187 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F17">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="H17">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="J17">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="P17">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>2.78</v>
+        <v>1.94</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S17">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="T17">
-        <v>2.24</v>
+        <v>1.74</v>
       </c>
       <c r="U17">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="Y17">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="Z17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC17">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AE17">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AF17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AG17">
         <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AI17">
+        <v>55</v>
+      </c>
+      <c r="AJ17">
+        <v>40</v>
+      </c>
+      <c r="AK17">
+        <v>30</v>
+      </c>
+      <c r="AL17">
+        <v>42</v>
+      </c>
+      <c r="AM17">
         <v>110</v>
       </c>
-      <c r="AJ17">
-        <v>36</v>
-      </c>
-      <c r="AK17">
-        <v>36</v>
-      </c>
-      <c r="AL17">
+      <c r="AN17">
+        <v>25</v>
+      </c>
+      <c r="AO17">
+        <v>32</v>
+      </c>
+      <c r="AP17">
+        <v>11</v>
+      </c>
+      <c r="AQ17">
+        <v>11</v>
+      </c>
+      <c r="AR17">
+        <v>18</v>
+      </c>
+      <c r="AS17">
+        <v>40</v>
+      </c>
+      <c r="AT17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU17">
+        <v>7</v>
+      </c>
+      <c r="AV17">
+        <v>12</v>
+      </c>
+      <c r="AW17">
+        <v>30</v>
+      </c>
+      <c r="AX17">
+        <v>14.5</v>
+      </c>
+      <c r="AY17">
+        <v>10</v>
+      </c>
+      <c r="AZ17">
+        <v>15.5</v>
+      </c>
+      <c r="BA17">
+        <v>40</v>
+      </c>
+      <c r="BB17">
+        <v>32</v>
+      </c>
+      <c r="BC17">
+        <v>24</v>
+      </c>
+      <c r="BD17">
+        <v>34</v>
+      </c>
+      <c r="BE17">
         <v>70</v>
       </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>38</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>7.6</v>
-      </c>
-      <c r="AQ17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR17">
-        <v>22</v>
-      </c>
-      <c r="AS17">
-        <v>55</v>
-      </c>
-      <c r="AT17">
-        <v>6.4</v>
-      </c>
-      <c r="AU17">
-        <v>6.6</v>
-      </c>
-      <c r="AV17">
-        <v>15.5</v>
-      </c>
-      <c r="AW17">
-        <v>50</v>
-      </c>
-      <c r="AX17">
-        <v>11.5</v>
-      </c>
-      <c r="AY17">
+      <c r="BF17">
+        <v>20</v>
+      </c>
+      <c r="BG17">
+        <v>27</v>
+      </c>
+      <c r="BH17">
+        <v>3.45</v>
+      </c>
+      <c r="BI17">
+        <v>3</v>
+      </c>
+      <c r="BJ17">
         <v>11</v>
-      </c>
-      <c r="AZ17">
-        <v>23</v>
-      </c>
-      <c r="BA17">
-        <v>80</v>
-      </c>
-      <c r="BB17">
-        <v>30</v>
-      </c>
-      <c r="BC17">
-        <v>30</v>
-      </c>
-      <c r="BD17">
-        <v>50</v>
-      </c>
-      <c r="BE17">
-        <v>48</v>
-      </c>
-      <c r="BF17">
-        <v>30</v>
-      </c>
-      <c r="BG17">
-        <v>85</v>
-      </c>
-      <c r="BH17">
-        <v>2.88</v>
-      </c>
-      <c r="BI17">
-        <v>2.22</v>
-      </c>
-      <c r="BJ17">
-        <v>13.5</v>
       </c>
       <c r="BK17">
         <v>4.2</v>
@@ -4822,294 +4831,536 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BN17">
+        <v>6.4</v>
+      </c>
+      <c r="BO17">
+        <v>4.4</v>
+      </c>
+      <c r="BP17">
+        <v>23</v>
+      </c>
+      <c r="BQ17">
+        <v>5.2</v>
+      </c>
+      <c r="BR17">
+        <v>38</v>
+      </c>
+      <c r="BS17">
+        <v>5.8</v>
+      </c>
+      <c r="BT17">
+        <v>6.8</v>
+      </c>
+      <c r="BU17">
+        <v>4.7</v>
+      </c>
+      <c r="BV17">
+        <v>27</v>
+      </c>
+      <c r="BW17">
+        <v>5.4</v>
+      </c>
+      <c r="BX17">
+        <v>40</v>
+      </c>
+      <c r="BY17">
+        <v>5.8</v>
+      </c>
+      <c r="BZ17">
+        <v>32</v>
+      </c>
+      <c r="CA17">
         <v>5.6</v>
       </c>
-      <c r="BO17">
-        <v>3.95</v>
-      </c>
-      <c r="BP17">
-        <v>25</v>
-      </c>
-      <c r="BQ17">
-        <v>5</v>
-      </c>
-      <c r="BR17">
-        <v>55</v>
-      </c>
-      <c r="BS17">
-        <v>5.6</v>
-      </c>
-      <c r="BT17">
-        <v>7.8</v>
-      </c>
-      <c r="BU17">
-        <v>5.4</v>
-      </c>
-      <c r="BV17">
-        <v>46</v>
-      </c>
-      <c r="BW17">
-        <v>5.5</v>
-      </c>
-      <c r="BX17">
-        <v>75</v>
-      </c>
-      <c r="BY17">
-        <v>5.7</v>
-      </c>
-      <c r="BZ17">
-        <v>65</v>
-      </c>
-      <c r="CA17">
-        <v>5.7</v>
-      </c>
       <c r="CB17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F18">
+        <v>2.38</v>
+      </c>
+      <c r="G18">
+        <v>2.4</v>
+      </c>
+      <c r="H18">
+        <v>3.8</v>
+      </c>
+      <c r="I18">
+        <v>3.85</v>
+      </c>
+      <c r="J18">
+        <v>3.1</v>
+      </c>
+      <c r="K18">
+        <v>3.15</v>
+      </c>
+      <c r="L18">
+        <v>1.63</v>
+      </c>
+      <c r="M18">
+        <v>1.14</v>
+      </c>
+      <c r="N18">
+        <v>2.58</v>
+      </c>
+      <c r="O18">
+        <v>1.59</v>
+      </c>
+      <c r="P18">
+        <v>1.52</v>
+      </c>
+      <c r="Q18">
+        <v>2.78</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>6</v>
+      </c>
+      <c r="T18">
+        <v>2.26</v>
+      </c>
+      <c r="U18">
+        <v>1.73</v>
+      </c>
+      <c r="V18">
+        <v>1.35</v>
+      </c>
+      <c r="W18">
+        <v>1.71</v>
+      </c>
+      <c r="X18">
+        <v>8</v>
+      </c>
+      <c r="Y18">
+        <v>9.6</v>
+      </c>
+      <c r="Z18">
+        <v>24</v>
+      </c>
+      <c r="AA18">
+        <v>85</v>
+      </c>
+      <c r="AB18">
+        <v>7</v>
+      </c>
+      <c r="AC18">
+        <v>6.8</v>
+      </c>
+      <c r="AD18">
+        <v>17</v>
+      </c>
+      <c r="AE18">
+        <v>70</v>
+      </c>
+      <c r="AF18">
+        <v>12.5</v>
+      </c>
+      <c r="AG18">
+        <v>12.5</v>
+      </c>
+      <c r="AH18">
+        <v>26</v>
+      </c>
+      <c r="AI18">
+        <v>100</v>
+      </c>
+      <c r="AJ18">
+        <v>34</v>
+      </c>
+      <c r="AK18">
+        <v>36</v>
+      </c>
+      <c r="AL18">
+        <v>70</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>38</v>
+      </c>
+      <c r="AO18">
+        <v>100</v>
+      </c>
+      <c r="AP18">
+        <v>7.6</v>
+      </c>
+      <c r="AQ18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR18">
+        <v>22</v>
+      </c>
+      <c r="AS18">
+        <v>55</v>
+      </c>
+      <c r="AT18">
+        <v>6.6</v>
+      </c>
+      <c r="AU18">
+        <v>6.6</v>
+      </c>
+      <c r="AV18">
+        <v>16</v>
+      </c>
+      <c r="AW18">
+        <v>55</v>
+      </c>
+      <c r="AX18">
+        <v>11.5</v>
+      </c>
+      <c r="AY18">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18">
+        <v>23</v>
+      </c>
+      <c r="BA18">
+        <v>80</v>
+      </c>
+      <c r="BB18">
+        <v>30</v>
+      </c>
+      <c r="BC18">
+        <v>30</v>
+      </c>
+      <c r="BD18">
+        <v>60</v>
+      </c>
+      <c r="BE18">
+        <v>48</v>
+      </c>
+      <c r="BF18">
+        <v>32</v>
+      </c>
+      <c r="BG18">
+        <v>85</v>
+      </c>
+      <c r="BH18">
+        <v>2.6</v>
+      </c>
+      <c r="BI18">
+        <v>2.42</v>
+      </c>
+      <c r="BJ18">
+        <v>13.5</v>
+      </c>
+      <c r="BK18">
+        <v>5</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>7.8</v>
+      </c>
+      <c r="BN18">
+        <v>5.6</v>
+      </c>
+      <c r="BO18">
+        <v>4.5</v>
+      </c>
+      <c r="BP18">
+        <v>25</v>
+      </c>
+      <c r="BQ18">
+        <v>6</v>
+      </c>
+      <c r="BR18">
+        <v>55</v>
+      </c>
+      <c r="BS18">
+        <v>7</v>
+      </c>
+      <c r="BT18">
+        <v>7.8</v>
+      </c>
+      <c r="BU18">
+        <v>6.2</v>
+      </c>
+      <c r="BV18">
+        <v>46</v>
+      </c>
+      <c r="BW18">
+        <v>6.8</v>
+      </c>
+      <c r="BX18">
+        <v>75</v>
+      </c>
+      <c r="BY18">
+        <v>7.2</v>
+      </c>
+      <c r="BZ18">
+        <v>65</v>
+      </c>
+      <c r="CA18">
+        <v>7.2</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19">
         <v>1.04</v>
       </c>
-      <c r="G18">
+      <c r="G19">
         <v>600</v>
       </c>
-      <c r="H18">
+      <c r="H19">
         <v>1.04</v>
       </c>
-      <c r="I18">
+      <c r="I19">
         <v>870</v>
       </c>
-      <c r="J18">
+      <c r="J19">
         <v>1.03</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>950</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>1.24</v>
       </c>
-      <c r="Q18">
+      <c r="Q19">
         <v>1.01</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
-      </c>
-      <c r="AI18">
-        <v>0</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18">
-        <v>0</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>0</v>
-      </c>
-      <c r="BC18">
-        <v>0</v>
-      </c>
-      <c r="BD18">
-        <v>0</v>
-      </c>
-      <c r="BE18">
-        <v>0</v>
-      </c>
-      <c r="BF18">
-        <v>0</v>
-      </c>
-      <c r="BG18">
-        <v>0</v>
-      </c>
-      <c r="BH18">
-        <v>0</v>
-      </c>
-      <c r="BI18">
-        <v>0</v>
-      </c>
-      <c r="BJ18">
-        <v>0</v>
-      </c>
-      <c r="BK18">
-        <v>0</v>
-      </c>
-      <c r="BL18">
-        <v>0</v>
-      </c>
-      <c r="BM18">
-        <v>0</v>
-      </c>
-      <c r="BN18">
-        <v>0</v>
-      </c>
-      <c r="BO18">
-        <v>0</v>
-      </c>
-      <c r="BP18">
-        <v>0</v>
-      </c>
-      <c r="BQ18">
-        <v>0</v>
-      </c>
-      <c r="BR18">
-        <v>0</v>
-      </c>
-      <c r="BS18">
-        <v>0</v>
-      </c>
-      <c r="BT18">
-        <v>0</v>
-      </c>
-      <c r="BU18">
-        <v>0</v>
-      </c>
-      <c r="BV18">
-        <v>0</v>
-      </c>
-      <c r="BW18">
-        <v>0</v>
-      </c>
-      <c r="BX18">
-        <v>0</v>
-      </c>
-      <c r="BY18">
-        <v>0</v>
-      </c>
-      <c r="BZ18">
-        <v>0</v>
-      </c>
-      <c r="CA18">
-        <v>0</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>135</v>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -430,7 +430,7 @@
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-18 17:37:54</t>
+    <t>2026-08-18 19:47:15</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1024,7 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G2">
         <v>3.8</v>
@@ -1066,16 +1066,16 @@
         <v>2.38</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U2">
         <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
         <v>27</v>
@@ -1123,7 +1123,7 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN2">
         <v>25</v>
@@ -1174,10 +1174,10 @@
         <v>22</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF2">
         <v>20</v>
@@ -1266,7 +1266,7 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
         <v>2.96</v>
@@ -1514,7 +1514,7 @@
         <v>1.76</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>6.2</v>
@@ -1523,7 +1523,7 @@
         <v>3.8</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1595,7 +1595,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
@@ -1637,7 +1637,7 @@
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1649,7 +1649,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1667,7 +1667,7 @@
         <v>9.6</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1759,7 +1759,7 @@
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1792,7 +1792,7 @@
         <v>2.92</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U5">
         <v>2.26</v>
@@ -1879,7 +1879,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1906,7 +1906,7 @@
         <v>36</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5">
         <v>38</v>
@@ -1992,7 +1992,7 @@
         <v>124</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G6">
         <v>990</v>
@@ -2004,7 +2004,7 @@
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2013,13 +2013,13 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
         <v>1.3</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
         <v>1.3</v>
@@ -2028,10 +2028,10 @@
         <v>1.43</v>
       </c>
       <c r="R6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2234,10 +2234,10 @@
         <v>125</v>
       </c>
       <c r="F7">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -2246,10 +2246,10 @@
         <v>4.2</v>
       </c>
       <c r="J7">
+        <v>3.9</v>
+      </c>
+      <c r="K7">
         <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2276,40 +2276,40 @@
         <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="X7">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Y7">
         <v>23</v>
       </c>
       <c r="Z7">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
@@ -2324,31 +2324,31 @@
         <v>100</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AM7">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AN7">
         <v>8.800000000000001</v>
       </c>
       <c r="AO7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP7">
         <v>21</v>
       </c>
       <c r="AQ7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AS7">
         <v>34</v>
@@ -2357,13 +2357,13 @@
         <v>12.5</v>
       </c>
       <c r="AU7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7">
         <v>15</v>
       </c>
       <c r="AW7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AX7">
         <v>13.5</v>
@@ -2372,28 +2372,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BB7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BE7">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BF7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BH7">
         <v>4.5</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
         <v>5.2</v>
@@ -2423,25 +2423,25 @@
         <v>13</v>
       </c>
       <c r="BQ7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7">
         <v>7.8</v>
       </c>
       <c r="BU7">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV7">
         <v>27</v>
       </c>
       <c r="BW7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX7">
         <v>32</v>
@@ -2450,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="BZ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA7">
         <v>7.4</v>
@@ -2476,19 +2476,19 @@
         <v>126</v>
       </c>
       <c r="F8">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
         <v>2.94</v>
       </c>
       <c r="H8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I8">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
         <v>3.8</v>
@@ -2518,13 +2518,13 @@
         <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
         <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W8">
         <v>1.51</v>
@@ -2536,22 +2536,22 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB8">
         <v>14.5</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>22</v>
@@ -2563,13 +2563,13 @@
         <v>15.5</v>
       </c>
       <c r="AI8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ8">
         <v>46</v>
       </c>
       <c r="AK8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL8">
         <v>75</v>
@@ -2596,7 +2596,7 @@
         <v>29</v>
       </c>
       <c r="AT8">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU8">
         <v>8</v>
@@ -2608,7 +2608,7 @@
         <v>21</v>
       </c>
       <c r="AX8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2620,7 +2620,7 @@
         <v>30</v>
       </c>
       <c r="BB8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BC8">
         <v>26</v>
@@ -2718,22 +2718,22 @@
         <v>127</v>
       </c>
       <c r="F9">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H9">
         <v>4.8</v>
       </c>
       <c r="I9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2742,13 +2742,13 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
         <v>1.62</v>
@@ -2790,22 +2790,22 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH9">
         <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AJ9">
         <v>19</v>
@@ -2847,7 +2847,7 @@
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2874,10 +2874,10 @@
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG9">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -2895,43 +2895,43 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
         <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
         <v>22</v>
       </c>
       <c r="BS9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT9">
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV9">
         <v>36</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>15</v>
@@ -2987,7 +2987,7 @@
         <v>3.7</v>
       </c>
       <c r="O10">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
         <v>1.91</v>
@@ -3202,13 +3202,13 @@
         <v>129</v>
       </c>
       <c r="F11">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G11">
         <v>2.2</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I11">
         <v>3.3</v>
@@ -3238,7 +3238,7 @@
         <v>1.42</v>
       </c>
       <c r="R11">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S11">
         <v>2.04</v>
@@ -3367,7 +3367,7 @@
         <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ11">
         <v>8.6</v>
@@ -3391,10 +3391,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS11">
         <v>5.4</v>
@@ -3409,7 +3409,7 @@
         <v>21</v>
       </c>
       <c r="BW11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX11">
         <v>24</v>
@@ -3495,7 +3495,7 @@
         <v>1.18</v>
       </c>
       <c r="W12">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X12">
         <v>27</v>
@@ -3516,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AE12">
         <v>1000</v>
@@ -3692,7 +3692,7 @@
         <v>2.46</v>
       </c>
       <c r="H13">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I13">
         <v>2.96</v>
@@ -3701,7 +3701,7 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.25</v>
@@ -3713,7 +3713,7 @@
         <v>6.8</v>
       </c>
       <c r="O13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P13">
         <v>2.96</v>
@@ -3725,7 +3725,7 @@
         <v>1.8</v>
       </c>
       <c r="S13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T13">
         <v>1.46</v>
@@ -3740,16 +3740,16 @@
         <v>1.68</v>
       </c>
       <c r="X13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y13">
         <v>22</v>
       </c>
       <c r="Z13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB13">
         <v>19</v>
@@ -3776,7 +3776,7 @@
         <v>32</v>
       </c>
       <c r="AJ13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK13">
         <v>23</v>
@@ -3785,7 +3785,7 @@
         <v>28</v>
       </c>
       <c r="AM13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN13">
         <v>10.5</v>
@@ -3800,7 +3800,7 @@
         <v>17.5</v>
       </c>
       <c r="AR13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS13">
         <v>25</v>
@@ -3827,10 +3827,10 @@
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC13">
         <v>18.5</v>
@@ -3839,7 +3839,7 @@
         <v>21</v>
       </c>
       <c r="BE13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BF13">
         <v>9.6</v>
@@ -3937,7 +3937,7 @@
         <v>3.05</v>
       </c>
       <c r="I14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -3955,13 +3955,13 @@
         <v>4.6</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P14">
         <v>2.22</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R14">
         <v>1.49</v>
@@ -4182,7 +4182,7 @@
         <v>3.1</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
         <v>4.5</v>
@@ -4194,19 +4194,19 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
         <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q15">
         <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S15">
         <v>2.32</v>
@@ -4215,13 +4215,13 @@
         <v>1.44</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4445,10 +4445,10 @@
         <v>2.74</v>
       </c>
       <c r="Q16">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R16">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S16">
         <v>2.18</v>
@@ -4466,16 +4466,16 @@
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y16">
         <v>13.5</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA16">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AB16">
         <v>60</v>
@@ -4520,7 +4520,7 @@
         <v>4.4</v>
       </c>
       <c r="AP16">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AQ16">
         <v>10</v>
@@ -4532,7 +4532,7 @@
         <v>8.4</v>
       </c>
       <c r="AT16">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU16">
         <v>14</v>
@@ -4544,31 +4544,31 @@
         <v>11</v>
       </c>
       <c r="AX16">
+        <v>6</v>
+      </c>
+      <c r="AY16">
+        <v>5.7</v>
+      </c>
+      <c r="AZ16">
+        <v>5.4</v>
+      </c>
+      <c r="BA16">
         <v>5.5</v>
       </c>
-      <c r="AY16">
-        <v>5.2</v>
-      </c>
-      <c r="AZ16">
-        <v>4.9</v>
-      </c>
-      <c r="BA16">
-        <v>5</v>
-      </c>
       <c r="BB16">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC16">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF16">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG16">
         <v>3.15</v>
@@ -4595,7 +4595,7 @@
         <v>20</v>
       </c>
       <c r="BO16">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BP16">
         <v>1000</v>
@@ -4613,19 +4613,19 @@
         <v>5.1</v>
       </c>
       <c r="BU16">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BV16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BW16">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY16">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BZ16">
         <v>13</v>
@@ -4678,7 +4678,7 @@
         <v>1.07</v>
       </c>
       <c r="N17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O17">
         <v>1.32</v>
@@ -4687,7 +4687,7 @@
         <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R17">
         <v>1.37</v>
@@ -4714,7 +4714,7 @@
         <v>12.5</v>
       </c>
       <c r="Z17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA17">
         <v>55</v>
@@ -4914,7 +4914,7 @@
         <v>3.15</v>
       </c>
       <c r="L18">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M18">
         <v>1.14</v>
@@ -4923,25 +4923,25 @@
         <v>2.58</v>
       </c>
       <c r="O18">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P18">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q18">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T18">
         <v>2.26</v>
       </c>
       <c r="U18">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V18">
         <v>1.35</v>
@@ -4959,7 +4959,7 @@
         <v>24</v>
       </c>
       <c r="AA18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -5025,7 +5025,7 @@
         <v>16</v>
       </c>
       <c r="AW18">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX18">
         <v>11.5</v>
@@ -5049,10 +5049,10 @@
         <v>60</v>
       </c>
       <c r="BE18">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="BF18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG18">
         <v>85</v>
@@ -5067,7 +5067,7 @@
         <v>13.5</v>
       </c>
       <c r="BK18">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5138,226 +5138,226 @@
         <v>137</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G19">
-        <v>600</v>
+        <v>2.9</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I19">
-        <v>870</v>
+        <v>3.45</v>
       </c>
       <c r="J19">
+        <v>3.15</v>
+      </c>
+      <c r="K19">
+        <v>4.8</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>3.6</v>
+      </c>
+      <c r="O19">
+        <v>1.32</v>
+      </c>
+      <c r="P19">
+        <v>1.86</v>
+      </c>
+      <c r="Q19">
+        <v>1.86</v>
+      </c>
+      <c r="R19">
+        <v>1.29</v>
+      </c>
+      <c r="S19">
+        <v>2.98</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.4</v>
+      </c>
+      <c r="W19">
+        <v>1.53</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
         <v>1.03</v>
       </c>
-      <c r="K19">
-        <v>950</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>1.24</v>
-      </c>
-      <c r="Q19">
-        <v>1.01</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
         <v>138</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -430,7 +430,7 @@
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-18 19:47:15</t>
+    <t>2026-08-18 21:56:48</t>
   </si>
 </sst>
 </file>
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.29</v>
@@ -1054,7 +1054,7 @@
         <v>1.18</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q2">
         <v>1.56</v>
@@ -1063,28 +1063,28 @@
         <v>1.68</v>
       </c>
       <c r="S2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U2">
         <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y2">
         <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA2">
         <v>26</v>
@@ -1093,10 +1093,10 @@
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
         <v>18.5</v>
@@ -1111,7 +1111,7 @@
         <v>15</v>
       </c>
       <c r="AI2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
@@ -1123,28 +1123,28 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2">
         <v>9</v>
       </c>
       <c r="AP2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
         <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU2">
         <v>9.199999999999999</v>
@@ -1156,34 +1156,34 @@
         <v>16.5</v>
       </c>
       <c r="AX2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AY2">
         <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BB2">
+        <v>55</v>
+      </c>
+      <c r="BC2">
         <v>32</v>
       </c>
-      <c r="BC2">
-        <v>22</v>
-      </c>
       <c r="BD2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH2">
         <v>5.1</v>
@@ -1195,13 +1195,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BL2">
         <v>85</v>
       </c>
       <c r="BM2">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN2">
         <v>8.4</v>
@@ -1210,19 +1210,19 @@
         <v>5.8</v>
       </c>
       <c r="BP2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2">
         <v>4.2</v>
@@ -1231,19 +1231,19 @@
         <v>15</v>
       </c>
       <c r="BW2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BX2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ2">
         <v>16.5</v>
       </c>
       <c r="CA2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="CB2" t="s">
         <v>138</v>
@@ -1266,7 +1266,7 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
         <v>2.96</v>
@@ -1275,7 +1275,7 @@
         <v>2.98</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
         <v>2.92</v>
@@ -1284,7 +1284,7 @@
         <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.13</v>
@@ -1299,7 +1299,7 @@
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R3">
         <v>1.19</v>
@@ -1508,22 +1508,22 @@
         <v>122</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="G4">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1532,76 +1532,76 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA4">
         <v>190</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1610,49 +1610,49 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>12</v>
       </c>
       <c r="AQ4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR4">
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC4">
         <v>16.5</v>
@@ -1661,13 +1661,13 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1721,7 +1721,7 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1750,22 +1750,22 @@
         <v>123</v>
       </c>
       <c r="F5">
+        <v>1.81</v>
+      </c>
+      <c r="G5">
         <v>1.82</v>
-      </c>
-      <c r="G5">
-        <v>1.86</v>
       </c>
       <c r="H5">
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1780,7 +1780,7 @@
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q5">
         <v>1.76</v>
@@ -1798,10 +1798,10 @@
         <v>2.26</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X5">
         <v>20</v>
@@ -1816,7 +1816,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
@@ -1828,10 +1828,10 @@
         <v>60</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>18</v>
@@ -1840,19 +1840,19 @@
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO5">
         <v>55</v>
@@ -1861,10 +1861,10 @@
         <v>17</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS5">
         <v>38</v>
@@ -1873,13 +1873,13 @@
         <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1891,7 +1891,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -1909,7 +1909,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BH5">
         <v>3.9</v>
@@ -1992,19 +1992,19 @@
         <v>124</v>
       </c>
       <c r="F6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G6">
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2040,10 +2040,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2240,13 +2240,13 @@
         <v>2.04</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -2258,7 +2258,7 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O7">
         <v>1.18</v>
@@ -2279,13 +2279,13 @@
         <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="V7">
         <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
         <v>24</v>
@@ -2300,7 +2300,7 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
@@ -2312,13 +2312,13 @@
         <v>40</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG7">
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI7">
         <v>100</v>
@@ -2327,16 +2327,16 @@
         <v>24</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM7">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="AN7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO7">
         <v>28</v>
@@ -2360,7 +2360,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW7">
         <v>34</v>
@@ -2369,13 +2369,13 @@
         <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BB7">
         <v>21</v>
@@ -2387,7 +2387,7 @@
         <v>23</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF7">
         <v>8.199999999999999</v>
@@ -2399,19 +2399,19 @@
         <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN7">
         <v>5.2</v>
@@ -2423,37 +2423,37 @@
         <v>13</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU7">
         <v>5.7</v>
       </c>
       <c r="BV7">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX7">
         <v>32</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7">
         <v>14.5</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
         <v>138</v>
@@ -2518,16 +2518,16 @@
         <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U8">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
         <v>1.62</v>
       </c>
       <c r="W8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
         <v>19</v>
@@ -2620,7 +2620,7 @@
         <v>30</v>
       </c>
       <c r="BB8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC8">
         <v>26</v>
@@ -2721,7 +2721,7 @@
         <v>1.77</v>
       </c>
       <c r="G9">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H9">
         <v>4.8</v>
@@ -2742,16 +2742,16 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R9">
         <v>1.61</v>
@@ -2769,7 +2769,7 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X9">
         <v>23</v>
@@ -2796,19 +2796,19 @@
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
         <v>10</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK9">
         <v>16.5</v>
@@ -2826,13 +2826,13 @@
         <v>44</v>
       </c>
       <c r="AP9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ9">
         <v>21</v>
       </c>
       <c r="AR9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AS9">
         <v>40</v>
@@ -2841,13 +2841,13 @@
         <v>11</v>
       </c>
       <c r="AU9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW9">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2859,13 +2859,13 @@
         <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD9">
         <v>23</v>
@@ -2874,10 +2874,10 @@
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -2889,7 +2889,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2919,7 +2919,7 @@
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
         <v>36</v>
@@ -2937,7 +2937,7 @@
         <v>15</v>
       </c>
       <c r="CA9">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="s">
         <v>138</v>
@@ -2963,16 +2963,16 @@
         <v>2.62</v>
       </c>
       <c r="G10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H10">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I10">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
         <v>4.4</v>
@@ -3008,7 +3008,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
         <v>1.48</v>
@@ -3205,7 +3205,7 @@
         <v>2.16</v>
       </c>
       <c r="G11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H11">
         <v>3.15</v>
@@ -3232,16 +3232,16 @@
         <v>1.13</v>
       </c>
       <c r="P11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
         <v>1.42</v>
       </c>
       <c r="R11">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T11">
         <v>1.43</v>
@@ -3265,13 +3265,13 @@
         <v>34</v>
       </c>
       <c r="AA11">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AB11">
         <v>19.5</v>
       </c>
       <c r="AC11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD11">
         <v>15.5</v>
@@ -3304,7 +3304,7 @@
         <v>44</v>
       </c>
       <c r="AN11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11">
         <v>15.5</v>
@@ -3319,7 +3319,7 @@
         <v>19.5</v>
       </c>
       <c r="AS11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT11">
         <v>17</v>
@@ -3346,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="BB11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC11">
         <v>16.5</v>
@@ -3364,7 +3364,7 @@
         <v>13</v>
       </c>
       <c r="BH11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI11">
         <v>4.2</v>
@@ -3379,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="BM11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN11">
         <v>6.2</v>
@@ -3388,16 +3388,16 @@
         <v>5.1</v>
       </c>
       <c r="BP11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR11">
         <v>20</v>
       </c>
       <c r="BS11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
@@ -3409,13 +3409,13 @@
         <v>21</v>
       </c>
       <c r="BW11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX11">
         <v>24</v>
       </c>
       <c r="BY11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ11">
         <v>13</v>
@@ -3465,7 +3465,7 @@
         <v>1.29</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
         <v>5.7</v>
@@ -3552,7 +3552,7 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12">
         <v>18</v>
@@ -3573,7 +3573,7 @@
         <v>20</v>
       </c>
       <c r="AW12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3701,7 +3701,7 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.25</v>
@@ -3722,7 +3722,7 @@
         <v>1.48</v>
       </c>
       <c r="R13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S13">
         <v>2.2</v>
@@ -3740,7 +3740,7 @@
         <v>1.68</v>
       </c>
       <c r="X13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y13">
         <v>22</v>
@@ -3842,7 +3842,7 @@
         <v>25</v>
       </c>
       <c r="BF13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG13">
         <v>12.5</v>
@@ -3937,7 +3937,7 @@
         <v>3.05</v>
       </c>
       <c r="I14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -3961,7 +3961,7 @@
         <v>2.22</v>
       </c>
       <c r="Q14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
         <v>1.49</v>
@@ -3976,7 +3976,7 @@
         <v>2.36</v>
       </c>
       <c r="V14">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
         <v>1.69</v>
@@ -4179,10 +4179,10 @@
         <v>2.72</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J15">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
         <v>4.5</v>
@@ -4194,13 +4194,13 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O15">
         <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q15">
         <v>1.64</v>
@@ -4218,10 +4218,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4430,7 +4430,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L16">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.01</v>
@@ -4481,13 +4481,13 @@
         <v>60</v>
       </c>
       <c r="AC16">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AD16">
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16">
         <v>150</v>
@@ -4496,7 +4496,7 @@
         <v>60</v>
       </c>
       <c r="AH16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI16">
         <v>44</v>
@@ -4517,10 +4517,10 @@
         <v>270</v>
       </c>
       <c r="AO16">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AP16">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16">
         <v>10</v>
@@ -4532,7 +4532,7 @@
         <v>8.4</v>
       </c>
       <c r="AT16">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AU16">
         <v>14</v>
@@ -4544,31 +4544,31 @@
         <v>11</v>
       </c>
       <c r="AX16">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AY16">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AZ16">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA16">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB16">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BC16">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD16">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BE16">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF16">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG16">
         <v>3.15</v>
@@ -4678,7 +4678,7 @@
         <v>1.07</v>
       </c>
       <c r="N17">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
         <v>1.32</v>
@@ -4690,7 +4690,7 @@
         <v>2</v>
       </c>
       <c r="R17">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S17">
         <v>3.4</v>
@@ -4702,7 +4702,7 @@
         <v>2.14</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W17">
         <v>1.64</v>
@@ -5049,7 +5049,7 @@
         <v>60</v>
       </c>
       <c r="BE18">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF18">
         <v>34</v>
@@ -5064,37 +5064,37 @@
         <v>2.42</v>
       </c>
       <c r="BJ18">
+        <v>12</v>
+      </c>
+      <c r="BK18">
+        <v>6.6</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
         <v>13.5</v>
       </c>
-      <c r="BK18">
-        <v>5.2</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>7.8</v>
-      </c>
       <c r="BN18">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BO18">
         <v>4.5</v>
       </c>
       <c r="BP18">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ18">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BR18">
         <v>55</v>
       </c>
       <c r="BS18">
+        <v>11</v>
+      </c>
+      <c r="BT18">
         <v>7</v>
-      </c>
-      <c r="BT18">
-        <v>7.8</v>
       </c>
       <c r="BU18">
         <v>6.2</v>
@@ -5103,19 +5103,19 @@
         <v>46</v>
       </c>
       <c r="BW18">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX18">
         <v>75</v>
       </c>
       <c r="BY18">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BZ18">
         <v>65</v>
       </c>
       <c r="CA18">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="CB18" t="s">
         <v>138</v>
@@ -5177,7 +5177,7 @@
         <v>1.29</v>
       </c>
       <c r="S19">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="T19">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="153">
   <si>
     <t>League</t>
   </si>
@@ -322,6 +322,18 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>22:45:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Kansas City</t>
   </si>
   <si>
@@ -349,15 +361,15 @@
     <t>Phoenix Rising FC</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Al-Wakra</t>
   </si>
   <si>
@@ -376,6 +388,21 @@
     <t>Real Santander</t>
   </si>
   <si>
+    <t>LDU</t>
+  </si>
+  <si>
+    <t>Leones FC</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>St Louis City SC</t>
   </si>
   <si>
@@ -403,15 +430,15 @@
     <t>Colorado Switchbacks FC</t>
   </si>
   <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes</t>
+  </si>
+  <si>
     <t>San Diego FC</t>
   </si>
   <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>San Jose Earthquakes</t>
-  </si>
-  <si>
     <t>Qatar SC</t>
   </si>
   <si>
@@ -430,7 +457,22 @@
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>2026-08-18 21:56:48</t>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Real Soacha Cundinamarca FC</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Bogota</t>
+  </si>
+  <si>
+    <t>America MG</t>
+  </si>
+  <si>
+    <t>2026-08-19 00:05:49</t>
   </si>
 </sst>
 </file>
@@ -762,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1018,10 +1060,10 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>3.65</v>
@@ -1036,10 +1078,10 @@
         <v>2.04</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
         <v>1.29</v>
@@ -1075,7 +1117,7 @@
         <v>1.96</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
         <v>26</v>
@@ -1093,7 +1135,7 @@
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2">
         <v>11</v>
@@ -1246,7 +1288,7 @@
         <v>4.3</v>
       </c>
       <c r="CB2" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1260,13 +1302,13 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G3">
         <v>2.96</v>
@@ -1290,7 +1332,7 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O3">
         <v>1.57</v>
@@ -1299,7 +1341,7 @@
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
         <v>1.19</v>
@@ -1323,7 +1365,7 @@
         <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>22</v>
@@ -1344,7 +1386,7 @@
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3">
         <v>16</v>
@@ -1359,7 +1401,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL3">
         <v>75</v>
@@ -1368,7 +1410,7 @@
         <v>220</v>
       </c>
       <c r="AN3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO3">
         <v>70</v>
@@ -1377,13 +1419,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1395,7 +1437,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1404,46 +1446,46 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>5.9</v>
+      </c>
+      <c r="BC3">
+        <v>5.8</v>
+      </c>
+      <c r="BD3">
+        <v>6</v>
+      </c>
+      <c r="BE3">
         <v>6.4</v>
       </c>
-      <c r="BB3">
-        <v>6.2</v>
-      </c>
-      <c r="BC3">
-        <v>6.2</v>
-      </c>
-      <c r="BD3">
-        <v>6.4</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
-      </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
@@ -1467,7 +1509,7 @@
         <v>5.9</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1479,16 +1521,16 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1502,34 +1544,34 @@
         <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G4">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H4">
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.7</v>
@@ -1538,7 +1580,7 @@
         <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
@@ -1547,25 +1589,25 @@
         <v>1.35</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
         <v>2</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X4">
         <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z4">
         <v>55</v>
@@ -1574,7 +1616,7 @@
         <v>190</v>
       </c>
       <c r="AB4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
         <v>11.5</v>
@@ -1583,7 +1625,7 @@
         <v>25</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF4">
         <v>9</v>
@@ -1592,7 +1634,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>110</v>
@@ -1601,7 +1643,7 @@
         <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1613,7 +1655,7 @@
         <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4">
         <v>12</v>
@@ -1625,49 +1667,49 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
         <v>21</v>
       </c>
       <c r="AW4">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>8.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB4">
         <v>14</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD4">
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
         <v>8.800000000000001</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1691,7 +1733,7 @@
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1730,7 +1772,7 @@
         <v>1.68</v>
       </c>
       <c r="CB4" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1744,25 +1786,25 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H5">
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -1774,7 +1816,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
         <v>1.25</v>
@@ -1783,25 +1825,25 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U5">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
         <v>20</v>
@@ -1825,10 +1867,10 @@
         <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1837,25 +1879,25 @@
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AK5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP5">
         <v>17</v>
@@ -1864,7 +1906,7 @@
         <v>17</v>
       </c>
       <c r="AR5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AS5">
         <v>38</v>
@@ -1873,34 +1915,34 @@
         <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5">
         <v>38</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE5">
         <v>36</v>
@@ -1921,7 +1963,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
         <v>110</v>
@@ -1963,16 +2005,16 @@
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA5">
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1986,28 +2028,28 @@
         <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F6">
-        <v>1.06</v>
+        <v>1.65</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>1.98</v>
       </c>
       <c r="H6">
-        <v>1.05</v>
+        <v>4.8</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2016,34 +2058,34 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.3</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q6">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
         <v>1.14</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2214,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2228,16 +2270,16 @@
         <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H7">
         <v>3.95</v>
@@ -2246,10 +2288,10 @@
         <v>4.1</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2264,13 +2306,13 @@
         <v>1.18</v>
       </c>
       <c r="P7">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
         <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S7">
         <v>2.44</v>
@@ -2279,13 +2321,13 @@
         <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V7">
         <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X7">
         <v>24</v>
@@ -2303,40 +2345,40 @@
         <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
         <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>14.5</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AJ7">
         <v>24</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM7">
         <v>60</v>
       </c>
       <c r="AN7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO7">
         <v>28</v>
@@ -2345,13 +2387,13 @@
         <v>21</v>
       </c>
       <c r="AQ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR7">
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT7">
         <v>12.5</v>
@@ -2366,19 +2408,19 @@
         <v>34</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY7">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA7">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7">
         <v>16</v>
@@ -2390,28 +2432,28 @@
         <v>44</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH7">
         <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
         <v>5.2</v>
@@ -2423,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2435,7 +2477,7 @@
         <v>7.6</v>
       </c>
       <c r="BU7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2444,7 +2486,7 @@
         <v>10</v>
       </c>
       <c r="BX7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
         <v>10.5</v>
@@ -2453,10 +2495,10 @@
         <v>14.5</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2470,28 +2512,28 @@
         <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G8">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H8">
+        <v>2.52</v>
+      </c>
+      <c r="I8">
         <v>2.56</v>
       </c>
-      <c r="I8">
-        <v>2.6</v>
-      </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2515,16 +2557,16 @@
         <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T8">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U8">
         <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W8">
         <v>1.52</v>
@@ -2536,10 +2578,10 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AB8">
         <v>14.5</v>
@@ -2596,7 +2638,7 @@
         <v>29</v>
       </c>
       <c r="AT8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU8">
         <v>8</v>
@@ -2608,7 +2650,7 @@
         <v>21</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2620,7 +2662,7 @@
         <v>30</v>
       </c>
       <c r="BB8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BC8">
         <v>26</v>
@@ -2629,7 +2671,7 @@
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF8">
         <v>19.5</v>
@@ -2698,7 +2740,7 @@
         <v>6.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2712,10 +2754,10 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F9">
         <v>1.77</v>
@@ -2736,7 +2778,7 @@
         <v>4.4</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.04</v>
@@ -2748,16 +2790,16 @@
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R9">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
         <v>1.65</v>
@@ -2775,10 +2817,10 @@
         <v>23</v>
       </c>
       <c r="Y9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2814,13 +2856,13 @@
         <v>16.5</v>
       </c>
       <c r="AL9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM9">
         <v>75</v>
       </c>
       <c r="AN9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO9">
         <v>44</v>
@@ -2844,10 +2886,10 @@
         <v>9</v>
       </c>
       <c r="AV9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2859,7 +2901,7 @@
         <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
@@ -2874,7 +2916,7 @@
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG9">
         <v>26</v>
@@ -2883,22 +2925,22 @@
         <v>4.3</v>
       </c>
       <c r="BI9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
         <v>4.2</v>
@@ -2907,40 +2949,40 @@
         <v>11</v>
       </c>
       <c r="BQ9">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9">
         <v>22</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>15</v>
       </c>
       <c r="CA9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2954,52 +2996,52 @@
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G10">
         <v>3.05</v>
       </c>
       <c r="H10">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I10">
         <v>2.98</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="P10">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q10">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T10">
         <v>1.65</v>
@@ -3008,13 +3050,13 @@
         <v>1.11</v>
       </c>
       <c r="V10">
+        <v>1.51</v>
+      </c>
+      <c r="W10">
         <v>1.5</v>
       </c>
-      <c r="W10">
-        <v>1.48</v>
-      </c>
       <c r="X10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y10">
         <v>14.5</v>
@@ -3029,7 +3071,7 @@
         <v>14.5</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
         <v>14.5</v>
@@ -3044,10 +3086,10 @@
         <v>14.5</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AI10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
         <v>48</v>
@@ -3056,46 +3098,46 @@
         <v>34</v>
       </c>
       <c r="AL10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU10">
         <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW10">
         <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
         <v>12.5</v>
@@ -3116,7 +3158,7 @@
         <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG10">
         <v>17</v>
@@ -3182,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3196,235 +3238,235 @@
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="H11">
-        <v>3.15</v>
+        <v>5.9</v>
       </c>
       <c r="I11">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="S11">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="U11">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="W11">
-        <v>1.83</v>
+        <v>2.68</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Y11">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Z11">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="AA11">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AC11">
         <v>11.5</v>
       </c>
       <c r="AD11">
+        <v>25</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>11</v>
+      </c>
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
         <v>15.5</v>
       </c>
-      <c r="AE11">
+      <c r="AK11">
+        <v>15.5</v>
+      </c>
+      <c r="AL11">
         <v>32</v>
       </c>
-      <c r="AF11">
-        <v>21</v>
-      </c>
-      <c r="AG11">
-        <v>12</v>
-      </c>
-      <c r="AH11">
-        <v>14.5</v>
-      </c>
-      <c r="AI11">
-        <v>30</v>
-      </c>
-      <c r="AJ11">
-        <v>32</v>
-      </c>
-      <c r="AK11">
-        <v>19.5</v>
-      </c>
-      <c r="AL11">
-        <v>23</v>
-      </c>
       <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>6.2</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>18</v>
+      </c>
+      <c r="AQ11">
+        <v>18</v>
+      </c>
+      <c r="AR11">
+        <v>27</v>
+      </c>
+      <c r="AS11">
         <v>44</v>
       </c>
-      <c r="AN11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO11">
-        <v>15.5</v>
-      </c>
-      <c r="AP11">
-        <v>24</v>
-      </c>
-      <c r="AQ11">
-        <v>21</v>
-      </c>
-      <c r="AR11">
-        <v>19.5</v>
-      </c>
-      <c r="AS11">
-        <v>28</v>
-      </c>
       <c r="AT11">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AU11">
         <v>10</v>
       </c>
       <c r="AV11">
+        <v>20</v>
+      </c>
+      <c r="AW11">
+        <v>32</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>17</v>
+      </c>
+      <c r="BA11">
+        <v>32</v>
+      </c>
+      <c r="BB11">
+        <v>13</v>
+      </c>
+      <c r="BC11">
+        <v>13</v>
+      </c>
+      <c r="BD11">
+        <v>24</v>
+      </c>
+      <c r="BE11">
+        <v>36</v>
+      </c>
+      <c r="BF11">
+        <v>5.6</v>
+      </c>
+      <c r="BG11">
+        <v>32</v>
+      </c>
+      <c r="BH11">
+        <v>4.6</v>
+      </c>
+      <c r="BI11">
+        <v>3.55</v>
+      </c>
+      <c r="BJ11">
+        <v>10.5</v>
+      </c>
+      <c r="BK11">
+        <v>5</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN11">
+        <v>4.6</v>
+      </c>
+      <c r="BO11">
+        <v>3.55</v>
+      </c>
+      <c r="BP11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ11">
+        <v>4.9</v>
+      </c>
+      <c r="BR11">
+        <v>22</v>
+      </c>
+      <c r="BS11">
+        <v>6.8</v>
+      </c>
+      <c r="BT11">
+        <v>10.5</v>
+      </c>
+      <c r="BU11">
+        <v>5</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>8</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>8</v>
+      </c>
+      <c r="BZ11">
         <v>13.5</v>
       </c>
-      <c r="AW11">
-        <v>18.5</v>
-      </c>
-      <c r="AX11">
-        <v>17.5</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11">
-        <v>12.5</v>
-      </c>
-      <c r="BA11">
-        <v>19</v>
-      </c>
-      <c r="BB11">
-        <v>19.5</v>
-      </c>
-      <c r="BC11">
-        <v>16.5</v>
-      </c>
-      <c r="BD11">
-        <v>18.5</v>
-      </c>
-      <c r="BE11">
-        <v>24</v>
-      </c>
-      <c r="BF11">
-        <v>7.4</v>
-      </c>
-      <c r="BG11">
-        <v>13</v>
-      </c>
-      <c r="BH11">
-        <v>6</v>
-      </c>
-      <c r="BI11">
-        <v>4.2</v>
-      </c>
-      <c r="BJ11">
-        <v>8.6</v>
-      </c>
-      <c r="BK11">
-        <v>5.4</v>
-      </c>
-      <c r="BL11">
-        <v>60</v>
-      </c>
-      <c r="BM11">
-        <v>6.8</v>
-      </c>
-      <c r="BN11">
-        <v>6.2</v>
-      </c>
-      <c r="BO11">
-        <v>5.1</v>
-      </c>
-      <c r="BP11">
-        <v>16</v>
-      </c>
-      <c r="BQ11">
-        <v>5.2</v>
-      </c>
-      <c r="BR11">
-        <v>20</v>
-      </c>
-      <c r="BS11">
-        <v>5.5</v>
-      </c>
-      <c r="BT11">
-        <v>7.6</v>
-      </c>
-      <c r="BU11">
-        <v>4.9</v>
-      </c>
-      <c r="BV11">
-        <v>21</v>
-      </c>
-      <c r="BW11">
+      <c r="CA11">
         <v>5.6</v>
       </c>
-      <c r="BX11">
-        <v>24</v>
-      </c>
-      <c r="BY11">
-        <v>5.8</v>
-      </c>
-      <c r="BZ11">
-        <v>13</v>
-      </c>
-      <c r="CA11">
-        <v>7.2</v>
-      </c>
       <c r="CB11" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3438,235 +3480,235 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F12">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>1.59</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>2.94</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>2.98</v>
       </c>
       <c r="J12">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="Q12">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="R12">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="S12">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T12">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="U12">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>2.68</v>
+        <v>1.74</v>
       </c>
       <c r="X12">
+        <v>32</v>
+      </c>
+      <c r="Y12">
+        <v>22</v>
+      </c>
+      <c r="Z12">
+        <v>28</v>
+      </c>
+      <c r="AA12">
+        <v>140</v>
+      </c>
+      <c r="AB12">
+        <v>17.5</v>
+      </c>
+      <c r="AC12">
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <v>14</v>
+      </c>
+      <c r="AE12">
+        <v>28</v>
+      </c>
+      <c r="AF12">
+        <v>19.5</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>14.5</v>
+      </c>
+      <c r="AI12">
+        <v>30</v>
+      </c>
+      <c r="AJ12">
+        <v>32</v>
+      </c>
+      <c r="AK12">
+        <v>20</v>
+      </c>
+      <c r="AL12">
+        <v>24</v>
+      </c>
+      <c r="AM12">
+        <v>48</v>
+      </c>
+      <c r="AN12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO12">
+        <v>15</v>
+      </c>
+      <c r="AP12">
+        <v>26</v>
+      </c>
+      <c r="AQ12">
+        <v>20</v>
+      </c>
+      <c r="AR12">
+        <v>24</v>
+      </c>
+      <c r="AS12">
+        <v>42</v>
+      </c>
+      <c r="AT12">
+        <v>16</v>
+      </c>
+      <c r="AU12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV12">
+        <v>12.5</v>
+      </c>
+      <c r="AW12">
+        <v>24</v>
+      </c>
+      <c r="AX12">
+        <v>17.5</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>19.5</v>
+      </c>
+      <c r="BB12">
         <v>27</v>
       </c>
-      <c r="Y12">
-        <v>29</v>
-      </c>
-      <c r="Z12">
-        <v>250</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>12</v>
-      </c>
-      <c r="AC12">
-        <v>11</v>
-      </c>
-      <c r="AD12">
-        <v>25</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>11</v>
-      </c>
-      <c r="AG12">
-        <v>10.5</v>
-      </c>
-      <c r="AH12">
+      <c r="BC12">
+        <v>18</v>
+      </c>
+      <c r="BD12">
         <v>22</v>
       </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>15.5</v>
-      </c>
-      <c r="AK12">
-        <v>15.5</v>
-      </c>
-      <c r="AL12">
-        <v>32</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
+      <c r="BE12">
+        <v>40</v>
+      </c>
+      <c r="BF12">
+        <v>9</v>
+      </c>
+      <c r="BG12">
+        <v>13.5</v>
+      </c>
+      <c r="BH12">
+        <v>5.1</v>
+      </c>
+      <c r="BI12">
+        <v>3.85</v>
+      </c>
+      <c r="BJ12">
+        <v>8.6</v>
+      </c>
+      <c r="BK12">
         <v>6.2</v>
       </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>18</v>
-      </c>
-      <c r="AQ12">
-        <v>18</v>
-      </c>
-      <c r="AR12">
-        <v>28</v>
-      </c>
-      <c r="AS12">
-        <v>44</v>
-      </c>
-      <c r="AT12">
-        <v>10.5</v>
-      </c>
-      <c r="AU12">
-        <v>10</v>
-      </c>
-      <c r="AV12">
-        <v>20</v>
-      </c>
-      <c r="AW12">
-        <v>34</v>
-      </c>
-      <c r="AX12">
-        <v>10</v>
-      </c>
-      <c r="AY12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12">
-        <v>17</v>
-      </c>
-      <c r="BA12">
-        <v>32</v>
-      </c>
-      <c r="BB12">
-        <v>13</v>
-      </c>
-      <c r="BC12">
-        <v>13</v>
-      </c>
-      <c r="BD12">
-        <v>19</v>
-      </c>
-      <c r="BE12">
-        <v>36</v>
-      </c>
-      <c r="BF12">
-        <v>5.6</v>
-      </c>
-      <c r="BG12">
-        <v>32</v>
-      </c>
-      <c r="BH12">
-        <v>4.6</v>
-      </c>
-      <c r="BI12">
-        <v>3.55</v>
-      </c>
-      <c r="BJ12">
-        <v>10.5</v>
-      </c>
-      <c r="BK12">
-        <v>5</v>
-      </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN12">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO12">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="BP12">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BQ12">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BR12">
         <v>22</v>
       </c>
       <c r="BS12">
+        <v>7.4</v>
+      </c>
+      <c r="BT12">
         <v>6.8</v>
       </c>
-      <c r="BT12">
-        <v>10.5</v>
-      </c>
       <c r="BU12">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY12">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12">
         <v>13.5</v>
       </c>
       <c r="CA12">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3680,235 +3722,235 @@
         <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F13">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="G13">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="H13">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="I13">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="P13">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R13">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="S13">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="T13">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="U13">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="X13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y13">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>350</v>
       </c>
       <c r="AB13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13">
         <v>14.5</v>
       </c>
       <c r="AI13">
+        <v>30</v>
+      </c>
+      <c r="AJ13">
         <v>32</v>
       </c>
-      <c r="AJ13">
-        <v>38</v>
-      </c>
       <c r="AK13">
+        <v>19.5</v>
+      </c>
+      <c r="AL13">
         <v>23</v>
       </c>
-      <c r="AL13">
+      <c r="AM13">
+        <v>44</v>
+      </c>
+      <c r="AN13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO13">
+        <v>15.5</v>
+      </c>
+      <c r="AP13">
+        <v>24</v>
+      </c>
+      <c r="AQ13">
+        <v>21</v>
+      </c>
+      <c r="AR13">
+        <v>19.5</v>
+      </c>
+      <c r="AS13">
         <v>28</v>
       </c>
-      <c r="AM13">
-        <v>120</v>
-      </c>
-      <c r="AN13">
+      <c r="AT13">
+        <v>17</v>
+      </c>
+      <c r="AU13">
+        <v>10</v>
+      </c>
+      <c r="AV13">
+        <v>13.5</v>
+      </c>
+      <c r="AW13">
+        <v>18.5</v>
+      </c>
+      <c r="AX13">
+        <v>17.5</v>
+      </c>
+      <c r="AY13">
         <v>10.5</v>
       </c>
-      <c r="AO13">
-        <v>14</v>
-      </c>
-      <c r="AP13">
-        <v>20</v>
-      </c>
-      <c r="AQ13">
-        <v>17.5</v>
-      </c>
-      <c r="AR13">
-        <v>17.5</v>
-      </c>
-      <c r="AS13">
-        <v>25</v>
-      </c>
-      <c r="AT13">
-        <v>16.5</v>
-      </c>
-      <c r="AU13">
-        <v>9.4</v>
-      </c>
-      <c r="AV13">
+      <c r="AZ13">
         <v>12.5</v>
-      </c>
-      <c r="AW13">
-        <v>18</v>
-      </c>
-      <c r="AX13">
-        <v>18.5</v>
-      </c>
-      <c r="AY13">
-        <v>11</v>
-      </c>
-      <c r="AZ13">
-        <v>12</v>
       </c>
       <c r="BA13">
         <v>19</v>
       </c>
       <c r="BB13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC13">
+        <v>16.5</v>
+      </c>
+      <c r="BD13">
         <v>18.5</v>
       </c>
-      <c r="BD13">
-        <v>21</v>
-      </c>
       <c r="BE13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BF13">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH13">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BI13">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
       </c>
       <c r="BK13">
+        <v>5.4</v>
+      </c>
+      <c r="BL13">
+        <v>60</v>
+      </c>
+      <c r="BM13">
+        <v>7</v>
+      </c>
+      <c r="BN13">
         <v>6.2</v>
       </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN13">
-        <v>6.4</v>
-      </c>
       <c r="BO13">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BQ13">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BR13">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BS13">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT13">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU13">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BW13">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BZ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA13">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3922,10 +3964,10 @@
         <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F14">
         <v>2.18</v>
@@ -3934,10 +3976,10 @@
         <v>2.44</v>
       </c>
       <c r="H14">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I14">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -3955,10 +3997,10 @@
         <v>4.6</v>
       </c>
       <c r="O14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q14">
         <v>1.64</v>
@@ -4150,7 +4192,7 @@
         <v>6.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4164,28 +4206,28 @@
         <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F15">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G15">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
         <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4194,16 +4236,16 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
         <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R15">
         <v>1.41</v>
@@ -4218,10 +4260,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4335,64 +4377,64 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4406,10 +4448,10 @@
         <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F16">
         <v>12.5</v>
@@ -4634,7 +4676,7 @@
         <v>1.83</v>
       </c>
       <c r="CB16" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4648,10 +4690,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F17">
         <v>2.48</v>
@@ -4816,7 +4858,7 @@
         <v>27</v>
       </c>
       <c r="BH17">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BI17">
         <v>3</v>
@@ -4825,13 +4867,13 @@
         <v>11</v>
       </c>
       <c r="BK17">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BN17">
         <v>6.4</v>
@@ -4843,13 +4885,13 @@
         <v>23</v>
       </c>
       <c r="BQ17">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BR17">
         <v>38</v>
       </c>
       <c r="BS17">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BT17">
         <v>6.8</v>
@@ -4861,22 +4903,22 @@
         <v>27</v>
       </c>
       <c r="BW17">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BX17">
         <v>40</v>
       </c>
       <c r="BY17">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BZ17">
         <v>32</v>
       </c>
       <c r="CA17">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB17" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4890,13 +4932,13 @@
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G18">
         <v>2.4</v>
@@ -4929,7 +4971,7 @@
         <v>1.51</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R18">
         <v>1.18</v>
@@ -4959,7 +5001,7 @@
         <v>24</v>
       </c>
       <c r="AA18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -5025,7 +5067,7 @@
         <v>16</v>
       </c>
       <c r="AW18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX18">
         <v>11.5</v>
@@ -5046,13 +5088,13 @@
         <v>30</v>
       </c>
       <c r="BD18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE18">
         <v>95</v>
       </c>
       <c r="BF18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG18">
         <v>85</v>
@@ -5070,13 +5112,13 @@
         <v>6.6</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO18">
         <v>4.5</v>
@@ -5085,13 +5127,13 @@
         <v>21</v>
       </c>
       <c r="BQ18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR18">
         <v>55</v>
       </c>
       <c r="BS18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT18">
         <v>7</v>
@@ -5103,22 +5145,22 @@
         <v>46</v>
       </c>
       <c r="BW18">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX18">
         <v>75</v>
       </c>
       <c r="BY18">
+        <v>12.5</v>
+      </c>
+      <c r="BZ18">
+        <v>60</v>
+      </c>
+      <c r="CA18">
         <v>12</v>
       </c>
-      <c r="BZ18">
-        <v>65</v>
-      </c>
-      <c r="CA18">
-        <v>11.5</v>
-      </c>
       <c r="CB18" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5132,10 +5174,10 @@
         <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F19">
         <v>2.38</v>
@@ -5177,13 +5219,13 @@
         <v>1.29</v>
       </c>
       <c r="S19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.4</v>
@@ -5303,64 +5345,1274 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>138</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20">
+        <v>1.54</v>
+      </c>
+      <c r="G20">
+        <v>1.65</v>
+      </c>
+      <c r="H20">
+        <v>7.2</v>
+      </c>
+      <c r="I20">
+        <v>8.6</v>
+      </c>
+      <c r="J20">
+        <v>3.8</v>
+      </c>
+      <c r="K20">
+        <v>4.3</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.08</v>
+      </c>
+      <c r="N20">
+        <v>3.1</v>
+      </c>
+      <c r="O20">
+        <v>1.38</v>
+      </c>
+      <c r="P20">
+        <v>1.71</v>
+      </c>
+      <c r="Q20">
+        <v>2.12</v>
+      </c>
+      <c r="R20">
+        <v>1.27</v>
+      </c>
+      <c r="S20">
+        <v>3.95</v>
+      </c>
+      <c r="T20">
+        <v>2.16</v>
+      </c>
+      <c r="U20">
+        <v>1.71</v>
+      </c>
+      <c r="V20">
+        <v>1.13</v>
+      </c>
+      <c r="W20">
+        <v>2.52</v>
+      </c>
+      <c r="X20">
+        <v>14.5</v>
+      </c>
+      <c r="Y20">
+        <v>25</v>
+      </c>
+      <c r="Z20">
+        <v>80</v>
+      </c>
+      <c r="AA20">
+        <v>360</v>
+      </c>
+      <c r="AB20">
+        <v>7</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>32</v>
+      </c>
+      <c r="AE20">
+        <v>180</v>
+      </c>
+      <c r="AF20">
+        <v>9</v>
+      </c>
+      <c r="AG20">
+        <v>11</v>
+      </c>
+      <c r="AH20">
+        <v>29</v>
+      </c>
+      <c r="AI20">
+        <v>170</v>
+      </c>
+      <c r="AJ20">
+        <v>16</v>
+      </c>
+      <c r="AK20">
+        <v>24</v>
+      </c>
+      <c r="AL20">
+        <v>60</v>
+      </c>
+      <c r="AM20">
+        <v>250</v>
+      </c>
+      <c r="AN20">
+        <v>14</v>
+      </c>
+      <c r="AO20">
+        <v>310</v>
+      </c>
+      <c r="AP20">
+        <v>10</v>
+      </c>
+      <c r="AQ20">
+        <v>17</v>
+      </c>
+      <c r="AR20">
+        <v>5.5</v>
+      </c>
+      <c r="AS20">
+        <v>5.8</v>
+      </c>
+      <c r="AT20">
+        <v>5.8</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>21</v>
+      </c>
+      <c r="AW20">
+        <v>5.7</v>
+      </c>
+      <c r="AX20">
+        <v>7.2</v>
+      </c>
+      <c r="AY20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
+        <v>5.7</v>
+      </c>
+      <c r="BB20">
+        <v>12.5</v>
+      </c>
+      <c r="BC20">
+        <v>16.5</v>
+      </c>
+      <c r="BD20">
+        <v>5.4</v>
+      </c>
+      <c r="BE20">
+        <v>5.8</v>
+      </c>
+      <c r="BF20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG20">
+        <v>5.8</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.74</v>
+      </c>
+      <c r="BJ20">
+        <v>17.5</v>
+      </c>
+      <c r="BK20">
+        <v>1.58</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.74</v>
+      </c>
+      <c r="BN20">
+        <v>5.3</v>
+      </c>
+      <c r="BO20">
+        <v>2.68</v>
+      </c>
+      <c r="BP20">
+        <v>15.5</v>
+      </c>
+      <c r="BQ20">
+        <v>1.56</v>
+      </c>
+      <c r="BR20">
+        <v>48</v>
+      </c>
+      <c r="BS20">
+        <v>1.68</v>
+      </c>
+      <c r="BT20">
+        <v>15.5</v>
+      </c>
+      <c r="BU20">
+        <v>1.56</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.74</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.74</v>
+      </c>
+      <c r="BZ20">
+        <v>36</v>
+      </c>
+      <c r="CA20">
+        <v>1.66</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21">
+        <v>1.04</v>
+      </c>
+      <c r="G21">
+        <v>990</v>
+      </c>
+      <c r="H21">
+        <v>1.04</v>
+      </c>
+      <c r="I21">
+        <v>990</v>
+      </c>
+      <c r="J21">
+        <v>1.08</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>1.25</v>
+      </c>
+      <c r="O21">
+        <v>1.02</v>
+      </c>
+      <c r="P21">
+        <v>1.25</v>
+      </c>
+      <c r="Q21">
+        <v>1.55</v>
+      </c>
+      <c r="R21">
+        <v>1.13</v>
+      </c>
+      <c r="S21">
+        <v>1.55</v>
+      </c>
+      <c r="T21">
+        <v>1.11</v>
+      </c>
+      <c r="U21">
+        <v>1.11</v>
+      </c>
+      <c r="V21">
+        <v>1.02</v>
+      </c>
+      <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21">
+        <v>1.03</v>
+      </c>
+      <c r="AR21">
+        <v>1.03</v>
+      </c>
+      <c r="AS21">
+        <v>1.03</v>
+      </c>
+      <c r="AT21">
+        <v>1.03</v>
+      </c>
+      <c r="AU21">
+        <v>1.03</v>
+      </c>
+      <c r="AV21">
+        <v>1.03</v>
+      </c>
+      <c r="AW21">
+        <v>1.03</v>
+      </c>
+      <c r="AX21">
+        <v>1.03</v>
+      </c>
+      <c r="AY21">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21">
+        <v>1.03</v>
+      </c>
+      <c r="BA21">
+        <v>1.03</v>
+      </c>
+      <c r="BB21">
+        <v>1.03</v>
+      </c>
+      <c r="BC21">
+        <v>1.03</v>
+      </c>
+      <c r="BD21">
+        <v>1.03</v>
+      </c>
+      <c r="BE21">
+        <v>1.03</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.04</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.04</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.04</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.04</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.04</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.04</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.04</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.04</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.04</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.04</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22">
+        <v>2.44</v>
+      </c>
+      <c r="G22">
+        <v>2.64</v>
+      </c>
+      <c r="H22">
+        <v>3.2</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>2.8</v>
+      </c>
+      <c r="K22">
+        <v>3.4</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.1</v>
+      </c>
+      <c r="N22">
+        <v>2.54</v>
+      </c>
+      <c r="O22">
+        <v>1.44</v>
+      </c>
+      <c r="P22">
+        <v>1.56</v>
+      </c>
+      <c r="Q22">
+        <v>2.32</v>
+      </c>
+      <c r="R22">
+        <v>1.24</v>
+      </c>
+      <c r="S22">
+        <v>4.5</v>
+      </c>
+      <c r="T22">
+        <v>1.11</v>
+      </c>
+      <c r="U22">
+        <v>1.11</v>
+      </c>
+      <c r="V22">
+        <v>1.33</v>
+      </c>
+      <c r="W22">
+        <v>1.6</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22">
+        <v>1.01</v>
+      </c>
+      <c r="AR22">
+        <v>1.01</v>
+      </c>
+      <c r="AS22">
+        <v>1.01</v>
+      </c>
+      <c r="AT22">
+        <v>1.01</v>
+      </c>
+      <c r="AU22">
+        <v>1.01</v>
+      </c>
+      <c r="AV22">
+        <v>1.01</v>
+      </c>
+      <c r="AW22">
+        <v>1.01</v>
+      </c>
+      <c r="AX22">
+        <v>1.01</v>
+      </c>
+      <c r="AY22">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22">
+        <v>1.01</v>
+      </c>
+      <c r="BA22">
+        <v>1.01</v>
+      </c>
+      <c r="BB22">
+        <v>1.01</v>
+      </c>
+      <c r="BC22">
+        <v>1.01</v>
+      </c>
+      <c r="BD22">
+        <v>1.01</v>
+      </c>
+      <c r="BE22">
+        <v>1.01</v>
+      </c>
+      <c r="BF22">
+        <v>1.01</v>
+      </c>
+      <c r="BG22">
+        <v>1.01</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.04</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.04</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.04</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.04</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.04</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.04</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.04</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.04</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.04</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.04</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23">
+        <v>1.61</v>
+      </c>
+      <c r="G23">
+        <v>1.68</v>
+      </c>
+      <c r="H23">
+        <v>5.7</v>
+      </c>
+      <c r="I23">
+        <v>7.8</v>
+      </c>
+      <c r="J23">
+        <v>3.95</v>
+      </c>
+      <c r="K23">
+        <v>4.7</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.06</v>
+      </c>
+      <c r="N23">
+        <v>3.4</v>
+      </c>
+      <c r="O23">
+        <v>1.31</v>
+      </c>
+      <c r="P23">
+        <v>1.93</v>
+      </c>
+      <c r="Q23">
+        <v>1.86</v>
+      </c>
+      <c r="R23">
+        <v>1.36</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
+      </c>
+      <c r="T23">
+        <v>1.93</v>
+      </c>
+      <c r="U23">
+        <v>1.87</v>
+      </c>
+      <c r="V23">
+        <v>1.14</v>
+      </c>
+      <c r="W23">
+        <v>2.46</v>
+      </c>
+      <c r="X23">
+        <v>16.5</v>
+      </c>
+      <c r="Y23">
+        <v>22</v>
+      </c>
+      <c r="Z23">
+        <v>60</v>
+      </c>
+      <c r="AA23">
+        <v>220</v>
+      </c>
+      <c r="AB23">
+        <v>8.4</v>
+      </c>
+      <c r="AC23">
+        <v>10</v>
+      </c>
+      <c r="AD23">
+        <v>27</v>
+      </c>
+      <c r="AE23">
+        <v>110</v>
+      </c>
+      <c r="AF23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG23">
+        <v>10.5</v>
+      </c>
+      <c r="AH23">
+        <v>24</v>
+      </c>
+      <c r="AI23">
+        <v>200</v>
+      </c>
+      <c r="AJ23">
+        <v>15.5</v>
+      </c>
+      <c r="AK23">
+        <v>17.5</v>
+      </c>
+      <c r="AL23">
+        <v>60</v>
+      </c>
+      <c r="AM23">
+        <v>290</v>
+      </c>
+      <c r="AN23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO23">
+        <v>150</v>
+      </c>
+      <c r="AP23">
+        <v>10</v>
+      </c>
+      <c r="AQ23">
+        <v>18.5</v>
+      </c>
+      <c r="AR23">
+        <v>38</v>
+      </c>
+      <c r="AS23">
+        <v>10</v>
+      </c>
+      <c r="AT23">
+        <v>7</v>
+      </c>
+      <c r="AU23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV23">
+        <v>18</v>
+      </c>
+      <c r="AW23">
+        <v>10.5</v>
+      </c>
+      <c r="AX23">
+        <v>7.8</v>
+      </c>
+      <c r="AY23">
+        <v>9</v>
+      </c>
+      <c r="AZ23">
+        <v>7.8</v>
+      </c>
+      <c r="BA23">
+        <v>10.5</v>
+      </c>
+      <c r="BB23">
+        <v>13</v>
+      </c>
+      <c r="BC23">
+        <v>7</v>
+      </c>
+      <c r="BD23">
+        <v>26</v>
+      </c>
+      <c r="BE23">
+        <v>10</v>
+      </c>
+      <c r="BF23">
+        <v>5.4</v>
+      </c>
+      <c r="BG23">
+        <v>10.5</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.04</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.04</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.04</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.04</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.04</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.04</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.04</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24">
+        <v>1.47</v>
+      </c>
+      <c r="G24">
+        <v>1.63</v>
+      </c>
+      <c r="H24">
+        <v>6.8</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>3.9</v>
+      </c>
+      <c r="K24">
+        <v>5.6</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>3.1</v>
+      </c>
+      <c r="O24">
+        <v>1.02</v>
+      </c>
+      <c r="P24">
+        <v>1.71</v>
+      </c>
+      <c r="Q24">
+        <v>2.08</v>
+      </c>
+      <c r="R24">
+        <v>1.26</v>
+      </c>
+      <c r="S24">
+        <v>3.7</v>
+      </c>
+      <c r="T24">
+        <v>1.11</v>
+      </c>
+      <c r="U24">
+        <v>1.65</v>
+      </c>
+      <c r="V24">
+        <v>1.11</v>
+      </c>
+      <c r="W24">
+        <v>2.58</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>1000</v>
+      </c>
+      <c r="AC24">
+        <v>1000</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>1000</v>
+      </c>
+      <c r="AG24">
+        <v>1000</v>
+      </c>
+      <c r="AH24">
+        <v>1000</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>1000</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>1000</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24">
+        <v>1.01</v>
+      </c>
+      <c r="AR24">
+        <v>1.01</v>
+      </c>
+      <c r="AS24">
+        <v>1.01</v>
+      </c>
+      <c r="AT24">
+        <v>1.01</v>
+      </c>
+      <c r="AU24">
+        <v>1.01</v>
+      </c>
+      <c r="AV24">
+        <v>1.01</v>
+      </c>
+      <c r="AW24">
+        <v>1.01</v>
+      </c>
+      <c r="AX24">
+        <v>1.01</v>
+      </c>
+      <c r="AY24">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24">
+        <v>1.01</v>
+      </c>
+      <c r="BA24">
+        <v>1.01</v>
+      </c>
+      <c r="BB24">
+        <v>1.01</v>
+      </c>
+      <c r="BC24">
+        <v>1.01</v>
+      </c>
+      <c r="BD24">
+        <v>1.01</v>
+      </c>
+      <c r="BE24">
+        <v>1.01</v>
+      </c>
+      <c r="BF24">
+        <v>1.01</v>
+      </c>
+      <c r="BG24">
+        <v>1.01</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.04</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.04</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.04</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.04</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.04</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.04</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.04</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.04</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="157">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>US United Soccer League</t>
   </si>
   <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
     <t>Qatari Stars League</t>
   </si>
   <si>
@@ -307,6 +310,9 @@
     <t>02:30:00</t>
   </si>
   <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
     <t>14:15:00</t>
   </si>
   <si>
@@ -370,6 +376,9 @@
     <t>Portland Timbers</t>
   </si>
   <si>
+    <t>FC Van Yerevan</t>
+  </si>
+  <si>
     <t>Al-Wakra</t>
   </si>
   <si>
@@ -439,6 +448,9 @@
     <t>San Diego FC</t>
   </si>
   <si>
+    <t>FC Syunik</t>
+  </si>
+  <si>
     <t>Qatar SC</t>
   </si>
   <si>
@@ -472,7 +484,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 00:05:49</t>
+    <t>2026-08-19 02:15:14</t>
   </si>
 </sst>
 </file>
@@ -804,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1054,31 +1066,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G2">
         <v>3.8</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I2">
         <v>2.04</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -1087,55 +1099,55 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>6</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q2">
+        <v>1.57</v>
+      </c>
+      <c r="R2">
+        <v>1.66</v>
+      </c>
+      <c r="S2">
+        <v>2.44</v>
+      </c>
+      <c r="T2">
         <v>1.56</v>
       </c>
-      <c r="R2">
-        <v>1.68</v>
-      </c>
-      <c r="S2">
-        <v>2.4</v>
-      </c>
-      <c r="T2">
-        <v>1.54</v>
-      </c>
       <c r="U2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.96</v>
       </c>
       <c r="W2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
         <v>26</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>16</v>
       </c>
       <c r="AA2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB2">
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
         <v>11</v>
@@ -1165,10 +1177,10 @@
         <v>38</v>
       </c>
       <c r="AM2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>9</v>
@@ -1189,7 +1201,7 @@
         <v>19</v>
       </c>
       <c r="AU2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1225,70 +1237,70 @@
         <v>21</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>5.1</v>
       </c>
       <c r="BI2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK2">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BL2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM2">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BN2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BU2">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV2">
+        <v>13.5</v>
+      </c>
+      <c r="BW2">
+        <v>5.3</v>
+      </c>
+      <c r="BX2">
+        <v>22</v>
+      </c>
+      <c r="BY2">
+        <v>6.2</v>
+      </c>
+      <c r="BZ2">
         <v>15</v>
       </c>
-      <c r="BW2">
-        <v>4.2</v>
-      </c>
-      <c r="BX2">
-        <v>24</v>
-      </c>
-      <c r="BY2">
-        <v>4.7</v>
-      </c>
-      <c r="BZ2">
-        <v>16.5</v>
-      </c>
       <c r="CA2">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1296,52 +1308,52 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
         <v>3.2</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
         <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>1.19</v>
@@ -1359,13 +1371,13 @@
         <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z3">
         <v>22</v>
@@ -1374,7 +1386,7 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AC3">
         <v>8</v>
@@ -1386,19 +1398,19 @@
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK3">
         <v>50</v>
@@ -1422,10 +1434,10 @@
         <v>7.8</v>
       </c>
       <c r="AR3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1437,100 +1449,100 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX3">
-        <v>13.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BA3">
+        <v>5.8</v>
+      </c>
+      <c r="BB3">
+        <v>5.6</v>
+      </c>
+      <c r="BC3">
+        <v>5.6</v>
+      </c>
+      <c r="BD3">
+        <v>5.7</v>
+      </c>
+      <c r="BE3">
         <v>6</v>
       </c>
-      <c r="BB3">
-        <v>5.9</v>
-      </c>
-      <c r="BC3">
+      <c r="BF3">
+        <v>5.6</v>
+      </c>
+      <c r="BG3">
         <v>5.8</v>
-      </c>
-      <c r="BD3">
-        <v>6</v>
-      </c>
-      <c r="BE3">
-        <v>6.4</v>
-      </c>
-      <c r="BF3">
-        <v>5.9</v>
-      </c>
-      <c r="BG3">
-        <v>6</v>
       </c>
       <c r="BH3">
         <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT3">
         <v>5.9</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1538,22 +1550,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F4">
         <v>1.66</v>
       </c>
       <c r="G4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H4">
         <v>6.2</v>
@@ -1568,49 +1580,49 @@
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
+        <v>3.75</v>
+      </c>
+      <c r="O4">
+        <v>1.33</v>
+      </c>
+      <c r="P4">
+        <v>1.89</v>
+      </c>
+      <c r="Q4">
+        <v>2.04</v>
+      </c>
+      <c r="R4">
+        <v>1.34</v>
+      </c>
+      <c r="S4">
         <v>3.7</v>
-      </c>
-      <c r="O4">
-        <v>1.32</v>
-      </c>
-      <c r="P4">
-        <v>1.87</v>
-      </c>
-      <c r="Q4">
-        <v>2.02</v>
-      </c>
-      <c r="R4">
-        <v>1.35</v>
-      </c>
-      <c r="S4">
-        <v>3.5</v>
       </c>
       <c r="T4">
         <v>2</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
         <v>19</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA4">
         <v>190</v>
@@ -1619,10 +1631,10 @@
         <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -1655,7 +1667,7 @@
         <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP4">
         <v>12</v>
@@ -1667,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
@@ -1679,7 +1691,7 @@
         <v>21</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>80</v>
       </c>
       <c r="AX4">
         <v>8.199999999999999</v>
@@ -1691,25 +1703,25 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="BB4">
         <v>14</v>
       </c>
       <c r="BC4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1721,13 +1733,13 @@
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
@@ -1739,25 +1751,25 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1769,10 +1781,10 @@
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1780,16 +1792,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F5">
         <v>1.82</v>
@@ -1798,13 +1810,13 @@
         <v>1.86</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
         <v>4.7</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -1816,28 +1828,28 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="T5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
         <v>1.27</v>
@@ -1846,16 +1858,16 @@
         <v>2.16</v>
       </c>
       <c r="X5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z5">
         <v>38</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB5">
         <v>11</v>
@@ -1867,52 +1879,52 @@
         <v>18.5</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5">
         <v>23</v>
       </c>
       <c r="AK5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
         <v>17</v>
       </c>
       <c r="AR5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AS5">
         <v>38</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU5">
         <v>8.4</v>
@@ -1921,19 +1933,19 @@
         <v>15</v>
       </c>
       <c r="AW5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX5">
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB5">
         <v>19</v>
@@ -1945,31 +1957,31 @@
         <v>19.5</v>
       </c>
       <c r="BE5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BH5">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -1981,40 +1993,40 @@
         <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BR5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BS5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT5">
         <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BV5">
         <v>36</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ5">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2022,31 +2034,31 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F6">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="G6">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="H6">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I6">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
         <v>3.8</v>
@@ -2055,145 +2067,145 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Q6">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="T6">
-        <v>1.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2256,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2264,19 +2276,19 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G7">
         <v>2.02</v>
@@ -2297,31 +2309,31 @@
         <v>1.28</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O7">
         <v>1.18</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R7">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="S7">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
         <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V7">
         <v>1.32</v>
@@ -2330,7 +2342,7 @@
         <v>1.98</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y7">
         <v>23</v>
@@ -2345,19 +2357,19 @@
         <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>14.5</v>
@@ -2375,16 +2387,16 @@
         <v>26</v>
       </c>
       <c r="AM7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ7">
         <v>20</v>
@@ -2393,10 +2405,10 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU7">
         <v>8.800000000000001</v>
@@ -2417,7 +2429,7 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB7">
         <v>22</v>
@@ -2432,22 +2444,22 @@
         <v>44</v>
       </c>
       <c r="BF7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BH7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2462,16 +2474,16 @@
         <v>4.6</v>
       </c>
       <c r="BP7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT7">
         <v>7.6</v>
@@ -2489,16 +2501,16 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2506,34 +2518,34 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F8">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G8">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H8">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I8">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2542,7 +2554,7 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O8">
         <v>1.25</v>
@@ -2551,25 +2563,25 @@
         <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8">
         <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
         <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W8">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X8">
         <v>19</v>
@@ -2578,10 +2590,10 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA8">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AB8">
         <v>14.5</v>
@@ -2593,7 +2605,7 @@
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF8">
         <v>22</v>
@@ -2623,7 +2635,7 @@
         <v>22</v>
       </c>
       <c r="AO8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
@@ -2635,7 +2647,7 @@
         <v>16.5</v>
       </c>
       <c r="AS8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT8">
         <v>13</v>
@@ -2650,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="AX8">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2665,16 +2677,16 @@
         <v>40</v>
       </c>
       <c r="BC8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD8">
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BF8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG8">
         <v>14.5</v>
@@ -2689,58 +2701,58 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT8">
         <v>5.9</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV8">
         <v>18.5</v>
       </c>
       <c r="BW8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
         <v>29</v>
       </c>
       <c r="BY8">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2748,31 +2760,31 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F9">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -2784,40 +2796,40 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z9">
         <v>40</v>
@@ -2829,10 +2841,10 @@
         <v>12</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2841,28 +2853,28 @@
         <v>13</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM9">
         <v>75</v>
       </c>
       <c r="AN9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO9">
         <v>44</v>
@@ -2871,7 +2883,7 @@
         <v>20</v>
       </c>
       <c r="AQ9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR9">
         <v>36</v>
@@ -2880,16 +2892,16 @@
         <v>40</v>
       </c>
       <c r="AT9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW9">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2904,85 +2916,85 @@
         <v>44</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC9">
         <v>15</v>
       </c>
       <c r="BD9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BH9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BR9">
         <v>22</v>
       </c>
       <c r="BS9">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
         <v>34</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2990,76 +3002,76 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G10">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="H10">
         <v>2.64</v>
       </c>
       <c r="I10">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
         <v>1.29</v>
       </c>
       <c r="P10">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="Q10">
         <v>1.88</v>
       </c>
       <c r="R10">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U10">
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X10">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z10">
         <v>22</v>
@@ -3068,10 +3080,10 @@
         <v>46</v>
       </c>
       <c r="AB10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC10">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
         <v>14.5</v>
@@ -3104,13 +3116,13 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO10">
         <v>24</v>
       </c>
       <c r="AP10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
@@ -3122,7 +3134,7 @@
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU10">
         <v>6.4</v>
@@ -3164,58 +3176,58 @@
         <v>17</v>
       </c>
       <c r="BH10">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3224,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3232,94 +3244,94 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F11">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G11">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H11">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K11">
         <v>5</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q11">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="T11">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X11">
+        <v>24</v>
+      </c>
+      <c r="Y11">
         <v>27</v>
       </c>
-      <c r="Y11">
-        <v>29</v>
-      </c>
       <c r="Z11">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF11">
         <v>11</v>
@@ -3331,103 +3343,103 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL11">
         <v>32</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AS11">
         <v>44</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AU11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB11">
         <v>13</v>
       </c>
       <c r="BC11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE11">
         <v>36</v>
       </c>
       <c r="BF11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO11">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP11">
         <v>9.800000000000001</v>
@@ -3436,37 +3448,37 @@
         <v>4.9</v>
       </c>
       <c r="BR11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA11">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3474,16 +3486,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F12">
         <v>2.3</v>
@@ -3492,13 +3504,13 @@
         <v>2.34</v>
       </c>
       <c r="H12">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I12">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
         <v>4.4</v>
@@ -3510,13 +3522,13 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <v>1.48</v>
@@ -3534,10 +3546,10 @@
         <v>2.98</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X12">
         <v>32</v>
@@ -3546,34 +3558,34 @@
         <v>22</v>
       </c>
       <c r="Z12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA12">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AB12">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
         <v>14</v>
       </c>
       <c r="AE12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG12">
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ12">
         <v>32</v>
@@ -3585,10 +3597,10 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO12">
         <v>15</v>
@@ -3603,7 +3615,7 @@
         <v>24</v>
       </c>
       <c r="AS12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT12">
         <v>16</v>
@@ -3621,13 +3633,13 @@
         <v>17.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
         <v>13</v>
       </c>
       <c r="BA12">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BB12">
         <v>27</v>
@@ -3651,7 +3663,7 @@
         <v>5.1</v>
       </c>
       <c r="BI12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
@@ -3660,10 +3672,10 @@
         <v>6.2</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN12">
         <v>6.2</v>
@@ -3672,7 +3684,7 @@
         <v>5.3</v>
       </c>
       <c r="BP12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ12">
         <v>6.6</v>
@@ -3681,34 +3693,34 @@
         <v>22</v>
       </c>
       <c r="BS12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
         <v>6.8</v>
       </c>
       <c r="BU12">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV12">
         <v>19</v>
       </c>
       <c r="BW12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX12">
         <v>24</v>
       </c>
       <c r="BY12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA12">
         <v>9.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3716,19 +3728,19 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G13">
         <v>2.2</v>
@@ -3752,25 +3764,25 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
+        <v>1.4</v>
+      </c>
+      <c r="R13">
+        <v>1.96</v>
+      </c>
+      <c r="S13">
+        <v>2</v>
+      </c>
+      <c r="T13">
         <v>1.42</v>
-      </c>
-      <c r="R13">
-        <v>1.9</v>
-      </c>
-      <c r="S13">
-        <v>2.04</v>
-      </c>
-      <c r="T13">
-        <v>1.43</v>
       </c>
       <c r="U13">
         <v>3.1</v>
@@ -3794,7 +3806,7 @@
         <v>350</v>
       </c>
       <c r="AB13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC13">
         <v>11.5</v>
@@ -3803,7 +3815,7 @@
         <v>15.5</v>
       </c>
       <c r="AE13">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF13">
         <v>21</v>
@@ -3815,7 +3827,7 @@
         <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ13">
         <v>32</v>
@@ -3827,16 +3839,16 @@
         <v>23</v>
       </c>
       <c r="AM13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN13">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AQ13">
         <v>21</v>
@@ -3845,7 +3857,7 @@
         <v>19.5</v>
       </c>
       <c r="AS13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT13">
         <v>17</v>
@@ -3857,7 +3869,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AX13">
         <v>17.5</v>
@@ -3869,7 +3881,7 @@
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BB13">
         <v>19.5</v>
@@ -3881,10 +3893,10 @@
         <v>18.5</v>
       </c>
       <c r="BE13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BF13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG13">
         <v>13</v>
@@ -3893,7 +3905,7 @@
         <v>6.2</v>
       </c>
       <c r="BI13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
@@ -3902,10 +3914,10 @@
         <v>5.4</v>
       </c>
       <c r="BL13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BM13">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BN13">
         <v>6.2</v>
@@ -3917,13 +3929,13 @@
         <v>14</v>
       </c>
       <c r="BQ13">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BR13">
         <v>19.5</v>
       </c>
       <c r="BS13">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BT13">
         <v>7.6</v>
@@ -3935,22 +3947,22 @@
         <v>21</v>
       </c>
       <c r="BW13">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CA13">
         <v>7.2</v>
       </c>
       <c r="CB13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3958,241 +3970,241 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F14">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G14">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="H14">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="I14">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="R14">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="X14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Y14">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF14">
         <v>21</v>
       </c>
       <c r="AG14">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>55</v>
+      </c>
+      <c r="AJ14">
+        <v>44</v>
+      </c>
+      <c r="AK14">
+        <v>34</v>
+      </c>
+      <c r="AL14">
+        <v>46</v>
+      </c>
+      <c r="AM14">
+        <v>100</v>
+      </c>
+      <c r="AN14">
+        <v>25</v>
+      </c>
+      <c r="AO14">
+        <v>36</v>
+      </c>
+      <c r="AP14">
+        <v>3.75</v>
+      </c>
+      <c r="AQ14">
+        <v>3.6</v>
+      </c>
+      <c r="AR14">
+        <v>3.95</v>
+      </c>
+      <c r="AS14">
+        <v>4.3</v>
+      </c>
+      <c r="AT14">
+        <v>3.5</v>
+      </c>
+      <c r="AU14">
+        <v>3.15</v>
+      </c>
+      <c r="AV14">
+        <v>3.5</v>
+      </c>
+      <c r="AW14">
+        <v>4.2</v>
+      </c>
+      <c r="AX14">
+        <v>3.85</v>
+      </c>
+      <c r="AY14">
+        <v>3.4</v>
+      </c>
+      <c r="AZ14">
+        <v>3.8</v>
+      </c>
+      <c r="BA14">
+        <v>4.3</v>
+      </c>
+      <c r="BB14">
+        <v>4.2</v>
+      </c>
+      <c r="BC14">
+        <v>4.1</v>
+      </c>
+      <c r="BD14">
+        <v>4.2</v>
+      </c>
+      <c r="BE14">
+        <v>4.5</v>
+      </c>
+      <c r="BF14">
+        <v>3.95</v>
+      </c>
+      <c r="BG14">
+        <v>4.1</v>
+      </c>
+      <c r="BH14">
+        <v>3.65</v>
+      </c>
+      <c r="BI14">
+        <v>2.82</v>
+      </c>
+      <c r="BJ14">
+        <v>9.6</v>
+      </c>
+      <c r="BK14">
+        <v>1.04</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.04</v>
+      </c>
+      <c r="BN14">
+        <v>5.8</v>
+      </c>
+      <c r="BO14">
+        <v>1.04</v>
+      </c>
+      <c r="BP14">
         <v>19</v>
       </c>
-      <c r="AI14">
-        <v>46</v>
-      </c>
-      <c r="AJ14">
-        <v>36</v>
-      </c>
-      <c r="AK14">
-        <v>27</v>
-      </c>
-      <c r="AL14">
-        <v>38</v>
-      </c>
-      <c r="AM14">
-        <v>80</v>
-      </c>
-      <c r="AN14">
-        <v>16.5</v>
-      </c>
-      <c r="AO14">
-        <v>29</v>
-      </c>
-      <c r="AP14">
-        <v>15</v>
-      </c>
-      <c r="AQ14">
-        <v>11.5</v>
-      </c>
-      <c r="AR14">
-        <v>18</v>
-      </c>
-      <c r="AS14">
-        <v>4</v>
-      </c>
-      <c r="AT14">
-        <v>9.6</v>
-      </c>
-      <c r="AU14">
-        <v>6.8</v>
-      </c>
-      <c r="AV14">
-        <v>10</v>
-      </c>
-      <c r="AW14">
-        <v>3.9</v>
-      </c>
-      <c r="AX14">
-        <v>12</v>
-      </c>
-      <c r="AY14">
-        <v>8.4</v>
-      </c>
-      <c r="AZ14">
-        <v>11</v>
-      </c>
-      <c r="BA14">
-        <v>3.95</v>
-      </c>
-      <c r="BB14">
-        <v>21</v>
-      </c>
-      <c r="BC14">
-        <v>16</v>
-      </c>
-      <c r="BD14">
-        <v>3.9</v>
-      </c>
-      <c r="BE14">
-        <v>4.1</v>
-      </c>
-      <c r="BF14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG14">
-        <v>17</v>
-      </c>
-      <c r="BH14">
-        <v>4.2</v>
-      </c>
-      <c r="BI14">
-        <v>3.15</v>
-      </c>
-      <c r="BJ14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK14">
-        <v>4.7</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN14">
-        <v>5.7</v>
-      </c>
-      <c r="BO14">
-        <v>4.2</v>
-      </c>
-      <c r="BP14">
-        <v>16.5</v>
-      </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU14">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>24</v>
       </c>
       <c r="BW14">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="CA14">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4200,241 +4212,241 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F15">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="H15">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
+        <v>4.3</v>
+      </c>
+      <c r="L15">
+        <v>1.31</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
         <v>4.6</v>
       </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.4</v>
-      </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S15">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4442,241 +4454,241 @@
         <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F16">
-        <v>12.5</v>
+        <v>2.44</v>
       </c>
       <c r="G16">
+        <v>2.7</v>
+      </c>
+      <c r="H16">
+        <v>2.7</v>
+      </c>
+      <c r="I16">
+        <v>3.05</v>
+      </c>
+      <c r="J16">
+        <v>3.65</v>
+      </c>
+      <c r="K16">
+        <v>4.2</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>4.8</v>
+      </c>
+      <c r="O16">
+        <v>1.21</v>
+      </c>
+      <c r="P16">
+        <v>2.26</v>
+      </c>
+      <c r="Q16">
+        <v>1.64</v>
+      </c>
+      <c r="R16">
+        <v>1.5</v>
+      </c>
+      <c r="S16">
+        <v>2.58</v>
+      </c>
+      <c r="T16">
+        <v>1.56</v>
+      </c>
+      <c r="U16">
+        <v>2.4</v>
+      </c>
+      <c r="V16">
+        <v>1.5</v>
+      </c>
+      <c r="W16">
+        <v>1.58</v>
+      </c>
+      <c r="X16">
+        <v>24</v>
+      </c>
+      <c r="Y16">
         <v>16</v>
       </c>
-      <c r="H16">
-        <v>1.23</v>
-      </c>
-      <c r="I16">
-        <v>1.29</v>
-      </c>
-      <c r="J16">
-        <v>6.6</v>
-      </c>
-      <c r="K16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>6.2</v>
-      </c>
-      <c r="O16">
-        <v>1.16</v>
-      </c>
-      <c r="P16">
-        <v>2.74</v>
-      </c>
-      <c r="Q16">
-        <v>1.47</v>
-      </c>
-      <c r="R16">
-        <v>1.7</v>
-      </c>
-      <c r="S16">
-        <v>2.18</v>
-      </c>
-      <c r="T16">
-        <v>2</v>
-      </c>
-      <c r="U16">
-        <v>1.83</v>
-      </c>
-      <c r="V16">
-        <v>4.4</v>
-      </c>
-      <c r="W16">
-        <v>1.06</v>
-      </c>
-      <c r="X16">
-        <v>34</v>
-      </c>
-      <c r="Y16">
-        <v>13.5</v>
-      </c>
       <c r="Z16">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AB16">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AC16">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="AD16">
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AF16">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="AG16">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="AH16">
+        <v>17.5</v>
+      </c>
+      <c r="AI16">
         <v>36</v>
       </c>
-      <c r="AI16">
-        <v>44</v>
-      </c>
       <c r="AJ16">
-        <v>560</v>
+        <v>38</v>
       </c>
       <c r="AK16">
-        <v>230</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="AM16">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="AN16">
-        <v>270</v>
+        <v>16.5</v>
       </c>
       <c r="AO16">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AP16">
+        <v>15.5</v>
+      </c>
+      <c r="AQ16">
+        <v>12.5</v>
+      </c>
+      <c r="AR16">
+        <v>16</v>
+      </c>
+      <c r="AS16">
+        <v>32</v>
+      </c>
+      <c r="AT16">
+        <v>10.5</v>
+      </c>
+      <c r="AU16">
+        <v>7.2</v>
+      </c>
+      <c r="AV16">
+        <v>11</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>16</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>11.5</v>
+      </c>
+      <c r="BA16">
         <v>6.4</v>
       </c>
-      <c r="AQ16">
-        <v>10</v>
-      </c>
-      <c r="AR16">
-        <v>7.4</v>
-      </c>
-      <c r="AS16">
-        <v>8.4</v>
-      </c>
-      <c r="AT16">
-        <v>7</v>
-      </c>
-      <c r="AU16">
-        <v>14</v>
-      </c>
-      <c r="AV16">
-        <v>10</v>
-      </c>
-      <c r="AW16">
-        <v>11</v>
-      </c>
-      <c r="AX16">
-        <v>7.6</v>
-      </c>
-      <c r="AY16">
-        <v>7</v>
-      </c>
-      <c r="AZ16">
+      <c r="BB16">
         <v>6.6</v>
       </c>
-      <c r="BA16">
-        <v>6.8</v>
-      </c>
-      <c r="BB16">
-        <v>8</v>
-      </c>
       <c r="BC16">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE16">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BG16">
-        <v>3.15</v>
+        <v>16</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4684,241 +4696,241 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F17">
-        <v>2.48</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>2.54</v>
+        <v>16.5</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="I17">
-        <v>3.15</v>
+        <v>1.28</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="K17">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="O17">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="P17">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="R17">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="S17">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="T17">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="U17">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="V17">
-        <v>1.46</v>
+        <v>4.5</v>
       </c>
       <c r="W17">
-        <v>1.64</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="Y17">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z17">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17">
-        <v>55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB17">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="AC17">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AD17">
         <v>14</v>
       </c>
       <c r="AE17">
+        <v>14</v>
+      </c>
+      <c r="AF17">
+        <v>150</v>
+      </c>
+      <c r="AG17">
+        <v>60</v>
+      </c>
+      <c r="AH17">
         <v>36</v>
       </c>
-      <c r="AF17">
+      <c r="AI17">
+        <v>44</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>230</v>
+      </c>
+      <c r="AL17">
+        <v>170</v>
+      </c>
+      <c r="AM17">
+        <v>180</v>
+      </c>
+      <c r="AN17">
+        <v>270</v>
+      </c>
+      <c r="AO17">
+        <v>3.85</v>
+      </c>
+      <c r="AP17">
+        <v>7</v>
+      </c>
+      <c r="AQ17">
+        <v>10</v>
+      </c>
+      <c r="AR17">
+        <v>7.4</v>
+      </c>
+      <c r="AS17">
+        <v>8.4</v>
+      </c>
+      <c r="AT17">
+        <v>7.6</v>
+      </c>
+      <c r="AU17">
+        <v>14</v>
+      </c>
+      <c r="AV17">
+        <v>10</v>
+      </c>
+      <c r="AW17">
+        <v>11</v>
+      </c>
+      <c r="AX17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY17">
+        <v>7.6</v>
+      </c>
+      <c r="AZ17">
+        <v>7</v>
+      </c>
+      <c r="BA17">
+        <v>7.2</v>
+      </c>
+      <c r="BB17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC17">
+        <v>8.4</v>
+      </c>
+      <c r="BD17">
+        <v>8.4</v>
+      </c>
+      <c r="BE17">
+        <v>8.4</v>
+      </c>
+      <c r="BF17">
+        <v>8.4</v>
+      </c>
+      <c r="BG17">
+        <v>3.4</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>2.12</v>
+      </c>
+      <c r="BJ17">
         <v>17</v>
       </c>
-      <c r="AG17">
-        <v>12.5</v>
-      </c>
-      <c r="AH17">
-        <v>18</v>
-      </c>
-      <c r="AI17">
-        <v>55</v>
-      </c>
-      <c r="AJ17">
-        <v>40</v>
-      </c>
-      <c r="AK17">
+      <c r="BK17">
+        <v>1.89</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>2.12</v>
+      </c>
+      <c r="BN17">
+        <v>20</v>
+      </c>
+      <c r="BO17">
+        <v>1.93</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>2.12</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>2.08</v>
+      </c>
+      <c r="BT17">
+        <v>5.1</v>
+      </c>
+      <c r="BU17">
+        <v>2.84</v>
+      </c>
+      <c r="BV17">
+        <v>9.6</v>
+      </c>
+      <c r="BW17">
+        <v>4.7</v>
+      </c>
+      <c r="BX17">
         <v>30</v>
       </c>
-      <c r="AL17">
-        <v>42</v>
-      </c>
-      <c r="AM17">
-        <v>110</v>
-      </c>
-      <c r="AN17">
-        <v>25</v>
-      </c>
-      <c r="AO17">
-        <v>32</v>
-      </c>
-      <c r="AP17">
-        <v>11</v>
-      </c>
-      <c r="AQ17">
-        <v>11</v>
-      </c>
-      <c r="AR17">
-        <v>18</v>
-      </c>
-      <c r="AS17">
-        <v>40</v>
-      </c>
-      <c r="AT17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU17">
-        <v>7</v>
-      </c>
-      <c r="AV17">
-        <v>12</v>
-      </c>
-      <c r="AW17">
-        <v>30</v>
-      </c>
-      <c r="AX17">
-        <v>14.5</v>
-      </c>
-      <c r="AY17">
-        <v>10</v>
-      </c>
-      <c r="AZ17">
-        <v>15.5</v>
-      </c>
-      <c r="BA17">
-        <v>40</v>
-      </c>
-      <c r="BB17">
-        <v>32</v>
-      </c>
-      <c r="BC17">
-        <v>24</v>
-      </c>
-      <c r="BD17">
-        <v>34</v>
-      </c>
-      <c r="BE17">
-        <v>70</v>
-      </c>
-      <c r="BF17">
-        <v>20</v>
-      </c>
-      <c r="BG17">
-        <v>27</v>
-      </c>
-      <c r="BH17">
-        <v>3.75</v>
-      </c>
-      <c r="BI17">
-        <v>3</v>
-      </c>
-      <c r="BJ17">
-        <v>11</v>
-      </c>
-      <c r="BK17">
-        <v>3.8</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>5.6</v>
-      </c>
-      <c r="BN17">
-        <v>6.4</v>
-      </c>
-      <c r="BO17">
-        <v>4.4</v>
-      </c>
-      <c r="BP17">
-        <v>23</v>
-      </c>
-      <c r="BQ17">
-        <v>4.7</v>
-      </c>
-      <c r="BR17">
-        <v>38</v>
-      </c>
-      <c r="BS17">
-        <v>5.1</v>
-      </c>
-      <c r="BT17">
-        <v>6.8</v>
-      </c>
-      <c r="BU17">
-        <v>4.7</v>
-      </c>
-      <c r="BV17">
-        <v>27</v>
-      </c>
-      <c r="BW17">
-        <v>4.8</v>
-      </c>
-      <c r="BX17">
-        <v>40</v>
-      </c>
       <c r="BY17">
-        <v>5.1</v>
+        <v>1.99</v>
       </c>
       <c r="BZ17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="CA17">
-        <v>4.9</v>
+        <v>1.83</v>
       </c>
       <c r="CB17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4926,1026 +4938,1026 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F18">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="G18">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>3.15</v>
+      </c>
+      <c r="J18">
+        <v>3.55</v>
+      </c>
+      <c r="K18">
+        <v>3.65</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.07</v>
+      </c>
+      <c r="N18">
+        <v>3.55</v>
+      </c>
+      <c r="O18">
+        <v>1.32</v>
+      </c>
+      <c r="P18">
+        <v>1.88</v>
+      </c>
+      <c r="Q18">
+        <v>2</v>
+      </c>
+      <c r="R18">
+        <v>1.34</v>
+      </c>
+      <c r="S18">
+        <v>3.4</v>
+      </c>
+      <c r="T18">
+        <v>1.74</v>
+      </c>
+      <c r="U18">
+        <v>2.14</v>
+      </c>
+      <c r="V18">
+        <v>1.47</v>
+      </c>
+      <c r="W18">
+        <v>1.64</v>
+      </c>
+      <c r="X18">
+        <v>14.5</v>
+      </c>
+      <c r="Y18">
+        <v>12.5</v>
+      </c>
+      <c r="Z18">
+        <v>21</v>
+      </c>
+      <c r="AA18">
+        <v>55</v>
+      </c>
+      <c r="AB18">
+        <v>11</v>
+      </c>
+      <c r="AC18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD18">
+        <v>14</v>
+      </c>
+      <c r="AE18">
+        <v>36</v>
+      </c>
+      <c r="AF18">
+        <v>17</v>
+      </c>
+      <c r="AG18">
+        <v>14</v>
+      </c>
+      <c r="AH18">
+        <v>18</v>
+      </c>
+      <c r="AI18">
+        <v>55</v>
+      </c>
+      <c r="AJ18">
+        <v>40</v>
+      </c>
+      <c r="AK18">
+        <v>30</v>
+      </c>
+      <c r="AL18">
+        <v>42</v>
+      </c>
+      <c r="AM18">
+        <v>110</v>
+      </c>
+      <c r="AN18">
+        <v>25</v>
+      </c>
+      <c r="AO18">
+        <v>32</v>
+      </c>
+      <c r="AP18">
+        <v>11</v>
+      </c>
+      <c r="AQ18">
+        <v>11</v>
+      </c>
+      <c r="AR18">
+        <v>18</v>
+      </c>
+      <c r="AS18">
+        <v>40</v>
+      </c>
+      <c r="AT18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18">
+        <v>7</v>
+      </c>
+      <c r="AV18">
+        <v>12</v>
+      </c>
+      <c r="AW18">
+        <v>30</v>
+      </c>
+      <c r="AX18">
+        <v>14.5</v>
+      </c>
+      <c r="AY18">
+        <v>10</v>
+      </c>
+      <c r="AZ18">
+        <v>15.5</v>
+      </c>
+      <c r="BA18">
+        <v>40</v>
+      </c>
+      <c r="BB18">
+        <v>32</v>
+      </c>
+      <c r="BC18">
+        <v>24</v>
+      </c>
+      <c r="BD18">
+        <v>34</v>
+      </c>
+      <c r="BE18">
+        <v>70</v>
+      </c>
+      <c r="BF18">
+        <v>20</v>
+      </c>
+      <c r="BG18">
+        <v>27</v>
+      </c>
+      <c r="BH18">
+        <v>3.75</v>
+      </c>
+      <c r="BI18">
+        <v>3</v>
+      </c>
+      <c r="BJ18">
+        <v>11</v>
+      </c>
+      <c r="BK18">
         <v>3.8</v>
       </c>
-      <c r="I18">
-        <v>3.85</v>
-      </c>
-      <c r="J18">
-        <v>3.1</v>
-      </c>
-      <c r="K18">
-        <v>3.15</v>
-      </c>
-      <c r="L18">
-        <v>1.64</v>
-      </c>
-      <c r="M18">
-        <v>1.14</v>
-      </c>
-      <c r="N18">
-        <v>2.58</v>
-      </c>
-      <c r="O18">
-        <v>1.6</v>
-      </c>
-      <c r="P18">
-        <v>1.51</v>
-      </c>
-      <c r="Q18">
-        <v>2.86</v>
-      </c>
-      <c r="R18">
-        <v>1.18</v>
-      </c>
-      <c r="S18">
-        <v>6.2</v>
-      </c>
-      <c r="T18">
-        <v>2.26</v>
-      </c>
-      <c r="U18">
-        <v>1.74</v>
-      </c>
-      <c r="V18">
-        <v>1.35</v>
-      </c>
-      <c r="W18">
-        <v>1.71</v>
-      </c>
-      <c r="X18">
-        <v>8</v>
-      </c>
-      <c r="Y18">
-        <v>9.6</v>
-      </c>
-      <c r="Z18">
-        <v>24</v>
-      </c>
-      <c r="AA18">
-        <v>95</v>
-      </c>
-      <c r="AB18">
-        <v>7</v>
-      </c>
-      <c r="AC18">
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>5.6</v>
+      </c>
+      <c r="BN18">
+        <v>6.4</v>
+      </c>
+      <c r="BO18">
+        <v>4.4</v>
+      </c>
+      <c r="BP18">
+        <v>23</v>
+      </c>
+      <c r="BQ18">
+        <v>4.7</v>
+      </c>
+      <c r="BR18">
+        <v>38</v>
+      </c>
+      <c r="BS18">
+        <v>5.1</v>
+      </c>
+      <c r="BT18">
         <v>6.8</v>
       </c>
-      <c r="AD18">
-        <v>17</v>
-      </c>
-      <c r="AE18">
-        <v>70</v>
-      </c>
-      <c r="AF18">
-        <v>12.5</v>
-      </c>
-      <c r="AG18">
-        <v>12.5</v>
-      </c>
-      <c r="AH18">
-        <v>26</v>
-      </c>
-      <c r="AI18">
-        <v>100</v>
-      </c>
-      <c r="AJ18">
-        <v>34</v>
-      </c>
-      <c r="AK18">
-        <v>36</v>
-      </c>
-      <c r="AL18">
-        <v>70</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>38</v>
-      </c>
-      <c r="AO18">
-        <v>100</v>
-      </c>
-      <c r="AP18">
-        <v>7.6</v>
-      </c>
-      <c r="AQ18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR18">
-        <v>22</v>
-      </c>
-      <c r="AS18">
-        <v>55</v>
-      </c>
-      <c r="AT18">
-        <v>6.6</v>
-      </c>
-      <c r="AU18">
-        <v>6.6</v>
-      </c>
-      <c r="AV18">
-        <v>16</v>
-      </c>
-      <c r="AW18">
-        <v>55</v>
-      </c>
-      <c r="AX18">
-        <v>11.5</v>
-      </c>
-      <c r="AY18">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18">
-        <v>23</v>
-      </c>
-      <c r="BA18">
-        <v>80</v>
-      </c>
-      <c r="BB18">
-        <v>30</v>
-      </c>
-      <c r="BC18">
-        <v>30</v>
-      </c>
-      <c r="BD18">
-        <v>55</v>
-      </c>
-      <c r="BE18">
-        <v>95</v>
-      </c>
-      <c r="BF18">
+      <c r="BU18">
+        <v>4.7</v>
+      </c>
+      <c r="BV18">
+        <v>27</v>
+      </c>
+      <c r="BW18">
+        <v>4.8</v>
+      </c>
+      <c r="BX18">
+        <v>40</v>
+      </c>
+      <c r="BY18">
+        <v>5.1</v>
+      </c>
+      <c r="BZ18">
         <v>32</v>
       </c>
-      <c r="BG18">
-        <v>85</v>
-      </c>
-      <c r="BH18">
-        <v>2.6</v>
-      </c>
-      <c r="BI18">
-        <v>2.42</v>
-      </c>
-      <c r="BJ18">
-        <v>12</v>
-      </c>
-      <c r="BK18">
-        <v>6.6</v>
-      </c>
-      <c r="BL18">
-        <v>260</v>
-      </c>
-      <c r="BM18">
-        <v>14.5</v>
-      </c>
-      <c r="BN18">
+      <c r="CA18">
         <v>4.9</v>
       </c>
-      <c r="BO18">
-        <v>4.5</v>
-      </c>
-      <c r="BP18">
-        <v>21</v>
-      </c>
-      <c r="BQ18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR18">
-        <v>55</v>
-      </c>
-      <c r="BS18">
-        <v>12</v>
-      </c>
-      <c r="BT18">
-        <v>7</v>
-      </c>
-      <c r="BU18">
-        <v>6.2</v>
-      </c>
-      <c r="BV18">
-        <v>46</v>
-      </c>
-      <c r="BW18">
-        <v>11.5</v>
-      </c>
-      <c r="BX18">
-        <v>75</v>
-      </c>
-      <c r="BY18">
-        <v>12.5</v>
-      </c>
-      <c r="BZ18">
-        <v>60</v>
-      </c>
-      <c r="CA18">
-        <v>12</v>
-      </c>
       <c r="CB18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F19">
+        <v>2.36</v>
+      </c>
+      <c r="G19">
         <v>2.38</v>
       </c>
-      <c r="G19">
-        <v>2.9</v>
-      </c>
       <c r="H19">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="I19">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="J19">
+        <v>3.1</v>
+      </c>
+      <c r="K19">
         <v>3.15</v>
       </c>
-      <c r="K19">
-        <v>4.8</v>
-      </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N19">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O19">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="P19">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="Q19">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="R19">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM19">
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>75</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>60</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>80</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>95</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F20">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="G20">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="H20">
-        <v>7.2</v>
+        <v>2.78</v>
       </c>
       <c r="I20">
-        <v>8.6</v>
+        <v>3.25</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="P20">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="Q20">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="R20">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S20">
-        <v>3.95</v>
+        <v>2.86</v>
       </c>
       <c r="T20">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U20">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>2.52</v>
+        <v>1.56</v>
       </c>
       <c r="X20">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>1.66</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I21">
-        <v>990</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
+        <v>3.85</v>
+      </c>
+      <c r="K21">
+        <v>4.1</v>
+      </c>
+      <c r="L21">
+        <v>1.38</v>
+      </c>
+      <c r="M21">
         <v>1.08</v>
       </c>
-      <c r="K21">
-        <v>950</v>
-      </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
       <c r="N21">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q21">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="R21">
+        <v>1.27</v>
+      </c>
+      <c r="S21">
+        <v>3.95</v>
+      </c>
+      <c r="T21">
+        <v>2.16</v>
+      </c>
+      <c r="U21">
+        <v>1.71</v>
+      </c>
+      <c r="V21">
         <v>1.13</v>
       </c>
-      <c r="S21">
-        <v>1.55</v>
-      </c>
-      <c r="T21">
-        <v>1.11</v>
-      </c>
-      <c r="U21">
-        <v>1.11</v>
-      </c>
-      <c r="V21">
-        <v>1.02</v>
-      </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB21" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F22">
-        <v>2.44</v>
+        <v>1.06</v>
       </c>
       <c r="G22">
-        <v>2.64</v>
+        <v>990</v>
       </c>
       <c r="H22">
-        <v>3.2</v>
+        <v>1.06</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>990</v>
       </c>
       <c r="J22">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="K22">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="O22">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="R22">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="S22">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
         <v>1.11</v>
@@ -5954,10 +5966,10 @@
         <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="W22">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6128,491 +6140,733 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F23">
+        <v>2.44</v>
+      </c>
+      <c r="G23">
+        <v>2.7</v>
+      </c>
+      <c r="H23">
+        <v>3.2</v>
+      </c>
+      <c r="I23">
+        <v>3.65</v>
+      </c>
+      <c r="J23">
+        <v>2.8</v>
+      </c>
+      <c r="K23">
+        <v>3.65</v>
+      </c>
+      <c r="L23">
+        <v>1.44</v>
+      </c>
+      <c r="M23">
+        <v>1.1</v>
+      </c>
+      <c r="N23">
+        <v>2.9</v>
+      </c>
+      <c r="O23">
+        <v>1.43</v>
+      </c>
+      <c r="P23">
         <v>1.61</v>
       </c>
-      <c r="G23">
-        <v>1.68</v>
-      </c>
-      <c r="H23">
-        <v>5.7</v>
-      </c>
-      <c r="I23">
-        <v>7.8</v>
-      </c>
-      <c r="J23">
-        <v>3.95</v>
-      </c>
-      <c r="K23">
-        <v>4.7</v>
-      </c>
-      <c r="L23">
-        <v>1.01</v>
-      </c>
-      <c r="M23">
-        <v>1.06</v>
-      </c>
-      <c r="N23">
-        <v>3.4</v>
-      </c>
-      <c r="O23">
-        <v>1.31</v>
-      </c>
-      <c r="P23">
-        <v>1.93</v>
-      </c>
       <c r="Q23">
-        <v>1.86</v>
+        <v>2.34</v>
       </c>
       <c r="R23">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S23">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="T23">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="U23">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="V23">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>2.46</v>
+        <v>1.58</v>
       </c>
       <c r="X23">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Y23">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Z23">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AA23">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="AB23">
+        <v>10</v>
+      </c>
+      <c r="AC23">
         <v>8.4</v>
       </c>
-      <c r="AC23">
-        <v>10</v>
-      </c>
       <c r="AD23">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AF23">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AG23">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AH23">
         <v>24</v>
       </c>
       <c r="AI23">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AJ23">
-        <v>15.5</v>
+        <v>44</v>
       </c>
       <c r="AK23">
-        <v>17.5</v>
+        <v>38</v>
       </c>
       <c r="AL23">
         <v>60</v>
       </c>
       <c r="AM23">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AN23">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AO23">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ23">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR23">
-        <v>38</v>
+        <v>4.3</v>
       </c>
       <c r="AS23">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AT23">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU23">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AV23">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AW23">
+        <v>4.8</v>
+      </c>
+      <c r="AX23">
+        <v>13.5</v>
+      </c>
+      <c r="AY23">
         <v>10.5</v>
       </c>
-      <c r="AX23">
-        <v>7.8</v>
-      </c>
-      <c r="AY23">
-        <v>9</v>
-      </c>
       <c r="AZ23">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BA23">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB23">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="BC23">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BD23">
-        <v>26</v>
+        <v>4.8</v>
       </c>
       <c r="BE23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BF23">
+        <v>4.6</v>
+      </c>
+      <c r="BG23">
+        <v>4.8</v>
+      </c>
+      <c r="BH23">
+        <v>3.25</v>
+      </c>
+      <c r="BI23">
+        <v>2.46</v>
+      </c>
+      <c r="BJ23">
+        <v>12</v>
+      </c>
+      <c r="BK23">
+        <v>4</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>5.9</v>
+      </c>
+      <c r="BN23">
+        <v>5.9</v>
+      </c>
+      <c r="BO23">
+        <v>4.2</v>
+      </c>
+      <c r="BP23">
+        <v>24</v>
+      </c>
+      <c r="BQ23">
+        <v>4.8</v>
+      </c>
+      <c r="BR23">
+        <v>46</v>
+      </c>
+      <c r="BS23">
+        <v>5.3</v>
+      </c>
+      <c r="BT23">
+        <v>7.2</v>
+      </c>
+      <c r="BU23">
+        <v>5</v>
+      </c>
+      <c r="BV23">
+        <v>36</v>
+      </c>
+      <c r="BW23">
+        <v>5.2</v>
+      </c>
+      <c r="BX23">
+        <v>55</v>
+      </c>
+      <c r="BY23">
         <v>5.4</v>
       </c>
-      <c r="BG23">
-        <v>10.5</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.04</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.04</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.04</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.04</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.04</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.04</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>1.04</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.04</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.04</v>
-      </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB23" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24">
+        <v>1.61</v>
+      </c>
+      <c r="G24">
+        <v>1.68</v>
+      </c>
+      <c r="H24">
+        <v>5.7</v>
+      </c>
+      <c r="I24">
+        <v>7.8</v>
+      </c>
+      <c r="J24">
+        <v>3.95</v>
+      </c>
+      <c r="K24">
+        <v>4.7</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.06</v>
+      </c>
+      <c r="N24">
+        <v>3.4</v>
+      </c>
+      <c r="O24">
+        <v>1.31</v>
+      </c>
+      <c r="P24">
+        <v>1.93</v>
+      </c>
+      <c r="Q24">
+        <v>1.86</v>
+      </c>
+      <c r="R24">
+        <v>1.36</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24">
+        <v>1.93</v>
+      </c>
+      <c r="U24">
+        <v>1.87</v>
+      </c>
+      <c r="V24">
+        <v>1.15</v>
+      </c>
+      <c r="W24">
+        <v>2.46</v>
+      </c>
+      <c r="X24">
+        <v>16.5</v>
+      </c>
+      <c r="Y24">
+        <v>22</v>
+      </c>
+      <c r="Z24">
+        <v>60</v>
+      </c>
+      <c r="AA24">
+        <v>220</v>
+      </c>
+      <c r="AB24">
+        <v>8.4</v>
+      </c>
+      <c r="AC24">
+        <v>10</v>
+      </c>
+      <c r="AD24">
+        <v>27</v>
+      </c>
+      <c r="AE24">
+        <v>110</v>
+      </c>
+      <c r="AF24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG24">
+        <v>10.5</v>
+      </c>
+      <c r="AH24">
+        <v>24</v>
+      </c>
+      <c r="AI24">
+        <v>110</v>
+      </c>
+      <c r="AJ24">
+        <v>15.5</v>
+      </c>
+      <c r="AK24">
+        <v>17.5</v>
+      </c>
+      <c r="AL24">
+        <v>60</v>
+      </c>
+      <c r="AM24">
+        <v>290</v>
+      </c>
+      <c r="AN24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO24">
+        <v>150</v>
+      </c>
+      <c r="AP24">
+        <v>10</v>
+      </c>
+      <c r="AQ24">
+        <v>18.5</v>
+      </c>
+      <c r="AR24">
+        <v>38</v>
+      </c>
+      <c r="AS24">
+        <v>10</v>
+      </c>
+      <c r="AT24">
+        <v>7</v>
+      </c>
+      <c r="AU24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV24">
+        <v>18</v>
+      </c>
+      <c r="AW24">
+        <v>10.5</v>
+      </c>
+      <c r="AX24">
+        <v>7.8</v>
+      </c>
+      <c r="AY24">
+        <v>9</v>
+      </c>
+      <c r="AZ24">
+        <v>7.8</v>
+      </c>
+      <c r="BA24">
+        <v>10.5</v>
+      </c>
+      <c r="BB24">
+        <v>13</v>
+      </c>
+      <c r="BC24">
+        <v>7</v>
+      </c>
+      <c r="BD24">
+        <v>26</v>
+      </c>
+      <c r="BE24">
+        <v>10</v>
+      </c>
+      <c r="BF24">
+        <v>5.4</v>
+      </c>
+      <c r="BG24">
+        <v>10.5</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.04</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.04</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.04</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.04</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.04</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.04</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.04</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
         <v>81</v>
       </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24">
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25">
         <v>1.47</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>1.63</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>6.8</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>10</v>
       </c>
-      <c r="J24">
+      <c r="J25">
         <v>3.9</v>
       </c>
-      <c r="K24">
-        <v>5.6</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>3.1</v>
-      </c>
-      <c r="O24">
+      <c r="K25">
+        <v>950</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>3.15</v>
+      </c>
+      <c r="O25">
         <v>1.02</v>
       </c>
-      <c r="P24">
+      <c r="P25">
         <v>1.71</v>
       </c>
-      <c r="Q24">
+      <c r="Q25">
         <v>2.08</v>
       </c>
-      <c r="R24">
+      <c r="R25">
         <v>1.26</v>
       </c>
-      <c r="S24">
+      <c r="S25">
         <v>3.7</v>
       </c>
-      <c r="T24">
+      <c r="T25">
         <v>1.11</v>
       </c>
-      <c r="U24">
+      <c r="U25">
         <v>1.65</v>
       </c>
-      <c r="V24">
+      <c r="V25">
         <v>1.11</v>
       </c>
-      <c r="W24">
+      <c r="W25">
         <v>2.58</v>
       </c>
-      <c r="X24">
-        <v>1000</v>
-      </c>
-      <c r="Y24">
-        <v>1000</v>
-      </c>
-      <c r="Z24">
-        <v>1000</v>
-      </c>
-      <c r="AA24">
-        <v>1000</v>
-      </c>
-      <c r="AB24">
-        <v>1000</v>
-      </c>
-      <c r="AC24">
-        <v>1000</v>
-      </c>
-      <c r="AD24">
-        <v>1000</v>
-      </c>
-      <c r="AE24">
-        <v>1000</v>
-      </c>
-      <c r="AF24">
-        <v>1000</v>
-      </c>
-      <c r="AG24">
-        <v>1000</v>
-      </c>
-      <c r="AH24">
-        <v>1000</v>
-      </c>
-      <c r="AI24">
-        <v>1000</v>
-      </c>
-      <c r="AJ24">
-        <v>1000</v>
-      </c>
-      <c r="AK24">
-        <v>1000</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>1000</v>
-      </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>1.01</v>
-      </c>
-      <c r="AQ24">
-        <v>1.01</v>
-      </c>
-      <c r="AR24">
-        <v>1.01</v>
-      </c>
-      <c r="AS24">
-        <v>1.01</v>
-      </c>
-      <c r="AT24">
-        <v>1.01</v>
-      </c>
-      <c r="AU24">
-        <v>1.01</v>
-      </c>
-      <c r="AV24">
-        <v>1.01</v>
-      </c>
-      <c r="AW24">
-        <v>1.01</v>
-      </c>
-      <c r="AX24">
-        <v>1.01</v>
-      </c>
-      <c r="AY24">
-        <v>1.01</v>
-      </c>
-      <c r="AZ24">
-        <v>1.01</v>
-      </c>
-      <c r="BA24">
-        <v>1.01</v>
-      </c>
-      <c r="BB24">
-        <v>1.01</v>
-      </c>
-      <c r="BC24">
-        <v>1.01</v>
-      </c>
-      <c r="BD24">
-        <v>1.01</v>
-      </c>
-      <c r="BE24">
-        <v>1.01</v>
-      </c>
-      <c r="BF24">
-        <v>1.01</v>
-      </c>
-      <c r="BG24">
-        <v>1.01</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.04</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.04</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.04</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.04</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>1.04</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>1.04</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>1.04</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>1.04</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
-      <c r="BY24">
-        <v>1.04</v>
-      </c>
-      <c r="BZ24">
-        <v>1000</v>
-      </c>
-      <c r="CA24">
-        <v>1.04</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>152</v>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>1.01</v>
+      </c>
+      <c r="AU25">
+        <v>1.01</v>
+      </c>
+      <c r="AV25">
+        <v>1.01</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>1.01</v>
+      </c>
+      <c r="AY25">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25">
+        <v>1.01</v>
+      </c>
+      <c r="BA25">
+        <v>1.01</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>1.01</v>
+      </c>
+      <c r="BD25">
+        <v>1.01</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.04</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.04</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.04</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.04</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.04</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.04</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.04</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.04</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -484,7 +484,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 02:15:14</t>
+    <t>2026-08-19 04:24:07</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1084,7 @@
         <v>3.8</v>
       </c>
       <c r="H2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2.04</v>
@@ -1138,7 +1138,7 @@
         <v>15</v>
       </c>
       <c r="Z2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA2">
         <v>25</v>
@@ -1180,19 +1180,19 @@
         <v>55</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO2">
         <v>9</v>
       </c>
       <c r="AP2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ2">
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS2">
         <v>22</v>
@@ -1323,43 +1323,43 @@
         <v>2.82</v>
       </c>
       <c r="G3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H3">
         <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P3">
         <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R3">
         <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T3">
         <v>2.12</v>
@@ -1368,16 +1368,16 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.52</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>22</v>
@@ -1386,7 +1386,7 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>8</v>
@@ -1434,10 +1434,10 @@
         <v>7.8</v>
       </c>
       <c r="AR3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1449,37 +1449,37 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
         <v>5.8</v>
       </c>
-      <c r="BB3">
-        <v>5.6</v>
-      </c>
       <c r="BC3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE3">
+        <v>6.4</v>
+      </c>
+      <c r="BF3">
+        <v>5.8</v>
+      </c>
+      <c r="BG3">
         <v>6</v>
-      </c>
-      <c r="BF3">
-        <v>5.6</v>
-      </c>
-      <c r="BG3">
-        <v>5.8</v>
       </c>
       <c r="BH3">
         <v>2.66</v>
@@ -1562,10 +1562,10 @@
         <v>134</v>
       </c>
       <c r="F4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H4">
         <v>6.2</v>
@@ -1574,31 +1574,31 @@
         <v>6.6</v>
       </c>
       <c r="J4">
+        <v>3.95</v>
+      </c>
+      <c r="K4">
         <v>4</v>
-      </c>
-      <c r="K4">
-        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.43</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.75</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
         <v>2.04</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
         <v>3.7</v>
@@ -1613,7 +1613,7 @@
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1622,7 +1622,7 @@
         <v>19</v>
       </c>
       <c r="Z4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA4">
         <v>190</v>
@@ -1652,10 +1652,10 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1679,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
@@ -1697,7 +1697,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
         <v>21</v>
@@ -1715,7 +1715,7 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF4">
         <v>9.6</v>
@@ -1724,64 +1724,64 @@
         <v>100</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="s">
         <v>156</v>
@@ -1804,13 +1804,13 @@
         <v>135</v>
       </c>
       <c r="F5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G5">
         <v>1.86</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
         <v>4.7</v>
@@ -1822,25 +1822,25 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
         <v>1.7</v>
       </c>
       <c r="R5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
         <v>2.74</v>
@@ -1870,7 +1870,7 @@
         <v>95</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
@@ -1897,7 +1897,7 @@
         <v>23</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
         <v>29</v>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5">
         <v>42</v>
@@ -1927,10 +1927,10 @@
         <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW5">
         <v>36</v>
@@ -1954,13 +1954,13 @@
         <v>16</v>
       </c>
       <c r="BD5">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BE5">
         <v>34</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
         <v>25</v>
@@ -1981,7 +1981,7 @@
         <v>95</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT5">
         <v>8.4</v>
@@ -2008,7 +2008,7 @@
         <v>6.6</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW5">
         <v>8.800000000000001</v>
@@ -2017,13 +2017,13 @@
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>17</v>
       </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>156</v>
@@ -2055,7 +2055,7 @@
         <v>5.4</v>
       </c>
       <c r="I6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
         <v>3.4</v>
@@ -2064,7 +2064,7 @@
         <v>3.8</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M6">
         <v>1.1</v>
@@ -2106,7 +2106,7 @@
         <v>17.5</v>
       </c>
       <c r="Z6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA6">
         <v>200</v>
@@ -2124,7 +2124,7 @@
         <v>120</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6">
         <v>11</v>
@@ -2160,106 +2160,106 @@
         <v>13</v>
       </c>
       <c r="AR6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU6">
         <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX6">
         <v>8.4</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB6">
         <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BD6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF6">
         <v>12.5</v>
       </c>
       <c r="BG6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2288,19 +2288,19 @@
         <v>137</v>
       </c>
       <c r="F7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I7">
         <v>4.1</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K7">
         <v>4.1</v>
@@ -2318,7 +2318,7 @@
         <v>1.18</v>
       </c>
       <c r="P7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q7">
         <v>1.56</v>
@@ -2333,13 +2333,13 @@
         <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
         <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X7">
         <v>26</v>
@@ -2348,13 +2348,13 @@
         <v>23</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
@@ -2363,10 +2363,10 @@
         <v>17</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
         <v>11</v>
@@ -2381,7 +2381,7 @@
         <v>24</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL7">
         <v>26</v>
@@ -2399,13 +2399,13 @@
         <v>22</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR7">
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AT7">
         <v>13</v>
@@ -2417,7 +2417,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX7">
         <v>14</v>
@@ -2426,7 +2426,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA7">
         <v>34</v>
@@ -2438,7 +2438,7 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE7">
         <v>44</v>
@@ -2447,7 +2447,7 @@
         <v>7.8</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH7">
         <v>4.6</v>
@@ -2530,22 +2530,22 @@
         <v>138</v>
       </c>
       <c r="F8">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
         <v>2.86</v>
       </c>
       <c r="H8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I8">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2554,7 +2554,7 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O8">
         <v>1.25</v>
@@ -2566,7 +2566,7 @@
         <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S8">
         <v>2.92</v>
@@ -2575,7 +2575,7 @@
         <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V8">
         <v>1.61</v>
@@ -2590,7 +2590,7 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA8">
         <v>38</v>
@@ -2626,7 +2626,7 @@
         <v>29</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM8">
         <v>70</v>
@@ -2638,7 +2638,7 @@
         <v>17.5</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
         <v>12</v>
@@ -2659,10 +2659,10 @@
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2677,19 +2677,19 @@
         <v>40</v>
       </c>
       <c r="BC8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD8">
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BF8">
         <v>18.5</v>
       </c>
       <c r="BG8">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH8">
         <v>4</v>
@@ -2701,13 +2701,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL8">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN8">
         <v>6.4</v>
@@ -2719,13 +2719,13 @@
         <v>21</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8">
         <v>5.9</v>
@@ -2737,19 +2737,19 @@
         <v>18.5</v>
       </c>
       <c r="BW8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX8">
         <v>29</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>156</v>
@@ -2772,19 +2772,19 @@
         <v>139</v>
       </c>
       <c r="F9">
+        <v>1.77</v>
+      </c>
+      <c r="G9">
         <v>1.78</v>
       </c>
-      <c r="G9">
-        <v>1.8</v>
-      </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
         <v>4.9</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -2796,7 +2796,7 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O9">
         <v>1.22</v>
@@ -2805,13 +2805,13 @@
         <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R9">
         <v>1.58</v>
       </c>
       <c r="S9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T9">
         <v>1.66</v>
@@ -2823,10 +2823,10 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9">
         <v>21</v>
@@ -2844,7 +2844,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2856,19 +2856,19 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI9">
         <v>50</v>
       </c>
       <c r="AJ9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9">
         <v>75</v>
@@ -2892,10 +2892,10 @@
         <v>40</v>
       </c>
       <c r="AT9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV9">
         <v>17</v>
@@ -2910,16 +2910,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
         <v>44</v>
       </c>
       <c r="BB9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD9">
         <v>25</v>
@@ -2928,7 +2928,7 @@
         <v>60</v>
       </c>
       <c r="BF9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG9">
         <v>38</v>
@@ -2937,61 +2937,61 @@
         <v>4.2</v>
       </c>
       <c r="BI9">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>90</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
         <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR9">
         <v>22</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV9">
         <v>34</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
         <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="s">
         <v>156</v>
@@ -3023,7 +3023,7 @@
         <v>2.64</v>
       </c>
       <c r="I10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J10">
         <v>3.45</v>
@@ -3032,7 +3032,7 @@
         <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M10">
         <v>1.06</v>
@@ -3041,13 +3041,13 @@
         <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
         <v>2.06</v>
       </c>
       <c r="Q10">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R10">
         <v>1.41</v>
@@ -3056,13 +3056,13 @@
         <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
         <v>1.53</v>
@@ -3137,7 +3137,7 @@
         <v>10.5</v>
       </c>
       <c r="AU10">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
         <v>11</v>
@@ -3176,58 +3176,58 @@
         <v>17</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>1.55</v>
       </c>
       <c r="G11">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H11">
         <v>6.4</v>
@@ -3280,25 +3280,25 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S11">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U11">
         <v>2.18</v>
@@ -3307,7 +3307,7 @@
         <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X11">
         <v>24</v>
@@ -3319,7 +3319,7 @@
         <v>65</v>
       </c>
       <c r="AA11">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
         <v>11</v>
@@ -3328,7 +3328,7 @@
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE11">
         <v>90</v>
@@ -3349,7 +3349,7 @@
         <v>15</v>
       </c>
       <c r="AK11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL11">
         <v>32</v>
@@ -3358,25 +3358,25 @@
         <v>95</v>
       </c>
       <c r="AN11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO11">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AS11">
         <v>44</v>
       </c>
       <c r="AT11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU11">
         <v>9.800000000000001</v>
@@ -3394,34 +3394,34 @@
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
         <v>34</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC11">
         <v>13.5</v>
       </c>
       <c r="BD11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BE11">
         <v>36</v>
       </c>
       <c r="BF11">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG11">
         <v>34</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3433,7 +3433,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN11">
         <v>4.4</v>
@@ -3445,7 +3445,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ11">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
         <v>23</v>
@@ -3457,25 +3457,25 @@
         <v>11</v>
       </c>
       <c r="BU11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV11">
         <v>55</v>
       </c>
       <c r="BW11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX11">
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="s">
         <v>156</v>
@@ -3537,7 +3537,7 @@
         <v>1.8</v>
       </c>
       <c r="S12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T12">
         <v>1.46</v>
@@ -3549,7 +3549,7 @@
         <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X12">
         <v>32</v>
@@ -3558,7 +3558,7 @@
         <v>22</v>
       </c>
       <c r="Z12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA12">
         <v>55</v>
@@ -3567,16 +3567,16 @@
         <v>18.5</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12">
         <v>12</v>
@@ -3585,13 +3585,13 @@
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ12">
         <v>32</v>
       </c>
       <c r="AK12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12">
         <v>24</v>
@@ -3600,43 +3600,43 @@
         <v>46</v>
       </c>
       <c r="AN12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO12">
         <v>15</v>
       </c>
       <c r="AP12">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AQ12">
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
+        <v>13</v>
+      </c>
+      <c r="AW12">
+        <v>25</v>
+      </c>
+      <c r="AX12">
+        <v>18.5</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
         <v>12.5</v>
-      </c>
-      <c r="AW12">
-        <v>24</v>
-      </c>
-      <c r="AX12">
-        <v>17.5</v>
-      </c>
-      <c r="AY12">
-        <v>11</v>
-      </c>
-      <c r="AZ12">
-        <v>13</v>
       </c>
       <c r="BA12">
         <v>26</v>
@@ -3645,19 +3645,19 @@
         <v>27</v>
       </c>
       <c r="BC12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF12">
         <v>9</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH12">
         <v>5.1</v>
@@ -3684,7 +3684,7 @@
         <v>5.3</v>
       </c>
       <c r="BP12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ12">
         <v>6.6</v>
@@ -3705,7 +3705,7 @@
         <v>19</v>
       </c>
       <c r="BW12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX12">
         <v>24</v>
@@ -3758,37 +3758,37 @@
         <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O13">
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q13">
         <v>1.4</v>
       </c>
       <c r="R13">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T13">
         <v>1.42</v>
       </c>
       <c r="U13">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
         <v>1.83</v>
@@ -3797,19 +3797,19 @@
         <v>38</v>
       </c>
       <c r="Y13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z13">
         <v>34</v>
       </c>
       <c r="AA13">
-        <v>350</v>
+        <v>460</v>
       </c>
       <c r="AB13">
         <v>20</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD13">
         <v>15.5</v>
@@ -3824,16 +3824,16 @@
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13">
         <v>32</v>
       </c>
       <c r="AK13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL13">
         <v>23</v>
@@ -3845,25 +3845,25 @@
         <v>7.8</v>
       </c>
       <c r="AO13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP13">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AQ13">
         <v>21</v>
       </c>
       <c r="AR13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AT13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV13">
         <v>13.5</v>
@@ -3872,10 +3872,10 @@
         <v>24</v>
       </c>
       <c r="AX13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <v>12.5</v>
@@ -3896,7 +3896,7 @@
         <v>23</v>
       </c>
       <c r="BF13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG13">
         <v>13</v>
@@ -3908,7 +3908,7 @@
         <v>4.4</v>
       </c>
       <c r="BJ13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK13">
         <v>5.4</v>
@@ -3917,7 +3917,7 @@
         <v>55</v>
       </c>
       <c r="BM13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN13">
         <v>6.2</v>
@@ -3929,13 +3929,13 @@
         <v>14</v>
       </c>
       <c r="BQ13">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT13">
         <v>7.6</v>
@@ -3947,16 +3947,16 @@
         <v>21</v>
       </c>
       <c r="BW13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA13">
         <v>7.2</v>
@@ -3982,22 +3982,22 @@
         <v>144</v>
       </c>
       <c r="F14">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="G14">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="H14">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="I14">
-        <v>3.7</v>
+        <v>2.74</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
         <v>1.37</v>
@@ -4012,16 +4012,16 @@
         <v>1.29</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="T14">
         <v>1.68</v>
@@ -4030,178 +4030,178 @@
         <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="X14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y14">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Z14">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AA14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB14">
+        <v>13.5</v>
+      </c>
+      <c r="AC14">
+        <v>8.4</v>
+      </c>
+      <c r="AD14">
+        <v>12.5</v>
+      </c>
+      <c r="AE14">
+        <v>40</v>
+      </c>
+      <c r="AF14">
+        <v>22</v>
+      </c>
+      <c r="AG14">
         <v>14</v>
       </c>
-      <c r="AC14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD14">
-        <v>14</v>
-      </c>
-      <c r="AE14">
-        <v>42</v>
-      </c>
-      <c r="AF14">
-        <v>21</v>
-      </c>
-      <c r="AG14">
-        <v>12.5</v>
-      </c>
       <c r="AH14">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AK14">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AM14">
         <v>100</v>
       </c>
       <c r="AN14">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AO14">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AP14">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR14">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="AS14">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AT14">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU14">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="AV14">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AW14">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX14">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AY14">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AZ14">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA14">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB14">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BC14">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BD14">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE14">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF14">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="BG14">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BH14">
         <v>3.65</v>
       </c>
       <c r="BI14">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14">
         <v>9.6</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BN14">
+        <v>6.4</v>
+      </c>
+      <c r="BO14">
+        <v>3.95</v>
+      </c>
+      <c r="BP14">
+        <v>24</v>
+      </c>
+      <c r="BQ14">
+        <v>7.2</v>
+      </c>
+      <c r="BR14">
+        <v>36</v>
+      </c>
+      <c r="BS14">
+        <v>2.52</v>
+      </c>
+      <c r="BT14">
         <v>5.8</v>
       </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>19</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
-      <c r="BT14">
-        <v>6.6</v>
-      </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14">
         <v>26</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB14" t="s">
         <v>156</v>
@@ -4227,16 +4227,16 @@
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H15">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4272,10 +4272,10 @@
         <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4484,7 +4484,7 @@
         <v>4.2</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
         <v>1.04</v>
@@ -4505,13 +4505,13 @@
         <v>1.5</v>
       </c>
       <c r="S16">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T16">
         <v>1.56</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V16">
         <v>1.5</v>
@@ -4550,7 +4550,7 @@
         <v>13</v>
       </c>
       <c r="AH16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI16">
         <v>36</v>
@@ -4610,7 +4610,7 @@
         <v>6.4</v>
       </c>
       <c r="BB16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC16">
         <v>20</v>
@@ -4619,7 +4619,7 @@
         <v>6.4</v>
       </c>
       <c r="BE16">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF16">
         <v>13</v>
@@ -4628,64 +4628,64 @@
         <v>16</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB16" t="s">
         <v>156</v>
@@ -4723,28 +4723,28 @@
         <v>6.6</v>
       </c>
       <c r="K17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M17">
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O17">
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q17">
         <v>1.47</v>
       </c>
       <c r="R17">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S17">
         <v>2.14</v>
@@ -4870,64 +4870,64 @@
         <v>3.4</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI17">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
       <c r="BJ17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BK17">
-        <v>1.89</v>
+        <v>4.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BN17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BO17">
-        <v>1.93</v>
+        <v>5</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BQ17">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BS17">
-        <v>2.08</v>
+        <v>6.8</v>
       </c>
       <c r="BT17">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BU17">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="BV17">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BW17">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BX17">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BY17">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="BZ17">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="CA17">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="CB17" t="s">
         <v>156</v>
@@ -4959,7 +4959,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J18">
         <v>3.55</v>
@@ -4968,7 +4968,7 @@
         <v>3.65</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M18">
         <v>1.07</v>
@@ -4977,7 +4977,7 @@
         <v>3.55</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P18">
         <v>1.88</v>
@@ -5043,7 +5043,7 @@
         <v>40</v>
       </c>
       <c r="AK18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL18">
         <v>42</v>
@@ -5115,19 +5115,19 @@
         <v>3.75</v>
       </c>
       <c r="BI18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18">
         <v>11</v>
       </c>
       <c r="BK18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
@@ -5139,13 +5139,13 @@
         <v>23</v>
       </c>
       <c r="BQ18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR18">
         <v>38</v>
       </c>
       <c r="BS18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT18">
         <v>6.8</v>
@@ -5154,22 +5154,22 @@
         <v>4.7</v>
       </c>
       <c r="BV18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX18">
         <v>40</v>
       </c>
       <c r="BY18">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BZ18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA18">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB18" t="s">
         <v>156</v>
@@ -5219,7 +5219,7 @@
         <v>2.6</v>
       </c>
       <c r="O19">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P19">
         <v>1.51</v>
@@ -5234,7 +5234,7 @@
         <v>6.2</v>
       </c>
       <c r="T19">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U19">
         <v>1.74</v>
@@ -5249,13 +5249,13 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z19">
         <v>24</v>
       </c>
       <c r="AA19">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -5369,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="BM19">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="BN19">
         <v>4.9</v>
@@ -5434,226 +5434,226 @@
         <v>150</v>
       </c>
       <c r="F20">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G20">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H20">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="I20">
+        <v>3.5</v>
+      </c>
+      <c r="J20">
         <v>3.25</v>
-      </c>
-      <c r="J20">
-        <v>3.2</v>
       </c>
       <c r="K20">
         <v>3.9</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O20">
         <v>1.32</v>
       </c>
       <c r="P20">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q20">
         <v>1.89</v>
       </c>
       <c r="R20">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S20">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U20">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB20" t="s">
         <v>156</v>
@@ -5694,7 +5694,7 @@
         <v>4.1</v>
       </c>
       <c r="L21">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M21">
         <v>1.08</v>
@@ -5859,7 +5859,7 @@
         <v>4</v>
       </c>
       <c r="BO21">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BP21">
         <v>11.5</v>
@@ -5918,226 +5918,226 @@
         <v>152</v>
       </c>
       <c r="F22">
-        <v>1.06</v>
+        <v>2.7</v>
       </c>
       <c r="G22">
-        <v>990</v>
+        <v>3.1</v>
       </c>
       <c r="H22">
-        <v>1.06</v>
+        <v>2.9</v>
       </c>
       <c r="I22">
-        <v>990</v>
+        <v>3.35</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N22">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O22">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q22">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="R22">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U22">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V22">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB22" t="s">
         <v>156</v>
@@ -6163,7 +6163,7 @@
         <v>2.44</v>
       </c>
       <c r="G23">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H23">
         <v>3.2</v>
@@ -6172,7 +6172,7 @@
         <v>3.65</v>
       </c>
       <c r="J23">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K23">
         <v>3.65</v>
@@ -6190,10 +6190,10 @@
         <v>1.43</v>
       </c>
       <c r="P23">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q23">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="R23">
         <v>1.24</v>
@@ -6211,7 +6211,7 @@
         <v>1.39</v>
       </c>
       <c r="W23">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X23">
         <v>12</v>
@@ -6420,7 +6420,7 @@
         <v>4.7</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -6441,7 +6441,7 @@
         <v>1.36</v>
       </c>
       <c r="S24">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T24">
         <v>1.93</v>
@@ -6564,58 +6564,58 @@
         <v>10.5</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6644,226 +6644,226 @@
         <v>155</v>
       </c>
       <c r="F25">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G25">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H25">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J25">
+        <v>3.95</v>
+      </c>
+      <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
+        <v>1.39</v>
+      </c>
+      <c r="M25">
+        <v>1.08</v>
+      </c>
+      <c r="N25">
+        <v>3.2</v>
+      </c>
+      <c r="O25">
+        <v>1.33</v>
+      </c>
+      <c r="P25">
+        <v>1.72</v>
+      </c>
+      <c r="Q25">
+        <v>2.12</v>
+      </c>
+      <c r="R25">
+        <v>1.27</v>
+      </c>
+      <c r="S25">
         <v>3.9</v>
       </c>
-      <c r="K25">
-        <v>950</v>
-      </c>
-      <c r="L25">
-        <v>1.01</v>
-      </c>
-      <c r="M25">
-        <v>1.01</v>
-      </c>
-      <c r="N25">
-        <v>3.15</v>
-      </c>
-      <c r="O25">
-        <v>1.02</v>
-      </c>
-      <c r="P25">
-        <v>1.71</v>
-      </c>
-      <c r="Q25">
-        <v>2.08</v>
-      </c>
-      <c r="R25">
-        <v>1.26</v>
-      </c>
-      <c r="S25">
-        <v>3.7</v>
-      </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V25">
         <v>1.11</v>
       </c>
       <c r="W25">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB25" t="s">
         <v>156</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -484,7 +484,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 04:24:07</t>
+    <t>2026-08-19 06:33:35</t>
   </si>
 </sst>
 </file>
@@ -1078,31 +1078,31 @@
         <v>132</v>
       </c>
       <c r="F2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="G2">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="I2">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O2">
         <v>1.19</v>
@@ -1123,91 +1123,91 @@
         <v>1.56</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X2">
         <v>26</v>
       </c>
       <c r="Y2">
+        <v>14</v>
+      </c>
+      <c r="Z2">
         <v>15</v>
       </c>
-      <c r="Z2">
-        <v>15.5</v>
-      </c>
       <c r="AA2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB2">
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
         <v>11</v>
       </c>
       <c r="AE2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF2">
         <v>32</v>
       </c>
       <c r="AG2">
+        <v>16.5</v>
+      </c>
+      <c r="AH2">
         <v>16</v>
-      </c>
-      <c r="AH2">
-        <v>15</v>
       </c>
       <c r="AI2">
         <v>26</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN2">
         <v>26</v>
       </c>
       <c r="AO2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AP2">
         <v>22</v>
       </c>
       <c r="AQ2">
+        <v>12.5</v>
+      </c>
+      <c r="AR2">
         <v>13.5</v>
-      </c>
-      <c r="AR2">
-        <v>14</v>
       </c>
       <c r="AS2">
         <v>22</v>
       </c>
       <c r="AT2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX2">
         <v>29</v>
@@ -1237,7 +1237,7 @@
         <v>21</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH2">
         <v>5.1</v>
@@ -1252,7 +1252,7 @@
         <v>4.4</v>
       </c>
       <c r="BL2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BM2">
         <v>8</v>
@@ -1326,13 +1326,13 @@
         <v>2.94</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1350,19 +1350,19 @@
         <v>1.58</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
         <v>1.79</v>
@@ -1428,7 +1428,7 @@
         <v>70</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
         <v>7.8</v>
@@ -1482,7 +1482,7 @@
         <v>6</v>
       </c>
       <c r="BH3">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI3">
         <v>2.34</v>
@@ -1491,7 +1491,7 @@
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1509,13 +1509,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT3">
         <v>5.9</v>
@@ -1527,19 +1527,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CB3" t="s">
         <v>156</v>
@@ -1571,7 +1571,7 @@
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>3.95</v>
@@ -1580,7 +1580,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
         <v>1.08</v>
@@ -1592,22 +1592,22 @@
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q4">
         <v>2.04</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
         <v>3.7</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
         <v>1.17</v>
@@ -1652,10 +1652,10 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1679,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
@@ -1694,7 +1694,7 @@
         <v>80</v>
       </c>
       <c r="AX4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY4">
         <v>9.6</v>
@@ -1715,7 +1715,7 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF4">
         <v>9.6</v>
@@ -1724,7 +1724,7 @@
         <v>100</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI4">
         <v>2.78</v>
@@ -1739,13 +1739,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
         <v>12</v>
@@ -1757,10 +1757,10 @@
         <v>30</v>
       </c>
       <c r="BS4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BU4">
         <v>7.6</v>
@@ -1769,19 +1769,19 @@
         <v>85</v>
       </c>
       <c r="BW4">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>70</v>
       </c>
       <c r="BY4">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>24</v>
       </c>
       <c r="CA4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="s">
         <v>156</v>
@@ -1804,22 +1804,22 @@
         <v>135</v>
       </c>
       <c r="F5">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="G5">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="H5">
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.33</v>
@@ -1834,7 +1834,7 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
         <v>1.7</v>
@@ -1846,19 +1846,19 @@
         <v>2.74</v>
       </c>
       <c r="T5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y5">
         <v>21</v>
@@ -1867,25 +1867,25 @@
         <v>38</v>
       </c>
       <c r="AA5">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
         <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE5">
         <v>50</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>17</v>
@@ -1894,46 +1894,46 @@
         <v>50</v>
       </c>
       <c r="AJ5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL5">
         <v>29</v>
       </c>
       <c r="AM5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AN5">
         <v>8.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ5">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AS5">
         <v>38</v>
       </c>
       <c r="AT5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AX5">
         <v>11</v>
@@ -1942,19 +1942,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BB5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC5">
         <v>16</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE5">
         <v>34</v>
@@ -1963,7 +1963,7 @@
         <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BH5">
         <v>4.2</v>
@@ -1975,7 +1975,7 @@
         <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL5">
         <v>95</v>
@@ -2005,7 +2005,7 @@
         <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV5">
         <v>34</v>
@@ -2046,220 +2046,220 @@
         <v>136</v>
       </c>
       <c r="F6">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="G6">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M6">
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P6">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R6">
         <v>1.24</v>
       </c>
       <c r="S6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T6">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z6">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA6">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AB6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE6">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AF6">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>950</v>
       </c>
       <c r="AI6">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ6">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AK6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM6">
+        <v>240</v>
+      </c>
+      <c r="AN6">
+        <v>16</v>
+      </c>
+      <c r="AO6">
         <v>210</v>
       </c>
-      <c r="AN6">
-        <v>17</v>
-      </c>
-      <c r="AO6">
-        <v>190</v>
-      </c>
       <c r="AP6">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR6">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AT6">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV6">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AW6">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA6">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC6">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE6">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BF6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
+        <v>15</v>
+      </c>
+      <c r="BN6">
+        <v>4.2</v>
+      </c>
+      <c r="BO6">
+        <v>3.75</v>
+      </c>
+      <c r="BP6">
         <v>13.5</v>
       </c>
-      <c r="BN6">
-        <v>4.3</v>
-      </c>
-      <c r="BO6">
-        <v>3.4</v>
-      </c>
-      <c r="BP6">
-        <v>14</v>
-      </c>
       <c r="BQ6">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2327,10 +2327,10 @@
         <v>1.69</v>
       </c>
       <c r="S7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U7">
         <v>2.7</v>
@@ -2342,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="X7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y7">
         <v>23</v>
@@ -2354,16 +2354,16 @@
         <v>80</v>
       </c>
       <c r="AB7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF7">
         <v>15.5</v>
@@ -2387,7 +2387,7 @@
         <v>26</v>
       </c>
       <c r="AM7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN7">
         <v>8.6</v>
@@ -2417,16 +2417,16 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA7">
         <v>34</v>
@@ -2438,13 +2438,13 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE7">
         <v>44</v>
       </c>
       <c r="BF7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG7">
         <v>23</v>
@@ -2530,22 +2530,22 @@
         <v>138</v>
       </c>
       <c r="F8">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H8">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2557,7 +2557,7 @@
         <v>4.7</v>
       </c>
       <c r="O8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
         <v>2.26</v>
@@ -2569,19 +2569,19 @@
         <v>1.49</v>
       </c>
       <c r="S8">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T8">
         <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X8">
         <v>19</v>
@@ -2590,10 +2590,10 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AB8">
         <v>14.5</v>
@@ -2626,7 +2626,7 @@
         <v>29</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM8">
         <v>70</v>
@@ -2635,10 +2635,10 @@
         <v>22</v>
       </c>
       <c r="AO8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
         <v>12</v>
@@ -2674,7 +2674,7 @@
         <v>30</v>
       </c>
       <c r="BB8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC8">
         <v>25</v>
@@ -2692,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="BH8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI8">
         <v>3.15</v>
@@ -2725,7 +2725,7 @@
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
         <v>5.9</v>
@@ -2737,13 +2737,13 @@
         <v>18.5</v>
       </c>
       <c r="BW8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX8">
         <v>29</v>
       </c>
       <c r="BY8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8">
         <v>21</v>
@@ -2775,7 +2775,7 @@
         <v>1.77</v>
       </c>
       <c r="G9">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H9">
         <v>4.8</v>
@@ -2796,19 +2796,19 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O9">
         <v>1.22</v>
       </c>
       <c r="P9">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q9">
         <v>1.65</v>
       </c>
       <c r="R9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
         <v>2.64</v>
@@ -2817,19 +2817,19 @@
         <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X9">
         <v>23</v>
       </c>
       <c r="Y9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z9">
         <v>40</v>
@@ -2853,7 +2853,7 @@
         <v>13</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH9">
         <v>17</v>
@@ -2862,7 +2862,7 @@
         <v>50</v>
       </c>
       <c r="AJ9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK9">
         <v>17</v>
@@ -2883,7 +2883,7 @@
         <v>20</v>
       </c>
       <c r="AQ9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR9">
         <v>36</v>
@@ -2922,7 +2922,7 @@
         <v>15.5</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE9">
         <v>60</v>
@@ -2946,7 +2946,7 @@
         <v>6</v>
       </c>
       <c r="BL9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
         <v>14.5</v>
@@ -2979,19 +2979,19 @@
         <v>34</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>156</v>
@@ -3026,10 +3026,10 @@
         <v>2.8</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.39</v>
@@ -3038,7 +3038,7 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
         <v>1.3</v>
@@ -3047,16 +3047,16 @@
         <v>2.06</v>
       </c>
       <c r="Q10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S10">
         <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
         <v>2.24</v>
@@ -3122,7 +3122,7 @@
         <v>24</v>
       </c>
       <c r="AP10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
@@ -3131,7 +3131,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT10">
         <v>10.5</v>
@@ -3143,10 +3143,10 @@
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY10">
         <v>11</v>
@@ -3155,19 +3155,19 @@
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF10">
         <v>17.5</v>
@@ -3176,7 +3176,7 @@
         <v>17</v>
       </c>
       <c r="BH10">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
         <v>2.94</v>
@@ -3185,13 +3185,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BN10">
         <v>5.9</v>
@@ -3203,16 +3203,16 @@
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU10">
         <v>4.6</v>
@@ -3221,13 +3221,13 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3262,16 +3262,16 @@
         <v>1.56</v>
       </c>
       <c r="H11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>4.7</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
         <v>1.31</v>
@@ -3286,46 +3286,46 @@
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T11">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U11">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W11">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y11">
         <v>27</v>
       </c>
       <c r="Z11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD11">
         <v>25</v>
@@ -3334,43 +3334,43 @@
         <v>90</v>
       </c>
       <c r="AF11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK11">
         <v>15.5</v>
       </c>
       <c r="AL11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM11">
+        <v>100</v>
+      </c>
+      <c r="AN11">
+        <v>6.4</v>
+      </c>
+      <c r="AO11">
         <v>95</v>
-      </c>
-      <c r="AN11">
-        <v>6.6</v>
-      </c>
-      <c r="AO11">
-        <v>90</v>
       </c>
       <c r="AP11">
         <v>19.5</v>
       </c>
       <c r="AQ11">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AR11">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AS11">
         <v>44</v>
@@ -3382,40 +3382,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW11">
         <v>34</v>
       </c>
       <c r="AX11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
         <v>34</v>
       </c>
       <c r="BB11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC11">
         <v>13.5</v>
       </c>
       <c r="BD11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE11">
+        <v>38</v>
+      </c>
+      <c r="BF11">
+        <v>6.2</v>
+      </c>
+      <c r="BG11">
         <v>36</v>
-      </c>
-      <c r="BF11">
-        <v>6</v>
-      </c>
-      <c r="BG11">
-        <v>34</v>
       </c>
       <c r="BH11">
         <v>4.3</v>
@@ -3424,58 +3424,58 @@
         <v>3.35</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
         <v>4.4</v>
       </c>
       <c r="BO11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ11">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BR11">
         <v>23</v>
       </c>
       <c r="BS11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT11">
         <v>11</v>
       </c>
       <c r="BU11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="s">
         <v>156</v>
@@ -3501,7 +3501,7 @@
         <v>2.3</v>
       </c>
       <c r="G12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H12">
         <v>2.98</v>
@@ -3570,7 +3570,7 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE12">
         <v>28</v>
@@ -3636,7 +3636,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA12">
         <v>26</v>
@@ -3743,13 +3743,13 @@
         <v>2.14</v>
       </c>
       <c r="G13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J13">
         <v>4.3</v>
@@ -3785,13 +3785,13 @@
         <v>1.42</v>
       </c>
       <c r="U13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V13">
         <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="X13">
         <v>38</v>
@@ -3803,7 +3803,7 @@
         <v>34</v>
       </c>
       <c r="AA13">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="AB13">
         <v>20</v>
@@ -3818,7 +3818,7 @@
         <v>29</v>
       </c>
       <c r="AF13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3839,7 +3839,7 @@
         <v>23</v>
       </c>
       <c r="AM13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN13">
         <v>7.8</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="AQ13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR13">
         <v>20</v>
@@ -3869,7 +3869,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AX13">
         <v>18.5</v>
@@ -3881,7 +3881,7 @@
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BB13">
         <v>19.5</v>
@@ -3896,7 +3896,7 @@
         <v>23</v>
       </c>
       <c r="BF13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG13">
         <v>13</v>
@@ -3991,7 +3991,7 @@
         <v>2.4</v>
       </c>
       <c r="I14">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J14">
         <v>3.05</v>
@@ -4030,7 +4030,7 @@
         <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
         <v>1.41</v>
@@ -4227,10 +4227,10 @@
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I15">
         <v>3.55</v>
@@ -4275,7 +4275,7 @@
         <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4481,7 +4481,7 @@
         <v>3.65</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
         <v>1.28</v>
@@ -4568,7 +4568,7 @@
         <v>75</v>
       </c>
       <c r="AN16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO16">
         <v>20</v>
@@ -4610,7 +4610,7 @@
         <v>6.4</v>
       </c>
       <c r="BB16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC16">
         <v>20</v>
@@ -4619,7 +4619,7 @@
         <v>6.4</v>
       </c>
       <c r="BE16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
         <v>13</v>
@@ -4714,10 +4714,10 @@
         <v>16.5</v>
       </c>
       <c r="H17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="I17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J17">
         <v>6.6</v>
@@ -4732,13 +4732,13 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O17">
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q17">
         <v>1.47</v>
@@ -4747,16 +4747,16 @@
         <v>1.72</v>
       </c>
       <c r="S17">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T17">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U17">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -4765,10 +4765,10 @@
         <v>34</v>
       </c>
       <c r="Y17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AA17">
         <v>9.800000000000001</v>
@@ -4810,13 +4810,13 @@
         <v>180</v>
       </c>
       <c r="AN17">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="AO17">
         <v>3.85</v>
       </c>
       <c r="AP17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ17">
         <v>10</v>
@@ -4825,13 +4825,13 @@
         <v>7.4</v>
       </c>
       <c r="AS17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV17">
         <v>10</v>
@@ -4840,94 +4840,94 @@
         <v>11</v>
       </c>
       <c r="AX17">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY17">
+        <v>8</v>
+      </c>
+      <c r="AZ17">
+        <v>7.2</v>
+      </c>
+      <c r="BA17">
         <v>7.6</v>
       </c>
-      <c r="AZ17">
-        <v>7</v>
-      </c>
-      <c r="BA17">
-        <v>7.2</v>
-      </c>
       <c r="BB17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC17">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC17">
-        <v>8.4</v>
-      </c>
       <c r="BD17">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE17">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG17">
         <v>3.4</v>
       </c>
       <c r="BH17">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK17">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BN17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BO17">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BP17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BR17">
         <v>95</v>
       </c>
       <c r="BS17">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BT17">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BU17">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BV17">
         <v>7.8</v>
       </c>
       <c r="BW17">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY17">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ17">
         <v>9.4</v>
       </c>
       <c r="CA17">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="CB17" t="s">
         <v>156</v>
@@ -4950,13 +4950,13 @@
         <v>148</v>
       </c>
       <c r="F18">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G18">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I18">
         <v>3.1</v>
@@ -4992,7 +4992,7 @@
         <v>3.4</v>
       </c>
       <c r="T18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U18">
         <v>2.14</v>
@@ -5001,7 +5001,7 @@
         <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X18">
         <v>14.5</v>
@@ -5031,7 +5031,7 @@
         <v>17</v>
       </c>
       <c r="AG18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH18">
         <v>18</v>
@@ -5109,7 +5109,7 @@
         <v>20</v>
       </c>
       <c r="BG18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH18">
         <v>3.75</v>
@@ -5195,7 +5195,7 @@
         <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H19">
         <v>3.85</v>
@@ -5243,7 +5243,7 @@
         <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -5255,7 +5255,7 @@
         <v>24</v>
       </c>
       <c r="AA19">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -5264,7 +5264,7 @@
         <v>6.8</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE19">
         <v>70</v>
@@ -5360,10 +5360,10 @@
         <v>2.44</v>
       </c>
       <c r="BJ19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL19">
         <v>260</v>
@@ -5381,13 +5381,13 @@
         <v>21</v>
       </c>
       <c r="BQ19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR19">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BT19">
         <v>7</v>
@@ -5396,22 +5396,22 @@
         <v>6.2</v>
       </c>
       <c r="BV19">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BW19">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX19">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BY19">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BZ19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA19">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB19" t="s">
         <v>156</v>
@@ -5437,16 +5437,16 @@
         <v>2.34</v>
       </c>
       <c r="G20">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H20">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J20">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K20">
         <v>3.9</v>
@@ -5476,13 +5476,13 @@
         <v>3.15</v>
       </c>
       <c r="T20">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U20">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
         <v>1.58</v>
@@ -5494,7 +5494,7 @@
         <v>14.5</v>
       </c>
       <c r="Z20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA20">
         <v>60</v>
@@ -5506,13 +5506,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE20">
         <v>42</v>
       </c>
       <c r="AF20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG20">
         <v>13.5</v>
@@ -5539,61 +5539,61 @@
         <v>25</v>
       </c>
       <c r="AO20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP20">
+        <v>4</v>
+      </c>
+      <c r="AQ20">
+        <v>3.85</v>
+      </c>
+      <c r="AR20">
+        <v>4.3</v>
+      </c>
+      <c r="AS20">
+        <v>4.8</v>
+      </c>
+      <c r="AT20">
+        <v>3.7</v>
+      </c>
+      <c r="AU20">
+        <v>3.35</v>
+      </c>
+      <c r="AV20">
         <v>3.9</v>
       </c>
-      <c r="AQ20">
-        <v>3.75</v>
-      </c>
-      <c r="AR20">
-        <v>4.2</v>
-      </c>
-      <c r="AS20">
+      <c r="AW20">
         <v>4.7</v>
       </c>
-      <c r="AT20">
-        <v>3.6</v>
-      </c>
-      <c r="AU20">
-        <v>3.25</v>
-      </c>
-      <c r="AV20">
-        <v>3.85</v>
-      </c>
-      <c r="AW20">
+      <c r="AX20">
+        <v>4.1</v>
+      </c>
+      <c r="AY20">
+        <v>3.8</v>
+      </c>
+      <c r="AZ20">
+        <v>4.1</v>
+      </c>
+      <c r="BA20">
+        <v>4.8</v>
+      </c>
+      <c r="BB20">
+        <v>4.7</v>
+      </c>
+      <c r="BC20">
         <v>4.5</v>
       </c>
-      <c r="AX20">
-        <v>4</v>
-      </c>
-      <c r="AY20">
-        <v>3.7</v>
-      </c>
-      <c r="AZ20">
-        <v>4</v>
-      </c>
-      <c r="BA20">
+      <c r="BD20">
+        <v>4.7</v>
+      </c>
+      <c r="BE20">
+        <v>5</v>
+      </c>
+      <c r="BF20">
+        <v>4.3</v>
+      </c>
+      <c r="BG20">
         <v>4.6</v>
-      </c>
-      <c r="BB20">
-        <v>4.5</v>
-      </c>
-      <c r="BC20">
-        <v>4.4</v>
-      </c>
-      <c r="BD20">
-        <v>4.6</v>
-      </c>
-      <c r="BE20">
-        <v>4.8</v>
-      </c>
-      <c r="BF20">
-        <v>4.2</v>
-      </c>
-      <c r="BG20">
-        <v>4.5</v>
       </c>
       <c r="BH20">
         <v>3.55</v>
@@ -5605,31 +5605,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BN20">
         <v>5.7</v>
       </c>
       <c r="BO20">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP20">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS20">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BT20">
         <v>6.6</v>
@@ -5641,19 +5641,19 @@
         <v>25</v>
       </c>
       <c r="BW20">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX20">
         <v>38</v>
       </c>
       <c r="BY20">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BZ20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA20">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB20" t="s">
         <v>156</v>
@@ -5694,7 +5694,7 @@
         <v>4.1</v>
       </c>
       <c r="L21">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.08</v>
@@ -5709,7 +5709,7 @@
         <v>1.73</v>
       </c>
       <c r="Q21">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R21">
         <v>1.27</v>
@@ -5745,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21">
         <v>32</v>
@@ -5790,10 +5790,10 @@
         <v>17</v>
       </c>
       <c r="AR21">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AS21">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT21">
         <v>5.8</v>
@@ -5805,7 +5805,7 @@
         <v>21</v>
       </c>
       <c r="AW21">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX21">
         <v>7.2</v>
@@ -5817,7 +5817,7 @@
         <v>21</v>
       </c>
       <c r="BA21">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB21">
         <v>12.5</v>
@@ -5826,16 +5826,16 @@
         <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE21">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF21">
         <v>9.800000000000001</v>
       </c>
       <c r="BG21">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH21">
         <v>3.25</v>
@@ -5918,16 +5918,16 @@
         <v>152</v>
       </c>
       <c r="F22">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G22">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H22">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="I22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J22">
         <v>2.62</v>
@@ -5942,13 +5942,13 @@
         <v>1.13</v>
       </c>
       <c r="N22">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="O22">
         <v>1.55</v>
       </c>
       <c r="P22">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5966,10 +5966,10 @@
         <v>1.74</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X22">
         <v>9.6</v>
@@ -5993,7 +5993,7 @@
         <v>16.5</v>
       </c>
       <c r="AE22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF22">
         <v>22</v>
@@ -6008,7 +6008,7 @@
         <v>90</v>
       </c>
       <c r="AJ22">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK22">
         <v>55</v>
@@ -6020,10 +6020,10 @@
         <v>220</v>
       </c>
       <c r="AN22">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO22">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP22">
         <v>3.3</v>
@@ -6056,7 +6056,7 @@
         <v>3.9</v>
       </c>
       <c r="AZ22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA22">
         <v>4.8</v>
@@ -6065,13 +6065,13 @@
         <v>4.7</v>
       </c>
       <c r="BC22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD22">
         <v>4.8</v>
       </c>
       <c r="BE22">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF22">
         <v>4.7</v>
@@ -6083,61 +6083,61 @@
         <v>2.7</v>
       </c>
       <c r="BI22">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="BJ22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK22">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>11</v>
+        <v>2.28</v>
       </c>
       <c r="BN22">
         <v>5.8</v>
       </c>
       <c r="BO22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>11.5</v>
+      </c>
+      <c r="BT22">
+        <v>5.8</v>
+      </c>
+      <c r="BU22">
+        <v>4.6</v>
+      </c>
+      <c r="BV22">
         <v>28</v>
       </c>
-      <c r="BQ22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR22">
-        <v>55</v>
-      </c>
-      <c r="BS22">
-        <v>9.6</v>
-      </c>
-      <c r="BT22">
-        <v>6.2</v>
-      </c>
-      <c r="BU22">
-        <v>4.7</v>
-      </c>
-      <c r="BV22">
-        <v>30</v>
-      </c>
       <c r="BW22">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX22">
         <v>55</v>
       </c>
       <c r="BY22">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BZ22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA22">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="CB22" t="s">
         <v>156</v>
@@ -6178,7 +6178,7 @@
         <v>3.65</v>
       </c>
       <c r="L23">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
         <v>1.1</v>
@@ -6190,10 +6190,10 @@
         <v>1.43</v>
       </c>
       <c r="P23">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q23">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R23">
         <v>1.24</v>
@@ -6202,7 +6202,7 @@
         <v>4.5</v>
       </c>
       <c r="T23">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U23">
         <v>1.91</v>
@@ -6229,7 +6229,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD23">
         <v>17</v>
@@ -6274,10 +6274,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS23">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT23">
         <v>7.6</v>
@@ -6289,7 +6289,7 @@
         <v>13</v>
       </c>
       <c r="AW23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX23">
         <v>13.5</v>
@@ -6298,28 +6298,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA23">
+        <v>5.1</v>
+      </c>
+      <c r="BB23">
         <v>4.9</v>
       </c>
-      <c r="BB23">
-        <v>4.7</v>
-      </c>
       <c r="BC23">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD23">
+        <v>5</v>
+      </c>
+      <c r="BE23">
+        <v>5.3</v>
+      </c>
+      <c r="BF23">
         <v>4.8</v>
       </c>
-      <c r="BE23">
-        <v>5</v>
-      </c>
-      <c r="BF23">
-        <v>4.6</v>
-      </c>
       <c r="BG23">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH23">
         <v>3.25</v>
@@ -6411,16 +6411,16 @@
         <v>5.7</v>
       </c>
       <c r="I24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>3.95</v>
       </c>
       <c r="K24">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -6444,7 +6444,7 @@
         <v>3.2</v>
       </c>
       <c r="T24">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U24">
         <v>1.87</v>
@@ -6456,7 +6456,7 @@
         <v>2.46</v>
       </c>
       <c r="X24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y24">
         <v>22</v>
@@ -6465,7 +6465,7 @@
         <v>60</v>
       </c>
       <c r="AA24">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB24">
         <v>8.4</v>
@@ -6477,10 +6477,10 @@
         <v>27</v>
       </c>
       <c r="AE24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6495,16 +6495,16 @@
         <v>15.5</v>
       </c>
       <c r="AK24">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL24">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AM24">
         <v>290</v>
       </c>
       <c r="AN24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO24">
         <v>150</v>
@@ -6519,7 +6519,7 @@
         <v>38</v>
       </c>
       <c r="AS24">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT24">
         <v>7</v>
@@ -6531,7 +6531,7 @@
         <v>18</v>
       </c>
       <c r="AW24">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX24">
         <v>7.8</v>
@@ -6540,10 +6540,10 @@
         <v>9</v>
       </c>
       <c r="AZ24">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA24">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB24">
         <v>13</v>
@@ -6555,67 +6555,67 @@
         <v>26</v>
       </c>
       <c r="BE24">
+        <v>9.6</v>
+      </c>
+      <c r="BF24">
+        <v>5</v>
+      </c>
+      <c r="BG24">
         <v>10</v>
-      </c>
-      <c r="BF24">
-        <v>5.4</v>
-      </c>
-      <c r="BG24">
-        <v>10.5</v>
       </c>
       <c r="BH24">
         <v>3.65</v>
       </c>
       <c r="BI24">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ24">
         <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BN24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO24">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR24">
         <v>28</v>
       </c>
       <c r="BS24">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU24">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6671,13 +6671,13 @@
         <v>3.2</v>
       </c>
       <c r="O25">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P25">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q25">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R25">
         <v>1.27</v>
@@ -6686,7 +6686,7 @@
         <v>3.9</v>
       </c>
       <c r="T25">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
         <v>1.67</v>
@@ -6713,7 +6713,7 @@
         <v>7.6</v>
       </c>
       <c r="AC25">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25">
         <v>38</v>
@@ -6758,52 +6758,52 @@
         <v>16.5</v>
       </c>
       <c r="AR25">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS25">
+        <v>6</v>
+      </c>
+      <c r="AT25">
+        <v>5.8</v>
+      </c>
+      <c r="AU25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV25">
         <v>5.2</v>
       </c>
-      <c r="AT25">
-        <v>5.2</v>
-      </c>
-      <c r="AU25">
-        <v>7.4</v>
-      </c>
-      <c r="AV25">
-        <v>4.7</v>
-      </c>
       <c r="AW25">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX25">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY25">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BA25">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB25">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC25">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD25">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE25">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF25">
         <v>8.4</v>
       </c>
       <c r="BG25">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH25">
         <v>3.55</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -484,7 +484,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 06:33:35</t>
+    <t>2026-08-19 08:43:11</t>
   </si>
 </sst>
 </file>
@@ -1084,10 +1084,10 @@
         <v>3.95</v>
       </c>
       <c r="H2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I2">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J2">
         <v>4.2</v>
@@ -1099,7 +1099,7 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>5.9</v>
@@ -1108,7 +1108,7 @@
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q2">
         <v>1.57</v>
@@ -1123,7 +1123,7 @@
         <v>1.56</v>
       </c>
       <c r="U2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V2">
         <v>2.02</v>
@@ -1141,7 +1141,7 @@
         <v>15</v>
       </c>
       <c r="AA2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB2">
         <v>22</v>
@@ -1153,7 +1153,7 @@
         <v>11</v>
       </c>
       <c r="AE2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF2">
         <v>32</v>
@@ -1171,7 +1171,7 @@
         <v>75</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL2">
         <v>40</v>
@@ -1189,7 +1189,7 @@
         <v>22</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2">
         <v>13.5</v>
@@ -1237,67 +1237,67 @@
         <v>21</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>5.1</v>
       </c>
       <c r="BI2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK2">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BL2">
         <v>75</v>
       </c>
       <c r="BM2">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BN2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
+        <v>3.45</v>
+      </c>
+      <c r="BP2">
+        <v>30</v>
+      </c>
+      <c r="BQ2">
+        <v>4.8</v>
+      </c>
+      <c r="BR2">
+        <v>36</v>
+      </c>
+      <c r="BS2">
+        <v>4.9</v>
+      </c>
+      <c r="BT2">
+        <v>5.9</v>
+      </c>
+      <c r="BU2">
+        <v>4.2</v>
+      </c>
+      <c r="BV2">
+        <v>14.5</v>
+      </c>
+      <c r="BW2">
         <v>4.1</v>
       </c>
-      <c r="BP2">
-        <v>26</v>
-      </c>
-      <c r="BQ2">
-        <v>6.6</v>
-      </c>
-      <c r="BR2">
-        <v>30</v>
-      </c>
-      <c r="BS2">
-        <v>6.8</v>
-      </c>
-      <c r="BT2">
-        <v>5.5</v>
-      </c>
-      <c r="BU2">
+      <c r="BX2">
+        <v>24</v>
+      </c>
+      <c r="BY2">
         <v>4.6</v>
       </c>
-      <c r="BV2">
-        <v>13.5</v>
-      </c>
-      <c r="BW2">
-        <v>5.3</v>
-      </c>
-      <c r="BX2">
-        <v>22</v>
-      </c>
-      <c r="BY2">
-        <v>6.2</v>
-      </c>
       <c r="BZ2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="CA2">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="s">
         <v>156</v>
@@ -1320,19 +1320,19 @@
         <v>133</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1347,10 +1347,10 @@
         <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q3">
         <v>2.84</v>
@@ -1365,58 +1365,58 @@
         <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y3">
         <v>9.4</v>
       </c>
-      <c r="Y3">
-        <v>10</v>
-      </c>
       <c r="Z3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
         <v>8</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM3">
         <v>220</v>
@@ -1425,121 +1425,121 @@
         <v>55</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
+        <v>7</v>
+      </c>
+      <c r="BF3">
         <v>6.4</v>
       </c>
-      <c r="BF3">
-        <v>5.8</v>
-      </c>
       <c r="BG3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
         <v>2.64</v>
       </c>
       <c r="BI3">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.32</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
         <v>5.2</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="s">
         <v>156</v>
@@ -1571,13 +1571,13 @@
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.44</v>
@@ -1604,10 +1604,10 @@
         <v>3.7</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
         <v>1.17</v>
@@ -1655,16 +1655,16 @@
         <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM4">
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO4">
         <v>130</v>
@@ -1676,16 +1676,16 @@
         <v>17</v>
       </c>
       <c r="AR4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
         <v>21</v>
@@ -1694,7 +1694,7 @@
         <v>80</v>
       </c>
       <c r="AX4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY4">
         <v>9.6</v>
@@ -1715,10 +1715,10 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4">
         <v>100</v>
@@ -1727,61 +1727,61 @@
         <v>3.35</v>
       </c>
       <c r="BI4">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
         <v>12</v>
       </c>
       <c r="BQ4">
+        <v>9</v>
+      </c>
+      <c r="BR4">
+        <v>32</v>
+      </c>
+      <c r="BS4">
+        <v>7.8</v>
+      </c>
+      <c r="BT4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU4">
+        <v>7.2</v>
+      </c>
+      <c r="BV4">
+        <v>60</v>
+      </c>
+      <c r="BW4">
         <v>8.800000000000001</v>
       </c>
-      <c r="BR4">
-        <v>30</v>
-      </c>
-      <c r="BS4">
-        <v>8.6</v>
-      </c>
-      <c r="BT4">
-        <v>9.6</v>
-      </c>
-      <c r="BU4">
-        <v>7.6</v>
-      </c>
-      <c r="BV4">
-        <v>85</v>
-      </c>
-      <c r="BW4">
-        <v>10</v>
-      </c>
       <c r="BX4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BZ4">
         <v>24</v>
       </c>
       <c r="CA4">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="s">
         <v>156</v>
@@ -1804,19 +1804,19 @@
         <v>135</v>
       </c>
       <c r="F5">
+        <v>1.78</v>
+      </c>
+      <c r="G5">
         <v>1.79</v>
       </c>
-      <c r="G5">
-        <v>1.81</v>
-      </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
         <v>4.8</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>4.4</v>
@@ -1825,7 +1825,7 @@
         <v>1.33</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
         <v>5.1</v>
@@ -1834,7 +1834,7 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
         <v>1.7</v>
@@ -1843,10 +1843,10 @@
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U5">
         <v>2.34</v>
@@ -1855,7 +1855,7 @@
         <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X5">
         <v>21</v>
@@ -1867,34 +1867,34 @@
         <v>38</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>18</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF5">
         <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK5">
         <v>18</v>
@@ -1909,10 +1909,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
         <v>18.5</v>
@@ -1921,7 +1921,7 @@
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1945,10 +1945,10 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC5">
         <v>16</v>
@@ -1957,16 +1957,16 @@
         <v>25</v>
       </c>
       <c r="BE5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
         <v>38</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
         <v>3.35</v>
@@ -1975,22 +1975,22 @@
         <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BL5">
         <v>95</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
         <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
         <v>9.4</v>
@@ -1999,10 +1999,10 @@
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
         <v>6.8</v>
@@ -2011,19 +2011,19 @@
         <v>34</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5">
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
         <v>17</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CB5" t="s">
         <v>156</v>
@@ -2046,25 +2046,25 @@
         <v>136</v>
       </c>
       <c r="F6">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
         <v>3.65</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M6">
         <v>1.1</v>
@@ -2073,10 +2073,10 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
         <v>2.36</v>
@@ -2088,16 +2088,16 @@
         <v>4.6</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X6">
         <v>13.5</v>
@@ -2106,34 +2106,34 @@
         <v>20</v>
       </c>
       <c r="Z6">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AA6">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AB6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
         <v>32</v>
       </c>
       <c r="AE6">
+        <v>130</v>
+      </c>
+      <c r="AF6">
+        <v>9</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>36</v>
+      </c>
+      <c r="AI6">
         <v>140</v>
-      </c>
-      <c r="AF6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>950</v>
-      </c>
-      <c r="AI6">
-        <v>150</v>
       </c>
       <c r="AJ6">
         <v>19</v>
@@ -2151,7 +2151,7 @@
         <v>16</v>
       </c>
       <c r="AO6">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AP6">
         <v>9.199999999999999</v>
@@ -2160,94 +2160,94 @@
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU6">
         <v>8</v>
       </c>
       <c r="AV6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX6">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY6">
         <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC6">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>1.55</v>
       </c>
       <c r="BN6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO6">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BP6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ6">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BR6">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>11</v>
       </c>
       <c r="BT6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2327,7 +2327,7 @@
         <v>1.69</v>
       </c>
       <c r="S7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
         <v>1.53</v>
@@ -2348,19 +2348,19 @@
         <v>23</v>
       </c>
       <c r="Z7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA7">
         <v>80</v>
       </c>
       <c r="AB7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
         <v>38</v>
@@ -2375,7 +2375,7 @@
         <v>14.5</v>
       </c>
       <c r="AI7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ7">
         <v>24</v>
@@ -2399,7 +2399,7 @@
         <v>22</v>
       </c>
       <c r="AQ7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR7">
         <v>30</v>
@@ -2408,7 +2408,7 @@
         <v>65</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU7">
         <v>8.800000000000001</v>
@@ -2417,7 +2417,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX7">
         <v>14.5</v>
@@ -2438,52 +2438,52 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH7">
         <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
       </c>
       <c r="BK7">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7">
         <v>7.6</v>
@@ -2495,19 +2495,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>14</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
         <v>156</v>
@@ -2530,22 +2530,22 @@
         <v>138</v>
       </c>
       <c r="F8">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G8">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="H8">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I8">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2560,43 +2560,43 @@
         <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q8">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S8">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T8">
         <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y8">
+        <v>14</v>
+      </c>
+      <c r="Z8">
+        <v>19.5</v>
+      </c>
+      <c r="AA8">
+        <v>40</v>
+      </c>
+      <c r="AB8">
         <v>13.5</v>
-      </c>
-      <c r="Z8">
-        <v>19</v>
-      </c>
-      <c r="AA8">
-        <v>80</v>
-      </c>
-      <c r="AB8">
-        <v>14.5</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
@@ -2605,13 +2605,13 @@
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>15.5</v>
@@ -2620,13 +2620,13 @@
         <v>34</v>
       </c>
       <c r="AJ8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>70</v>
@@ -2635,25 +2635,25 @@
         <v>22</v>
       </c>
       <c r="AO8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ8">
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
         <v>11</v>
@@ -2662,10 +2662,10 @@
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
         <v>14</v>
@@ -2686,7 +2686,7 @@
         <v>32</v>
       </c>
       <c r="BF8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG8">
         <v>16</v>
@@ -2695,61 +2695,61 @@
         <v>3.95</v>
       </c>
       <c r="BI8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
         <v>21</v>
       </c>
       <c r="BQ8">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BV8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BW8">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY8">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="s">
         <v>156</v>
@@ -2772,19 +2772,19 @@
         <v>139</v>
       </c>
       <c r="F9">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G9">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H9">
+        <v>4.6</v>
+      </c>
+      <c r="I9">
         <v>4.8</v>
       </c>
-      <c r="I9">
-        <v>4.9</v>
-      </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -2799,7 +2799,7 @@
         <v>5.3</v>
       </c>
       <c r="O9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
         <v>2.48</v>
@@ -2811,19 +2811,19 @@
         <v>1.59</v>
       </c>
       <c r="S9">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T9">
         <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X9">
         <v>23</v>
@@ -2832,7 +2832,7 @@
         <v>22</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2844,13 +2844,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -2871,7 +2871,7 @@
         <v>27</v>
       </c>
       <c r="AM9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN9">
         <v>8.199999999999999</v>
@@ -2886,10 +2886,10 @@
         <v>19.5</v>
       </c>
       <c r="AR9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT9">
         <v>11</v>
@@ -2898,10 +2898,10 @@
         <v>9</v>
       </c>
       <c r="AV9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2910,16 +2910,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB9">
         <v>17.5</v>
       </c>
       <c r="BC9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD9">
         <v>24</v>
@@ -2937,19 +2937,19 @@
         <v>4.2</v>
       </c>
       <c r="BI9">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
@@ -2961,37 +2961,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ9">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
         <v>22</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ9">
         <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>156</v>
@@ -3017,13 +3017,13 @@
         <v>2.7</v>
       </c>
       <c r="G10">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="H10">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I10">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J10">
         <v>3.4</v>
@@ -3044,10 +3044,10 @@
         <v>1.3</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R10">
         <v>1.4</v>
@@ -3056,16 +3056,16 @@
         <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X10">
         <v>17.5</v>
@@ -3077,7 +3077,7 @@
         <v>22</v>
       </c>
       <c r="AA10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB10">
         <v>14</v>
@@ -3098,88 +3098,88 @@
         <v>14.5</v>
       </c>
       <c r="AH10">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP10">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS10">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT10">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX10">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB10">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC10">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD10">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE10">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF10">
+        <v>18</v>
+      </c>
+      <c r="BG10">
         <v>17.5</v>
       </c>
-      <c r="BG10">
-        <v>17</v>
-      </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI10">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10">
         <v>9.199999999999999</v>
@@ -3191,7 +3191,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="BN10">
         <v>5.9</v>
@@ -3203,7 +3203,7 @@
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3218,7 +3218,7 @@
         <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW10">
         <v>9.199999999999999</v>
@@ -3227,7 +3227,7 @@
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3256,16 +3256,16 @@
         <v>141</v>
       </c>
       <c r="F11">
+        <v>1.53</v>
+      </c>
+      <c r="G11">
         <v>1.55</v>
-      </c>
-      <c r="G11">
-        <v>1.56</v>
       </c>
       <c r="H11">
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>4.7</v>
@@ -3286,13 +3286,13 @@
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q11">
         <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S11">
         <v>2.72</v>
@@ -3307,7 +3307,7 @@
         <v>1.16</v>
       </c>
       <c r="W11">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X11">
         <v>23</v>
@@ -3346,10 +3346,10 @@
         <v>80</v>
       </c>
       <c r="AJ11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL11">
         <v>30</v>
@@ -3358,7 +3358,7 @@
         <v>100</v>
       </c>
       <c r="AN11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO11">
         <v>95</v>
@@ -3373,10 +3373,10 @@
         <v>50</v>
       </c>
       <c r="AS11">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11">
         <v>9.800000000000001</v>
@@ -3385,7 +3385,7 @@
         <v>22</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX11">
         <v>9.199999999999999</v>
@@ -3397,7 +3397,7 @@
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB11">
         <v>13</v>
@@ -3412,7 +3412,7 @@
         <v>38</v>
       </c>
       <c r="BF11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG11">
         <v>36</v>
@@ -3427,13 +3427,13 @@
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN11">
         <v>4.4</v>
@@ -3442,7 +3442,7 @@
         <v>3.4</v>
       </c>
       <c r="BP11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ11">
         <v>4.8</v>
@@ -3454,7 +3454,7 @@
         <v>6.8</v>
       </c>
       <c r="BT11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU11">
         <v>5.2</v>
@@ -3475,7 +3475,7 @@
         <v>14.5</v>
       </c>
       <c r="CA11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB11" t="s">
         <v>156</v>
@@ -3501,7 +3501,7 @@
         <v>2.3</v>
       </c>
       <c r="G12">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
         <v>2.98</v>
@@ -3543,10 +3543,10 @@
         <v>1.46</v>
       </c>
       <c r="U12">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W12">
         <v>1.74</v>
@@ -3558,7 +3558,7 @@
         <v>22</v>
       </c>
       <c r="Z12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA12">
         <v>55</v>
@@ -3582,19 +3582,19 @@
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK12">
         <v>21</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM12">
         <v>46</v>
@@ -3606,7 +3606,7 @@
         <v>15</v>
       </c>
       <c r="AP12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3621,7 +3621,7 @@
         <v>17</v>
       </c>
       <c r="AU12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV12">
         <v>13</v>
@@ -3633,7 +3633,7 @@
         <v>18.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
         <v>12</v>
@@ -3642,82 +3642,82 @@
         <v>26</v>
       </c>
       <c r="BB12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC12">
         <v>18.5</v>
       </c>
       <c r="BD12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE12">
         <v>38</v>
       </c>
       <c r="BF12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BL12">
         <v>65</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BN12">
         <v>6.2</v>
       </c>
       <c r="BO12">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ12">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BR12">
         <v>22</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU12">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BW12">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BZ12">
         <v>13</v>
       </c>
       <c r="CA12">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="s">
         <v>156</v>
@@ -3740,19 +3740,19 @@
         <v>143</v>
       </c>
       <c r="F13">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G13">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H13">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K13">
         <v>4.5</v>
@@ -3770,40 +3770,40 @@
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
         <v>1.4</v>
       </c>
       <c r="R13">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S13">
         <v>1.97</v>
       </c>
       <c r="T13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U13">
         <v>3.2</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="X13">
         <v>38</v>
       </c>
       <c r="Y13">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA13">
-        <v>550</v>
+        <v>70</v>
       </c>
       <c r="AB13">
         <v>20</v>
@@ -3812,13 +3812,13 @@
         <v>12</v>
       </c>
       <c r="AD13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3827,88 +3827,88 @@
         <v>14</v>
       </c>
       <c r="AI13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ13">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM13">
         <v>40</v>
       </c>
       <c r="AN13">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO13">
+        <v>16</v>
+      </c>
+      <c r="AP13">
+        <v>32</v>
+      </c>
+      <c r="AQ13">
+        <v>24</v>
+      </c>
+      <c r="AR13">
+        <v>32</v>
+      </c>
+      <c r="AS13">
+        <v>55</v>
+      </c>
+      <c r="AT13">
+        <v>17.5</v>
+      </c>
+      <c r="AU13">
+        <v>10.5</v>
+      </c>
+      <c r="AV13">
         <v>14.5</v>
       </c>
-      <c r="AP13">
-        <v>24</v>
-      </c>
-      <c r="AQ13">
-        <v>22</v>
-      </c>
-      <c r="AR13">
-        <v>20</v>
-      </c>
-      <c r="AS13">
-        <v>42</v>
-      </c>
-      <c r="AT13">
+      <c r="AW13">
+        <v>28</v>
+      </c>
+      <c r="AX13">
         <v>18</v>
       </c>
-      <c r="AU13">
-        <v>11</v>
-      </c>
-      <c r="AV13">
-        <v>13.5</v>
-      </c>
-      <c r="AW13">
-        <v>18.5</v>
-      </c>
-      <c r="AX13">
-        <v>18.5</v>
-      </c>
       <c r="AY13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13">
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BB13">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BC13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE13">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BF13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI13">
         <v>4.4</v>
       </c>
       <c r="BJ13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK13">
         <v>5.4</v>
@@ -3917,43 +3917,43 @@
         <v>55</v>
       </c>
       <c r="BM13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN13">
         <v>6.2</v>
       </c>
       <c r="BO13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ13">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR13">
         <v>19</v>
       </c>
       <c r="BS13">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU13">
         <v>4.9</v>
       </c>
       <c r="BV13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW13">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY13">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BZ13">
         <v>11</v>
@@ -3991,13 +3991,13 @@
         <v>2.4</v>
       </c>
       <c r="I14">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J14">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L14">
         <v>1.37</v>
@@ -4024,13 +4024,13 @@
         <v>2.86</v>
       </c>
       <c r="T14">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.41</v>
@@ -4060,13 +4060,13 @@
         <v>40</v>
       </c>
       <c r="AF14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG14">
         <v>14</v>
       </c>
       <c r="AH14">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI14">
         <v>55</v>
@@ -4227,16 +4227,16 @@
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H15">
         <v>2.98</v>
       </c>
       <c r="I15">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4272,10 +4272,10 @@
         <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4475,7 +4475,7 @@
         <v>2.7</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J16">
         <v>3.65</v>
@@ -4505,7 +4505,7 @@
         <v>1.5</v>
       </c>
       <c r="S16">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T16">
         <v>1.56</v>
@@ -4514,7 +4514,7 @@
         <v>2.42</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
         <v>1.58</v>
@@ -4523,7 +4523,7 @@
         <v>24</v>
       </c>
       <c r="Y16">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z16">
         <v>23</v>
@@ -4568,19 +4568,19 @@
         <v>75</v>
       </c>
       <c r="AN16">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO16">
         <v>20</v>
       </c>
       <c r="AP16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ16">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS16">
         <v>32</v>
@@ -4589,10 +4589,10 @@
         <v>10.5</v>
       </c>
       <c r="AU16">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW16">
         <v>21</v>
@@ -4607,19 +4607,19 @@
         <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE16">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF16">
         <v>13</v>
@@ -4711,25 +4711,25 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H17">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="I17">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="J17">
         <v>6.6</v>
       </c>
       <c r="K17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L17">
         <v>1.25</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
         <v>6.2</v>
@@ -4738,13 +4738,13 @@
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
         <v>1.47</v>
       </c>
       <c r="R17">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S17">
         <v>2.18</v>
@@ -4756,7 +4756,7 @@
         <v>1.79</v>
       </c>
       <c r="V17">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -4813,13 +4813,13 @@
         <v>310</v>
       </c>
       <c r="AO17">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AP17">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR17">
         <v>7.4</v>
@@ -4828,7 +4828,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT17">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AU17">
         <v>15</v>
@@ -4840,31 +4840,31 @@
         <v>11</v>
       </c>
       <c r="AX17">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AY17">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ17">
+        <v>6</v>
+      </c>
+      <c r="BA17">
+        <v>6.2</v>
+      </c>
+      <c r="BB17">
+        <v>7.4</v>
+      </c>
+      <c r="BC17">
+        <v>7</v>
+      </c>
+      <c r="BD17">
+        <v>7</v>
+      </c>
+      <c r="BE17">
+        <v>7</v>
+      </c>
+      <c r="BF17">
         <v>7.2</v>
-      </c>
-      <c r="BA17">
-        <v>7.6</v>
-      </c>
-      <c r="BB17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF17">
-        <v>9</v>
       </c>
       <c r="BG17">
         <v>3.4</v>
@@ -4950,7 +4950,7 @@
         <v>148</v>
       </c>
       <c r="F18">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G18">
         <v>2.6</v>
@@ -4959,7 +4959,7 @@
         <v>2.96</v>
       </c>
       <c r="I18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>3.55</v>
@@ -4986,7 +4986,7 @@
         <v>2</v>
       </c>
       <c r="R18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18">
         <v>3.4</v>
@@ -4995,10 +4995,10 @@
         <v>1.75</v>
       </c>
       <c r="U18">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
         <v>1.62</v>
@@ -5022,7 +5022,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE18">
         <v>36</v>
@@ -5037,7 +5037,7 @@
         <v>18</v>
       </c>
       <c r="AI18">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ18">
         <v>40</v>
@@ -5103,7 +5103,7 @@
         <v>34</v>
       </c>
       <c r="BE18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF18">
         <v>20</v>
@@ -5115,19 +5115,19 @@
         <v>3.75</v>
       </c>
       <c r="BI18">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18">
         <v>11</v>
       </c>
       <c r="BK18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
@@ -5139,13 +5139,13 @@
         <v>23</v>
       </c>
       <c r="BQ18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR18">
         <v>38</v>
       </c>
       <c r="BS18">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT18">
         <v>6.8</v>
@@ -5157,16 +5157,16 @@
         <v>26</v>
       </c>
       <c r="BW18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BX18">
         <v>40</v>
       </c>
       <c r="BY18">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BZ18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="CA18">
         <v>5</v>
@@ -5195,10 +5195,10 @@
         <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H19">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I19">
         <v>3.9</v>
@@ -5237,13 +5237,13 @@
         <v>2.24</v>
       </c>
       <c r="U19">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V19">
         <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -5255,7 +5255,7 @@
         <v>24</v>
       </c>
       <c r="AA19">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -5354,25 +5354,25 @@
         <v>85</v>
       </c>
       <c r="BH19">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ19">
         <v>11.5</v>
       </c>
       <c r="BK19">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BL19">
         <v>260</v>
       </c>
       <c r="BM19">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN19">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BO19">
         <v>4.5</v>
@@ -5381,37 +5381,37 @@
         <v>21</v>
       </c>
       <c r="BQ19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BR19">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BS19">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT19">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BU19">
         <v>6.2</v>
       </c>
       <c r="BV19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BW19">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX19">
+        <v>75</v>
+      </c>
+      <c r="BY19">
+        <v>9</v>
+      </c>
+      <c r="BZ19">
         <v>65</v>
       </c>
-      <c r="BY19">
-        <v>15.5</v>
-      </c>
-      <c r="BZ19">
-        <v>55</v>
-      </c>
       <c r="CA19">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="s">
         <v>156</v>
@@ -5437,16 +5437,16 @@
         <v>2.34</v>
       </c>
       <c r="G20">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H20">
         <v>2.92</v>
       </c>
       <c r="I20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J20">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <v>3.9</v>
@@ -5473,7 +5473,7 @@
         <v>1.35</v>
       </c>
       <c r="S20">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T20">
         <v>1.7</v>
@@ -5482,10 +5482,10 @@
         <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X20">
         <v>17</v>
@@ -5512,7 +5512,7 @@
         <v>42</v>
       </c>
       <c r="AF20">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG20">
         <v>13.5</v>
@@ -5557,19 +5557,19 @@
         <v>3.7</v>
       </c>
       <c r="AU20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV20">
         <v>3.9</v>
       </c>
       <c r="AW20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX20">
         <v>4.1</v>
       </c>
       <c r="AY20">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ20">
         <v>4.1</v>
@@ -5578,7 +5578,7 @@
         <v>4.8</v>
       </c>
       <c r="BB20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC20">
         <v>4.5</v>
@@ -5593,7 +5593,7 @@
         <v>4.3</v>
       </c>
       <c r="BG20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH20">
         <v>3.55</v>
@@ -5676,10 +5676,10 @@
         <v>151</v>
       </c>
       <c r="F21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G21">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="H21">
         <v>7.2</v>
@@ -5688,10 +5688,10 @@
         <v>8.4</v>
       </c>
       <c r="J21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5706,7 +5706,7 @@
         <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q21">
         <v>2.14</v>
@@ -5715,22 +5715,22 @@
         <v>1.27</v>
       </c>
       <c r="S21">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T21">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U21">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V21">
         <v>1.13</v>
       </c>
       <c r="W21">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="X21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y21">
         <v>25</v>
@@ -5742,13 +5742,13 @@
         <v>350</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9.800000000000001</v>
       </c>
       <c r="AD21">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE21">
         <v>180</v>
@@ -5757,16 +5757,16 @@
         <v>9</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH21">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI21">
         <v>170</v>
       </c>
       <c r="AJ21">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AK21">
         <v>24</v>
@@ -5787,13 +5787,13 @@
         <v>10</v>
       </c>
       <c r="AQ21">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AR21">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AS21">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT21">
         <v>5.8</v>
@@ -5805,7 +5805,7 @@
         <v>21</v>
       </c>
       <c r="AW21">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX21">
         <v>7.2</v>
@@ -5817,7 +5817,7 @@
         <v>21</v>
       </c>
       <c r="BA21">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB21">
         <v>12.5</v>
@@ -5826,76 +5826,76 @@
         <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE21">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF21">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG21">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH21">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>156</v>
@@ -5918,226 +5918,226 @@
         <v>152</v>
       </c>
       <c r="F22">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="G22">
         <v>3.3</v>
       </c>
       <c r="H22">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="I22">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="J22">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K22">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="L22">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N22">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="P22">
         <v>1.54</v>
       </c>
       <c r="Q22">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S22">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="T22">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W22">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X22">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z22">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA22">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB22">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE22">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF22">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AG22">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH22">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI22">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ22">
+        <v>75</v>
+      </c>
+      <c r="AK22">
         <v>65</v>
       </c>
-      <c r="AK22">
-        <v>55</v>
-      </c>
       <c r="AL22">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AM22">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO22">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP22">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="AQ22">
-        <v>3.35</v>
+        <v>2.02</v>
       </c>
       <c r="AR22">
-        <v>4.1</v>
+        <v>2.24</v>
       </c>
       <c r="AS22">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="AT22">
-        <v>3.35</v>
+        <v>2.02</v>
       </c>
       <c r="AU22">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AV22">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="AW22">
-        <v>4.7</v>
+        <v>2.36</v>
       </c>
       <c r="AX22">
-        <v>4.1</v>
+        <v>2.24</v>
       </c>
       <c r="AY22">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="AZ22">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="BA22">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="BB22">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="BC22">
-        <v>4.7</v>
+        <v>2.36</v>
       </c>
       <c r="BD22">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="BE22">
-        <v>5</v>
+        <v>2.46</v>
       </c>
       <c r="BF22">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="BG22">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="BH22">
         <v>2.7</v>
       </c>
       <c r="BI22">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BJ22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK22">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>2.28</v>
+        <v>11.5</v>
       </c>
       <c r="BN22">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO22">
         <v>4.5</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ22">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS22">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT22">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU22">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW22">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BX22">
         <v>55</v>
       </c>
       <c r="BY22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CB22" t="s">
         <v>156</v>
@@ -6160,22 +6160,22 @@
         <v>153</v>
       </c>
       <c r="F23">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G23">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H23">
         <v>3.2</v>
       </c>
       <c r="I23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J23">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K23">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6190,10 +6190,10 @@
         <v>1.43</v>
       </c>
       <c r="P23">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Q23">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="R23">
         <v>1.24</v>
@@ -6202,10 +6202,10 @@
         <v>4.5</v>
       </c>
       <c r="T23">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
         <v>1.39</v>
@@ -6214,112 +6214,112 @@
         <v>1.6</v>
       </c>
       <c r="X23">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
         <v>7.8</v>
       </c>
       <c r="AD23">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>9</v>
+        <v>1.15</v>
       </c>
       <c r="AQ23">
-        <v>9.199999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR23">
-        <v>4.5</v>
+        <v>1.15</v>
       </c>
       <c r="AS23">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="AT23">
-        <v>7.6</v>
+        <v>1.15</v>
       </c>
       <c r="AU23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>13</v>
+        <v>1.15</v>
       </c>
       <c r="AW23">
-        <v>5</v>
+        <v>1.15</v>
       </c>
       <c r="AX23">
-        <v>13.5</v>
+        <v>1.15</v>
       </c>
       <c r="AY23">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="AZ23">
-        <v>4.4</v>
+        <v>1.15</v>
       </c>
       <c r="BA23">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="BB23">
-        <v>4.9</v>
+        <v>1.15</v>
       </c>
       <c r="BC23">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="BD23">
-        <v>5</v>
+        <v>1.15</v>
       </c>
       <c r="BE23">
-        <v>5.3</v>
+        <v>1.15</v>
       </c>
       <c r="BF23">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="BG23">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="BH23">
         <v>3.25</v>
@@ -6355,7 +6355,7 @@
         <v>46</v>
       </c>
       <c r="BS23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT23">
         <v>7.2</v>
@@ -6364,7 +6364,7 @@
         <v>5</v>
       </c>
       <c r="BV23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW23">
         <v>5.2</v>
@@ -6373,13 +6373,13 @@
         <v>55</v>
       </c>
       <c r="BY23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ23">
         <v>46</v>
       </c>
       <c r="CA23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB23" t="s">
         <v>156</v>
@@ -6405,19 +6405,19 @@
         <v>1.61</v>
       </c>
       <c r="G24">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H24">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
         <v>3.95</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L24">
         <v>1.37</v>
@@ -6426,10 +6426,10 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O24">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P24">
         <v>1.93</v>
@@ -6441,37 +6441,37 @@
         <v>1.36</v>
       </c>
       <c r="S24">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T24">
         <v>1.94</v>
       </c>
       <c r="U24">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W24">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z24">
         <v>60</v>
       </c>
       <c r="AA24">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB24">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD24">
         <v>27</v>
@@ -6480,37 +6480,37 @@
         <v>120</v>
       </c>
       <c r="AF24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH24">
         <v>24</v>
       </c>
       <c r="AI24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK24">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL24">
         <v>42</v>
       </c>
       <c r="AM24">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="AN24">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO24">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ24">
         <v>18.5</v>
@@ -6519,37 +6519,37 @@
         <v>38</v>
       </c>
       <c r="AS24">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV24">
         <v>18</v>
       </c>
       <c r="AW24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY24">
         <v>9</v>
       </c>
       <c r="AZ24">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB24">
         <v>13</v>
       </c>
       <c r="BC24">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BD24">
         <v>26</v>
@@ -6558,16 +6558,16 @@
         <v>9.6</v>
       </c>
       <c r="BF24">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI24">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ24">
         <v>11.5</v>
@@ -6579,7 +6579,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BN24">
         <v>4.1</v>
@@ -6588,34 +6588,34 @@
         <v>3</v>
       </c>
       <c r="BP24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU24">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6650,13 +6650,13 @@
         <v>1.59</v>
       </c>
       <c r="H25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25">
         <v>5</v>
@@ -6668,16 +6668,16 @@
         <v>1.08</v>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O25">
         <v>1.38</v>
       </c>
       <c r="P25">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q25">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R25">
         <v>1.27</v>
@@ -6686,16 +6686,16 @@
         <v>3.9</v>
       </c>
       <c r="T25">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U25">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V25">
         <v>1.11</v>
       </c>
       <c r="W25">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X25">
         <v>14.5</v>
@@ -6707,7 +6707,7 @@
         <v>85</v>
       </c>
       <c r="AA25">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AB25">
         <v>7.6</v>
@@ -6722,7 +6722,7 @@
         <v>200</v>
       </c>
       <c r="AF25">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG25">
         <v>12</v>
@@ -6755,13 +6755,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ25">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR25">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS25">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT25">
         <v>5.8</v>
@@ -6773,7 +6773,7 @@
         <v>5.2</v>
       </c>
       <c r="AW25">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX25">
         <v>6.8</v>
@@ -6785,7 +6785,7 @@
         <v>5.1</v>
       </c>
       <c r="BA25">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB25">
         <v>11.5</v>
@@ -6794,22 +6794,22 @@
         <v>16</v>
       </c>
       <c r="BD25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE25">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF25">
         <v>8.4</v>
       </c>
       <c r="BG25">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH25">
         <v>3.55</v>
       </c>
       <c r="BI25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ25">
         <v>14.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -484,7 +484,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 08:43:11</t>
+    <t>2026-08-19 10:51:58</t>
   </si>
 </sst>
 </file>
@@ -1078,79 +1078,79 @@
         <v>132</v>
       </c>
       <c r="F2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G2">
         <v>3.95</v>
       </c>
       <c r="H2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q2">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R2">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="S2">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T2">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U2">
         <v>2.62</v>
       </c>
       <c r="V2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W2">
         <v>1.33</v>
       </c>
       <c r="X2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z2">
         <v>15</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2">
         <v>10.5</v>
-      </c>
-      <c r="AD2">
-        <v>11</v>
       </c>
       <c r="AE2">
         <v>18</v>
@@ -1159,19 +1159,19 @@
         <v>32</v>
       </c>
       <c r="AG2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL2">
         <v>40</v>
@@ -1180,28 +1180,28 @@
         <v>60</v>
       </c>
       <c r="AN2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR2">
         <v>13.5</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AU2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV2">
         <v>9.800000000000001</v>
@@ -1228,76 +1228,76 @@
         <v>32</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2">
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BL2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BM2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BN2">
         <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BP2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2">
+        <v>5.2</v>
+      </c>
+      <c r="BT2">
+        <v>5.8</v>
+      </c>
+      <c r="BU2">
+        <v>4.1</v>
+      </c>
+      <c r="BV2">
+        <v>15</v>
+      </c>
+      <c r="BW2">
+        <v>4.4</v>
+      </c>
+      <c r="BX2">
+        <v>23</v>
+      </c>
+      <c r="BY2">
         <v>4.9</v>
-      </c>
-      <c r="BT2">
-        <v>5.9</v>
-      </c>
-      <c r="BU2">
-        <v>4.2</v>
-      </c>
-      <c r="BV2">
-        <v>14.5</v>
-      </c>
-      <c r="BW2">
-        <v>4.1</v>
-      </c>
-      <c r="BX2">
-        <v>24</v>
-      </c>
-      <c r="BY2">
-        <v>4.6</v>
       </c>
       <c r="BZ2">
         <v>16.5</v>
       </c>
       <c r="CA2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="s">
         <v>156</v>
@@ -1320,19 +1320,19 @@
         <v>133</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G3">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1344,16 +1344,16 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P3">
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
         <v>1.18</v>
@@ -1365,16 +1365,16 @@
         <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
         <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y3">
         <v>9.4</v>
@@ -1383,10 +1383,10 @@
         <v>25</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
         <v>8</v>
@@ -1398,7 +1398,7 @@
         <v>65</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
         <v>55</v>
@@ -1416,31 +1416,31 @@
         <v>46</v>
       </c>
       <c r="AL3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM3">
         <v>220</v>
       </c>
       <c r="AN3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP3">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR3">
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
@@ -1449,10 +1449,10 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
         <v>11.5</v>
@@ -1461,31 +1461,31 @@
         <v>20</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
         <v>2.64</v>
       </c>
       <c r="BI3">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1497,7 +1497,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BN3">
         <v>5.4</v>
@@ -1515,16 +1515,16 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT3">
         <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
         <v>11.5</v>
@@ -1533,13 +1533,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>156</v>
@@ -1562,22 +1562,22 @@
         <v>134</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G4">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="H4">
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.44</v>
@@ -1586,34 +1586,34 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
         <v>1.34</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1625,163 +1625,163 @@
         <v>55</v>
       </c>
       <c r="AA4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AK4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM4">
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP4">
         <v>12</v>
       </c>
       <c r="AQ4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR4">
         <v>42</v>
       </c>
       <c r="AS4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BB4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC4">
+        <v>17</v>
+      </c>
+      <c r="BD4">
+        <v>36</v>
+      </c>
+      <c r="BE4">
+        <v>90</v>
+      </c>
+      <c r="BF4">
+        <v>10</v>
+      </c>
+      <c r="BG4">
         <v>16.5</v>
-      </c>
-      <c r="BD4">
-        <v>34</v>
-      </c>
-      <c r="BE4">
-        <v>13.5</v>
-      </c>
-      <c r="BF4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG4">
-        <v>100</v>
       </c>
       <c r="BH4">
         <v>3.35</v>
       </c>
       <c r="BI4">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
+        <v>11.5</v>
+      </c>
+      <c r="BK4">
+        <v>7.4</v>
+      </c>
+      <c r="BL4">
+        <v>160</v>
+      </c>
+      <c r="BM4">
         <v>12</v>
       </c>
-      <c r="BK4">
-        <v>9</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP4">
         <v>12</v>
       </c>
       <c r="BQ4">
+        <v>9.6</v>
+      </c>
+      <c r="BR4">
+        <v>30</v>
+      </c>
+      <c r="BS4">
         <v>9</v>
       </c>
-      <c r="BR4">
-        <v>32</v>
-      </c>
-      <c r="BS4">
-        <v>7.8</v>
-      </c>
       <c r="BT4">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>60</v>
       </c>
       <c r="BW4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>24</v>
       </c>
       <c r="CA4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="s">
         <v>156</v>
@@ -1804,25 +1804,25 @@
         <v>135</v>
       </c>
       <c r="F5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G5">
         <v>1.79</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J5">
         <v>4.3</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1834,25 +1834,25 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T5">
         <v>1.7</v>
       </c>
       <c r="U5">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
         <v>2.26</v>
@@ -1864,7 +1864,7 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA5">
         <v>110</v>
@@ -1873,31 +1873,31 @@
         <v>11</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE5">
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL5">
         <v>29</v>
@@ -1906,19 +1906,19 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
         <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS5">
         <v>80</v>
@@ -1927,22 +1927,22 @@
         <v>10</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>46</v>
@@ -1951,25 +1951,25 @@
         <v>17.5</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
         <v>25</v>
       </c>
       <c r="BE5">
+        <v>48</v>
+      </c>
+      <c r="BF5">
+        <v>8</v>
+      </c>
+      <c r="BG5">
         <v>36</v>
-      </c>
-      <c r="BF5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG5">
-        <v>38</v>
       </c>
       <c r="BH5">
         <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5">
         <v>9.6</v>
@@ -1981,16 +1981,16 @@
         <v>95</v>
       </c>
       <c r="BM5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
         <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
         <v>9.4</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT5">
         <v>8.6</v>
@@ -2008,19 +2008,19 @@
         <v>6.8</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA5">
         <v>12</v>
@@ -2046,7 +2046,7 @@
         <v>136</v>
       </c>
       <c r="F6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G6">
         <v>1.74</v>
@@ -2055,13 +2055,13 @@
         <v>6.2</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>3.65</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2097,16 +2097,16 @@
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA6">
         <v>260</v>
@@ -2115,10 +2115,10 @@
         <v>6.2</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE6">
         <v>130</v>
@@ -2130,82 +2130,82 @@
         <v>11</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK6">
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO6">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AP6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR6">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AS6">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AT6">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AU6">
         <v>8</v>
       </c>
       <c r="AV6">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AW6">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BA6">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="BB6">
         <v>15</v>
       </c>
       <c r="BC6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>6.4</v>
+        <v>42</v>
       </c>
       <c r="BE6">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BF6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BH6">
         <v>2.96</v>
@@ -2288,85 +2288,85 @@
         <v>137</v>
       </c>
       <c r="F7">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H7">
+        <v>3.8</v>
+      </c>
+      <c r="I7">
         <v>3.9</v>
       </c>
-      <c r="I7">
-        <v>4.1</v>
-      </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R7">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="S7">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U7">
         <v>2.7</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
+        <v>15.5</v>
+      </c>
+      <c r="AE7">
+        <v>40</v>
+      </c>
+      <c r="AF7">
         <v>16</v>
-      </c>
-      <c r="AE7">
-        <v>38</v>
-      </c>
-      <c r="AF7">
-        <v>15.5</v>
       </c>
       <c r="AG7">
         <v>11</v>
@@ -2375,82 +2375,82 @@
         <v>14.5</v>
       </c>
       <c r="AI7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK7">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM7">
         <v>60</v>
       </c>
       <c r="AN7">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO7">
         <v>26</v>
       </c>
       <c r="AP7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ7">
         <v>19.5</v>
       </c>
       <c r="AR7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AX7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
         <v>34</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF7">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
         <v>24</v>
       </c>
       <c r="BH7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI7">
         <v>3.55</v>
@@ -2462,13 +2462,13 @@
         <v>6.8</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
         <v>4.7</v>
@@ -2483,28 +2483,28 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
         <v>6</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CA7">
         <v>10.5</v>
@@ -2530,22 +2530,22 @@
         <v>138</v>
       </c>
       <c r="F8">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="G8">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H8">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="I8">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2554,34 +2554,34 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O8">
         <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S8">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U8">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V8">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X8">
         <v>18</v>
@@ -2590,10 +2590,10 @@
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB8">
         <v>13.5</v>
@@ -2605,40 +2605,40 @@
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AF8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8">
         <v>15.5</v>
       </c>
       <c r="AI8">
+        <v>36</v>
+      </c>
+      <c r="AJ8">
+        <v>40</v>
+      </c>
+      <c r="AK8">
         <v>34</v>
       </c>
-      <c r="AJ8">
-        <v>44</v>
-      </c>
-      <c r="AK8">
-        <v>28</v>
-      </c>
       <c r="AL8">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AM8">
         <v>70</v>
       </c>
       <c r="AN8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
         <v>12</v>
@@ -2653,43 +2653,43 @@
         <v>12.5</v>
       </c>
       <c r="AU8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV8">
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY8">
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
         <v>30</v>
       </c>
       <c r="BB8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE8">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH8">
         <v>3.95</v>
@@ -2701,55 +2701,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT8">
         <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX8">
         <v>30</v>
       </c>
       <c r="BY8">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>156</v>
@@ -2772,16 +2772,16 @@
         <v>139</v>
       </c>
       <c r="F9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9">
         <v>4.2</v>
@@ -2796,43 +2796,43 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S9">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T9">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="X9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z9">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2850,31 +2850,31 @@
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>17</v>
       </c>
       <c r="AI9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ9">
         <v>19.5</v>
       </c>
       <c r="AK9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL9">
         <v>27</v>
       </c>
       <c r="AM9">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO9">
         <v>44</v>
@@ -2883,10 +2883,10 @@
         <v>20</v>
       </c>
       <c r="AQ9">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS9">
         <v>42</v>
@@ -2916,10 +2916,10 @@
         <v>42</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD9">
         <v>24</v>
@@ -2928,7 +2928,7 @@
         <v>60</v>
       </c>
       <c r="BF9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG9">
         <v>38</v>
@@ -2937,28 +2937,28 @@
         <v>4.2</v>
       </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9">
         <v>9</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO9">
         <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ9">
         <v>8.800000000000001</v>
@@ -2967,31 +2967,31 @@
         <v>22</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU9">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV9">
         <v>32</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>36</v>
       </c>
       <c r="BY9">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
         <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="s">
         <v>156</v>
@@ -3017,7 +3017,7 @@
         <v>2.7</v>
       </c>
       <c r="G10">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H10">
         <v>2.62</v>
@@ -3050,22 +3050,22 @@
         <v>1.89</v>
       </c>
       <c r="R10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
         <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
         <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X10">
         <v>17.5</v>
@@ -3077,7 +3077,7 @@
         <v>22</v>
       </c>
       <c r="AA10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB10">
         <v>14</v>
@@ -3098,7 +3098,7 @@
         <v>14.5</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI10">
         <v>46</v>
@@ -3113,7 +3113,7 @@
         <v>46</v>
       </c>
       <c r="AM10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN10">
         <v>29</v>
@@ -3131,7 +3131,7 @@
         <v>4.2</v>
       </c>
       <c r="AS10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT10">
         <v>9.4</v>
@@ -3155,7 +3155,7 @@
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB10">
         <v>4.7</v>
@@ -3164,7 +3164,7 @@
         <v>4.5</v>
       </c>
       <c r="BD10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE10">
         <v>4.9</v>
@@ -3256,46 +3256,46 @@
         <v>141</v>
       </c>
       <c r="F11">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="G11">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
         <v>6.6</v>
       </c>
-      <c r="I11">
-        <v>7.2</v>
-      </c>
       <c r="J11">
+        <v>4.5</v>
+      </c>
+      <c r="K11">
         <v>4.7</v>
       </c>
-      <c r="K11">
+      <c r="L11">
+        <v>1.33</v>
+      </c>
+      <c r="M11">
+        <v>1.05</v>
+      </c>
+      <c r="N11">
         <v>4.9</v>
       </c>
-      <c r="L11">
-        <v>1.31</v>
-      </c>
-      <c r="M11">
-        <v>1.04</v>
-      </c>
-      <c r="N11">
-        <v>5.2</v>
-      </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P11">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R11">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S11">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T11">
         <v>1.81</v>
@@ -3304,25 +3304,25 @@
         <v>2.14</v>
       </c>
       <c r="V11">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W11">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA11">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11">
         <v>10.5</v>
@@ -3331,151 +3331,151 @@
         <v>25</v>
       </c>
       <c r="AE11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH11">
         <v>21</v>
       </c>
       <c r="AI11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AO11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AQ11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AR11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS11">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AT11">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW11">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY11">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD11">
         <v>27</v>
       </c>
       <c r="BE11">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF11">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
         <v>3.35</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
         <v>4.4</v>
       </c>
       <c r="BO11">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ11">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BR11">
         <v>23</v>
       </c>
       <c r="BS11">
+        <v>7.8</v>
+      </c>
+      <c r="BT11">
+        <v>10.5</v>
+      </c>
+      <c r="BU11">
+        <v>5.5</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX11">
+        <v>55</v>
+      </c>
+      <c r="BY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ11">
+        <v>16</v>
+      </c>
+      <c r="CA11">
         <v>6.8</v>
-      </c>
-      <c r="BT11">
-        <v>11.5</v>
-      </c>
-      <c r="BU11">
-        <v>5.2</v>
-      </c>
-      <c r="BV11">
-        <v>60</v>
-      </c>
-      <c r="BW11">
-        <v>8.4</v>
-      </c>
-      <c r="BX11">
-        <v>60</v>
-      </c>
-      <c r="BY11">
-        <v>8.4</v>
-      </c>
-      <c r="BZ11">
-        <v>14.5</v>
-      </c>
-      <c r="CA11">
-        <v>5.8</v>
       </c>
       <c r="CB11" t="s">
         <v>156</v>
@@ -3498,16 +3498,16 @@
         <v>142</v>
       </c>
       <c r="F12">
+        <v>2.28</v>
+      </c>
+      <c r="G12">
         <v>2.3</v>
       </c>
-      <c r="G12">
-        <v>2.34</v>
-      </c>
       <c r="H12">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J12">
         <v>4.1</v>
@@ -3525,13 +3525,13 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P12">
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R12">
         <v>1.8</v>
@@ -3540,16 +3540,16 @@
         <v>2.18</v>
       </c>
       <c r="T12">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X12">
         <v>32</v>
@@ -3567,10 +3567,10 @@
         <v>18.5</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE12">
         <v>28</v>
@@ -3591,7 +3591,7 @@
         <v>34</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL12">
         <v>25</v>
@@ -3600,13 +3600,13 @@
         <v>46</v>
       </c>
       <c r="AN12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO12">
         <v>15</v>
       </c>
       <c r="AP12">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3621,7 +3621,7 @@
         <v>17</v>
       </c>
       <c r="AU12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
         <v>13</v>
@@ -3636,7 +3636,7 @@
         <v>11</v>
       </c>
       <c r="AZ12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA12">
         <v>26</v>
@@ -3654,7 +3654,7 @@
         <v>38</v>
       </c>
       <c r="BF12">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12">
         <v>13.5</v>
@@ -3663,19 +3663,19 @@
         <v>5.2</v>
       </c>
       <c r="BI12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
       </c>
       <c r="BK12">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
         <v>65</v>
       </c>
       <c r="BM12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12">
         <v>6.2</v>
@@ -3684,13 +3684,13 @@
         <v>4.5</v>
       </c>
       <c r="BP12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ12">
         <v>6</v>
       </c>
       <c r="BR12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS12">
         <v>6.8</v>
@@ -3702,22 +3702,22 @@
         <v>5.2</v>
       </c>
       <c r="BV12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX12">
         <v>25</v>
       </c>
       <c r="BY12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12">
         <v>13</v>
       </c>
       <c r="CA12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB12" t="s">
         <v>156</v>
@@ -3740,88 +3740,88 @@
         <v>143</v>
       </c>
       <c r="F13">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I13">
         <v>3.5</v>
       </c>
       <c r="J13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13">
         <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R13">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S13">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="T13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U13">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V13">
         <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Z13">
         <v>36</v>
       </c>
       <c r="AA13">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB13">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE13">
         <v>32</v>
       </c>
       <c r="AF13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
         <v>14</v>
@@ -3830,7 +3830,7 @@
         <v>30</v>
       </c>
       <c r="AJ13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK13">
         <v>18</v>
@@ -3839,22 +3839,22 @@
         <v>22</v>
       </c>
       <c r="AM13">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AN13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO13">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AP13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ13">
         <v>24</v>
       </c>
       <c r="AR13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS13">
         <v>55</v>
@@ -3872,7 +3872,7 @@
         <v>28</v>
       </c>
       <c r="AX13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY13">
         <v>10.5</v>
@@ -3896,16 +3896,16 @@
         <v>34</v>
       </c>
       <c r="BF13">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG13">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH13">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BI13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
@@ -3914,19 +3914,19 @@
         <v>5.4</v>
       </c>
       <c r="BL13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BM13">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BN13">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ13">
         <v>9.800000000000001</v>
@@ -3935,7 +3935,7 @@
         <v>19</v>
       </c>
       <c r="BS13">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BT13">
         <v>8</v>
@@ -3947,16 +3947,16 @@
         <v>23</v>
       </c>
       <c r="BW13">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX13">
         <v>25</v>
       </c>
       <c r="BY13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BZ13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA13">
         <v>7.2</v>
@@ -3982,16 +3982,16 @@
         <v>144</v>
       </c>
       <c r="F14">
+        <v>2.8</v>
+      </c>
+      <c r="G14">
+        <v>3.35</v>
+      </c>
+      <c r="H14">
+        <v>2.46</v>
+      </c>
+      <c r="I14">
         <v>2.82</v>
-      </c>
-      <c r="G14">
-        <v>3.6</v>
-      </c>
-      <c r="H14">
-        <v>2.4</v>
-      </c>
-      <c r="I14">
-        <v>2.74</v>
       </c>
       <c r="J14">
         <v>2.98</v>
@@ -4012,34 +4012,34 @@
         <v>1.29</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R14">
         <v>1.38</v>
       </c>
       <c r="S14">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
         <v>18.5</v>
@@ -4051,7 +4051,7 @@
         <v>13.5</v>
       </c>
       <c r="AC14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
         <v>12.5</v>
@@ -4060,7 +4060,7 @@
         <v>40</v>
       </c>
       <c r="AF14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG14">
         <v>14</v>
@@ -4087,106 +4087,106 @@
         <v>40</v>
       </c>
       <c r="AO14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP14">
+        <v>5.9</v>
+      </c>
+      <c r="AQ14">
+        <v>5.1</v>
+      </c>
+      <c r="AR14">
+        <v>5.9</v>
+      </c>
+      <c r="AS14">
+        <v>7</v>
+      </c>
+      <c r="AT14">
+        <v>5.2</v>
+      </c>
+      <c r="AU14">
+        <v>4.3</v>
+      </c>
+      <c r="AV14">
+        <v>5.1</v>
+      </c>
+      <c r="AW14">
+        <v>6.6</v>
+      </c>
+      <c r="AX14">
+        <v>6.2</v>
+      </c>
+      <c r="AY14">
+        <v>5.3</v>
+      </c>
+      <c r="AZ14">
         <v>5.7</v>
       </c>
-      <c r="AQ14">
-        <v>4.9</v>
-      </c>
-      <c r="AR14">
-        <v>5.7</v>
-      </c>
-      <c r="AS14">
+      <c r="BA14">
+        <v>7</v>
+      </c>
+      <c r="BB14">
+        <v>7.2</v>
+      </c>
+      <c r="BC14">
         <v>6.8</v>
       </c>
-      <c r="AT14">
-        <v>5.1</v>
-      </c>
-      <c r="AU14">
-        <v>4.1</v>
-      </c>
-      <c r="AV14">
-        <v>5</v>
-      </c>
-      <c r="AW14">
-        <v>6.4</v>
-      </c>
-      <c r="AX14">
-        <v>6</v>
-      </c>
-      <c r="AY14">
-        <v>5.2</v>
-      </c>
-      <c r="AZ14">
-        <v>5.6</v>
-      </c>
-      <c r="BA14">
-        <v>6.8</v>
-      </c>
-      <c r="BB14">
-        <v>7</v>
-      </c>
-      <c r="BC14">
-        <v>6.6</v>
-      </c>
       <c r="BD14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF14">
         <v>6.4</v>
       </c>
       <c r="BG14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI14">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14">
         <v>9.6</v>
       </c>
       <c r="BK14">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BN14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO14">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR14">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>2.52</v>
+        <v>7.8</v>
       </c>
       <c r="BT14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BU14">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW14">
         <v>6.8</v>
@@ -4227,16 +4227,16 @@
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H15">
         <v>2.98</v>
       </c>
       <c r="I15">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4272,10 +4272,10 @@
         <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4505,10 +4505,10 @@
         <v>1.5</v>
       </c>
       <c r="S16">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T16">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U16">
         <v>2.42</v>
@@ -4711,19 +4711,19 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="I17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K17">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="L17">
         <v>1.25</v>
@@ -4747,19 +4747,19 @@
         <v>1.69</v>
       </c>
       <c r="S17">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T17">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>34</v>
@@ -4771,7 +4771,7 @@
         <v>8.6</v>
       </c>
       <c r="AA17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB17">
         <v>60</v>
@@ -4792,7 +4792,7 @@
         <v>60</v>
       </c>
       <c r="AH17">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI17">
         <v>44</v>
@@ -4801,13 +4801,13 @@
         <v>1000</v>
       </c>
       <c r="AK17">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="AL17">
         <v>170</v>
       </c>
       <c r="AM17">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AN17">
         <v>310</v>
@@ -4816,13 +4816,13 @@
         <v>4.3</v>
       </c>
       <c r="AP17">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ17">
         <v>9.6</v>
       </c>
       <c r="AR17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS17">
         <v>8.199999999999999</v>
@@ -4840,7 +4840,7 @@
         <v>11</v>
       </c>
       <c r="AX17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY17">
         <v>6.4</v>
@@ -4852,43 +4852,43 @@
         <v>6.2</v>
       </c>
       <c r="BB17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC17">
         <v>7</v>
       </c>
       <c r="BD17">
+        <v>6.8</v>
+      </c>
+      <c r="BE17">
+        <v>6.8</v>
+      </c>
+      <c r="BF17">
         <v>7</v>
-      </c>
-      <c r="BE17">
-        <v>7</v>
-      </c>
-      <c r="BF17">
-        <v>7.2</v>
       </c>
       <c r="BG17">
         <v>3.4</v>
       </c>
       <c r="BH17">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BN17">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BO17">
         <v>4.7</v>
@@ -4897,19 +4897,19 @@
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR17">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BS17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU17">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BV17">
         <v>7.8</v>
@@ -4921,13 +4921,13 @@
         <v>25</v>
       </c>
       <c r="BY17">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BZ17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CA17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CB17" t="s">
         <v>156</v>
@@ -4950,16 +4950,16 @@
         <v>148</v>
       </c>
       <c r="F18">
+        <v>2.48</v>
+      </c>
+      <c r="G18">
         <v>2.58</v>
-      </c>
-      <c r="G18">
-        <v>2.6</v>
       </c>
       <c r="H18">
         <v>2.96</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J18">
         <v>3.55</v>
@@ -4974,19 +4974,19 @@
         <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
         <v>1.33</v>
       </c>
       <c r="P18">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
         <v>2</v>
       </c>
       <c r="R18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S18">
         <v>3.4</v>
@@ -4998,10 +4998,10 @@
         <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X18">
         <v>14.5</v>
@@ -5031,7 +5031,7 @@
         <v>17</v>
       </c>
       <c r="AG18">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH18">
         <v>18</v>
@@ -5040,7 +5040,7 @@
         <v>50</v>
       </c>
       <c r="AJ18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK18">
         <v>29</v>
@@ -5049,10 +5049,10 @@
         <v>42</v>
       </c>
       <c r="AM18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO18">
         <v>32</v>
@@ -5061,10 +5061,10 @@
         <v>11</v>
       </c>
       <c r="AQ18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS18">
         <v>40</v>
@@ -5103,7 +5103,7 @@
         <v>34</v>
       </c>
       <c r="BE18">
-        <v>75</v>
+        <v>10.5</v>
       </c>
       <c r="BF18">
         <v>20</v>
@@ -5121,13 +5121,13 @@
         <v>11</v>
       </c>
       <c r="BK18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BN18">
         <v>6.4</v>
@@ -5139,28 +5139,28 @@
         <v>23</v>
       </c>
       <c r="BQ18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR18">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS18">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BT18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW18">
         <v>4.8</v>
       </c>
       <c r="BX18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY18">
         <v>5.1</v>
@@ -5169,7 +5169,7 @@
         <v>32</v>
       </c>
       <c r="CA18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB18" t="s">
         <v>156</v>
@@ -5192,16 +5192,16 @@
         <v>149</v>
       </c>
       <c r="F19">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G19">
         <v>2.38</v>
       </c>
       <c r="H19">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I19">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J19">
         <v>3.1</v>
@@ -5222,7 +5222,7 @@
         <v>1.59</v>
       </c>
       <c r="P19">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q19">
         <v>2.86</v>
@@ -5234,13 +5234,13 @@
         <v>6.2</v>
       </c>
       <c r="T19">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U19">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
         <v>1.72</v>
@@ -5309,7 +5309,7 @@
         <v>22</v>
       </c>
       <c r="AS19">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AT19">
         <v>6.6</v>
@@ -5342,7 +5342,7 @@
         <v>30</v>
       </c>
       <c r="BD19">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE19">
         <v>95</v>
@@ -5369,10 +5369,10 @@
         <v>260</v>
       </c>
       <c r="BM19">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN19">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BO19">
         <v>4.5</v>
@@ -5387,7 +5387,7 @@
         <v>55</v>
       </c>
       <c r="BS19">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT19">
         <v>7.8</v>
@@ -5399,19 +5399,19 @@
         <v>46</v>
       </c>
       <c r="BW19">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX19">
         <v>75</v>
       </c>
       <c r="BY19">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19">
         <v>65</v>
       </c>
       <c r="CA19">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="s">
         <v>156</v>
@@ -5458,25 +5458,25 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P20">
         <v>1.9</v>
       </c>
       <c r="Q20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R20">
         <v>1.35</v>
       </c>
       <c r="S20">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U20">
         <v>2.12</v>
@@ -5542,37 +5542,37 @@
         <v>36</v>
       </c>
       <c r="AP20">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AS20">
         <v>4.8</v>
       </c>
       <c r="AT20">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AU20">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV20">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AW20">
         <v>4.6</v>
       </c>
       <c r="AX20">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AY20">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="BA20">
         <v>4.8</v>
@@ -5581,7 +5581,7 @@
         <v>4.6</v>
       </c>
       <c r="BC20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD20">
         <v>4.7</v>
@@ -5590,7 +5590,7 @@
         <v>5</v>
       </c>
       <c r="BF20">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BG20">
         <v>4.5</v>
@@ -5685,13 +5685,13 @@
         <v>7.2</v>
       </c>
       <c r="I21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5706,7 +5706,7 @@
         <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q21">
         <v>2.14</v>
@@ -5742,7 +5742,7 @@
         <v>350</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC21">
         <v>9.800000000000001</v>
@@ -5754,10 +5754,10 @@
         <v>180</v>
       </c>
       <c r="AF21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH21">
         <v>34</v>
@@ -5766,7 +5766,7 @@
         <v>170</v>
       </c>
       <c r="AJ21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK21">
         <v>24</v>
@@ -5778,7 +5778,7 @@
         <v>250</v>
       </c>
       <c r="AN21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO21">
         <v>300</v>
@@ -5790,10 +5790,10 @@
         <v>14.5</v>
       </c>
       <c r="AR21">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS21">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT21">
         <v>5.8</v>
@@ -5805,7 +5805,7 @@
         <v>21</v>
       </c>
       <c r="AW21">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX21">
         <v>7.2</v>
@@ -5817,7 +5817,7 @@
         <v>21</v>
       </c>
       <c r="BA21">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB21">
         <v>12.5</v>
@@ -5826,16 +5826,16 @@
         <v>16.5</v>
       </c>
       <c r="BD21">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE21">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF21">
         <v>8.4</v>
       </c>
       <c r="BG21">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5921,19 +5921,19 @@
         <v>2.5</v>
       </c>
       <c r="G22">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="H22">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="I22">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="J22">
         <v>2.56</v>
       </c>
       <c r="K22">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5942,10 +5942,10 @@
         <v>1.1</v>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O22">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="P22">
         <v>1.54</v>
@@ -5954,7 +5954,7 @@
         <v>2.42</v>
       </c>
       <c r="R22">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="S22">
         <v>3.05</v>
@@ -5966,10 +5966,10 @@
         <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W22">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -5996,7 +5996,7 @@
         <v>65</v>
       </c>
       <c r="AF22">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG22">
         <v>19.5</v>
@@ -6008,10 +6008,10 @@
         <v>100</v>
       </c>
       <c r="AJ22">
+        <v>100</v>
+      </c>
+      <c r="AK22">
         <v>75</v>
-      </c>
-      <c r="AK22">
-        <v>65</v>
       </c>
       <c r="AL22">
         <v>100</v>
@@ -6020,70 +6020,70 @@
         <v>1000</v>
       </c>
       <c r="AN22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AO22">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP22">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AQ22">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AR22">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AS22">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AT22">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AU22">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AV22">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AW22">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AX22">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AY22">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AZ22">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="BA22">
+        <v>2.34</v>
+      </c>
+      <c r="BB22">
+        <v>2.34</v>
+      </c>
+      <c r="BC22">
+        <v>2.32</v>
+      </c>
+      <c r="BD22">
+        <v>2.34</v>
+      </c>
+      <c r="BE22">
         <v>2.4</v>
       </c>
-      <c r="BB22">
-        <v>2.38</v>
-      </c>
-      <c r="BC22">
-        <v>2.36</v>
-      </c>
-      <c r="BD22">
-        <v>2.4</v>
-      </c>
-      <c r="BE22">
-        <v>2.46</v>
-      </c>
       <c r="BF22">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BG22">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BH22">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BI22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ22">
         <v>12</v>
@@ -6095,49 +6095,49 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN22">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BO22">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP22">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BQ22">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS22">
         <v>10</v>
       </c>
       <c r="BT22">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BU22">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV22">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX22">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB22" t="s">
         <v>156</v>
@@ -6175,7 +6175,7 @@
         <v>3.05</v>
       </c>
       <c r="K23">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6405,61 +6405,61 @@
         <v>1.61</v>
       </c>
       <c r="G24">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H24">
         <v>6.2</v>
       </c>
       <c r="I24">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K24">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24">
         <v>3.65</v>
       </c>
       <c r="O24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P24">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R24">
         <v>1.36</v>
       </c>
       <c r="S24">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="T24">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U24">
         <v>1.86</v>
       </c>
       <c r="V24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W24">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z24">
         <v>60</v>
@@ -6471,7 +6471,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
         <v>27</v>
@@ -6483,10 +6483,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24">
         <v>120</v>
@@ -6495,40 +6495,40 @@
         <v>15</v>
       </c>
       <c r="AK24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM24">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AN24">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24">
         <v>160</v>
       </c>
       <c r="AP24">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AQ24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR24">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="AS24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT24">
         <v>7.2</v>
       </c>
       <c r="AU24">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW24">
         <v>10.5</v>
@@ -6540,7 +6540,7 @@
         <v>9</v>
       </c>
       <c r="AZ24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA24">
         <v>10.5</v>
@@ -6552,70 +6552,70 @@
         <v>14.5</v>
       </c>
       <c r="BD24">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE24">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF24">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BG24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH24">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI24">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ24">
         <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BN24">
         <v>4.1</v>
       </c>
       <c r="BO24">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU24">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6644,22 +6644,22 @@
         <v>155</v>
       </c>
       <c r="F25">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G25">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H25">
         <v>8</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J25">
         <v>4</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L25">
         <v>1.39</v>
@@ -6668,13 +6668,13 @@
         <v>1.08</v>
       </c>
       <c r="N25">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O25">
         <v>1.38</v>
       </c>
       <c r="P25">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q25">
         <v>2.12</v>
@@ -6686,7 +6686,7 @@
         <v>3.9</v>
       </c>
       <c r="T25">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
         <v>1.7</v>
@@ -6695,7 +6695,7 @@
         <v>1.11</v>
       </c>
       <c r="W25">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="X25">
         <v>14.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="163">
   <si>
     <t>League</t>
   </si>
@@ -283,6 +283,9 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>English Sky Bet League 1</t>
   </si>
   <si>
@@ -316,6 +319,9 @@
     <t>14:15:00</t>
   </si>
   <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -367,27 +373,33 @@
     <t>Phoenix Rising FC</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>FC Van Yerevan</t>
   </si>
   <si>
     <t>Al-Wakra</t>
   </si>
   <si>
+    <t>Al Rayyan</t>
+  </si>
+  <si>
     <t>Vendsyssel FF</t>
   </si>
   <si>
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>Atletico Rojiblanco</t>
+  </si>
+  <si>
     <t>Sheff Wed</t>
   </si>
   <si>
@@ -439,27 +451,33 @@
     <t>Colorado Switchbacks FC</t>
   </si>
   <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
     <t>San Jose Earthquakes</t>
   </si>
   <si>
-    <t>San Diego FC</t>
-  </si>
-  <si>
     <t>FC Syunik</t>
   </si>
   <si>
     <t>Qatar SC</t>
   </si>
   <si>
+    <t>Lusail</t>
+  </si>
+  <si>
     <t>Hillerod Fodbold</t>
   </si>
   <si>
     <t>Al-Hilal</t>
   </si>
   <si>
+    <t>Cumbaya FC</t>
+  </si>
+  <si>
     <t>Bradford</t>
   </si>
   <si>
@@ -484,7 +502,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 10:51:58</t>
+    <t>2026-08-19 13:01:38</t>
   </si>
 </sst>
 </file>
@@ -816,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1066,34 +1084,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="I2">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.3</v>
@@ -1117,73 +1135,73 @@
         <v>1.63</v>
       </c>
       <c r="S2">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T2">
         <v>1.59</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V2">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X2">
         <v>24</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA2">
         <v>23</v>
       </c>
       <c r="AB2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD2">
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH2">
         <v>15.5</v>
       </c>
       <c r="AI2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM2">
         <v>60</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP2">
         <v>21</v>
@@ -1192,22 +1210,22 @@
         <v>12</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AT2">
         <v>18.5</v>
       </c>
       <c r="AU2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX2">
         <v>29</v>
@@ -1216,7 +1234,7 @@
         <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA2">
         <v>23</v>
@@ -1225,7 +1243,7 @@
         <v>55</v>
       </c>
       <c r="BC2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD2">
         <v>36</v>
@@ -1234,10 +1252,10 @@
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH2">
         <v>4.9</v>
@@ -1246,61 +1264,61 @@
         <v>3.5</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BL2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ2">
         <v>5.1</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BX2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY2">
         <v>4.9</v>
       </c>
       <c r="BZ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1308,34 +1326,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H3">
         <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1347,13 +1365,13 @@
         <v>2.64</v>
       </c>
       <c r="O3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P3">
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R3">
         <v>1.18</v>
@@ -1365,13 +1383,13 @@
         <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
         <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
         <v>9.4</v>
@@ -1380,13 +1398,13 @@
         <v>9.4</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>85</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
         <v>8</v>
@@ -1398,7 +1416,7 @@
         <v>65</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG3">
         <v>15</v>
@@ -1407,7 +1425,7 @@
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
         <v>55</v>
@@ -1443,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3">
         <v>13.5</v>
@@ -1473,13 +1491,13 @@
         <v>7.4</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF3">
         <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH3">
         <v>2.64</v>
@@ -1542,7 +1560,7 @@
         <v>14</v>
       </c>
       <c r="CB3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1550,97 +1568,97 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F4">
+        <v>1.7</v>
+      </c>
+      <c r="G4">
         <v>1.71</v>
-      </c>
-      <c r="G4">
-        <v>1.73</v>
       </c>
       <c r="H4">
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB4">
         <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1649,43 +1667,43 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>17</v>
       </c>
       <c r="AK4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL4">
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP4">
         <v>12</v>
       </c>
       <c r="AQ4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR4">
         <v>42</v>
       </c>
       <c r="AS4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV4">
         <v>22</v>
@@ -1694,7 +1712,7 @@
         <v>85</v>
       </c>
       <c r="AX4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
@@ -1703,31 +1721,31 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BB4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG4">
-        <v>16.5</v>
+        <v>80</v>
       </c>
       <c r="BH4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
@@ -1736,10 +1754,10 @@
         <v>7.4</v>
       </c>
       <c r="BL4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
@@ -1757,10 +1775,10 @@
         <v>30</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU4">
         <v>5.8</v>
@@ -1769,22 +1787,22 @@
         <v>60</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1792,100 +1810,100 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F5">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="H5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
+        <v>1.22</v>
+      </c>
+      <c r="P5">
+        <v>2.48</v>
+      </c>
+      <c r="Q5">
+        <v>1.66</v>
+      </c>
+      <c r="R5">
+        <v>1.58</v>
+      </c>
+      <c r="S5">
+        <v>2.64</v>
+      </c>
+      <c r="T5">
+        <v>1.69</v>
+      </c>
+      <c r="U5">
+        <v>2.34</v>
+      </c>
+      <c r="V5">
         <v>1.23</v>
       </c>
-      <c r="P5">
+      <c r="W5">
         <v>2.38</v>
       </c>
-      <c r="Q5">
-        <v>1.69</v>
-      </c>
-      <c r="R5">
-        <v>1.54</v>
-      </c>
-      <c r="S5">
-        <v>2.74</v>
-      </c>
-      <c r="T5">
-        <v>1.7</v>
-      </c>
-      <c r="U5">
-        <v>2.32</v>
-      </c>
-      <c r="V5">
-        <v>1.25</v>
-      </c>
-      <c r="W5">
-        <v>2.26</v>
-      </c>
       <c r="X5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
         <v>18</v>
@@ -1894,43 +1912,43 @@
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS5">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW5">
         <v>48</v>
@@ -1942,37 +1960,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB5">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
         <v>25</v>
       </c>
       <c r="BE5">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF5">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
         <v>7.2</v>
@@ -1981,52 +1999,52 @@
         <v>95</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BR5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5">
         <v>6.8</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA5">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2034,28 +2052,28 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F6">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G6">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H6">
         <v>6.2</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>3.65</v>
@@ -2076,7 +2094,7 @@
         <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q6">
         <v>2.36</v>
@@ -2097,7 +2115,7 @@
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X6">
         <v>11.5</v>
@@ -2106,7 +2124,7 @@
         <v>18.5</v>
       </c>
       <c r="Z6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA6">
         <v>260</v>
@@ -2127,13 +2145,13 @@
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
         <v>18</v>
@@ -2142,7 +2160,7 @@
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>250</v>
@@ -2157,10 +2175,10 @@
         <v>10</v>
       </c>
       <c r="AQ6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS6">
         <v>11</v>
@@ -2175,7 +2193,7 @@
         <v>23</v>
       </c>
       <c r="AW6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX6">
         <v>7.6</v>
@@ -2184,7 +2202,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA6">
         <v>65</v>
@@ -2205,28 +2223,28 @@
         <v>13</v>
       </c>
       <c r="BG6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH6">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.55</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO6">
         <v>3.3</v>
@@ -2235,31 +2253,31 @@
         <v>13</v>
       </c>
       <c r="BQ6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT6">
         <v>9.4</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2268,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2276,19 +2294,19 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
         <v>2.06</v>
@@ -2297,70 +2315,70 @@
         <v>3.8</v>
       </c>
       <c r="I7">
+        <v>3.95</v>
+      </c>
+      <c r="J7">
         <v>3.9</v>
       </c>
-      <c r="J7">
-        <v>3.85</v>
-      </c>
       <c r="K7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M7">
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="Q7">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S7">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U7">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
         <v>1.94</v>
       </c>
       <c r="X7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y7">
         <v>22</v>
       </c>
       <c r="Z7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
         <v>40</v>
@@ -2375,82 +2393,82 @@
         <v>14.5</v>
       </c>
       <c r="AI7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
         <v>25</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT7">
         <v>13</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7">
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA7">
         <v>34</v>
       </c>
       <c r="BB7">
+        <v>22</v>
+      </c>
+      <c r="BC7">
+        <v>16.5</v>
+      </c>
+      <c r="BD7">
         <v>23</v>
       </c>
-      <c r="BC7">
-        <v>17</v>
-      </c>
-      <c r="BD7">
-        <v>24</v>
-      </c>
       <c r="BE7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF7">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI7">
         <v>3.55</v>
@@ -2462,13 +2480,13 @@
         <v>6.8</v>
       </c>
       <c r="BL7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BN7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
         <v>4.7</v>
@@ -2483,10 +2501,10 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU7">
         <v>6</v>
@@ -2495,22 +2513,22 @@
         <v>25</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA7">
         <v>10.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2518,73 +2536,73 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F8">
+        <v>2.62</v>
+      </c>
+      <c r="G8">
         <v>2.64</v>
       </c>
-      <c r="G8">
-        <v>2.68</v>
-      </c>
       <c r="H8">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
         <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
         <v>1.49</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
         <v>2.48</v>
       </c>
       <c r="V8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y8">
         <v>14</v>
@@ -2596,7 +2614,7 @@
         <v>42</v>
       </c>
       <c r="AB8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
@@ -2605,10 +2623,10 @@
         <v>12</v>
       </c>
       <c r="AE8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
@@ -2620,34 +2638,34 @@
         <v>36</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8">
+        <v>25</v>
+      </c>
+      <c r="AL8">
         <v>34</v>
       </c>
-      <c r="AL8">
-        <v>46</v>
-      </c>
       <c r="AM8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR8">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT8">
         <v>12.5</v>
@@ -2662,19 +2680,19 @@
         <v>25</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY8">
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC8">
         <v>23</v>
@@ -2686,49 +2704,49 @@
         <v>55</v>
       </c>
       <c r="BF8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG8">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
         <v>6</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
         <v>29</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
         <v>5.2</v>
@@ -2737,22 +2755,22 @@
         <v>21</v>
       </c>
       <c r="BW8">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY8">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2760,64 +2778,64 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O9">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S9">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T9">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.27</v>
@@ -2826,22 +2844,22 @@
         <v>2.16</v>
       </c>
       <c r="X9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y9">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z9">
         <v>36</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2850,7 +2868,7 @@
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2859,43 +2877,43 @@
         <v>17</v>
       </c>
       <c r="AI9">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK9">
         <v>18</v>
       </c>
       <c r="AL9">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN9">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AP9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ9">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR9">
         <v>32</v>
       </c>
       <c r="AS9">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
         <v>16.5</v>
@@ -2904,16 +2922,16 @@
         <v>44</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB9">
         <v>18</v>
@@ -2922,37 +2940,37 @@
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF9">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9">
         <v>9</v>
       </c>
       <c r="BK9">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BN9">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
         <v>4.2</v>
@@ -2964,37 +2982,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ9">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="CA9">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3002,28 +3020,28 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G10">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J10">
         <v>3.4</v>
@@ -3035,37 +3053,37 @@
         <v>1.39</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P10">
         <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T10">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X10">
         <v>17.5</v>
@@ -3080,7 +3098,7 @@
         <v>46</v>
       </c>
       <c r="AB10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
         <v>9.4</v>
@@ -3107,13 +3125,13 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL10">
         <v>46</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN10">
         <v>29</v>
@@ -3125,49 +3143,49 @@
         <v>12</v>
       </c>
       <c r="AQ10">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>4.7</v>
+        <v>27</v>
       </c>
       <c r="AT10">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU10">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
         <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="AX10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY10">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BB10">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BC10">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BD10">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BE10">
-        <v>4.9</v>
+        <v>60</v>
       </c>
       <c r="BF10">
         <v>18</v>
@@ -3176,22 +3194,22 @@
         <v>17.5</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10">
         <v>9.199999999999999</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.82</v>
+        <v>13.5</v>
       </c>
       <c r="BN10">
         <v>5.9</v>
@@ -3203,13 +3221,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT10">
         <v>5.8</v>
@@ -3221,7 +3239,7 @@
         <v>21</v>
       </c>
       <c r="BW10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX10">
         <v>1000</v>
@@ -3236,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3244,241 +3262,241 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F11">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="G11">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="I11">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="S11">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="T11">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="U11">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="V11">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="X11">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Z11">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AA11">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AB11">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AC11">
+        <v>12</v>
+      </c>
+      <c r="AD11">
+        <v>16</v>
+      </c>
+      <c r="AE11">
+        <v>34</v>
+      </c>
+      <c r="AF11">
+        <v>19.5</v>
+      </c>
+      <c r="AG11">
+        <v>12</v>
+      </c>
+      <c r="AH11">
+        <v>14</v>
+      </c>
+      <c r="AI11">
+        <v>30</v>
+      </c>
+      <c r="AJ11">
+        <v>27</v>
+      </c>
+      <c r="AK11">
+        <v>17.5</v>
+      </c>
+      <c r="AL11">
+        <v>22</v>
+      </c>
+      <c r="AM11">
+        <v>42</v>
+      </c>
+      <c r="AN11">
+        <v>7.2</v>
+      </c>
+      <c r="AO11">
+        <v>16.5</v>
+      </c>
+      <c r="AP11">
+        <v>32</v>
+      </c>
+      <c r="AQ11">
+        <v>25</v>
+      </c>
+      <c r="AR11">
+        <v>30</v>
+      </c>
+      <c r="AS11">
+        <v>30</v>
+      </c>
+      <c r="AT11">
+        <v>18</v>
+      </c>
+      <c r="AU11">
+        <v>11</v>
+      </c>
+      <c r="AV11">
+        <v>14.5</v>
+      </c>
+      <c r="AW11">
+        <v>28</v>
+      </c>
+      <c r="AX11">
+        <v>18</v>
+      </c>
+      <c r="AY11">
         <v>10.5</v>
       </c>
-      <c r="AD11">
+      <c r="AZ11">
+        <v>13</v>
+      </c>
+      <c r="BA11">
+        <v>27</v>
+      </c>
+      <c r="BB11">
         <v>25</v>
       </c>
-      <c r="AE11">
-        <v>85</v>
-      </c>
-      <c r="AF11">
-        <v>10.5</v>
-      </c>
-      <c r="AG11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH11">
-        <v>21</v>
-      </c>
-      <c r="AI11">
-        <v>75</v>
-      </c>
-      <c r="AJ11">
-        <v>15.5</v>
-      </c>
-      <c r="AK11">
+      <c r="BC11">
         <v>16</v>
       </c>
-      <c r="AL11">
-        <v>32</v>
-      </c>
-      <c r="AM11">
-        <v>110</v>
-      </c>
-      <c r="AN11">
-        <v>7.6</v>
-      </c>
-      <c r="AO11">
-        <v>85</v>
-      </c>
-      <c r="AP11">
-        <v>18</v>
-      </c>
-      <c r="AQ11">
+      <c r="BD11">
         <v>20</v>
       </c>
-      <c r="AR11">
-        <v>46</v>
-      </c>
-      <c r="AS11">
-        <v>75</v>
-      </c>
-      <c r="AT11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU11">
-        <v>9.4</v>
-      </c>
-      <c r="AV11">
-        <v>21</v>
-      </c>
-      <c r="AW11">
-        <v>46</v>
-      </c>
-      <c r="AX11">
-        <v>9.4</v>
-      </c>
-      <c r="AY11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11">
-        <v>18.5</v>
-      </c>
-      <c r="BA11">
-        <v>60</v>
-      </c>
-      <c r="BB11">
-        <v>14</v>
-      </c>
-      <c r="BC11">
-        <v>14</v>
-      </c>
-      <c r="BD11">
-        <v>27</v>
-      </c>
       <c r="BE11">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BF11">
         <v>6.8</v>
       </c>
       <c r="BG11">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="BH11">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BI11">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK11">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="BP11">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BQ11">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11">
+        <v>19</v>
+      </c>
+      <c r="BS11">
+        <v>6.6</v>
+      </c>
+      <c r="BT11">
+        <v>8</v>
+      </c>
+      <c r="BU11">
+        <v>4.9</v>
+      </c>
+      <c r="BV11">
         <v>23</v>
       </c>
-      <c r="BS11">
-        <v>7.8</v>
-      </c>
-      <c r="BT11">
-        <v>10.5</v>
-      </c>
-      <c r="BU11">
-        <v>5.5</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
       <c r="BW11">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="BY11">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CA11">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB11" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3486,241 +3504,241 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F12">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="G12">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="I12">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="T12">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="W12">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="X12">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z12">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="AB12">
+        <v>10</v>
+      </c>
+      <c r="AC12">
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <v>24</v>
+      </c>
+      <c r="AE12">
+        <v>85</v>
+      </c>
+      <c r="AF12">
+        <v>10.5</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>75</v>
+      </c>
+      <c r="AJ12">
+        <v>15.5</v>
+      </c>
+      <c r="AK12">
+        <v>16</v>
+      </c>
+      <c r="AL12">
+        <v>30</v>
+      </c>
+      <c r="AM12">
+        <v>100</v>
+      </c>
+      <c r="AN12">
+        <v>7.4</v>
+      </c>
+      <c r="AO12">
+        <v>80</v>
+      </c>
+      <c r="AP12">
         <v>18.5</v>
-      </c>
-      <c r="AC12">
-        <v>11</v>
-      </c>
-      <c r="AD12">
-        <v>14.5</v>
-      </c>
-      <c r="AE12">
-        <v>28</v>
-      </c>
-      <c r="AF12">
-        <v>21</v>
-      </c>
-      <c r="AG12">
-        <v>12</v>
-      </c>
-      <c r="AH12">
-        <v>13.5</v>
-      </c>
-      <c r="AI12">
-        <v>29</v>
-      </c>
-      <c r="AJ12">
-        <v>34</v>
-      </c>
-      <c r="AK12">
-        <v>20</v>
-      </c>
-      <c r="AL12">
-        <v>25</v>
-      </c>
-      <c r="AM12">
-        <v>46</v>
-      </c>
-      <c r="AN12">
-        <v>9.6</v>
-      </c>
-      <c r="AO12">
-        <v>15</v>
-      </c>
-      <c r="AP12">
-        <v>23</v>
       </c>
       <c r="AQ12">
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AS12">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AT12">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="AU12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AW12">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AX12">
-        <v>18.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BB12">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="BC12">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE12">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF12">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BH12">
+        <v>4.1</v>
+      </c>
+      <c r="BI12">
+        <v>3.25</v>
+      </c>
+      <c r="BJ12">
+        <v>10.5</v>
+      </c>
+      <c r="BK12">
         <v>5.2</v>
       </c>
-      <c r="BI12">
-        <v>3.9</v>
-      </c>
-      <c r="BJ12">
-        <v>8.6</v>
-      </c>
-      <c r="BK12">
-        <v>6.2</v>
-      </c>
       <c r="BL12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN12">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO12">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP12">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BQ12">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BR12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BS12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT12">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BU12">
         <v>5.2</v>
       </c>
       <c r="BV12">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="BW12">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX12">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="BY12">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="CA12">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3728,34 +3746,34 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F13">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="G13">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13">
         <v>1.24</v>
@@ -3764,205 +3782,205 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R13">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S13">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T13">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="X13">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z13">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA13">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB13">
+        <v>19</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
+        <v>14.5</v>
+      </c>
+      <c r="AE13">
+        <v>28</v>
+      </c>
+      <c r="AF13">
+        <v>21</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13">
+        <v>13.5</v>
+      </c>
+      <c r="AI13">
+        <v>29</v>
+      </c>
+      <c r="AJ13">
+        <v>34</v>
+      </c>
+      <c r="AK13">
+        <v>20</v>
+      </c>
+      <c r="AL13">
+        <v>24</v>
+      </c>
+      <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
+        <v>9.6</v>
+      </c>
+      <c r="AO13">
+        <v>15</v>
+      </c>
+      <c r="AP13">
+        <v>27</v>
+      </c>
+      <c r="AQ13">
+        <v>20</v>
+      </c>
+      <c r="AR13">
+        <v>25</v>
+      </c>
+      <c r="AS13">
+        <v>46</v>
+      </c>
+      <c r="AT13">
+        <v>17</v>
+      </c>
+      <c r="AU13">
+        <v>10</v>
+      </c>
+      <c r="AV13">
+        <v>13</v>
+      </c>
+      <c r="AW13">
+        <v>24</v>
+      </c>
+      <c r="AX13">
         <v>18.5</v>
       </c>
-      <c r="AC13">
-        <v>11.5</v>
-      </c>
-      <c r="AD13">
-        <v>16</v>
-      </c>
-      <c r="AE13">
-        <v>32</v>
-      </c>
-      <c r="AF13">
-        <v>19.5</v>
-      </c>
-      <c r="AG13">
-        <v>11.5</v>
-      </c>
-      <c r="AH13">
-        <v>14</v>
-      </c>
-      <c r="AI13">
-        <v>30</v>
-      </c>
-      <c r="AJ13">
-        <v>28</v>
-      </c>
-      <c r="AK13">
-        <v>18</v>
-      </c>
-      <c r="AL13">
-        <v>22</v>
-      </c>
-      <c r="AM13">
-        <v>44</v>
-      </c>
-      <c r="AN13">
-        <v>7.6</v>
-      </c>
-      <c r="AO13">
-        <v>17.5</v>
-      </c>
-      <c r="AP13">
-        <v>30</v>
-      </c>
-      <c r="AQ13">
-        <v>24</v>
-      </c>
-      <c r="AR13">
-        <v>30</v>
-      </c>
-      <c r="AS13">
-        <v>55</v>
-      </c>
-      <c r="AT13">
-        <v>17.5</v>
-      </c>
-      <c r="AU13">
-        <v>10.5</v>
-      </c>
-      <c r="AV13">
-        <v>14.5</v>
-      </c>
-      <c r="AW13">
-        <v>28</v>
-      </c>
-      <c r="AX13">
-        <v>17</v>
-      </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BC13">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD13">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF13">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BG13">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BH13">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BI13">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>60</v>
       </c>
       <c r="BM13">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO13">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BQ13">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BR13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BS13">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT13">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BU13">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BW13">
         <v>6.8</v>
       </c>
       <c r="BX13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA13">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="CB13" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3970,19 +3988,19 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F14">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="G14">
         <v>3.35</v>
@@ -4057,7 +4075,7 @@
         <v>12.5</v>
       </c>
       <c r="AE14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF14">
         <v>22</v>
@@ -4087,61 +4105,61 @@
         <v>40</v>
       </c>
       <c r="AO14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP14">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14">
+        <v>4.9</v>
+      </c>
+      <c r="AR14">
+        <v>5.7</v>
+      </c>
+      <c r="AS14">
+        <v>6.8</v>
+      </c>
+      <c r="AT14">
         <v>5.1</v>
       </c>
-      <c r="AR14">
-        <v>5.9</v>
-      </c>
-      <c r="AS14">
+      <c r="AU14">
+        <v>4.2</v>
+      </c>
+      <c r="AV14">
+        <v>4.9</v>
+      </c>
+      <c r="AW14">
+        <v>6.4</v>
+      </c>
+      <c r="AX14">
+        <v>6</v>
+      </c>
+      <c r="AY14">
+        <v>5.2</v>
+      </c>
+      <c r="AZ14">
+        <v>5.5</v>
+      </c>
+      <c r="BA14">
+        <v>6.8</v>
+      </c>
+      <c r="BB14">
         <v>7</v>
       </c>
-      <c r="AT14">
-        <v>5.2</v>
-      </c>
-      <c r="AU14">
-        <v>4.3</v>
-      </c>
-      <c r="AV14">
-        <v>5.1</v>
-      </c>
-      <c r="AW14">
+      <c r="BC14">
         <v>6.6</v>
       </c>
-      <c r="AX14">
+      <c r="BD14">
+        <v>6.8</v>
+      </c>
+      <c r="BE14">
+        <v>7.6</v>
+      </c>
+      <c r="BF14">
         <v>6.2</v>
       </c>
-      <c r="AY14">
-        <v>5.3</v>
-      </c>
-      <c r="AZ14">
-        <v>5.7</v>
-      </c>
-      <c r="BA14">
-        <v>7</v>
-      </c>
-      <c r="BB14">
-        <v>7.2</v>
-      </c>
-      <c r="BC14">
-        <v>6.8</v>
-      </c>
-      <c r="BD14">
-        <v>7.2</v>
-      </c>
-      <c r="BE14">
-        <v>8</v>
-      </c>
-      <c r="BF14">
-        <v>6.4</v>
-      </c>
       <c r="BG14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH14">
         <v>3.7</v>
@@ -4204,7 +4222,7 @@
         <v>7.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4212,31 +4230,31 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F15">
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H15">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="I15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4257,31 +4275,31 @@
         <v>2.24</v>
       </c>
       <c r="Q15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T15">
         <v>1.58</v>
       </c>
       <c r="U15">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X15">
         <v>25</v>
       </c>
       <c r="Y15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z15">
         <v>30</v>
@@ -4293,7 +4311,7 @@
         <v>16</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
         <v>17</v>
@@ -4353,7 +4371,7 @@
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AX15">
         <v>12</v>
@@ -4365,7 +4383,7 @@
         <v>11</v>
       </c>
       <c r="BA15">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB15">
         <v>21</v>
@@ -4374,10 +4392,10 @@
         <v>16</v>
       </c>
       <c r="BD15">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF15">
         <v>9.800000000000001</v>
@@ -4395,13 +4413,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN15">
         <v>5.7</v>
@@ -4419,7 +4437,7 @@
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT15">
         <v>7</v>
@@ -4437,691 +4455,691 @@
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA15">
         <v>6.4</v>
       </c>
       <c r="CB15" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F16">
-        <v>2.44</v>
+        <v>1.25</v>
       </c>
       <c r="G16">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="H16">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="I16">
-        <v>3.15</v>
+        <v>990</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="O16">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="P16">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="Q16">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="R16">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="S16">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="T16">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="W16">
-        <v>1.58</v>
+        <v>2.92</v>
       </c>
       <c r="X16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>2.44</v>
       </c>
       <c r="G17">
-        <v>15.5</v>
+        <v>2.7</v>
       </c>
       <c r="H17">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="I17">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="J17">
-        <v>6.8</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="O17">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q17">
+        <v>1.64</v>
+      </c>
+      <c r="R17">
+        <v>1.5</v>
+      </c>
+      <c r="S17">
+        <v>2.62</v>
+      </c>
+      <c r="T17">
+        <v>1.56</v>
+      </c>
+      <c r="U17">
+        <v>2.42</v>
+      </c>
+      <c r="V17">
         <v>1.47</v>
       </c>
-      <c r="R17">
-        <v>1.69</v>
-      </c>
-      <c r="S17">
-        <v>2.2</v>
-      </c>
-      <c r="T17">
-        <v>2.1</v>
-      </c>
-      <c r="U17">
-        <v>1.75</v>
-      </c>
-      <c r="V17">
-        <v>4.7</v>
-      </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="X17">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Y17">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="Z17">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AA17">
+        <v>50</v>
+      </c>
+      <c r="AB17">
+        <v>15</v>
+      </c>
+      <c r="AC17">
         <v>9.6</v>
-      </c>
-      <c r="AB17">
-        <v>60</v>
-      </c>
-      <c r="AC17">
-        <v>18</v>
       </c>
       <c r="AD17">
         <v>14</v>
       </c>
       <c r="AE17">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AF17">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="AG17">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="AH17">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AI17">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK17">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="AL17">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="AM17">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="AN17">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="AO17">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="AP17">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="AQ17">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR17">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="AS17">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AT17">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="AV17">
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AX17">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AY17">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
+        <v>11.5</v>
+      </c>
+      <c r="BA17">
         <v>6</v>
       </c>
-      <c r="BA17">
-        <v>6.2</v>
-      </c>
       <c r="BB17">
+        <v>6</v>
+      </c>
+      <c r="BC17">
+        <v>20</v>
+      </c>
+      <c r="BD17">
+        <v>6</v>
+      </c>
+      <c r="BE17">
+        <v>6.6</v>
+      </c>
+      <c r="BF17">
+        <v>13</v>
+      </c>
+      <c r="BG17">
+        <v>16</v>
+      </c>
+      <c r="BH17">
+        <v>4.6</v>
+      </c>
+      <c r="BI17">
+        <v>3.3</v>
+      </c>
+      <c r="BJ17">
+        <v>10</v>
+      </c>
+      <c r="BK17">
+        <v>3.55</v>
+      </c>
+      <c r="BL17">
+        <v>95</v>
+      </c>
+      <c r="BM17">
+        <v>5.2</v>
+      </c>
+      <c r="BN17">
+        <v>6.6</v>
+      </c>
+      <c r="BO17">
+        <v>4.6</v>
+      </c>
+      <c r="BP17">
+        <v>20</v>
+      </c>
+      <c r="BQ17">
+        <v>4.3</v>
+      </c>
+      <c r="BR17">
+        <v>30</v>
+      </c>
+      <c r="BS17">
+        <v>4.7</v>
+      </c>
+      <c r="BT17">
         <v>7.2</v>
       </c>
-      <c r="BC17">
-        <v>7</v>
-      </c>
-      <c r="BD17">
-        <v>6.8</v>
-      </c>
-      <c r="BE17">
-        <v>6.8</v>
-      </c>
-      <c r="BF17">
-        <v>7</v>
-      </c>
-      <c r="BG17">
-        <v>3.4</v>
-      </c>
-      <c r="BH17">
-        <v>5.3</v>
-      </c>
-      <c r="BI17">
-        <v>3.8</v>
-      </c>
-      <c r="BJ17">
-        <v>13.5</v>
-      </c>
-      <c r="BK17">
-        <v>4.3</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>6</v>
-      </c>
-      <c r="BN17">
-        <v>18.5</v>
-      </c>
-      <c r="BO17">
+      <c r="BU17">
+        <v>4.9</v>
+      </c>
+      <c r="BV17">
+        <v>23</v>
+      </c>
+      <c r="BW17">
+        <v>4.5</v>
+      </c>
+      <c r="BX17">
+        <v>32</v>
+      </c>
+      <c r="BY17">
         <v>4.7</v>
       </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>6</v>
-      </c>
-      <c r="BR17">
-        <v>110</v>
-      </c>
-      <c r="BS17">
-        <v>6</v>
-      </c>
-      <c r="BT17">
-        <v>4.3</v>
-      </c>
-      <c r="BU17">
-        <v>3.1</v>
-      </c>
-      <c r="BV17">
-        <v>7.8</v>
-      </c>
-      <c r="BW17">
-        <v>5.3</v>
-      </c>
-      <c r="BX17">
-        <v>25</v>
-      </c>
-      <c r="BY17">
-        <v>5.1</v>
-      </c>
       <c r="BZ17">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="CA17">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="CB17" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F18">
-        <v>2.48</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>2.58</v>
+        <v>15.5</v>
       </c>
       <c r="H18">
-        <v>2.96</v>
+        <v>1.25</v>
       </c>
       <c r="I18">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="K18">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="L18">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="M18">
+        <v>1.02</v>
+      </c>
+      <c r="N18">
+        <v>6</v>
+      </c>
+      <c r="O18">
+        <v>1.16</v>
+      </c>
+      <c r="P18">
+        <v>2.8</v>
+      </c>
+      <c r="Q18">
+        <v>1.48</v>
+      </c>
+      <c r="R18">
+        <v>1.68</v>
+      </c>
+      <c r="S18">
+        <v>2.22</v>
+      </c>
+      <c r="T18">
+        <v>2.1</v>
+      </c>
+      <c r="U18">
+        <v>1.75</v>
+      </c>
+      <c r="V18">
+        <v>4.7</v>
+      </c>
+      <c r="W18">
         <v>1.07</v>
       </c>
-      <c r="N18">
-        <v>3.6</v>
-      </c>
-      <c r="O18">
-        <v>1.33</v>
-      </c>
-      <c r="P18">
-        <v>1.91</v>
-      </c>
-      <c r="Q18">
-        <v>2</v>
-      </c>
-      <c r="R18">
-        <v>1.36</v>
-      </c>
-      <c r="S18">
-        <v>3.4</v>
-      </c>
-      <c r="T18">
-        <v>1.75</v>
-      </c>
-      <c r="U18">
-        <v>2.12</v>
-      </c>
-      <c r="V18">
-        <v>1.47</v>
-      </c>
-      <c r="W18">
-        <v>1.63</v>
-      </c>
       <c r="X18">
+        <v>34</v>
+      </c>
+      <c r="Y18">
+        <v>13</v>
+      </c>
+      <c r="Z18">
+        <v>8.4</v>
+      </c>
+      <c r="AA18">
+        <v>9.6</v>
+      </c>
+      <c r="AB18">
+        <v>60</v>
+      </c>
+      <c r="AC18">
+        <v>18</v>
+      </c>
+      <c r="AD18">
+        <v>14</v>
+      </c>
+      <c r="AE18">
+        <v>14</v>
+      </c>
+      <c r="AF18">
+        <v>150</v>
+      </c>
+      <c r="AG18">
+        <v>60</v>
+      </c>
+      <c r="AH18">
+        <v>40</v>
+      </c>
+      <c r="AI18">
+        <v>44</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>280</v>
+      </c>
+      <c r="AL18">
+        <v>170</v>
+      </c>
+      <c r="AM18">
+        <v>220</v>
+      </c>
+      <c r="AN18">
+        <v>310</v>
+      </c>
+      <c r="AO18">
+        <v>4.3</v>
+      </c>
+      <c r="AP18">
+        <v>6</v>
+      </c>
+      <c r="AQ18">
+        <v>9.6</v>
+      </c>
+      <c r="AR18">
+        <v>7.2</v>
+      </c>
+      <c r="AS18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT18">
+        <v>6.6</v>
+      </c>
+      <c r="AU18">
         <v>14.5</v>
       </c>
-      <c r="Y18">
-        <v>12.5</v>
-      </c>
-      <c r="Z18">
-        <v>21</v>
-      </c>
-      <c r="AA18">
-        <v>55</v>
-      </c>
-      <c r="AB18">
+      <c r="AV18">
+        <v>10</v>
+      </c>
+      <c r="AW18">
         <v>11</v>
       </c>
-      <c r="AC18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD18">
-        <v>13.5</v>
-      </c>
-      <c r="AE18">
-        <v>36</v>
-      </c>
-      <c r="AF18">
-        <v>17</v>
-      </c>
-      <c r="AG18">
-        <v>12</v>
-      </c>
-      <c r="AH18">
-        <v>18</v>
-      </c>
-      <c r="AI18">
-        <v>50</v>
-      </c>
-      <c r="AJ18">
-        <v>42</v>
-      </c>
-      <c r="AK18">
-        <v>29</v>
-      </c>
-      <c r="AL18">
-        <v>42</v>
-      </c>
-      <c r="AM18">
-        <v>100</v>
-      </c>
-      <c r="AN18">
-        <v>24</v>
-      </c>
-      <c r="AO18">
-        <v>32</v>
-      </c>
-      <c r="AP18">
-        <v>11</v>
-      </c>
-      <c r="AQ18">
-        <v>10.5</v>
-      </c>
-      <c r="AR18">
-        <v>18.5</v>
-      </c>
-      <c r="AS18">
-        <v>40</v>
-      </c>
-      <c r="AT18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18">
+      <c r="AX18">
         <v>7</v>
       </c>
-      <c r="AV18">
-        <v>12</v>
-      </c>
-      <c r="AW18">
-        <v>30</v>
-      </c>
-      <c r="AX18">
+      <c r="AY18">
+        <v>6.6</v>
+      </c>
+      <c r="AZ18">
+        <v>6.2</v>
+      </c>
+      <c r="BA18">
+        <v>6.2</v>
+      </c>
+      <c r="BB18">
+        <v>7.4</v>
+      </c>
+      <c r="BC18">
+        <v>7.2</v>
+      </c>
+      <c r="BD18">
+        <v>7</v>
+      </c>
+      <c r="BE18">
+        <v>7</v>
+      </c>
+      <c r="BF18">
+        <v>7.2</v>
+      </c>
+      <c r="BG18">
+        <v>3.5</v>
+      </c>
+      <c r="BH18">
+        <v>5.3</v>
+      </c>
+      <c r="BI18">
+        <v>3.8</v>
+      </c>
+      <c r="BJ18">
         <v>14.5</v>
       </c>
-      <c r="AY18">
-        <v>10</v>
-      </c>
-      <c r="AZ18">
-        <v>15.5</v>
-      </c>
-      <c r="BA18">
-        <v>40</v>
-      </c>
-      <c r="BB18">
-        <v>32</v>
-      </c>
-      <c r="BC18">
-        <v>24</v>
-      </c>
-      <c r="BD18">
-        <v>34</v>
-      </c>
-      <c r="BE18">
-        <v>10.5</v>
-      </c>
-      <c r="BF18">
-        <v>20</v>
-      </c>
-      <c r="BG18">
-        <v>26</v>
-      </c>
-      <c r="BH18">
-        <v>3.75</v>
-      </c>
-      <c r="BI18">
-        <v>2.78</v>
-      </c>
-      <c r="BJ18">
-        <v>11</v>
-      </c>
       <c r="BK18">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5130,329 +5148,329 @@
         <v>5.6</v>
       </c>
       <c r="BN18">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="BO18">
         <v>4.4</v>
       </c>
       <c r="BP18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BR18">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="BS18">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BT18">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BU18">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BV18">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BW18">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BX18">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="BY18">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BZ18">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="CA18">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F19">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="G19">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="H19">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K19">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L19">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>1.26</v>
       </c>
       <c r="O19">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q19">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>6.2</v>
+        <v>1.43</v>
       </c>
       <c r="T19">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F20">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="G20">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H20">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I20">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K20">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L20">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M20">
         <v>1.07</v>
@@ -5461,444 +5479,444 @@
         <v>3.6</v>
       </c>
       <c r="O20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P20">
         <v>1.9</v>
       </c>
       <c r="Q20">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T20">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="U20">
         <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X20">
+        <v>14.5</v>
+      </c>
+      <c r="Y20">
+        <v>12.5</v>
+      </c>
+      <c r="Z20">
+        <v>21</v>
+      </c>
+      <c r="AA20">
+        <v>55</v>
+      </c>
+      <c r="AB20">
+        <v>10.5</v>
+      </c>
+      <c r="AC20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD20">
+        <v>13.5</v>
+      </c>
+      <c r="AE20">
+        <v>36</v>
+      </c>
+      <c r="AF20">
         <v>17</v>
       </c>
-      <c r="Y20">
-        <v>14.5</v>
-      </c>
-      <c r="Z20">
-        <v>25</v>
-      </c>
-      <c r="AA20">
-        <v>60</v>
-      </c>
-      <c r="AB20">
-        <v>12.5</v>
-      </c>
-      <c r="AC20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD20">
-        <v>15.5</v>
-      </c>
-      <c r="AE20">
-        <v>42</v>
-      </c>
-      <c r="AF20">
-        <v>19.5</v>
-      </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ20">
         <v>42</v>
       </c>
       <c r="AK20">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL20">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP20">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ20">
         <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS20">
-        <v>4.8</v>
+        <v>40</v>
       </c>
       <c r="AT20">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU20">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW20">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="AX20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY20">
         <v>10</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA20">
-        <v>4.8</v>
+        <v>40</v>
       </c>
       <c r="BB20">
+        <v>32</v>
+      </c>
+      <c r="BC20">
+        <v>24</v>
+      </c>
+      <c r="BD20">
+        <v>34</v>
+      </c>
+      <c r="BE20">
+        <v>10.5</v>
+      </c>
+      <c r="BF20">
+        <v>20</v>
+      </c>
+      <c r="BG20">
+        <v>26</v>
+      </c>
+      <c r="BH20">
+        <v>3.7</v>
+      </c>
+      <c r="BI20">
+        <v>2.76</v>
+      </c>
+      <c r="BJ20">
+        <v>11</v>
+      </c>
+      <c r="BK20">
+        <v>7.6</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>5.6</v>
+      </c>
+      <c r="BN20">
+        <v>6.4</v>
+      </c>
+      <c r="BO20">
+        <v>4.4</v>
+      </c>
+      <c r="BP20">
+        <v>23</v>
+      </c>
+      <c r="BQ20">
         <v>4.6</v>
-      </c>
-      <c r="BC20">
-        <v>4.6</v>
-      </c>
-      <c r="BD20">
-        <v>4.7</v>
-      </c>
-      <c r="BE20">
-        <v>5</v>
-      </c>
-      <c r="BF20">
-        <v>18</v>
-      </c>
-      <c r="BG20">
-        <v>4.5</v>
-      </c>
-      <c r="BH20">
-        <v>3.55</v>
-      </c>
-      <c r="BI20">
-        <v>2.84</v>
-      </c>
-      <c r="BJ20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK20">
-        <v>4.9</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>2.58</v>
-      </c>
-      <c r="BN20">
-        <v>5.7</v>
-      </c>
-      <c r="BO20">
-        <v>3.65</v>
-      </c>
-      <c r="BP20">
-        <v>19.5</v>
-      </c>
-      <c r="BQ20">
-        <v>6.6</v>
       </c>
       <c r="BR20">
         <v>34</v>
       </c>
       <c r="BS20">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="BT20">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU20">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BV20">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BW20">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BX20">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY20">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="BZ20">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="CA20">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="CB20" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F21">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="G21">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H21">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="I21">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="M21">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="P21">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Q21">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="R21">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="T21">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="X21">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="Y21">
+        <v>9.6</v>
+      </c>
+      <c r="Z21">
+        <v>24</v>
+      </c>
+      <c r="AA21">
+        <v>100</v>
+      </c>
+      <c r="AB21">
+        <v>7</v>
+      </c>
+      <c r="AC21">
+        <v>6.8</v>
+      </c>
+      <c r="AD21">
+        <v>17</v>
+      </c>
+      <c r="AE21">
+        <v>65</v>
+      </c>
+      <c r="AF21">
+        <v>12.5</v>
+      </c>
+      <c r="AG21">
+        <v>12.5</v>
+      </c>
+      <c r="AH21">
         <v>25</v>
       </c>
-      <c r="Z21">
+      <c r="AI21">
+        <v>90</v>
+      </c>
+      <c r="AJ21">
+        <v>34</v>
+      </c>
+      <c r="AK21">
+        <v>36</v>
+      </c>
+      <c r="AL21">
+        <v>70</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>38</v>
+      </c>
+      <c r="AO21">
+        <v>95</v>
+      </c>
+      <c r="AP21">
+        <v>7.6</v>
+      </c>
+      <c r="AQ21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR21">
+        <v>21</v>
+      </c>
+      <c r="AS21">
+        <v>75</v>
+      </c>
+      <c r="AT21">
+        <v>6.6</v>
+      </c>
+      <c r="AU21">
+        <v>6.6</v>
+      </c>
+      <c r="AV21">
+        <v>16</v>
+      </c>
+      <c r="AW21">
+        <v>55</v>
+      </c>
+      <c r="AX21">
+        <v>11.5</v>
+      </c>
+      <c r="AY21">
+        <v>11.5</v>
+      </c>
+      <c r="AZ21">
+        <v>23</v>
+      </c>
+      <c r="BA21">
         <v>80</v>
       </c>
-      <c r="AA21">
-        <v>350</v>
-      </c>
-      <c r="AB21">
-        <v>7.8</v>
-      </c>
-      <c r="AC21">
+      <c r="BB21">
+        <v>30</v>
+      </c>
+      <c r="BC21">
+        <v>30</v>
+      </c>
+      <c r="BD21">
+        <v>60</v>
+      </c>
+      <c r="BE21">
+        <v>95</v>
+      </c>
+      <c r="BF21">
+        <v>34</v>
+      </c>
+      <c r="BG21">
+        <v>85</v>
+      </c>
+      <c r="BH21">
+        <v>2.62</v>
+      </c>
+      <c r="BI21">
+        <v>2.44</v>
+      </c>
+      <c r="BJ21">
+        <v>11.5</v>
+      </c>
+      <c r="BK21">
+        <v>10</v>
+      </c>
+      <c r="BL21">
+        <v>260</v>
+      </c>
+      <c r="BM21">
+        <v>12</v>
+      </c>
+      <c r="BN21">
+        <v>5</v>
+      </c>
+      <c r="BO21">
+        <v>4.5</v>
+      </c>
+      <c r="BP21">
+        <v>22</v>
+      </c>
+      <c r="BQ21">
+        <v>16</v>
+      </c>
+      <c r="BR21">
+        <v>55</v>
+      </c>
+      <c r="BS21">
+        <v>11</v>
+      </c>
+      <c r="BT21">
+        <v>7.6</v>
+      </c>
+      <c r="BU21">
+        <v>6</v>
+      </c>
+      <c r="BV21">
+        <v>40</v>
+      </c>
+      <c r="BW21">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD21">
-        <v>36</v>
-      </c>
-      <c r="AE21">
-        <v>180</v>
-      </c>
-      <c r="AF21">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG21">
-        <v>12</v>
-      </c>
-      <c r="AH21">
-        <v>34</v>
-      </c>
-      <c r="AI21">
-        <v>170</v>
-      </c>
-      <c r="AJ21">
-        <v>18</v>
-      </c>
-      <c r="AK21">
-        <v>24</v>
-      </c>
-      <c r="AL21">
-        <v>60</v>
-      </c>
-      <c r="AM21">
-        <v>250</v>
-      </c>
-      <c r="AN21">
-        <v>13.5</v>
-      </c>
-      <c r="AO21">
-        <v>300</v>
-      </c>
-      <c r="AP21">
-        <v>10</v>
-      </c>
-      <c r="AQ21">
-        <v>14.5</v>
-      </c>
-      <c r="AR21">
-        <v>5</v>
-      </c>
-      <c r="AS21">
-        <v>5.2</v>
-      </c>
-      <c r="AT21">
-        <v>5.8</v>
-      </c>
-      <c r="AU21">
-        <v>8</v>
-      </c>
-      <c r="AV21">
-        <v>21</v>
-      </c>
-      <c r="AW21">
-        <v>5.1</v>
-      </c>
-      <c r="AX21">
-        <v>7.2</v>
-      </c>
-      <c r="AY21">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ21">
-        <v>21</v>
-      </c>
-      <c r="BA21">
-        <v>5.1</v>
-      </c>
-      <c r="BB21">
-        <v>12.5</v>
-      </c>
-      <c r="BC21">
-        <v>16.5</v>
-      </c>
-      <c r="BD21">
-        <v>4.9</v>
-      </c>
-      <c r="BE21">
-        <v>5.2</v>
-      </c>
-      <c r="BF21">
-        <v>8.4</v>
-      </c>
-      <c r="BG21">
-        <v>5.2</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.04</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.04</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.04</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.04</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.04</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.04</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.04</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.04</v>
-      </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB21" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5906,483 +5924,483 @@
         <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F22">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="G22">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="H22">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="I22">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="J22">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="K22">
+        <v>3.9</v>
+      </c>
+      <c r="L22">
+        <v>1.39</v>
+      </c>
+      <c r="M22">
+        <v>1.07</v>
+      </c>
+      <c r="N22">
+        <v>3.55</v>
+      </c>
+      <c r="O22">
+        <v>1.3</v>
+      </c>
+      <c r="P22">
+        <v>1.9</v>
+      </c>
+      <c r="Q22">
+        <v>1.89</v>
+      </c>
+      <c r="R22">
+        <v>1.35</v>
+      </c>
+      <c r="S22">
+        <v>3.25</v>
+      </c>
+      <c r="T22">
+        <v>1.7</v>
+      </c>
+      <c r="U22">
+        <v>2.12</v>
+      </c>
+      <c r="V22">
+        <v>1.43</v>
+      </c>
+      <c r="W22">
+        <v>1.59</v>
+      </c>
+      <c r="X22">
+        <v>17</v>
+      </c>
+      <c r="Y22">
+        <v>14.5</v>
+      </c>
+      <c r="Z22">
+        <v>25</v>
+      </c>
+      <c r="AA22">
+        <v>60</v>
+      </c>
+      <c r="AB22">
+        <v>12.5</v>
+      </c>
+      <c r="AC22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD22">
+        <v>15.5</v>
+      </c>
+      <c r="AE22">
+        <v>42</v>
+      </c>
+      <c r="AF22">
+        <v>19.5</v>
+      </c>
+      <c r="AG22">
+        <v>13.5</v>
+      </c>
+      <c r="AH22">
+        <v>19.5</v>
+      </c>
+      <c r="AI22">
+        <v>55</v>
+      </c>
+      <c r="AJ22">
+        <v>42</v>
+      </c>
+      <c r="AK22">
+        <v>32</v>
+      </c>
+      <c r="AL22">
+        <v>46</v>
+      </c>
+      <c r="AM22">
+        <v>110</v>
+      </c>
+      <c r="AN22">
+        <v>25</v>
+      </c>
+      <c r="AO22">
+        <v>36</v>
+      </c>
+      <c r="AP22">
+        <v>12.5</v>
+      </c>
+      <c r="AQ22">
+        <v>10.5</v>
+      </c>
+      <c r="AR22">
+        <v>18</v>
+      </c>
+      <c r="AS22">
+        <v>4.8</v>
+      </c>
+      <c r="AT22">
+        <v>8.4</v>
+      </c>
+      <c r="AU22">
         <v>6.2</v>
       </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.1</v>
-      </c>
-      <c r="N22">
+      <c r="AV22">
+        <v>11.5</v>
+      </c>
+      <c r="AW22">
+        <v>4.6</v>
+      </c>
+      <c r="AX22">
+        <v>14</v>
+      </c>
+      <c r="AY22">
+        <v>10</v>
+      </c>
+      <c r="AZ22">
+        <v>14</v>
+      </c>
+      <c r="BA22">
+        <v>4.8</v>
+      </c>
+      <c r="BB22">
+        <v>4.6</v>
+      </c>
+      <c r="BC22">
+        <v>4.6</v>
+      </c>
+      <c r="BD22">
+        <v>4.7</v>
+      </c>
+      <c r="BE22">
+        <v>5</v>
+      </c>
+      <c r="BF22">
+        <v>18</v>
+      </c>
+      <c r="BG22">
+        <v>4.5</v>
+      </c>
+      <c r="BH22">
+        <v>3.55</v>
+      </c>
+      <c r="BI22">
+        <v>2.84</v>
+      </c>
+      <c r="BJ22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK22">
+        <v>4.9</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>2.58</v>
+      </c>
+      <c r="BN22">
+        <v>5.7</v>
+      </c>
+      <c r="BO22">
+        <v>3.65</v>
+      </c>
+      <c r="BP22">
+        <v>19.5</v>
+      </c>
+      <c r="BQ22">
+        <v>6.6</v>
+      </c>
+      <c r="BR22">
+        <v>34</v>
+      </c>
+      <c r="BS22">
+        <v>2.44</v>
+      </c>
+      <c r="BT22">
+        <v>6.6</v>
+      </c>
+      <c r="BU22">
+        <v>4</v>
+      </c>
+      <c r="BV22">
+        <v>25</v>
+      </c>
+      <c r="BW22">
+        <v>7.2</v>
+      </c>
+      <c r="BX22">
+        <v>38</v>
+      </c>
+      <c r="BY22">
         <v>2.46</v>
       </c>
-      <c r="O22">
-        <v>1.28</v>
-      </c>
-      <c r="P22">
-        <v>1.54</v>
-      </c>
-      <c r="Q22">
-        <v>2.42</v>
-      </c>
-      <c r="R22">
-        <v>1.13</v>
-      </c>
-      <c r="S22">
-        <v>3.05</v>
-      </c>
-      <c r="T22">
-        <v>1.11</v>
-      </c>
-      <c r="U22">
-        <v>1.11</v>
-      </c>
-      <c r="V22">
-        <v>1.56</v>
-      </c>
-      <c r="W22">
-        <v>1.34</v>
-      </c>
-      <c r="X22">
-        <v>1000</v>
-      </c>
-      <c r="Y22">
-        <v>11.5</v>
-      </c>
-      <c r="Z22">
-        <v>26</v>
-      </c>
-      <c r="AA22">
-        <v>75</v>
-      </c>
-      <c r="AB22">
-        <v>11.5</v>
-      </c>
-      <c r="AC22">
-        <v>9.4</v>
-      </c>
-      <c r="AD22">
-        <v>19.5</v>
-      </c>
-      <c r="AE22">
-        <v>65</v>
-      </c>
-      <c r="AF22">
-        <v>30</v>
-      </c>
-      <c r="AG22">
-        <v>19.5</v>
-      </c>
-      <c r="AH22">
-        <v>950</v>
-      </c>
-      <c r="AI22">
-        <v>100</v>
-      </c>
-      <c r="AJ22">
-        <v>100</v>
-      </c>
-      <c r="AK22">
-        <v>75</v>
-      </c>
-      <c r="AL22">
-        <v>100</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>100</v>
-      </c>
-      <c r="AO22">
-        <v>65</v>
-      </c>
-      <c r="AP22">
-        <v>2.4</v>
-      </c>
-      <c r="AQ22">
-        <v>1.98</v>
-      </c>
-      <c r="AR22">
-        <v>2.2</v>
-      </c>
-      <c r="AS22">
-        <v>2.32</v>
-      </c>
-      <c r="AT22">
-        <v>1.98</v>
-      </c>
-      <c r="AU22">
-        <v>1.91</v>
-      </c>
-      <c r="AV22">
-        <v>2.14</v>
-      </c>
-      <c r="AW22">
-        <v>2.32</v>
-      </c>
-      <c r="AX22">
-        <v>2.22</v>
-      </c>
-      <c r="AY22">
-        <v>2.14</v>
-      </c>
-      <c r="AZ22">
-        <v>2.22</v>
-      </c>
-      <c r="BA22">
-        <v>2.34</v>
-      </c>
-      <c r="BB22">
-        <v>2.34</v>
-      </c>
-      <c r="BC22">
-        <v>2.32</v>
-      </c>
-      <c r="BD22">
-        <v>2.34</v>
-      </c>
-      <c r="BE22">
-        <v>2.4</v>
-      </c>
-      <c r="BF22">
-        <v>2.34</v>
-      </c>
-      <c r="BG22">
-        <v>2.32</v>
-      </c>
-      <c r="BH22">
-        <v>2.72</v>
-      </c>
-      <c r="BI22">
-        <v>2.26</v>
-      </c>
-      <c r="BJ22">
-        <v>12</v>
-      </c>
-      <c r="BK22">
-        <v>6</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>11</v>
-      </c>
-      <c r="BN22">
-        <v>6.6</v>
-      </c>
-      <c r="BO22">
-        <v>5.1</v>
-      </c>
-      <c r="BP22">
-        <v>36</v>
-      </c>
-      <c r="BQ22">
-        <v>9</v>
-      </c>
-      <c r="BR22">
-        <v>60</v>
-      </c>
-      <c r="BS22">
-        <v>10</v>
-      </c>
-      <c r="BT22">
-        <v>5.4</v>
-      </c>
-      <c r="BU22">
-        <v>4.1</v>
-      </c>
-      <c r="BV22">
-        <v>24</v>
-      </c>
-      <c r="BW22">
-        <v>8</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>9.6</v>
-      </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA22">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F23">
-        <v>2.42</v>
+        <v>1.57</v>
       </c>
       <c r="G23">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="H23">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="I23">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="K23">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O23">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P23">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R23">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="W23">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC23">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP23">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>1.15</v>
+        <v>18</v>
       </c>
       <c r="AR23">
-        <v>1.15</v>
+        <v>50</v>
       </c>
       <c r="AS23">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AT23">
-        <v>1.15</v>
+        <v>5.9</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV23">
-        <v>1.15</v>
+        <v>26</v>
       </c>
       <c r="AW23">
-        <v>1.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX23">
-        <v>1.15</v>
+        <v>7.2</v>
       </c>
       <c r="AY23">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AZ23">
-        <v>1.15</v>
+        <v>25</v>
       </c>
       <c r="BA23">
-        <v>1.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB23">
-        <v>1.15</v>
+        <v>13</v>
       </c>
       <c r="BC23">
-        <v>1.15</v>
+        <v>17</v>
       </c>
       <c r="BD23">
-        <v>1.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BF23">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BG23">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="BH23">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6390,241 +6408,241 @@
         <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
         <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F24">
-        <v>1.61</v>
+        <v>3.35</v>
       </c>
       <c r="G24">
-        <v>1.68</v>
+        <v>3.9</v>
       </c>
       <c r="H24">
-        <v>6.2</v>
+        <v>2.38</v>
       </c>
       <c r="I24">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
       <c r="J24">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="K24">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M24">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N24">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="O24">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="Q24">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S24">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U24">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="V24">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
-        <v>2.46</v>
+        <v>1.34</v>
       </c>
       <c r="X24">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="Y24">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="Z24">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AA24">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="AB24">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC24">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24">
+        <v>14.5</v>
+      </c>
+      <c r="AE24">
+        <v>44</v>
+      </c>
+      <c r="AF24">
         <v>27</v>
       </c>
-      <c r="AE24">
-        <v>120</v>
-      </c>
-      <c r="AF24">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AG24">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AH24">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI24">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AJ24">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="AK24">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="AL24">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM24">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="AN24">
-        <v>9.800000000000001</v>
+        <v>95</v>
       </c>
       <c r="AO24">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AP24">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="AR24">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS24">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT24">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU24">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV24">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX24">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AY24">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AZ24">
         <v>20</v>
       </c>
       <c r="BA24">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB24">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BC24">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD24">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="BE24">
+        <v>5.1</v>
+      </c>
+      <c r="BF24">
+        <v>5</v>
+      </c>
+      <c r="BG24">
+        <v>4.7</v>
+      </c>
+      <c r="BH24">
+        <v>2.74</v>
+      </c>
+      <c r="BI24">
+        <v>2.26</v>
+      </c>
+      <c r="BJ24">
+        <v>12</v>
+      </c>
+      <c r="BK24">
+        <v>5.9</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
         <v>11</v>
       </c>
-      <c r="BF24">
-        <v>8</v>
-      </c>
-      <c r="BG24">
-        <v>11</v>
-      </c>
-      <c r="BH24">
-        <v>3.65</v>
-      </c>
-      <c r="BI24">
-        <v>2.92</v>
-      </c>
-      <c r="BJ24">
-        <v>11.5</v>
-      </c>
-      <c r="BK24">
-        <v>5.6</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>2.72</v>
-      </c>
       <c r="BN24">
+        <v>6.8</v>
+      </c>
+      <c r="BO24">
+        <v>5.1</v>
+      </c>
+      <c r="BP24">
+        <v>36</v>
+      </c>
+      <c r="BQ24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR24">
+        <v>60</v>
+      </c>
+      <c r="BS24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT24">
+        <v>5.3</v>
+      </c>
+      <c r="BU24">
         <v>4.1</v>
       </c>
-      <c r="BO24">
-        <v>3.2</v>
-      </c>
-      <c r="BP24">
-        <v>10.5</v>
-      </c>
-      <c r="BQ24">
-        <v>5.4</v>
-      </c>
-      <c r="BR24">
-        <v>28</v>
-      </c>
-      <c r="BS24">
-        <v>8</v>
-      </c>
-      <c r="BT24">
-        <v>11</v>
-      </c>
-      <c r="BU24">
-        <v>5.5</v>
-      </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW24">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2.66</v>
+        <v>9.4</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB24" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6632,241 +6650,725 @@
         <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
         <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F25">
-        <v>1.51</v>
+        <v>2.46</v>
       </c>
       <c r="G25">
-        <v>1.58</v>
+        <v>2.68</v>
       </c>
       <c r="H25">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="I25">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="K25">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="L25">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
         <v>1.08</v>
       </c>
       <c r="N25">
+        <v>2.66</v>
+      </c>
+      <c r="O25">
+        <v>1.43</v>
+      </c>
+      <c r="P25">
+        <v>1.56</v>
+      </c>
+      <c r="Q25">
+        <v>2.22</v>
+      </c>
+      <c r="R25">
+        <v>1.17</v>
+      </c>
+      <c r="S25">
+        <v>3.8</v>
+      </c>
+      <c r="T25">
+        <v>1.94</v>
+      </c>
+      <c r="U25">
+        <v>1.91</v>
+      </c>
+      <c r="V25">
+        <v>1.39</v>
+      </c>
+      <c r="W25">
+        <v>1.59</v>
+      </c>
+      <c r="X25">
+        <v>12</v>
+      </c>
+      <c r="Y25">
+        <v>12.5</v>
+      </c>
+      <c r="Z25">
+        <v>26</v>
+      </c>
+      <c r="AA25">
+        <v>75</v>
+      </c>
+      <c r="AB25">
+        <v>10</v>
+      </c>
+      <c r="AC25">
+        <v>7.4</v>
+      </c>
+      <c r="AD25">
+        <v>17</v>
+      </c>
+      <c r="AE25">
+        <v>55</v>
+      </c>
+      <c r="AF25">
+        <v>18</v>
+      </c>
+      <c r="AG25">
+        <v>14</v>
+      </c>
+      <c r="AH25">
+        <v>24</v>
+      </c>
+      <c r="AI25">
+        <v>75</v>
+      </c>
+      <c r="AJ25">
+        <v>44</v>
+      </c>
+      <c r="AK25">
+        <v>38</v>
+      </c>
+      <c r="AL25">
+        <v>65</v>
+      </c>
+      <c r="AM25">
+        <v>160</v>
+      </c>
+      <c r="AN25">
+        <v>38</v>
+      </c>
+      <c r="AO25">
+        <v>65</v>
+      </c>
+      <c r="AP25">
+        <v>9</v>
+      </c>
+      <c r="AQ25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR25">
+        <v>4.6</v>
+      </c>
+      <c r="AS25">
+        <v>5.2</v>
+      </c>
+      <c r="AT25">
+        <v>7.6</v>
+      </c>
+      <c r="AU25">
+        <v>6.4</v>
+      </c>
+      <c r="AV25">
+        <v>12.5</v>
+      </c>
+      <c r="AW25">
+        <v>5</v>
+      </c>
+      <c r="AX25">
+        <v>13.5</v>
+      </c>
+      <c r="AY25">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25">
+        <v>4.5</v>
+      </c>
+      <c r="BA25">
+        <v>5.2</v>
+      </c>
+      <c r="BB25">
+        <v>4.9</v>
+      </c>
+      <c r="BC25">
+        <v>4.8</v>
+      </c>
+      <c r="BD25">
+        <v>5.1</v>
+      </c>
+      <c r="BE25">
+        <v>5.4</v>
+      </c>
+      <c r="BF25">
+        <v>4.8</v>
+      </c>
+      <c r="BG25">
+        <v>5.1</v>
+      </c>
+      <c r="BH25">
+        <v>3.25</v>
+      </c>
+      <c r="BI25">
+        <v>2.46</v>
+      </c>
+      <c r="BJ25">
+        <v>12</v>
+      </c>
+      <c r="BK25">
+        <v>4</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>5.9</v>
+      </c>
+      <c r="BN25">
+        <v>5.9</v>
+      </c>
+      <c r="BO25">
+        <v>4.2</v>
+      </c>
+      <c r="BP25">
+        <v>24</v>
+      </c>
+      <c r="BQ25">
+        <v>4.8</v>
+      </c>
+      <c r="BR25">
+        <v>46</v>
+      </c>
+      <c r="BS25">
+        <v>5.4</v>
+      </c>
+      <c r="BT25">
+        <v>7.2</v>
+      </c>
+      <c r="BU25">
+        <v>5</v>
+      </c>
+      <c r="BV25">
+        <v>34</v>
+      </c>
+      <c r="BW25">
+        <v>5.2</v>
+      </c>
+      <c r="BX25">
+        <v>55</v>
+      </c>
+      <c r="BY25">
+        <v>5.5</v>
+      </c>
+      <c r="BZ25">
+        <v>46</v>
+      </c>
+      <c r="CA25">
+        <v>5.4</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26">
+        <v>1.61</v>
+      </c>
+      <c r="G26">
+        <v>1.67</v>
+      </c>
+      <c r="H26">
+        <v>6.2</v>
+      </c>
+      <c r="I26">
+        <v>7.8</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <v>4.3</v>
+      </c>
+      <c r="L26">
+        <v>1.34</v>
+      </c>
+      <c r="M26">
+        <v>1.07</v>
+      </c>
+      <c r="N26">
+        <v>3.65</v>
+      </c>
+      <c r="O26">
+        <v>1.3</v>
+      </c>
+      <c r="P26">
+        <v>1.9</v>
+      </c>
+      <c r="Q26">
+        <v>1.81</v>
+      </c>
+      <c r="R26">
+        <v>1.35</v>
+      </c>
+      <c r="S26">
+        <v>3.3</v>
+      </c>
+      <c r="T26">
+        <v>1.95</v>
+      </c>
+      <c r="U26">
+        <v>1.86</v>
+      </c>
+      <c r="V26">
+        <v>1.15</v>
+      </c>
+      <c r="W26">
+        <v>2.5</v>
+      </c>
+      <c r="X26">
+        <v>15</v>
+      </c>
+      <c r="Y26">
+        <v>22</v>
+      </c>
+      <c r="Z26">
+        <v>60</v>
+      </c>
+      <c r="AA26">
+        <v>240</v>
+      </c>
+      <c r="AB26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC26">
+        <v>9.4</v>
+      </c>
+      <c r="AD26">
+        <v>27</v>
+      </c>
+      <c r="AE26">
+        <v>120</v>
+      </c>
+      <c r="AF26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG26">
+        <v>11.5</v>
+      </c>
+      <c r="AH26">
+        <v>23</v>
+      </c>
+      <c r="AI26">
+        <v>120</v>
+      </c>
+      <c r="AJ26">
+        <v>15.5</v>
+      </c>
+      <c r="AK26">
+        <v>19</v>
+      </c>
+      <c r="AL26">
+        <v>44</v>
+      </c>
+      <c r="AM26">
+        <v>140</v>
+      </c>
+      <c r="AN26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO26">
+        <v>160</v>
+      </c>
+      <c r="AP26">
+        <v>12</v>
+      </c>
+      <c r="AQ26">
+        <v>18</v>
+      </c>
+      <c r="AR26">
+        <v>8.4</v>
+      </c>
+      <c r="AS26">
+        <v>9.4</v>
+      </c>
+      <c r="AT26">
+        <v>7.2</v>
+      </c>
+      <c r="AU26">
+        <v>7.6</v>
+      </c>
+      <c r="AV26">
+        <v>21</v>
+      </c>
+      <c r="AW26">
+        <v>10.5</v>
+      </c>
+      <c r="AX26">
+        <v>8</v>
+      </c>
+      <c r="AY26">
+        <v>9</v>
+      </c>
+      <c r="AZ26">
+        <v>20</v>
+      </c>
+      <c r="BA26">
+        <v>10.5</v>
+      </c>
+      <c r="BB26">
+        <v>13</v>
+      </c>
+      <c r="BC26">
+        <v>15.5</v>
+      </c>
+      <c r="BD26">
+        <v>30</v>
+      </c>
+      <c r="BE26">
+        <v>10.5</v>
+      </c>
+      <c r="BF26">
+        <v>8</v>
+      </c>
+      <c r="BG26">
+        <v>10.5</v>
+      </c>
+      <c r="BH26">
+        <v>3.65</v>
+      </c>
+      <c r="BI26">
+        <v>2.92</v>
+      </c>
+      <c r="BJ26">
+        <v>11.5</v>
+      </c>
+      <c r="BK26">
+        <v>5.6</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>2.72</v>
+      </c>
+      <c r="BN26">
+        <v>4.1</v>
+      </c>
+      <c r="BO26">
+        <v>3.2</v>
+      </c>
+      <c r="BP26">
+        <v>10.5</v>
+      </c>
+      <c r="BQ26">
+        <v>5.4</v>
+      </c>
+      <c r="BR26">
+        <v>28</v>
+      </c>
+      <c r="BS26">
+        <v>8</v>
+      </c>
+      <c r="BT26">
+        <v>11</v>
+      </c>
+      <c r="BU26">
+        <v>5.5</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>2.66</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>2.66</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27">
+        <v>1.51</v>
+      </c>
+      <c r="G27">
+        <v>1.58</v>
+      </c>
+      <c r="H27">
+        <v>8</v>
+      </c>
+      <c r="I27">
+        <v>9.6</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27">
+        <v>4.6</v>
+      </c>
+      <c r="L27">
+        <v>1.43</v>
+      </c>
+      <c r="M27">
+        <v>1.08</v>
+      </c>
+      <c r="N27">
+        <v>3.25</v>
+      </c>
+      <c r="O27">
+        <v>1.38</v>
+      </c>
+      <c r="P27">
+        <v>1.74</v>
+      </c>
+      <c r="Q27">
+        <v>2.1</v>
+      </c>
+      <c r="R27">
+        <v>1.27</v>
+      </c>
+      <c r="S27">
+        <v>3.9</v>
+      </c>
+      <c r="T27">
+        <v>2.2</v>
+      </c>
+      <c r="U27">
+        <v>1.68</v>
+      </c>
+      <c r="V27">
+        <v>1.11</v>
+      </c>
+      <c r="W27">
+        <v>2.72</v>
+      </c>
+      <c r="X27">
+        <v>14.5</v>
+      </c>
+      <c r="Y27">
+        <v>25</v>
+      </c>
+      <c r="Z27">
+        <v>85</v>
+      </c>
+      <c r="AA27">
+        <v>390</v>
+      </c>
+      <c r="AB27">
+        <v>7</v>
+      </c>
+      <c r="AC27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27">
+        <v>34</v>
+      </c>
+      <c r="AE27">
+        <v>200</v>
+      </c>
+      <c r="AF27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG27">
+        <v>11</v>
+      </c>
+      <c r="AH27">
+        <v>32</v>
+      </c>
+      <c r="AI27">
+        <v>180</v>
+      </c>
+      <c r="AJ27">
+        <v>16.5</v>
+      </c>
+      <c r="AK27">
+        <v>20</v>
+      </c>
+      <c r="AL27">
+        <v>60</v>
+      </c>
+      <c r="AM27">
+        <v>250</v>
+      </c>
+      <c r="AN27">
+        <v>12.5</v>
+      </c>
+      <c r="AO27">
+        <v>340</v>
+      </c>
+      <c r="AP27">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27">
+        <v>18</v>
+      </c>
+      <c r="AR27">
+        <v>7</v>
+      </c>
+      <c r="AS27">
+        <v>7.4</v>
+      </c>
+      <c r="AT27">
+        <v>5.8</v>
+      </c>
+      <c r="AU27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27">
+        <v>6.2</v>
+      </c>
+      <c r="AW27">
+        <v>7.2</v>
+      </c>
+      <c r="AX27">
+        <v>6.8</v>
+      </c>
+      <c r="AY27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ27">
+        <v>6</v>
+      </c>
+      <c r="BA27">
+        <v>7.2</v>
+      </c>
+      <c r="BB27">
+        <v>11.5</v>
+      </c>
+      <c r="BC27">
+        <v>16</v>
+      </c>
+      <c r="BD27">
+        <v>6.8</v>
+      </c>
+      <c r="BE27">
+        <v>7.4</v>
+      </c>
+      <c r="BF27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG27">
+        <v>7.4</v>
+      </c>
+      <c r="BH27">
+        <v>3.55</v>
+      </c>
+      <c r="BI27">
+        <v>2.66</v>
+      </c>
+      <c r="BJ27">
+        <v>14.5</v>
+      </c>
+      <c r="BK27">
+        <v>4.2</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>5.7</v>
+      </c>
+      <c r="BN27">
+        <v>4.3</v>
+      </c>
+      <c r="BO27">
         <v>3.1</v>
       </c>
-      <c r="O25">
-        <v>1.38</v>
-      </c>
-      <c r="P25">
-        <v>1.73</v>
-      </c>
-      <c r="Q25">
-        <v>2.12</v>
-      </c>
-      <c r="R25">
-        <v>1.27</v>
-      </c>
-      <c r="S25">
-        <v>3.9</v>
-      </c>
-      <c r="T25">
-        <v>2.2</v>
-      </c>
-      <c r="U25">
-        <v>1.7</v>
-      </c>
-      <c r="V25">
-        <v>1.11</v>
-      </c>
-      <c r="W25">
-        <v>2.7</v>
-      </c>
-      <c r="X25">
-        <v>14.5</v>
-      </c>
-      <c r="Y25">
-        <v>25</v>
-      </c>
-      <c r="Z25">
-        <v>85</v>
-      </c>
-      <c r="AA25">
-        <v>390</v>
-      </c>
-      <c r="AB25">
-        <v>7.6</v>
-      </c>
-      <c r="AC25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD25">
-        <v>38</v>
-      </c>
-      <c r="AE25">
-        <v>200</v>
-      </c>
-      <c r="AF25">
-        <v>9.4</v>
-      </c>
-      <c r="AG25">
+      <c r="BP27">
         <v>12</v>
       </c>
-      <c r="AH25">
-        <v>34</v>
-      </c>
-      <c r="AI25">
-        <v>180</v>
-      </c>
-      <c r="AJ25">
-        <v>16.5</v>
-      </c>
-      <c r="AK25">
-        <v>22</v>
-      </c>
-      <c r="AL25">
-        <v>60</v>
-      </c>
-      <c r="AM25">
-        <v>250</v>
-      </c>
-      <c r="AN25">
-        <v>12.5</v>
-      </c>
-      <c r="AO25">
-        <v>340</v>
-      </c>
-      <c r="AP25">
-        <v>10.5</v>
-      </c>
-      <c r="AQ25">
-        <v>18</v>
-      </c>
-      <c r="AR25">
+      <c r="BQ27">
+        <v>3.95</v>
+      </c>
+      <c r="BR27">
+        <v>36</v>
+      </c>
+      <c r="BS27">
+        <v>5</v>
+      </c>
+      <c r="BT27">
+        <v>13</v>
+      </c>
+      <c r="BU27">
+        <v>4</v>
+      </c>
+      <c r="BV27">
+        <v>100</v>
+      </c>
+      <c r="BW27">
+        <v>5.5</v>
+      </c>
+      <c r="BX27">
+        <v>110</v>
+      </c>
+      <c r="BY27">
         <v>5.6</v>
       </c>
-      <c r="AS25">
-        <v>5.9</v>
-      </c>
-      <c r="AT25">
-        <v>5.8</v>
-      </c>
-      <c r="AU25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV25">
-        <v>5.2</v>
-      </c>
-      <c r="AW25">
-        <v>5.8</v>
-      </c>
-      <c r="AX25">
-        <v>6.8</v>
-      </c>
-      <c r="AY25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ25">
-        <v>5.1</v>
-      </c>
-      <c r="BA25">
-        <v>5.8</v>
-      </c>
-      <c r="BB25">
-        <v>11.5</v>
-      </c>
-      <c r="BC25">
-        <v>16</v>
-      </c>
-      <c r="BD25">
-        <v>5.4</v>
-      </c>
-      <c r="BE25">
-        <v>5.8</v>
-      </c>
-      <c r="BF25">
-        <v>8.4</v>
-      </c>
-      <c r="BG25">
-        <v>5.9</v>
-      </c>
-      <c r="BH25">
-        <v>3.55</v>
-      </c>
-      <c r="BI25">
-        <v>2.66</v>
-      </c>
-      <c r="BJ25">
-        <v>14.5</v>
-      </c>
-      <c r="BK25">
-        <v>4.2</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>5.7</v>
-      </c>
-      <c r="BN25">
-        <v>4.3</v>
-      </c>
-      <c r="BO25">
-        <v>3.1</v>
-      </c>
-      <c r="BP25">
-        <v>12</v>
-      </c>
-      <c r="BQ25">
-        <v>3.95</v>
-      </c>
-      <c r="BR25">
-        <v>36</v>
-      </c>
-      <c r="BS25">
-        <v>5</v>
-      </c>
-      <c r="BT25">
-        <v>13</v>
-      </c>
-      <c r="BU25">
-        <v>4</v>
-      </c>
-      <c r="BV25">
-        <v>100</v>
-      </c>
-      <c r="BW25">
-        <v>5.5</v>
-      </c>
-      <c r="BX25">
-        <v>110</v>
-      </c>
-      <c r="BY25">
-        <v>5.6</v>
-      </c>
-      <c r="BZ25">
+      <c r="BZ27">
         <v>27</v>
       </c>
-      <c r="CA25">
+      <c r="CA27">
         <v>4.8</v>
       </c>
-      <c r="CB25" t="s">
-        <v>156</v>
+      <c r="CB27" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -502,7 +502,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 13:01:38</t>
+    <t>2026-08-19 15:13:06</t>
   </si>
 </sst>
 </file>
@@ -1096,16 +1096,16 @@
         <v>136</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G2">
         <v>4.2</v>
       </c>
       <c r="H2">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J2">
         <v>4.2</v>
@@ -1114,7 +1114,7 @@
         <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1126,22 +1126,22 @@
         <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S2">
         <v>2.54</v>
       </c>
       <c r="T2">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V2">
         <v>2.08</v>
@@ -1201,7 +1201,7 @@
         <v>32</v>
       </c>
       <c r="AO2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP2">
         <v>21</v>
@@ -1213,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="AS2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT2">
         <v>18.5</v>
@@ -1231,7 +1231,7 @@
         <v>29</v>
       </c>
       <c r="AY2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ2">
         <v>14.5</v>
@@ -1249,10 +1249,10 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BF2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG2">
         <v>8</v>
@@ -1261,61 +1261,61 @@
         <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BP2">
         <v>30</v>
       </c>
       <c r="BQ2">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BT2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BU2">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BV2">
         <v>13</v>
       </c>
       <c r="BW2">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BX2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY2">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2">
         <v>16</v>
       </c>
       <c r="CA2">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>162</v>
@@ -1338,22 +1338,22 @@
         <v>137</v>
       </c>
       <c r="F3">
+        <v>2.62</v>
+      </c>
+      <c r="G3">
         <v>2.68</v>
       </c>
-      <c r="G3">
-        <v>2.76</v>
-      </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1362,7 +1362,7 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
         <v>1.58</v>
@@ -1371,70 +1371,70 @@
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X3">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB3">
         <v>7.8</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AD3">
         <v>16</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
         <v>15</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM3">
         <v>220</v>
@@ -1455,7 +1455,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
         <v>7</v>
@@ -1479,31 +1479,31 @@
         <v>20</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BC3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
         <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1518,10 +1518,10 @@
         <v>17</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1533,19 +1533,19 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1580,22 +1580,22 @@
         <v>138</v>
       </c>
       <c r="F4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
         <v>6.2</v>
       </c>
-      <c r="I4">
-        <v>6.6</v>
-      </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.45</v>
@@ -1604,85 +1604,85 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T4">
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="X4">
         <v>13</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
         <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH4">
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL4">
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO4">
         <v>130</v>
@@ -1691,28 +1691,28 @@
         <v>12</v>
       </c>
       <c r="AQ4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
         <v>42</v>
       </c>
       <c r="AS4">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AX4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
@@ -1721,31 +1721,31 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BB4">
         <v>15</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF4">
         <v>11</v>
       </c>
       <c r="BG4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BH4">
         <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
@@ -1754,13 +1754,13 @@
         <v>7.4</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO4">
         <v>3.75</v>
@@ -1775,10 +1775,10 @@
         <v>30</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BU4">
         <v>5.8</v>
@@ -1787,19 +1787,19 @@
         <v>60</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1828,7 +1828,7 @@
         <v>1.71</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
         <v>5.2</v>
@@ -1840,28 +1840,28 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T5">
         <v>1.69</v>
@@ -1873,13 +1873,13 @@
         <v>1.23</v>
       </c>
       <c r="W5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X5">
         <v>24</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z5">
         <v>44</v>
@@ -1894,7 +1894,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE5">
         <v>60</v>
@@ -1903,16 +1903,16 @@
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
         <v>16</v>
@@ -1924,10 +1924,10 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP5">
         <v>21</v>
@@ -1951,7 +1951,7 @@
         <v>18</v>
       </c>
       <c r="AW5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1972,7 +1972,7 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE5">
         <v>60</v>
@@ -1984,64 +1984,64 @@
         <v>42</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>95</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
         <v>11</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
+        <v>6.8</v>
+      </c>
+      <c r="BT5">
+        <v>9.4</v>
+      </c>
+      <c r="BU5">
         <v>7.2</v>
-      </c>
-      <c r="BT5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU5">
-        <v>6.8</v>
       </c>
       <c r="BV5">
         <v>40</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ5">
         <v>15</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="s">
         <v>162</v>
@@ -2064,7 +2064,7 @@
         <v>140</v>
       </c>
       <c r="F6">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
         <v>1.76</v>
@@ -2076,10 +2076,10 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2100,25 +2100,25 @@
         <v>2.36</v>
       </c>
       <c r="R6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
         <v>4.6</v>
       </c>
       <c r="T6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U6">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V6">
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
         <v>18.5</v>
@@ -2151,7 +2151,7 @@
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ6">
         <v>18</v>
@@ -2169,7 +2169,7 @@
         <v>15.5</v>
       </c>
       <c r="AO6">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AP6">
         <v>10</v>
@@ -2181,7 +2181,7 @@
         <v>38</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6">
         <v>5.7</v>
@@ -2199,7 +2199,7 @@
         <v>7.6</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
         <v>22</v>
@@ -2217,13 +2217,13 @@
         <v>42</v>
       </c>
       <c r="BE6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF6">
         <v>13</v>
       </c>
       <c r="BG6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2241,7 +2241,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN6">
         <v>4.2</v>
@@ -2271,13 +2271,13 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>141</v>
       </c>
       <c r="F7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I7">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J7">
         <v>3.9</v>
@@ -2333,10 +2333,10 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q7">
         <v>1.58</v>
@@ -2345,7 +2345,7 @@
         <v>1.67</v>
       </c>
       <c r="S7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T7">
         <v>1.55</v>
@@ -2354,22 +2354,22 @@
         <v>2.72</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X7">
         <v>24</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA7">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB7">
         <v>14.5</v>
@@ -2381,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF7">
         <v>16</v>
@@ -2408,7 +2408,7 @@
         <v>55</v>
       </c>
       <c r="AN7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO7">
         <v>25</v>
@@ -2420,10 +2420,10 @@
         <v>20</v>
       </c>
       <c r="AR7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT7">
         <v>13</v>
@@ -2432,7 +2432,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW7">
         <v>34</v>
@@ -2450,7 +2450,7 @@
         <v>34</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7">
         <v>16.5</v>
@@ -2462,16 +2462,16 @@
         <v>46</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH7">
         <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7">
         <v>8.6</v>
@@ -2483,13 +2483,13 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
         <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP7">
         <v>13</v>
@@ -2498,19 +2498,19 @@
         <v>9.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW7">
         <v>9.800000000000001</v>
@@ -2519,10 +2519,10 @@
         <v>29</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA7">
         <v>10.5</v>
@@ -2548,25 +2548,25 @@
         <v>142</v>
       </c>
       <c r="F8">
+        <v>2.58</v>
+      </c>
+      <c r="G8">
         <v>2.62</v>
       </c>
-      <c r="G8">
-        <v>2.64</v>
-      </c>
       <c r="H8">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I8">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2584,28 +2584,28 @@
         <v>1.75</v>
       </c>
       <c r="R8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
         <v>18.5</v>
       </c>
       <c r="Y8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
         <v>21</v>
@@ -2614,16 +2614,16 @@
         <v>42</v>
       </c>
       <c r="AB8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF8">
         <v>18.5</v>
@@ -2647,7 +2647,7 @@
         <v>34</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN8">
         <v>18</v>
@@ -2656,7 +2656,7 @@
         <v>21</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2674,13 +2674,13 @@
         <v>8</v>
       </c>
       <c r="AV8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW8">
         <v>25</v>
       </c>
       <c r="AX8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY8">
         <v>11</v>
@@ -2713,19 +2713,19 @@
         <v>4</v>
       </c>
       <c r="BI8">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM8">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
         <v>6</v>
@@ -2734,40 +2734,40 @@
         <v>5</v>
       </c>
       <c r="BP8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV8">
         <v>21</v>
       </c>
       <c r="BW8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>162</v>
@@ -2796,16 +2796,16 @@
         <v>1.86</v>
       </c>
       <c r="H9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J9">
         <v>4.1</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>1.33</v>
@@ -2814,25 +2814,25 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
         <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R9">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S9">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -2844,22 +2844,22 @@
         <v>2.16</v>
       </c>
       <c r="X9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z9">
         <v>36</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
         <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2880,7 +2880,7 @@
         <v>55</v>
       </c>
       <c r="AJ9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK9">
         <v>18</v>
@@ -2898,10 +2898,10 @@
         <v>48</v>
       </c>
       <c r="AP9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR9">
         <v>32</v>
@@ -2925,25 +2925,25 @@
         <v>11</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB9">
         <v>18</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF9">
         <v>8.800000000000001</v>
@@ -2952,25 +2952,25 @@
         <v>40</v>
       </c>
       <c r="BH9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
         <v>4.2</v>
@@ -2985,31 +2985,31 @@
         <v>23</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT9">
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <v>38</v>
       </c>
       <c r="BY9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="s">
         <v>162</v>
@@ -3035,7 +3035,7 @@
         <v>2.72</v>
       </c>
       <c r="G10">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H10">
         <v>2.64</v>
@@ -3044,7 +3044,7 @@
         <v>2.8</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
         <v>3.75</v>
@@ -3062,10 +3062,10 @@
         <v>1.31</v>
       </c>
       <c r="P10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
         <v>1.39</v>
@@ -3086,58 +3086,58 @@
         <v>1.53</v>
       </c>
       <c r="X10">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA10">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF10">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AG10">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH10">
         <v>19</v>
       </c>
       <c r="AI10">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK10">
+        <v>32</v>
+      </c>
+      <c r="AL10">
         <v>42</v>
       </c>
-      <c r="AL10">
-        <v>46</v>
-      </c>
       <c r="AM10">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP10">
         <v>12</v>
@@ -3146,7 +3146,7 @@
         <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS10">
         <v>27</v>
@@ -3164,16 +3164,16 @@
         <v>22</v>
       </c>
       <c r="AX10">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB10">
         <v>29</v>
@@ -3209,22 +3209,22 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN10">
         <v>5.9</v>
       </c>
       <c r="BO10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS10">
         <v>10.5</v>
@@ -3239,10 +3239,10 @@
         <v>21</v>
       </c>
       <c r="BW10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY10">
         <v>10.5</v>
@@ -3280,7 +3280,7 @@
         <v>2.06</v>
       </c>
       <c r="H11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
         <v>3.5</v>
@@ -3304,19 +3304,19 @@
         <v>1.13</v>
       </c>
       <c r="P11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T11">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U11">
         <v>3.15</v>
@@ -3340,7 +3340,7 @@
         <v>65</v>
       </c>
       <c r="AB11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC11">
         <v>12</v>
@@ -3349,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF11">
         <v>19.5</v>
@@ -3367,13 +3367,13 @@
         <v>27</v>
       </c>
       <c r="AK11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL11">
         <v>22</v>
       </c>
       <c r="AM11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN11">
         <v>7.2</v>
@@ -3391,7 +3391,7 @@
         <v>30</v>
       </c>
       <c r="AS11">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AT11">
         <v>18</v>
@@ -3433,10 +3433,10 @@
         <v>6.8</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH11">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BI11">
         <v>4.4</v>
@@ -3445,55 +3445,55 @@
         <v>8.6</v>
       </c>
       <c r="BK11">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL11">
         <v>55</v>
       </c>
       <c r="BM11">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BN11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP11">
         <v>13</v>
       </c>
       <c r="BQ11">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BR11">
         <v>19</v>
       </c>
       <c r="BS11">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BT11">
         <v>8</v>
       </c>
       <c r="BU11">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BV11">
         <v>23</v>
       </c>
       <c r="BW11">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BX11">
         <v>25</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BZ11">
         <v>11</v>
       </c>
       <c r="CA11">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="s">
         <v>162</v>
@@ -3516,13 +3516,13 @@
         <v>146</v>
       </c>
       <c r="F12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>6.2</v>
@@ -3531,7 +3531,7 @@
         <v>4.5</v>
       </c>
       <c r="K12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L12">
         <v>1.33</v>
@@ -3549,7 +3549,7 @@
         <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R12">
         <v>1.53</v>
@@ -3558,7 +3558,7 @@
         <v>2.84</v>
       </c>
       <c r="T12">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U12">
         <v>2.16</v>
@@ -3567,7 +3567,7 @@
         <v>1.19</v>
       </c>
       <c r="W12">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X12">
         <v>21</v>
@@ -3588,7 +3588,7 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12">
         <v>85</v>
@@ -3642,7 +3642,7 @@
         <v>9.4</v>
       </c>
       <c r="AV12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW12">
         <v>65</v>
@@ -3657,7 +3657,7 @@
         <v>18</v>
       </c>
       <c r="BA12">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BB12">
         <v>14</v>
@@ -3669,7 +3669,7 @@
         <v>27</v>
       </c>
       <c r="BE12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF12">
         <v>6.8</v>
@@ -3678,7 +3678,7 @@
         <v>55</v>
       </c>
       <c r="BH12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI12">
         <v>3.25</v>
@@ -3687,13 +3687,13 @@
         <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12">
         <v>4.4</v>
@@ -3705,37 +3705,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR12">
         <v>24</v>
       </c>
       <c r="BS12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT12">
         <v>10.5</v>
       </c>
       <c r="BU12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV12">
         <v>55</v>
       </c>
       <c r="BW12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX12">
         <v>55</v>
       </c>
       <c r="BY12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB12" t="s">
         <v>162</v>
@@ -3758,7 +3758,7 @@
         <v>147</v>
       </c>
       <c r="F13">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G13">
         <v>2.32</v>
@@ -3767,7 +3767,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J13">
         <v>4.1</v>
@@ -3776,37 +3776,37 @@
         <v>4.4</v>
       </c>
       <c r="L13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R13">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="S13">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="T13">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W13">
         <v>1.76</v>
@@ -3815,7 +3815,7 @@
         <v>32</v>
       </c>
       <c r="Y13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z13">
         <v>28</v>
@@ -3824,46 +3824,46 @@
         <v>55</v>
       </c>
       <c r="AB13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC13">
         <v>11</v>
       </c>
       <c r="AD13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE13">
         <v>28</v>
       </c>
       <c r="AF13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
         <v>13.5</v>
       </c>
       <c r="AI13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK13">
         <v>20</v>
       </c>
       <c r="AL13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="AN13">
         <v>9.6</v>
       </c>
       <c r="AO13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP13">
         <v>27</v>
@@ -3881,13 +3881,13 @@
         <v>17</v>
       </c>
       <c r="AU13">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX13">
         <v>18.5</v>
@@ -3914,13 +3914,13 @@
         <v>38</v>
       </c>
       <c r="BF13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH13">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI13">
         <v>4</v>
@@ -3929,55 +3929,55 @@
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BL13">
         <v>60</v>
       </c>
       <c r="BM13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN13">
         <v>6.2</v>
       </c>
       <c r="BO13">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP13">
         <v>15</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR13">
         <v>21</v>
       </c>
       <c r="BS13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT13">
         <v>7.2</v>
       </c>
       <c r="BU13">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV13">
         <v>20</v>
       </c>
       <c r="BW13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13">
         <v>12.5</v>
       </c>
       <c r="CA13">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB13" t="s">
         <v>162</v>
@@ -4000,19 +4000,19 @@
         <v>148</v>
       </c>
       <c r="F14">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G14">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H14">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I14">
         <v>2.82</v>
       </c>
       <c r="J14">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="K14">
         <v>3.8</v>
@@ -4051,7 +4051,7 @@
         <v>1.54</v>
       </c>
       <c r="W14">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X14">
         <v>19</v>
@@ -4075,7 +4075,7 @@
         <v>12.5</v>
       </c>
       <c r="AE14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AF14">
         <v>22</v>
@@ -4108,10 +4108,10 @@
         <v>23</v>
       </c>
       <c r="AP14">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR14">
         <v>5.7</v>
@@ -4126,7 +4126,7 @@
         <v>4.2</v>
       </c>
       <c r="AV14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW14">
         <v>6.4</v>
@@ -4138,7 +4138,7 @@
         <v>5.2</v>
       </c>
       <c r="AZ14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA14">
         <v>6.8</v>
@@ -4150,7 +4150,7 @@
         <v>6.6</v>
       </c>
       <c r="BD14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE14">
         <v>7.6</v>
@@ -4245,10 +4245,10 @@
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H15">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I15">
         <v>3.55</v>
@@ -4281,7 +4281,7 @@
         <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
         <v>1.58</v>
@@ -4290,10 +4290,10 @@
         <v>2.38</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4434,7 +4434,7 @@
         <v>6.2</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS15">
         <v>7.2</v>
@@ -4484,22 +4484,22 @@
         <v>150</v>
       </c>
       <c r="F16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G16">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I16">
-        <v>990</v>
+        <v>13.5</v>
       </c>
       <c r="J16">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K16">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4526,22 +4526,22 @@
         <v>1.72</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V16">
         <v>1.08</v>
       </c>
       <c r="W16">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X16">
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z16">
         <v>1000</v>
@@ -4550,154 +4550,154 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE16">
         <v>1000</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI16">
         <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM16">
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4732,13 +4732,13 @@
         <v>2.7</v>
       </c>
       <c r="H17">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I17">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K17">
         <v>4.1</v>
@@ -4759,16 +4759,16 @@
         <v>2.26</v>
       </c>
       <c r="Q17">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R17">
         <v>1.5</v>
       </c>
       <c r="S17">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T17">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U17">
         <v>2.42</v>
@@ -4777,13 +4777,13 @@
         <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X17">
         <v>24</v>
       </c>
       <c r="Y17">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z17">
         <v>23</v>
@@ -4822,7 +4822,7 @@
         <v>26</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM17">
         <v>75</v>
@@ -4834,52 +4834,52 @@
         <v>20</v>
       </c>
       <c r="AP17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ17">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR17">
         <v>18.5</v>
       </c>
       <c r="AS17">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="AT17">
         <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV17">
         <v>10</v>
       </c>
       <c r="AW17">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AX17">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
         <v>10</v>
       </c>
       <c r="AZ17">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC17">
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF17">
         <v>13</v>
@@ -4891,7 +4891,7 @@
         <v>4.6</v>
       </c>
       <c r="BI17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17">
         <v>10</v>
@@ -4968,25 +4968,25 @@
         <v>152</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G18">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="H18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="I18">
         <v>1.27</v>
       </c>
       <c r="J18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="L18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M18">
         <v>1.02</v>
@@ -4998,10 +4998,10 @@
         <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q18">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R18">
         <v>1.68</v>
@@ -5010,28 +5010,28 @@
         <v>2.22</v>
       </c>
       <c r="T18">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V18">
         <v>4.7</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>34</v>
       </c>
       <c r="Y18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18">
         <v>8.4</v>
       </c>
       <c r="AA18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB18">
         <v>60</v>
@@ -5046,13 +5046,13 @@
         <v>14</v>
       </c>
       <c r="AF18">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AG18">
         <v>60</v>
       </c>
       <c r="AH18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI18">
         <v>44</v>
@@ -5061,73 +5061,73 @@
         <v>1000</v>
       </c>
       <c r="AK18">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL18">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AM18">
         <v>220</v>
       </c>
       <c r="AN18">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AO18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AP18">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS18">
         <v>8.199999999999999</v>
       </c>
       <c r="AT18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU18">
         <v>14.5</v>
       </c>
       <c r="AV18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW18">
         <v>11</v>
       </c>
       <c r="AX18">
+        <v>6.8</v>
+      </c>
+      <c r="AY18">
+        <v>6.4</v>
+      </c>
+      <c r="AZ18">
+        <v>6</v>
+      </c>
+      <c r="BA18">
+        <v>6</v>
+      </c>
+      <c r="BB18">
+        <v>7.2</v>
+      </c>
+      <c r="BC18">
         <v>7</v>
       </c>
-      <c r="AY18">
-        <v>6.6</v>
-      </c>
-      <c r="AZ18">
-        <v>6.2</v>
-      </c>
-      <c r="BA18">
-        <v>6.2</v>
-      </c>
-      <c r="BB18">
-        <v>7.4</v>
-      </c>
-      <c r="BC18">
-        <v>7.2</v>
-      </c>
       <c r="BD18">
+        <v>6.8</v>
+      </c>
+      <c r="BE18">
+        <v>6.8</v>
+      </c>
+      <c r="BF18">
         <v>7</v>
       </c>
-      <c r="BE18">
-        <v>7</v>
-      </c>
-      <c r="BF18">
-        <v>7.2</v>
-      </c>
       <c r="BG18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BH18">
         <v>5.3</v>
@@ -5210,22 +5210,22 @@
         <v>153</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5234,40 +5234,40 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q19">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="R19">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X19">
         <v>1000</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z19">
         <v>1000</v>
@@ -5318,55 +5318,55 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG19">
         <v>1.01</v>
@@ -5375,61 +5375,61 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>162</v>
@@ -5458,7 +5458,7 @@
         <v>2.58</v>
       </c>
       <c r="H20">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I20">
         <v>3.1</v>
@@ -5476,16 +5476,16 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O20">
         <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R20">
         <v>1.36</v>
@@ -5497,7 +5497,7 @@
         <v>1.76</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
         <v>1.47</v>
@@ -5518,7 +5518,7 @@
         <v>55</v>
       </c>
       <c r="AB20">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC20">
         <v>8.199999999999999</v>
@@ -5539,10 +5539,10 @@
         <v>18</v>
       </c>
       <c r="AI20">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK20">
         <v>29</v>
@@ -5560,22 +5560,22 @@
         <v>34</v>
       </c>
       <c r="AP20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ20">
         <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS20">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT20">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>12</v>
@@ -5590,7 +5590,7 @@
         <v>10</v>
       </c>
       <c r="AZ20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA20">
         <v>40</v>
@@ -5605,13 +5605,13 @@
         <v>34</v>
       </c>
       <c r="BE20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF20">
         <v>20</v>
       </c>
       <c r="BG20">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH20">
         <v>3.7</v>
@@ -5694,16 +5694,16 @@
         <v>155</v>
       </c>
       <c r="F21">
+        <v>2.34</v>
+      </c>
+      <c r="G21">
         <v>2.38</v>
       </c>
-      <c r="G21">
-        <v>2.4</v>
-      </c>
       <c r="H21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I21">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J21">
         <v>3.1</v>
@@ -5724,10 +5724,10 @@
         <v>1.59</v>
       </c>
       <c r="P21">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q21">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R21">
         <v>1.18</v>
@@ -5736,28 +5736,28 @@
         <v>6.2</v>
       </c>
       <c r="T21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U21">
         <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>24</v>
       </c>
       <c r="AA21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB21">
         <v>7</v>
@@ -5766,10 +5766,10 @@
         <v>6.8</v>
       </c>
       <c r="AD21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE21">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF21">
         <v>12.5</v>
@@ -5781,25 +5781,25 @@
         <v>25</v>
       </c>
       <c r="AI21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ21">
         <v>34</v>
       </c>
       <c r="AK21">
+        <v>34</v>
+      </c>
+      <c r="AL21">
+        <v>65</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
         <v>36</v>
       </c>
-      <c r="AL21">
-        <v>70</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>38</v>
-      </c>
       <c r="AO21">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP21">
         <v>7.6</v>
@@ -5808,7 +5808,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS21">
         <v>75</v>
@@ -5823,7 +5823,7 @@
         <v>16</v>
       </c>
       <c r="AW21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
@@ -5832,7 +5832,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA21">
         <v>80</v>
@@ -5844,13 +5844,13 @@
         <v>30</v>
       </c>
       <c r="BD21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE21">
         <v>95</v>
       </c>
       <c r="BF21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG21">
         <v>85</v>
@@ -5871,49 +5871,49 @@
         <v>260</v>
       </c>
       <c r="BM21">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BN21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO21">
         <v>4.5</v>
       </c>
       <c r="BP21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ21">
         <v>16</v>
       </c>
       <c r="BR21">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS21">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BT21">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BU21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV21">
         <v>40</v>
       </c>
       <c r="BW21">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BX21">
         <v>65</v>
       </c>
       <c r="BY21">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BZ21">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CA21">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CB21" t="s">
         <v>162</v>
@@ -5936,22 +5936,22 @@
         <v>156</v>
       </c>
       <c r="F22">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G22">
         <v>2.68</v>
       </c>
       <c r="H22">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I22">
         <v>3.35</v>
       </c>
       <c r="J22">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L22">
         <v>1.39</v>
@@ -5960,16 +5960,16 @@
         <v>1.07</v>
       </c>
       <c r="N22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P22">
         <v>1.9</v>
       </c>
       <c r="Q22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R22">
         <v>1.35</v>
@@ -5978,7 +5978,7 @@
         <v>3.25</v>
       </c>
       <c r="T22">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U22">
         <v>2.12</v>
@@ -6181,16 +6181,16 @@
         <v>1.57</v>
       </c>
       <c r="G23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H23">
         <v>7.6</v>
       </c>
       <c r="I23">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K23">
         <v>4.3</v>
@@ -6199,52 +6199,52 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P23">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q23">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S23">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T23">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V23">
         <v>1.13</v>
       </c>
       <c r="W23">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z23">
         <v>70</v>
       </c>
       <c r="AA23">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AB23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC23">
         <v>9.6</v>
@@ -6265,10 +6265,10 @@
         <v>32</v>
       </c>
       <c r="AI23">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ23">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK23">
         <v>20</v>
@@ -6277,13 +6277,13 @@
         <v>55</v>
       </c>
       <c r="AM23">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO23">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AP23">
         <v>10</v>
@@ -6295,7 +6295,7 @@
         <v>50</v>
       </c>
       <c r="AS23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT23">
         <v>5.9</v>
@@ -6307,7 +6307,7 @@
         <v>26</v>
       </c>
       <c r="AW23">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AX23">
         <v>7.2</v>
@@ -6319,25 +6319,25 @@
         <v>25</v>
       </c>
       <c r="BA23">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB23">
         <v>13</v>
       </c>
       <c r="BC23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD23">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF23">
         <v>10</v>
       </c>
       <c r="BG23">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6444,22 +6444,22 @@
         <v>1.11</v>
       </c>
       <c r="N24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="P24">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Q24">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R24">
         <v>1.18</v>
       </c>
       <c r="S24">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T24">
         <v>2.08</v>
@@ -6665,7 +6665,7 @@
         <v>2.46</v>
       </c>
       <c r="G25">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H25">
         <v>3.2</v>
@@ -6683,19 +6683,19 @@
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N25">
-        <v>2.66</v>
+        <v>1.1</v>
       </c>
       <c r="O25">
         <v>1.43</v>
       </c>
       <c r="P25">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R25">
         <v>1.17</v>
@@ -6713,7 +6713,7 @@
         <v>1.39</v>
       </c>
       <c r="W25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X25">
         <v>12</v>
@@ -6776,7 +6776,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR25">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AS25">
         <v>5.2</v>
@@ -6788,16 +6788,16 @@
         <v>6.4</v>
       </c>
       <c r="AV25">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW25">
         <v>5</v>
       </c>
       <c r="AX25">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY25">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25">
         <v>4.5</v>
@@ -6916,7 +6916,7 @@
         <v>7.8</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K26">
         <v>4.3</v>
@@ -6937,7 +6937,7 @@
         <v>1.9</v>
       </c>
       <c r="Q26">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R26">
         <v>1.35</v>
@@ -6946,7 +6946,7 @@
         <v>3.3</v>
       </c>
       <c r="T26">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U26">
         <v>1.86</v>
@@ -7033,7 +7033,7 @@
         <v>21</v>
       </c>
       <c r="AW26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX26">
         <v>8</v>
@@ -7042,10 +7042,10 @@
         <v>9</v>
       </c>
       <c r="AZ26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB26">
         <v>13</v>
@@ -7054,13 +7054,13 @@
         <v>15.5</v>
       </c>
       <c r="BD26">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE26">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26">
         <v>10.5</v>
@@ -7146,7 +7146,7 @@
         <v>161</v>
       </c>
       <c r="F27">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G27">
         <v>1.58</v>
@@ -7155,22 +7155,22 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27">
         <v>4</v>
       </c>
       <c r="K27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M27">
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O27">
         <v>1.38</v>
@@ -7188,13 +7188,13 @@
         <v>3.9</v>
       </c>
       <c r="T27">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U27">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W27">
         <v>2.72</v>
@@ -7224,7 +7224,7 @@
         <v>200</v>
       </c>
       <c r="AF27">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG27">
         <v>11</v>
@@ -7260,10 +7260,10 @@
         <v>18</v>
       </c>
       <c r="AR27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS27">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT27">
         <v>5.8</v>
@@ -7272,10 +7272,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV27">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX27">
         <v>6.8</v>
@@ -7284,10 +7284,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
@@ -7296,16 +7296,16 @@
         <v>16</v>
       </c>
       <c r="BD27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF27">
         <v>9.199999999999999</v>
       </c>
       <c r="BG27">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH27">
         <v>3.55</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -502,7 +502,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 15:13:06</t>
+    <t>2026-08-19 17:25:47</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1102,7 @@
         <v>4.2</v>
       </c>
       <c r="H2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I2">
         <v>1.91</v>
@@ -1111,10 +1111,10 @@
         <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1126,13 +1126,13 @@
         <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S2">
         <v>2.54</v>
@@ -1141,7 +1141,7 @@
         <v>1.61</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V2">
         <v>2.08</v>
@@ -1153,13 +1153,13 @@
         <v>24</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB2">
         <v>22</v>
@@ -1177,7 +1177,7 @@
         <v>36</v>
       </c>
       <c r="AG2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH2">
         <v>15.5</v>
@@ -1195,10 +1195,10 @@
         <v>42</v>
       </c>
       <c r="AM2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO2">
         <v>8.6</v>
@@ -1216,7 +1216,7 @@
         <v>20</v>
       </c>
       <c r="AT2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU2">
         <v>9.199999999999999</v>
@@ -1228,7 +1228,7 @@
         <v>15.5</v>
       </c>
       <c r="AX2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AY2">
         <v>15.5</v>
@@ -1237,25 +1237,25 @@
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BC2">
         <v>36</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
         <v>4.9</v>
@@ -1267,31 +1267,31 @@
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL2">
         <v>85</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP2">
         <v>30</v>
       </c>
       <c r="BQ2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
         <v>36</v>
       </c>
       <c r="BS2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT2">
         <v>5.2</v>
@@ -1303,19 +1303,19 @@
         <v>13</v>
       </c>
       <c r="BW2">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>23</v>
       </c>
       <c r="BY2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ2">
         <v>16</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
         <v>162</v>
@@ -1338,10 +1338,10 @@
         <v>137</v>
       </c>
       <c r="F3">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H3">
         <v>3.45</v>
@@ -1356,7 +1356,7 @@
         <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M3">
         <v>1.14</v>
@@ -1371,16 +1371,16 @@
         <v>1.52</v>
       </c>
       <c r="Q3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="R3">
         <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
         <v>1.81</v>
@@ -1389,19 +1389,19 @@
         <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
         <v>8.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AB3">
         <v>7.8</v>
@@ -1416,10 +1416,10 @@
         <v>90</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>44</v>
@@ -1428,46 +1428,46 @@
         <v>140</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL3">
         <v>110</v>
       </c>
       <c r="AM3">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN3">
+        <v>46</v>
+      </c>
+      <c r="AO3">
         <v>80</v>
-      </c>
-      <c r="AO3">
-        <v>100</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AT3">
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1476,31 +1476,31 @@
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BB3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BC3">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BD3">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF3">
         <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH3">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI3">
         <v>2.5</v>
@@ -1509,13 +1509,13 @@
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>17</v>
+        <v>2.3</v>
       </c>
       <c r="BN3">
         <v>5.2</v>
@@ -1524,7 +1524,7 @@
         <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
         <v>10.5</v>
@@ -1533,7 +1533,7 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>2.22</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1542,22 +1542,22 @@
         <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>2.24</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>2.24</v>
       </c>
       <c r="CB3" t="s">
         <v>162</v>
@@ -1580,10 +1580,10 @@
         <v>138</v>
       </c>
       <c r="F4">
+        <v>1.71</v>
+      </c>
+      <c r="G4">
         <v>1.72</v>
-      </c>
-      <c r="G4">
-        <v>1.74</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -1592,64 +1592,64 @@
         <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T4">
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>46</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB4">
         <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
         <v>23</v>
@@ -1661,25 +1661,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>95</v>
       </c>
       <c r="AJ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK4">
         <v>19</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN4">
         <v>12</v>
@@ -1688,16 +1688,16 @@
         <v>130</v>
       </c>
       <c r="AP4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR4">
         <v>42</v>
       </c>
       <c r="AS4">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
@@ -1724,28 +1724,28 @@
         <v>80</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
         <v>100</v>
       </c>
       <c r="BH4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
@@ -1757,7 +1757,7 @@
         <v>160</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>4.2</v>
@@ -1769,37 +1769,37 @@
         <v>12</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4">
         <v>9.4</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BV4">
         <v>60</v>
       </c>
       <c r="BW4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>24</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1825,7 +1825,7 @@
         <v>1.7</v>
       </c>
       <c r="G5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H5">
         <v>5.1</v>
@@ -1840,7 +1840,7 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1858,7 +1858,7 @@
         <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
         <v>2.6</v>
@@ -1867,13 +1867,13 @@
         <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V5">
         <v>1.23</v>
       </c>
       <c r="W5">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -1906,13 +1906,13 @@
         <v>10</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK5">
         <v>16</v>
@@ -1924,7 +1924,7 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO5">
         <v>50</v>
@@ -1963,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>16</v>
@@ -1975,7 +1975,7 @@
         <v>24</v>
       </c>
       <c r="BE5">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF5">
         <v>7.2</v>
@@ -1984,10 +1984,10 @@
         <v>42</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
@@ -1996,13 +1996,13 @@
         <v>7.4</v>
       </c>
       <c r="BL5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
         <v>4.2</v>
@@ -2017,31 +2017,31 @@
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BT5">
         <v>9.4</v>
       </c>
       <c r="BU5">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
         <v>40</v>
       </c>
       <c r="BW5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
         <v>15</v>
       </c>
       <c r="CA5">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="s">
         <v>162</v>
@@ -2064,13 +2064,13 @@
         <v>140</v>
       </c>
       <c r="F6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G6">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -2079,55 +2079,55 @@
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
         <v>1.51</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
         <v>3</v>
       </c>
       <c r="O6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
         <v>1.66</v>
       </c>
       <c r="Q6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
         <v>2.24</v>
       </c>
       <c r="U6">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X6">
         <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z6">
         <v>55</v>
       </c>
       <c r="AA6">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB6">
         <v>6.2</v>
@@ -2136,13 +2136,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE6">
         <v>130</v>
       </c>
       <c r="AF6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
@@ -2154,22 +2154,22 @@
         <v>150</v>
       </c>
       <c r="AJ6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN6">
         <v>15.5</v>
       </c>
       <c r="AO6">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AP6">
         <v>10</v>
@@ -2178,19 +2178,19 @@
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS6">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AT6">
         <v>5.7</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW6">
         <v>60</v>
@@ -2217,67 +2217,67 @@
         <v>42</v>
       </c>
       <c r="BE6">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BF6">
         <v>13</v>
       </c>
       <c r="BG6">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO6">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2306,25 +2306,25 @@
         <v>141</v>
       </c>
       <c r="F7">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H7">
         <v>3.7</v>
       </c>
       <c r="I7">
+        <v>3.8</v>
+      </c>
+      <c r="J7">
         <v>3.85</v>
-      </c>
-      <c r="J7">
-        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M7">
         <v>1.04</v>
@@ -2333,19 +2333,19 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P7">
         <v>2.66</v>
       </c>
       <c r="Q7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
         <v>1.67</v>
       </c>
       <c r="S7">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T7">
         <v>1.55</v>
@@ -2354,10 +2354,10 @@
         <v>2.72</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X7">
         <v>24</v>
@@ -2369,7 +2369,7 @@
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AB7">
         <v>14.5</v>
@@ -2378,7 +2378,7 @@
         <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
         <v>38</v>
@@ -2396,10 +2396,10 @@
         <v>38</v>
       </c>
       <c r="AJ7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL7">
         <v>26</v>
@@ -2408,10 +2408,10 @@
         <v>55</v>
       </c>
       <c r="AN7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP7">
         <v>22</v>
@@ -2420,7 +2420,7 @@
         <v>20</v>
       </c>
       <c r="AR7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS7">
         <v>60</v>
@@ -2435,7 +2435,7 @@
         <v>14</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX7">
         <v>14.5</v>
@@ -2468,22 +2468,22 @@
         <v>22</v>
       </c>
       <c r="BH7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BJ7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN7">
         <v>5.3</v>
@@ -2495,13 +2495,13 @@
         <v>13</v>
       </c>
       <c r="BQ7">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
         <v>21</v>
       </c>
       <c r="BS7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT7">
         <v>7.4</v>
@@ -2513,19 +2513,19 @@
         <v>24</v>
       </c>
       <c r="BW7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>29</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
         <v>14.5</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="s">
         <v>162</v>
@@ -2548,22 +2548,22 @@
         <v>142</v>
       </c>
       <c r="F8">
+        <v>2.54</v>
+      </c>
+      <c r="G8">
         <v>2.58</v>
       </c>
-      <c r="G8">
-        <v>2.62</v>
-      </c>
       <c r="H8">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2572,13 +2572,13 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q8">
         <v>1.75</v>
@@ -2587,7 +2587,7 @@
         <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T8">
         <v>1.63</v>
@@ -2596,10 +2596,10 @@
         <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W8">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X8">
         <v>18.5</v>
@@ -2611,7 +2611,7 @@
         <v>21</v>
       </c>
       <c r="AA8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB8">
         <v>13.5</v>
@@ -2620,10 +2620,10 @@
         <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF8">
         <v>18.5</v>
@@ -2650,7 +2650,7 @@
         <v>65</v>
       </c>
       <c r="AN8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO8">
         <v>21</v>
@@ -2659,7 +2659,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR8">
         <v>19</v>
@@ -2680,10 +2680,10 @@
         <v>25</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
         <v>14</v>
@@ -2695,7 +2695,7 @@
         <v>34</v>
       </c>
       <c r="BC8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD8">
         <v>30</v>
@@ -2704,70 +2704,70 @@
         <v>55</v>
       </c>
       <c r="BF8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG8">
         <v>18.5</v>
       </c>
       <c r="BH8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI8">
         <v>3.65</v>
       </c>
       <c r="BJ8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BL8">
         <v>90</v>
       </c>
       <c r="BM8">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP8">
         <v>18.5</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="BR8">
         <v>28</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>21</v>
       </c>
       <c r="BW8">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BX8">
         <v>30</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>162</v>
@@ -2790,10 +2790,10 @@
         <v>143</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G9">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H9">
         <v>4.4</v>
@@ -2808,7 +2808,7 @@
         <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2820,28 +2820,28 @@
         <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X9">
         <v>19</v>
@@ -2853,16 +2853,16 @@
         <v>36</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB9">
         <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2874,7 +2874,7 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
         <v>55</v>
@@ -2886,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="AL9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM9">
         <v>80</v>
@@ -2907,7 +2907,7 @@
         <v>32</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AT9">
         <v>10</v>
@@ -2922,7 +2922,7 @@
         <v>44</v>
       </c>
       <c r="AX9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
         <v>9.6</v>
@@ -2955,61 +2955,61 @@
         <v>3.95</v>
       </c>
       <c r="BI9">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP9">
         <v>12</v>
       </c>
       <c r="BQ9">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR9">
         <v>23</v>
       </c>
       <c r="BS9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
         <v>38</v>
       </c>
       <c r="BY9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ9">
         <v>17.5</v>
       </c>
       <c r="CA9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>162</v>
@@ -3032,22 +3032,22 @@
         <v>144</v>
       </c>
       <c r="F10">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G10">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="H10">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="I10">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
         <v>1.39</v>
@@ -3056,22 +3056,22 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
         <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
         <v>1.39</v>
       </c>
       <c r="S10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
         <v>1.72</v>
@@ -3080,10 +3080,10 @@
         <v>2.22</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X10">
         <v>15.5</v>
@@ -3098,7 +3098,7 @@
         <v>42</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC10">
         <v>8.199999999999999</v>
@@ -3110,31 +3110,31 @@
         <v>30</v>
       </c>
       <c r="AF10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
         <v>19</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO10">
         <v>24</v>
@@ -3149,7 +3149,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AT10">
         <v>10.5</v>
@@ -3161,7 +3161,7 @@
         <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AX10">
         <v>17</v>
@@ -3173,16 +3173,16 @@
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BB10">
         <v>29</v>
       </c>
       <c r="BC10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BD10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE10">
         <v>60</v>
@@ -3203,16 +3203,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK10">
+        <v>7</v>
+      </c>
+      <c r="BL10">
+        <v>110</v>
+      </c>
+      <c r="BM10">
+        <v>8.6</v>
+      </c>
+      <c r="BN10">
         <v>5.8</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>14</v>
-      </c>
-      <c r="BN10">
-        <v>5.9</v>
       </c>
       <c r="BO10">
         <v>4.7</v>
@@ -3221,31 +3221,31 @@
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BR10">
         <v>32</v>
       </c>
       <c r="BS10">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BT10">
         <v>5.8</v>
       </c>
       <c r="BU10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX10">
         <v>32</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3274,19 +3274,19 @@
         <v>145</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H11">
         <v>3.45</v>
       </c>
       <c r="I11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
         <v>4.6</v>
@@ -3307,31 +3307,31 @@
         <v>3.35</v>
       </c>
       <c r="Q11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R11">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T11">
         <v>1.43</v>
       </c>
       <c r="U11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X11">
         <v>38</v>
       </c>
       <c r="Y11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z11">
         <v>34</v>
@@ -3340,13 +3340,13 @@
         <v>65</v>
       </c>
       <c r="AB11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC11">
         <v>12</v>
       </c>
       <c r="AD11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE11">
         <v>32</v>
@@ -3355,31 +3355,31 @@
         <v>19.5</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
         <v>14</v>
       </c>
       <c r="AI11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ11">
         <v>27</v>
       </c>
       <c r="AK11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL11">
         <v>22</v>
       </c>
       <c r="AM11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AN11">
         <v>7.2</v>
       </c>
       <c r="AO11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP11">
         <v>32</v>
@@ -3391,13 +3391,13 @@
         <v>30</v>
       </c>
       <c r="AS11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT11">
         <v>18</v>
       </c>
       <c r="AU11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
         <v>14.5</v>
@@ -3412,7 +3412,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA11">
         <v>27</v>
@@ -3436,7 +3436,7 @@
         <v>15</v>
       </c>
       <c r="BH11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI11">
         <v>4.4</v>
@@ -3445,13 +3445,13 @@
         <v>8.6</v>
       </c>
       <c r="BK11">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>55</v>
       </c>
       <c r="BM11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BN11">
         <v>6</v>
@@ -3463,37 +3463,37 @@
         <v>13</v>
       </c>
       <c r="BQ11">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11">
         <v>19</v>
       </c>
       <c r="BS11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT11">
         <v>8</v>
       </c>
       <c r="BU11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
         <v>23</v>
       </c>
       <c r="BW11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX11">
         <v>25</v>
       </c>
       <c r="BY11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11">
         <v>11</v>
       </c>
       <c r="CA11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="s">
         <v>162</v>
@@ -3525,13 +3525,13 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L12">
         <v>1.33</v>
@@ -3540,28 +3540,28 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q12">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
         <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T12">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
         <v>1.19</v>
@@ -3579,7 +3579,7 @@
         <v>55</v>
       </c>
       <c r="AA12">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
         <v>10</v>
@@ -3612,7 +3612,7 @@
         <v>16</v>
       </c>
       <c r="AL12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM12">
         <v>100</v>
@@ -3624,16 +3624,16 @@
         <v>80</v>
       </c>
       <c r="AP12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ12">
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS12">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AT12">
         <v>9.4</v>
@@ -3642,7 +3642,7 @@
         <v>9.4</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW12">
         <v>65</v>
@@ -3675,67 +3675,67 @@
         <v>6.8</v>
       </c>
       <c r="BG12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BJ12">
         <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM12">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO12">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BP12">
         <v>10.5</v>
       </c>
       <c r="BQ12">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BR12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS12">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
         <v>10.5</v>
       </c>
       <c r="BU12">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW12">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX12">
         <v>55</v>
       </c>
       <c r="BY12">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
         <v>16</v>
       </c>
       <c r="CA12">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="s">
         <v>162</v>
@@ -3758,10 +3758,10 @@
         <v>147</v>
       </c>
       <c r="F13">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H13">
         <v>3</v>
@@ -3779,10 +3779,10 @@
         <v>1.25</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O13">
         <v>1.15</v>
@@ -3791,13 +3791,13 @@
         <v>3</v>
       </c>
       <c r="Q13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S13">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T13">
         <v>1.47</v>
@@ -3809,7 +3809,7 @@
         <v>1.47</v>
       </c>
       <c r="W13">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X13">
         <v>32</v>
@@ -3833,10 +3833,10 @@
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG13">
         <v>11.5</v>
@@ -3845,16 +3845,16 @@
         <v>13.5</v>
       </c>
       <c r="AI13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ13">
         <v>32</v>
       </c>
       <c r="AK13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM13">
         <v>46</v>
@@ -3863,10 +3863,10 @@
         <v>9.6</v>
       </c>
       <c r="AO13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ13">
         <v>20</v>
@@ -3881,10 +3881,10 @@
         <v>17</v>
       </c>
       <c r="AU13">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW13">
         <v>25</v>
@@ -3893,7 +3893,7 @@
         <v>18.5</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13">
         <v>12.5</v>
@@ -3914,10 +3914,10 @@
         <v>38</v>
       </c>
       <c r="BF13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH13">
         <v>5.3</v>
@@ -4000,16 +4000,16 @@
         <v>148</v>
       </c>
       <c r="F14">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="G14">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="H14">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="I14">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="J14">
         <v>3.35</v>
@@ -4048,40 +4048,40 @@
         <v>2.22</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="X14">
         <v>19</v>
       </c>
       <c r="Y14">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z14">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AA14">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC14">
         <v>8.6</v>
       </c>
       <c r="AD14">
+        <v>14.5</v>
+      </c>
+      <c r="AE14">
+        <v>50</v>
+      </c>
+      <c r="AF14">
+        <v>17.5</v>
+      </c>
+      <c r="AG14">
         <v>12.5</v>
-      </c>
-      <c r="AE14">
-        <v>40</v>
-      </c>
-      <c r="AF14">
-        <v>22</v>
-      </c>
-      <c r="AG14">
-        <v>14</v>
       </c>
       <c r="AH14">
         <v>17</v>
@@ -4093,7 +4093,7 @@
         <v>70</v>
       </c>
       <c r="AK14">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AL14">
         <v>65</v>
@@ -4102,70 +4102,70 @@
         <v>100</v>
       </c>
       <c r="AN14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AO14">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AP14">
         <v>5.8</v>
       </c>
       <c r="AQ14">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AR14">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS14">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT14">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU14">
         <v>4.2</v>
       </c>
       <c r="AV14">
+        <v>5.3</v>
+      </c>
+      <c r="AW14">
+        <v>6.8</v>
+      </c>
+      <c r="AX14">
+        <v>5.7</v>
+      </c>
+      <c r="AY14">
         <v>5</v>
-      </c>
-      <c r="AW14">
-        <v>6.4</v>
-      </c>
-      <c r="AX14">
-        <v>6</v>
-      </c>
-      <c r="AY14">
-        <v>5.2</v>
       </c>
       <c r="AZ14">
         <v>5.6</v>
       </c>
       <c r="BA14">
+        <v>7</v>
+      </c>
+      <c r="BB14">
         <v>6.8</v>
       </c>
-      <c r="BB14">
-        <v>7</v>
-      </c>
       <c r="BC14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD14">
         <v>7</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF14">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG14">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH14">
         <v>3.7</v>
       </c>
       <c r="BI14">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14">
         <v>9.6</v>
@@ -4180,46 +4180,46 @@
         <v>2.66</v>
       </c>
       <c r="BN14">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BO14">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ14">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS14">
         <v>7.8</v>
       </c>
       <c r="BT14">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BU14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV14">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB14" t="s">
         <v>162</v>
@@ -4242,7 +4242,7 @@
         <v>149</v>
       </c>
       <c r="F15">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G15">
         <v>2.42</v>
@@ -4254,7 +4254,7 @@
         <v>3.55</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4353,7 +4353,7 @@
         <v>15</v>
       </c>
       <c r="AQ15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR15">
         <v>18</v>
@@ -4362,10 +4362,10 @@
         <v>4</v>
       </c>
       <c r="AT15">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV15">
         <v>10</v>
@@ -4380,7 +4380,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA15">
         <v>3.9</v>
@@ -4487,7 +4487,7 @@
         <v>1.26</v>
       </c>
       <c r="G16">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H16">
         <v>7.2</v>
@@ -4526,16 +4526,16 @@
         <v>1.72</v>
       </c>
       <c r="T16">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="U16">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="V16">
         <v>1.08</v>
       </c>
       <c r="W16">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4726,22 +4726,22 @@
         <v>151</v>
       </c>
       <c r="F17">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G17">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H17">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I17">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J17">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.28</v>
@@ -4759,13 +4759,13 @@
         <v>2.26</v>
       </c>
       <c r="Q17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R17">
         <v>1.5</v>
       </c>
       <c r="S17">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T17">
         <v>1.59</v>
@@ -4774,10 +4774,10 @@
         <v>2.42</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X17">
         <v>24</v>
@@ -4810,7 +4810,7 @@
         <v>13</v>
       </c>
       <c r="AH17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
         <v>36</v>
@@ -4822,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="AL17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM17">
         <v>75</v>
       </c>
       <c r="AN17">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO17">
         <v>20</v>
@@ -4843,22 +4843,22 @@
         <v>18.5</v>
       </c>
       <c r="AS17">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AT17">
         <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX17">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY17">
         <v>10</v>
@@ -4867,19 +4867,19 @@
         <v>13</v>
       </c>
       <c r="BA17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB17">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC17">
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE17">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF17">
         <v>13</v>
@@ -4974,58 +4974,58 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="I18">
         <v>1.27</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M18">
         <v>1.02</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O18">
         <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q18">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R18">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S18">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T18">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
         <v>4.7</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>34</v>
       </c>
       <c r="Y18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z18">
         <v>8.4</v>
@@ -5037,10 +5037,10 @@
         <v>60</v>
       </c>
       <c r="AC18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE18">
         <v>14</v>
@@ -5055,7 +5055,7 @@
         <v>38</v>
       </c>
       <c r="AI18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ18">
         <v>1000</v>
@@ -5064,19 +5064,19 @@
         <v>270</v>
       </c>
       <c r="AL18">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AM18">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN18">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AO18">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AP18">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AQ18">
         <v>9.4</v>
@@ -5085,55 +5085,55 @@
         <v>7</v>
       </c>
       <c r="AS18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT18">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU18">
         <v>14.5</v>
       </c>
       <c r="AV18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW18">
         <v>11</v>
       </c>
       <c r="AX18">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY18">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ18">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BA18">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BB18">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BC18">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD18">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE18">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF18">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BH18">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI18">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ18">
         <v>14.5</v>
@@ -5145,34 +5145,34 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN18">
         <v>18.5</v>
       </c>
       <c r="BO18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU18">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BV18">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BW18">
         <v>5.3</v>
@@ -5181,13 +5181,13 @@
         <v>25</v>
       </c>
       <c r="BY18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ18">
         <v>10.5</v>
       </c>
       <c r="CA18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="CB18" t="s">
         <v>162</v>
@@ -5210,154 +5210,154 @@
         <v>153</v>
       </c>
       <c r="F19">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="G19">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="H19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="K19">
-        <v>500</v>
+        <v>3.65</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
+        <v>1.1</v>
+      </c>
+      <c r="N19">
+        <v>2.46</v>
+      </c>
+      <c r="O19">
+        <v>1.45</v>
+      </c>
+      <c r="P19">
+        <v>1.56</v>
+      </c>
+      <c r="Q19">
+        <v>2.32</v>
+      </c>
+      <c r="R19">
+        <v>1.2</v>
+      </c>
+      <c r="S19">
+        <v>3.45</v>
+      </c>
+      <c r="T19">
+        <v>2.06</v>
+      </c>
+      <c r="U19">
+        <v>1.71</v>
+      </c>
+      <c r="V19">
+        <v>1.18</v>
+      </c>
+      <c r="W19">
+        <v>1.94</v>
+      </c>
+      <c r="X19">
+        <v>12</v>
+      </c>
+      <c r="Y19">
+        <v>15</v>
+      </c>
+      <c r="Z19">
+        <v>50</v>
+      </c>
+      <c r="AA19">
+        <v>200</v>
+      </c>
+      <c r="AB19">
+        <v>7.2</v>
+      </c>
+      <c r="AC19">
+        <v>9.4</v>
+      </c>
+      <c r="AD19">
+        <v>27</v>
+      </c>
+      <c r="AE19">
+        <v>120</v>
+      </c>
+      <c r="AF19">
+        <v>12.5</v>
+      </c>
+      <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
+        <v>30</v>
+      </c>
+      <c r="AI19">
+        <v>140</v>
+      </c>
+      <c r="AJ19">
+        <v>27</v>
+      </c>
+      <c r="AK19">
+        <v>27</v>
+      </c>
+      <c r="AL19">
+        <v>65</v>
+      </c>
+      <c r="AM19">
+        <v>240</v>
+      </c>
+      <c r="AN19">
+        <v>25</v>
+      </c>
+      <c r="AO19">
+        <v>190</v>
+      </c>
+      <c r="AP19">
         <v>1.01</v>
       </c>
-      <c r="N19">
-        <v>1.47</v>
-      </c>
-      <c r="O19">
-        <v>1.43</v>
-      </c>
-      <c r="P19">
-        <v>1.47</v>
-      </c>
-      <c r="Q19">
-        <v>2.12</v>
-      </c>
-      <c r="R19">
-        <v>1.19</v>
-      </c>
-      <c r="S19">
-        <v>4</v>
-      </c>
-      <c r="T19">
-        <v>1.89</v>
-      </c>
-      <c r="U19">
-        <v>1.58</v>
-      </c>
-      <c r="V19">
-        <v>1.17</v>
-      </c>
-      <c r="W19">
-        <v>1.78</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>18</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.03</v>
-      </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
         <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
         <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
         <v>1.03</v>
@@ -5366,7 +5366,7 @@
         <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
         <v>1.01</v>
@@ -5458,7 +5458,7 @@
         <v>2.58</v>
       </c>
       <c r="H20">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I20">
         <v>3.1</v>
@@ -5476,13 +5476,13 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O20">
         <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q20">
         <v>2.04</v>
@@ -5494,16 +5494,16 @@
         <v>3.5</v>
       </c>
       <c r="T20">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
         <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X20">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>36</v>
       </c>
       <c r="AF20">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG20">
         <v>12</v>
@@ -5545,7 +5545,7 @@
         <v>44</v>
       </c>
       <c r="AK20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL20">
         <v>42</v>
@@ -5566,7 +5566,7 @@
         <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS20">
         <v>44</v>
@@ -5590,7 +5590,7 @@
         <v>10</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA20">
         <v>40</v>
@@ -5605,7 +5605,7 @@
         <v>34</v>
       </c>
       <c r="BE20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF20">
         <v>20</v>
@@ -5614,7 +5614,7 @@
         <v>28</v>
       </c>
       <c r="BH20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI20">
         <v>2.76</v>
@@ -5629,7 +5629,7 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN20">
         <v>6.4</v>
@@ -5641,7 +5641,7 @@
         <v>23</v>
       </c>
       <c r="BQ20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR20">
         <v>34</v>
@@ -5659,13 +5659,13 @@
         <v>28</v>
       </c>
       <c r="BW20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX20">
         <v>42</v>
       </c>
       <c r="BY20">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ20">
         <v>34</v>
@@ -5703,7 +5703,7 @@
         <v>3.85</v>
       </c>
       <c r="I21">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J21">
         <v>3.1</v>
@@ -5712,13 +5712,13 @@
         <v>3.15</v>
       </c>
       <c r="L21">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M21">
         <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O21">
         <v>1.59</v>
@@ -5739,7 +5739,7 @@
         <v>2.26</v>
       </c>
       <c r="U21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V21">
         <v>1.34</v>
@@ -5751,10 +5751,10 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA21">
         <v>95</v>
@@ -5778,7 +5778,7 @@
         <v>12.5</v>
       </c>
       <c r="AH21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21">
         <v>95</v>
@@ -5787,31 +5787,31 @@
         <v>34</v>
       </c>
       <c r="AK21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL21">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO21">
         <v>110</v>
       </c>
       <c r="AP21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ21">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS21">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT21">
         <v>6.6</v>
@@ -5820,7 +5820,7 @@
         <v>6.6</v>
       </c>
       <c r="AV21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW21">
         <v>60</v>
@@ -5856,10 +5856,10 @@
         <v>85</v>
       </c>
       <c r="BH21">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI21">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
@@ -5883,13 +5883,13 @@
         <v>21</v>
       </c>
       <c r="BQ21">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BR21">
         <v>46</v>
       </c>
       <c r="BS21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT21">
         <v>7</v>
@@ -5901,7 +5901,7 @@
         <v>40</v>
       </c>
       <c r="BW21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX21">
         <v>65</v>
@@ -6059,7 +6059,7 @@
         <v>8.4</v>
       </c>
       <c r="AU22">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
@@ -6080,7 +6080,7 @@
         <v>4.8</v>
       </c>
       <c r="BB22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC22">
         <v>4.6</v>
@@ -6095,7 +6095,7 @@
         <v>18</v>
       </c>
       <c r="BG22">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH22">
         <v>3.55</v>
@@ -6184,13 +6184,13 @@
         <v>1.62</v>
       </c>
       <c r="H23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
         <v>4.3</v>
@@ -6205,31 +6205,31 @@
         <v>3.05</v>
       </c>
       <c r="O23">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P23">
         <v>1.71</v>
       </c>
       <c r="Q23">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T23">
         <v>2.26</v>
       </c>
       <c r="U23">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V23">
         <v>1.13</v>
       </c>
       <c r="W23">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X23">
         <v>12</v>
@@ -6250,7 +6250,7 @@
         <v>9.6</v>
       </c>
       <c r="AD23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE23">
         <v>170</v>
@@ -6307,7 +6307,7 @@
         <v>26</v>
       </c>
       <c r="AW23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX23">
         <v>7.2</v>
@@ -6328,16 +6328,16 @@
         <v>17.5</v>
       </c>
       <c r="BD23">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BE23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF23">
         <v>10</v>
       </c>
       <c r="BG23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6423,7 +6423,7 @@
         <v>3.35</v>
       </c>
       <c r="G24">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H24">
         <v>2.38</v>
@@ -6447,37 +6447,37 @@
         <v>2.5</v>
       </c>
       <c r="O24">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="P24">
         <v>1.5</v>
       </c>
       <c r="Q24">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R24">
         <v>1.18</v>
       </c>
       <c r="S24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T24">
         <v>2.08</v>
       </c>
       <c r="U24">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V24">
         <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X24">
         <v>9.6</v>
       </c>
       <c r="Y24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z24">
         <v>17</v>
@@ -6501,7 +6501,7 @@
         <v>27</v>
       </c>
       <c r="AG24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH24">
         <v>27</v>
@@ -6564,7 +6564,7 @@
         <v>4.9</v>
       </c>
       <c r="BB24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC24">
         <v>4.9</v>
@@ -6662,28 +6662,28 @@
         <v>159</v>
       </c>
       <c r="F25">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G25">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="H25">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="I25">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J25">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="K25">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N25">
         <v>1.1</v>
@@ -6695,7 +6695,7 @@
         <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
         <v>1.17</v>
@@ -6710,10 +6710,10 @@
         <v>1.91</v>
       </c>
       <c r="V25">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X25">
         <v>12</v>
@@ -6907,7 +6907,7 @@
         <v>1.61</v>
       </c>
       <c r="G26">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H26">
         <v>6.2</v>
@@ -6931,7 +6931,7 @@
         <v>3.65</v>
       </c>
       <c r="O26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P26">
         <v>1.9</v>
@@ -7039,7 +7039,7 @@
         <v>8</v>
       </c>
       <c r="AY26">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26">
         <v>19</v>
@@ -7149,7 +7149,7 @@
         <v>1.52</v>
       </c>
       <c r="G27">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H27">
         <v>8</v>
@@ -7170,37 +7170,37 @@
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
         <v>1.38</v>
       </c>
       <c r="P27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
         <v>1.27</v>
       </c>
       <c r="S27">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T27">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U27">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V27">
         <v>1.13</v>
       </c>
       <c r="W27">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X27">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y27">
         <v>25</v>
@@ -7260,10 +7260,10 @@
         <v>18</v>
       </c>
       <c r="AR27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS27">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27">
         <v>5.8</v>
@@ -7272,10 +7272,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV27">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="AW27">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX27">
         <v>6.8</v>
@@ -7284,10 +7284,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA27">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
@@ -7296,16 +7296,16 @@
         <v>16</v>
       </c>
       <c r="BD27">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BE27">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF27">
         <v>9.199999999999999</v>
       </c>
       <c r="BG27">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH27">
         <v>3.55</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -502,7 +502,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 17:25:47</t>
+    <t>2026-08-19 19:39:32</t>
   </si>
 </sst>
 </file>
@@ -1096,19 +1096,19 @@
         <v>136</v>
       </c>
       <c r="F2">
+        <v>4.2</v>
+      </c>
+      <c r="G2">
+        <v>4.4</v>
+      </c>
+      <c r="H2">
+        <v>1.87</v>
+      </c>
+      <c r="I2">
+        <v>1.9</v>
+      </c>
+      <c r="J2">
         <v>4.1</v>
-      </c>
-      <c r="G2">
-        <v>4.2</v>
-      </c>
-      <c r="H2">
-        <v>1.89</v>
-      </c>
-      <c r="I2">
-        <v>1.91</v>
-      </c>
-      <c r="J2">
-        <v>4.2</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -1126,7 +1126,7 @@
         <v>1.2</v>
       </c>
       <c r="P2">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q2">
         <v>1.61</v>
@@ -1141,16 +1141,16 @@
         <v>1.61</v>
       </c>
       <c r="U2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -1165,13 +1165,13 @@
         <v>22</v>
       </c>
       <c r="AC2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2">
         <v>10</v>
       </c>
-      <c r="AD2">
-        <v>10.5</v>
-      </c>
       <c r="AE2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF2">
         <v>36</v>
@@ -1189,13 +1189,13 @@
         <v>80</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2">
         <v>34</v>
@@ -1207,19 +1207,19 @@
         <v>21</v>
       </c>
       <c r="AQ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
         <v>13</v>
       </c>
       <c r="AS2">
+        <v>19.5</v>
+      </c>
+      <c r="AT2">
         <v>20</v>
       </c>
-      <c r="AT2">
-        <v>19</v>
-      </c>
       <c r="AU2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV2">
         <v>9.6</v>
@@ -1243,7 +1243,7 @@
         <v>70</v>
       </c>
       <c r="BC2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD2">
         <v>38</v>
@@ -1255,16 +1255,16 @@
         <v>29</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BI2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2">
         <v>8</v>
@@ -1273,10 +1273,10 @@
         <v>85</v>
       </c>
       <c r="BM2">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO2">
         <v>7</v>
@@ -1285,31 +1285,31 @@
         <v>30</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>36</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BU2">
         <v>4.6</v>
       </c>
       <c r="BV2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW2">
         <v>11</v>
       </c>
       <c r="BX2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY2">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="BZ2">
         <v>16</v>
@@ -1338,25 +1338,25 @@
         <v>137</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
         <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.14</v>
@@ -1368,10 +1368,10 @@
         <v>1.58</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>1.19</v>
@@ -1380,16 +1380,16 @@
         <v>5.9</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X3">
         <v>8.199999999999999</v>
@@ -1401,7 +1401,7 @@
         <v>22</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AB3">
         <v>7.8</v>
@@ -1413,19 +1413,19 @@
         <v>16</v>
       </c>
       <c r="AE3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF3">
         <v>15</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AI3">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
         <v>42</v>
@@ -1434,22 +1434,22 @@
         <v>40</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AM3">
         <v>210</v>
       </c>
       <c r="AN3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3">
         <v>19.5</v>
@@ -1479,10 +1479,10 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC3">
         <v>34</v>
@@ -1491,13 +1491,13 @@
         <v>46</v>
       </c>
       <c r="BE3">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF3">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BG3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH3">
         <v>2.64</v>
@@ -1580,118 +1580,118 @@
         <v>138</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G4">
         <v>1.72</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
         <v>3.9</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
+        <v>1.34</v>
+      </c>
+      <c r="P4">
+        <v>1.94</v>
+      </c>
+      <c r="Q4">
+        <v>2.02</v>
+      </c>
+      <c r="R4">
         <v>1.35</v>
       </c>
-      <c r="P4">
-        <v>1.9</v>
-      </c>
-      <c r="Q4">
-        <v>2.08</v>
-      </c>
-      <c r="R4">
-        <v>1.34</v>
-      </c>
       <c r="S4">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
         <v>2.38</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA4">
         <v>160</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
         <v>23</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF4">
+        <v>9.4</v>
+      </c>
+      <c r="AG4">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AG4">
-        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL4">
         <v>40</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR4">
         <v>42</v>
@@ -1700,46 +1700,46 @@
         <v>110</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU4">
         <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW4">
         <v>80</v>
       </c>
       <c r="AX4">
+        <v>9</v>
+      </c>
+      <c r="AY4">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
       </c>
       <c r="AZ4">
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD4">
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BH4">
         <v>3.4</v>
@@ -1748,22 +1748,22 @@
         <v>3.05</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN4">
         <v>4.2</v>
       </c>
       <c r="BO4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP4">
         <v>12</v>
@@ -1775,7 +1775,7 @@
         <v>29</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
         <v>9.4</v>
@@ -1784,22 +1784,22 @@
         <v>8</v>
       </c>
       <c r="BV4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1822,25 +1822,25 @@
         <v>139</v>
       </c>
       <c r="F5">
+        <v>1.68</v>
+      </c>
+      <c r="G5">
         <v>1.7</v>
       </c>
-      <c r="G5">
-        <v>1.72</v>
-      </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1855,7 +1855,7 @@
         <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
         <v>1.6</v>
@@ -1867,13 +1867,13 @@
         <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
         <v>1.23</v>
       </c>
       <c r="W5">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -1894,7 +1894,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE5">
         <v>60</v>
@@ -1903,7 +1903,7 @@
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
         <v>18</v>
@@ -1912,7 +1912,7 @@
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
         <v>16</v>
@@ -1939,13 +1939,13 @@
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5">
         <v>18</v>
@@ -1963,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB5">
         <v>16</v>
@@ -1975,13 +1975,13 @@
         <v>24</v>
       </c>
       <c r="BE5">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH5">
         <v>4.3</v>
@@ -1990,16 +1990,16 @@
         <v>3.95</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>90</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
         <v>4.6</v>
@@ -2011,37 +2011,37 @@
         <v>11</v>
       </c>
       <c r="BQ5">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BV5">
         <v>40</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
         <v>15</v>
       </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
         <v>162</v>
@@ -2064,13 +2064,13 @@
         <v>140</v>
       </c>
       <c r="F6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -2085,43 +2085,43 @@
         <v>1.51</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
         <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
         <v>1.24</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V6">
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X6">
         <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z6">
         <v>55</v>
@@ -2133,25 +2133,25 @@
         <v>6.2</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE6">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI6">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
         <v>17.5</v>
@@ -2163,13 +2163,13 @@
         <v>60</v>
       </c>
       <c r="AM6">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AN6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO6">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AP6">
         <v>10</v>
@@ -2178,10 +2178,10 @@
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT6">
         <v>5.7</v>
@@ -2190,7 +2190,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW6">
         <v>60</v>
@@ -2202,28 +2202,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA6">
         <v>65</v>
       </c>
       <c r="BB6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC6">
         <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF6">
         <v>13</v>
       </c>
       <c r="BG6">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2241,7 +2241,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN6">
         <v>4.1</v>
@@ -2265,7 +2265,7 @@
         <v>9.6</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2306,19 +2306,19 @@
         <v>141</v>
       </c>
       <c r="F7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G7">
         <v>2.1</v>
       </c>
       <c r="H7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.1</v>
@@ -2333,25 +2333,25 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S7">
         <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -2363,13 +2363,13 @@
         <v>24</v>
       </c>
       <c r="Y7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z7">
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7">
         <v>14.5</v>
@@ -2381,13 +2381,13 @@
         <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF7">
         <v>16</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>14.5</v>
@@ -2399,7 +2399,7 @@
         <v>26</v>
       </c>
       <c r="AK7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
         <v>26</v>
@@ -2411,7 +2411,7 @@
         <v>9.4</v>
       </c>
       <c r="AO7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP7">
         <v>22</v>
@@ -2426,7 +2426,7 @@
         <v>60</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU7">
         <v>8.800000000000001</v>
@@ -2450,10 +2450,10 @@
         <v>34</v>
       </c>
       <c r="BB7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD7">
         <v>23</v>
@@ -2462,7 +2462,7 @@
         <v>46</v>
       </c>
       <c r="BF7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
         <v>22</v>
@@ -2501,7 +2501,7 @@
         <v>21</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
         <v>7.4</v>
@@ -2513,19 +2513,19 @@
         <v>24</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX7">
         <v>29</v>
       </c>
       <c r="BY7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ7">
         <v>14.5</v>
       </c>
       <c r="CA7">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>162</v>
@@ -2581,25 +2581,25 @@
         <v>2.28</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8">
         <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T8">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V8">
         <v>1.52</v>
       </c>
       <c r="W8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X8">
         <v>18.5</v>
@@ -2617,7 +2617,7 @@
         <v>13.5</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
@@ -2626,19 +2626,19 @@
         <v>28</v>
       </c>
       <c r="AF8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
         <v>36</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK8">
         <v>25</v>
@@ -2656,7 +2656,7 @@
         <v>21</v>
       </c>
       <c r="AP8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
         <v>13.5</v>
@@ -2668,7 +2668,7 @@
         <v>40</v>
       </c>
       <c r="AT8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU8">
         <v>8</v>
@@ -2680,22 +2680,22 @@
         <v>25</v>
       </c>
       <c r="AX8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
         <v>32</v>
       </c>
       <c r="BB8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD8">
         <v>30</v>
@@ -2707,7 +2707,7 @@
         <v>16</v>
       </c>
       <c r="BG8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH8">
         <v>3.9</v>
@@ -2767,7 +2767,7 @@
         <v>20</v>
       </c>
       <c r="CA8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="s">
         <v>162</v>
@@ -2790,19 +2790,19 @@
         <v>143</v>
       </c>
       <c r="F9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G9">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H9">
         <v>4.4</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.2</v>
@@ -2832,16 +2832,16 @@
         <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
         <v>19</v>
@@ -2859,10 +2859,10 @@
         <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2871,19 +2871,19 @@
         <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI9">
         <v>55</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL9">
         <v>30</v>
@@ -2892,16 +2892,16 @@
         <v>80</v>
       </c>
       <c r="AN9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP9">
         <v>17.5</v>
       </c>
       <c r="AQ9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR9">
         <v>32</v>
@@ -2916,16 +2916,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
         <v>16</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="BB9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
@@ -2943,10 +2943,10 @@
         <v>27</v>
       </c>
       <c r="BE9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG9">
         <v>40</v>
@@ -2955,7 +2955,7 @@
         <v>3.95</v>
       </c>
       <c r="BI9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
@@ -3032,16 +3032,16 @@
         <v>144</v>
       </c>
       <c r="F10">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="G10">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="H10">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="I10">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="J10">
         <v>3.5</v>
@@ -3050,7 +3050,7 @@
         <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -3059,7 +3059,7 @@
         <v>4.1</v>
       </c>
       <c r="O10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P10">
         <v>2.02</v>
@@ -3071,76 +3071,76 @@
         <v>1.39</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T10">
         <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="X10">
         <v>15.5</v>
       </c>
       <c r="Y10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA10">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC10">
         <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM10">
         <v>85</v>
       </c>
       <c r="AN10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AP10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
@@ -3149,25 +3149,25 @@
         <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU10">
         <v>7.2</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
         <v>26</v>
       </c>
       <c r="AX10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10">
         <v>14.5</v>
@@ -3176,13 +3176,13 @@
         <v>34</v>
       </c>
       <c r="BB10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BD10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE10">
         <v>60</v>
@@ -3191,61 +3191,61 @@
         <v>18</v>
       </c>
       <c r="BG10">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="BH10">
         <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10">
         <v>9.199999999999999</v>
       </c>
       <c r="BK10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL10">
         <v>110</v>
       </c>
       <c r="BM10">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BN10">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO10">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP10">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS10">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BT10">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY10">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>2.08</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I11">
         <v>3.55</v>
@@ -3289,49 +3289,49 @@
         <v>4.3</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M11">
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P11">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R11">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T11">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U11">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V11">
         <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z11">
         <v>34</v>
@@ -3340,10 +3340,10 @@
         <v>65</v>
       </c>
       <c r="AB11">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD11">
         <v>15.5</v>
@@ -3355,19 +3355,19 @@
         <v>19.5</v>
       </c>
       <c r="AG11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
         <v>14</v>
       </c>
       <c r="AI11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ11">
         <v>27</v>
       </c>
       <c r="AK11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL11">
         <v>22</v>
@@ -3376,16 +3376,16 @@
         <v>42</v>
       </c>
       <c r="AN11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR11">
         <v>30</v>
@@ -3394,7 +3394,7 @@
         <v>50</v>
       </c>
       <c r="AT11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU11">
         <v>10.5</v>
@@ -3403,43 +3403,43 @@
         <v>14.5</v>
       </c>
       <c r="AW11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
         <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11">
         <v>25</v>
       </c>
       <c r="BC11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
         <v>20</v>
       </c>
       <c r="BE11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH11">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BI11">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BJ11">
         <v>8.6</v>
@@ -3451,13 +3451,13 @@
         <v>55</v>
       </c>
       <c r="BM11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP11">
         <v>13</v>
@@ -3469,31 +3469,31 @@
         <v>19</v>
       </c>
       <c r="BS11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV11">
         <v>23</v>
       </c>
       <c r="BW11">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX11">
         <v>25</v>
       </c>
       <c r="BY11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA11">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="s">
         <v>162</v>
@@ -3516,10 +3516,10 @@
         <v>146</v>
       </c>
       <c r="F12">
+        <v>1.59</v>
+      </c>
+      <c r="G12">
         <v>1.6</v>
-      </c>
-      <c r="G12">
-        <v>1.62</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -3546,28 +3546,28 @@
         <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
         <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T12">
         <v>1.82</v>
       </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X12">
         <v>21</v>
@@ -3579,7 +3579,7 @@
         <v>55</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB12">
         <v>10</v>
@@ -3591,7 +3591,7 @@
         <v>23</v>
       </c>
       <c r="AE12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF12">
         <v>10.5</v>
@@ -3603,13 +3603,13 @@
         <v>20</v>
       </c>
       <c r="AI12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
         <v>15.5</v>
       </c>
       <c r="AK12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -3618,43 +3618,43 @@
         <v>100</v>
       </c>
       <c r="AN12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO12">
         <v>80</v>
       </c>
       <c r="AP12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS12">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AT12">
         <v>9.4</v>
       </c>
       <c r="AU12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW12">
         <v>65</v>
       </c>
       <c r="AX12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY12">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA12">
         <v>60</v>
@@ -3663,13 +3663,13 @@
         <v>14</v>
       </c>
       <c r="BC12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF12">
         <v>6.8</v>
@@ -3681,19 +3681,19 @@
         <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ12">
         <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL12">
         <v>110</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN12">
         <v>4.3</v>
@@ -3702,40 +3702,40 @@
         <v>3.9</v>
       </c>
       <c r="BP12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ12">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR12">
         <v>23</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BV12">
         <v>50</v>
       </c>
       <c r="BW12">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BX12">
         <v>55</v>
       </c>
       <c r="BY12">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA12">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="s">
         <v>162</v>
@@ -3761,16 +3761,16 @@
         <v>2.24</v>
       </c>
       <c r="G13">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
         <v>4.4</v>
@@ -3788,52 +3788,52 @@
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R13">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
         <v>2.16</v>
       </c>
       <c r="T13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X13">
         <v>32</v>
       </c>
       <c r="Y13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC13">
         <v>11</v>
       </c>
       <c r="AD13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF13">
         <v>20</v>
@@ -3851,7 +3851,7 @@
         <v>32</v>
       </c>
       <c r="AK13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL13">
         <v>24</v>
@@ -3860,7 +3860,7 @@
         <v>46</v>
       </c>
       <c r="AN13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO13">
         <v>15</v>
@@ -3893,7 +3893,7 @@
         <v>18.5</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <v>12.5</v>
@@ -3905,7 +3905,7 @@
         <v>29</v>
       </c>
       <c r="BC13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD13">
         <v>22</v>
@@ -3920,64 +3920,64 @@
         <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BI13">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK13">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
         <v>60</v>
       </c>
       <c r="BM13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BN13">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO13">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BP13">
         <v>15</v>
       </c>
       <c r="BQ13">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BR13">
         <v>21</v>
       </c>
       <c r="BS13">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV13">
         <v>20</v>
       </c>
       <c r="BW13">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>12.5</v>
       </c>
       <c r="CA13">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
         <v>162</v>
@@ -4000,7 +4000,7 @@
         <v>148</v>
       </c>
       <c r="F14">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G14">
         <v>2.66</v>
@@ -4054,7 +4054,7 @@
         <v>1.6</v>
       </c>
       <c r="X14">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y14">
         <v>14</v>
@@ -4099,7 +4099,7 @@
         <v>65</v>
       </c>
       <c r="AM14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN14">
         <v>20</v>
@@ -4108,58 +4108,58 @@
         <v>44</v>
       </c>
       <c r="AP14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ14">
+        <v>5.6</v>
+      </c>
+      <c r="AR14">
+        <v>6.6</v>
+      </c>
+      <c r="AS14">
+        <v>8</v>
+      </c>
+      <c r="AT14">
         <v>5.2</v>
       </c>
-      <c r="AR14">
+      <c r="AU14">
+        <v>4.4</v>
+      </c>
+      <c r="AV14">
+        <v>5.6</v>
+      </c>
+      <c r="AW14">
+        <v>7.4</v>
+      </c>
+      <c r="AX14">
+        <v>6</v>
+      </c>
+      <c r="AY14">
+        <v>5.3</v>
+      </c>
+      <c r="AZ14">
+        <v>6</v>
+      </c>
+      <c r="BA14">
+        <v>7.6</v>
+      </c>
+      <c r="BB14">
+        <v>7.4</v>
+      </c>
+      <c r="BC14">
+        <v>7</v>
+      </c>
+      <c r="BD14">
+        <v>7.4</v>
+      </c>
+      <c r="BE14">
+        <v>8.4</v>
+      </c>
+      <c r="BF14">
         <v>6.2</v>
       </c>
-      <c r="AS14">
-        <v>7.2</v>
-      </c>
-      <c r="AT14">
-        <v>4.9</v>
-      </c>
-      <c r="AU14">
-        <v>4.2</v>
-      </c>
-      <c r="AV14">
-        <v>5.3</v>
-      </c>
-      <c r="AW14">
-        <v>6.8</v>
-      </c>
-      <c r="AX14">
-        <v>5.7</v>
-      </c>
-      <c r="AY14">
-        <v>5</v>
-      </c>
-      <c r="AZ14">
-        <v>5.6</v>
-      </c>
-      <c r="BA14">
+      <c r="BG14">
         <v>7</v>
-      </c>
-      <c r="BB14">
-        <v>6.8</v>
-      </c>
-      <c r="BC14">
-        <v>6.4</v>
-      </c>
-      <c r="BD14">
-        <v>7</v>
-      </c>
-      <c r="BE14">
-        <v>7.8</v>
-      </c>
-      <c r="BF14">
-        <v>5.9</v>
-      </c>
-      <c r="BG14">
-        <v>6.6</v>
       </c>
       <c r="BH14">
         <v>3.7</v>
@@ -4242,25 +4242,25 @@
         <v>149</v>
       </c>
       <c r="F15">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="G15">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="H15">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="I15">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J15">
         <v>3.65</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
         <v>1.04</v>
@@ -4275,79 +4275,79 @@
         <v>2.24</v>
       </c>
       <c r="Q15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R15">
         <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T15">
         <v>1.58</v>
       </c>
       <c r="U15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y15">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z15">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB15">
         <v>16</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD15">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE15">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AF15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG15">
         <v>14</v>
       </c>
       <c r="AH15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI15">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AJ15">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AK15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL15">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AM15">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO15">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AP15">
         <v>15</v>
@@ -4356,109 +4356,109 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS15">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AT15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU15">
         <v>8</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW15">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AX15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY15">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>3.9</v>
+        <v>18</v>
       </c>
       <c r="BB15">
         <v>21</v>
       </c>
       <c r="BC15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD15">
-        <v>3.8</v>
+        <v>14.5</v>
       </c>
       <c r="BE15">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BF15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH15">
         <v>4.2</v>
       </c>
       <c r="BI15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15">
         <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP15">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ15">
         <v>6.2</v>
       </c>
       <c r="BR15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS15">
         <v>7.2</v>
       </c>
       <c r="BT15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA15">
         <v>6.4</v>
@@ -4487,16 +4487,16 @@
         <v>1.26</v>
       </c>
       <c r="G16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H16">
         <v>7.2</v>
       </c>
       <c r="I16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J16">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
         <v>7.8</v>
@@ -4517,13 +4517,13 @@
         <v>2.88</v>
       </c>
       <c r="Q16">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="R16">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="S16">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="T16">
         <v>1.55</v>
@@ -4535,7 +4535,7 @@
         <v>1.08</v>
       </c>
       <c r="W16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4595,13 +4595,13 @@
         <v>2.56</v>
       </c>
       <c r="AQ16">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="AR16">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="AS16">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="AT16">
         <v>9.4</v>
@@ -4610,13 +4610,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="AW16">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="AX16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY16">
         <v>7.4</v>
@@ -4625,13 +4625,13 @@
         <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="BB16">
-        <v>8</v>
+        <v>2.24</v>
       </c>
       <c r="BC16">
-        <v>8.6</v>
+        <v>2.26</v>
       </c>
       <c r="BD16">
         <v>16.5</v>
@@ -4643,7 +4643,7 @@
         <v>2.6</v>
       </c>
       <c r="BG16">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4726,67 +4726,67 @@
         <v>151</v>
       </c>
       <c r="F17">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G17">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="H17">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="I17">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J17">
         <v>3.7</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.28</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
         <v>4.8</v>
       </c>
       <c r="O17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
         <v>1.67</v>
       </c>
       <c r="R17">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S17">
         <v>2.62</v>
       </c>
       <c r="T17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="X17">
         <v>24</v>
       </c>
       <c r="Y17">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AA17">
         <v>50</v>
@@ -4801,7 +4801,7 @@
         <v>14</v>
       </c>
       <c r="AE17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF17">
         <v>20</v>
@@ -4810,28 +4810,28 @@
         <v>13</v>
       </c>
       <c r="AH17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI17">
         <v>36</v>
       </c>
       <c r="AJ17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17">
         <v>26</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AP17">
         <v>15.5</v>
@@ -4855,10 +4855,10 @@
         <v>11</v>
       </c>
       <c r="AW17">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX17">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
         <v>10</v>
@@ -4867,28 +4867,28 @@
         <v>13</v>
       </c>
       <c r="BA17">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BB17">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BC17">
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BE17">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BF17">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG17">
         <v>16</v>
       </c>
       <c r="BH17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI17">
         <v>3.25</v>
@@ -4897,22 +4897,22 @@
         <v>10</v>
       </c>
       <c r="BK17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BL17">
         <v>95</v>
       </c>
       <c r="BM17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ17">
         <v>4.3</v>
@@ -4924,28 +4924,28 @@
         <v>4.7</v>
       </c>
       <c r="BT17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BW17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ17">
         <v>22</v>
       </c>
       <c r="CA17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="s">
         <v>162</v>
@@ -4974,7 +4974,7 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="I18">
         <v>1.27</v>
@@ -5007,19 +5007,19 @@
         <v>1.71</v>
       </c>
       <c r="S18">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T18">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V18">
         <v>4.7</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>34</v>
@@ -5037,13 +5037,13 @@
         <v>60</v>
       </c>
       <c r="AC18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD18">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF18">
         <v>170</v>
@@ -5076,19 +5076,19 @@
         <v>3.9</v>
       </c>
       <c r="AP18">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18">
         <v>9.4</v>
       </c>
       <c r="AR18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS18">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT18">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU18">
         <v>14.5</v>
@@ -5100,31 +5100,31 @@
         <v>11</v>
       </c>
       <c r="AX18">
+        <v>9.6</v>
+      </c>
+      <c r="AY18">
         <v>8.6</v>
       </c>
-      <c r="AY18">
-        <v>7.8</v>
-      </c>
       <c r="AZ18">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BA18">
         <v>32</v>
       </c>
       <c r="BB18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC18">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD18">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE18">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18">
         <v>3.35</v>
@@ -5145,28 +5145,28 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN18">
         <v>18.5</v>
       </c>
       <c r="BO18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BS18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU18">
         <v>3.15</v>
@@ -5181,13 +5181,13 @@
         <v>25</v>
       </c>
       <c r="BY18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ18">
         <v>10.5</v>
       </c>
       <c r="CA18">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="s">
         <v>162</v>
@@ -5219,10 +5219,10 @@
         <v>4.3</v>
       </c>
       <c r="I19">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J19">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K19">
         <v>3.65</v>
@@ -5258,7 +5258,7 @@
         <v>1.71</v>
       </c>
       <c r="V19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W19">
         <v>1.94</v>
@@ -5273,13 +5273,13 @@
         <v>50</v>
       </c>
       <c r="AA19">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AB19">
         <v>7.2</v>
       </c>
       <c r="AC19">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD19">
         <v>27</v>
@@ -5288,10 +5288,10 @@
         <v>120</v>
       </c>
       <c r="AF19">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
         <v>30</v>
@@ -5300,7 +5300,7 @@
         <v>140</v>
       </c>
       <c r="AJ19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK19">
         <v>27</v>
@@ -5312,64 +5312,64 @@
         <v>240</v>
       </c>
       <c r="AN19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO19">
         <v>190</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5455,10 +5455,10 @@
         <v>2.48</v>
       </c>
       <c r="G20">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H20">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>3.1</v>
@@ -5476,13 +5476,13 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O20">
         <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q20">
         <v>2.04</v>
@@ -5497,16 +5497,16 @@
         <v>1.77</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
         <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X20">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y20">
         <v>12.5</v>
@@ -5521,13 +5521,13 @@
         <v>12</v>
       </c>
       <c r="AC20">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD20">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AE20">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF20">
         <v>19</v>
@@ -5548,10 +5548,10 @@
         <v>28</v>
       </c>
       <c r="AL20">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN20">
         <v>24</v>
@@ -5590,10 +5590,10 @@
         <v>10</v>
       </c>
       <c r="AZ20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB20">
         <v>32</v>
@@ -5605,7 +5605,7 @@
         <v>34</v>
       </c>
       <c r="BE20">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BF20">
         <v>20</v>
@@ -5694,16 +5694,16 @@
         <v>155</v>
       </c>
       <c r="F21">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G21">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H21">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I21">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J21">
         <v>3.1</v>
@@ -5733,7 +5733,7 @@
         <v>1.18</v>
       </c>
       <c r="S21">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>2.26</v>
@@ -5742,10 +5742,10 @@
         <v>1.76</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -5757,22 +5757,22 @@
         <v>25</v>
       </c>
       <c r="AA21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC21">
         <v>6.8</v>
       </c>
       <c r="AD21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE21">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG21">
         <v>12.5</v>
@@ -5784,7 +5784,7 @@
         <v>95</v>
       </c>
       <c r="AJ21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK21">
         <v>36</v>
@@ -5793,28 +5793,28 @@
         <v>70</v>
       </c>
       <c r="AM21">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AN21">
         <v>38</v>
       </c>
       <c r="AO21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ21">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS21">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU21">
         <v>6.6</v>
@@ -5823,7 +5823,7 @@
         <v>15.5</v>
       </c>
       <c r="AW21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
@@ -5841,16 +5841,16 @@
         <v>30</v>
       </c>
       <c r="BC21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE21">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="BF21">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG21">
         <v>85</v>
@@ -5871,7 +5871,7 @@
         <v>260</v>
       </c>
       <c r="BM21">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN21">
         <v>4.9</v>
@@ -5883,13 +5883,13 @@
         <v>21</v>
       </c>
       <c r="BQ21">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BR21">
         <v>46</v>
       </c>
       <c r="BS21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BT21">
         <v>7</v>
@@ -5901,19 +5901,19 @@
         <v>40</v>
       </c>
       <c r="BW21">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX21">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BY21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CB21" t="s">
         <v>162</v>
@@ -5936,19 +5936,19 @@
         <v>156</v>
       </c>
       <c r="F22">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G22">
         <v>2.68</v>
       </c>
       <c r="H22">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I22">
         <v>3.35</v>
       </c>
       <c r="J22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
         <v>3.85</v>
@@ -5963,7 +5963,7 @@
         <v>3.6</v>
       </c>
       <c r="O22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P22">
         <v>1.9</v>
@@ -5990,7 +5990,7 @@
         <v>1.59</v>
       </c>
       <c r="X22">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y22">
         <v>14.5</v>
@@ -5999,7 +5999,7 @@
         <v>25</v>
       </c>
       <c r="AA22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB22">
         <v>12.5</v>
@@ -6011,7 +6011,7 @@
         <v>15.5</v>
       </c>
       <c r="AE22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF22">
         <v>19.5</v>
@@ -6020,31 +6020,31 @@
         <v>13.5</v>
       </c>
       <c r="AH22">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI22">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ22">
+        <v>38</v>
+      </c>
+      <c r="AK22">
+        <v>29</v>
+      </c>
+      <c r="AL22">
         <v>42</v>
       </c>
-      <c r="AK22">
-        <v>32</v>
-      </c>
-      <c r="AL22">
-        <v>46</v>
-      </c>
       <c r="AM22">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="AN22">
         <v>25</v>
       </c>
       <c r="AO22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ22">
         <v>10.5</v>
@@ -6053,10 +6053,10 @@
         <v>18</v>
       </c>
       <c r="AS22">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT22">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU22">
         <v>6.8</v>
@@ -6065,7 +6065,7 @@
         <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AX22">
         <v>14</v>
@@ -6074,28 +6074,28 @@
         <v>10</v>
       </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB22">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="BC22">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD22">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE22">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF22">
         <v>18</v>
       </c>
       <c r="BG22">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH22">
         <v>3.55</v>
@@ -6178,10 +6178,10 @@
         <v>157</v>
       </c>
       <c r="F23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G23">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H23">
         <v>7.4</v>
@@ -6190,10 +6190,10 @@
         <v>8.4</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6205,7 +6205,7 @@
         <v>3.05</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P23">
         <v>1.71</v>
@@ -6220,19 +6220,19 @@
         <v>4.2</v>
       </c>
       <c r="T23">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W23">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y23">
         <v>21</v>
@@ -6241,7 +6241,7 @@
         <v>70</v>
       </c>
       <c r="AA23">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB23">
         <v>6.4</v>
@@ -6253,7 +6253,7 @@
         <v>32</v>
       </c>
       <c r="AE23">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF23">
         <v>8.4</v>
@@ -6262,10 +6262,10 @@
         <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI23">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ23">
         <v>15</v>
@@ -6280,16 +6280,16 @@
         <v>240</v>
       </c>
       <c r="AN23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO23">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AP23">
         <v>10</v>
       </c>
       <c r="AQ23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR23">
         <v>50</v>
@@ -6301,10 +6301,10 @@
         <v>5.9</v>
       </c>
       <c r="AU23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV23">
-        <v>26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23">
         <v>11.5</v>
@@ -6319,7 +6319,7 @@
         <v>25</v>
       </c>
       <c r="BA23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB23">
         <v>13</v>
@@ -6331,13 +6331,13 @@
         <v>42</v>
       </c>
       <c r="BE23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF23">
         <v>10</v>
       </c>
       <c r="BG23">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6420,40 +6420,40 @@
         <v>158</v>
       </c>
       <c r="F24">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G24">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H24">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I24">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J24">
         <v>2.86</v>
       </c>
       <c r="K24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L24">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O24">
         <v>1.54</v>
       </c>
       <c r="P24">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q24">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R24">
         <v>1.18</v>
@@ -6462,97 +6462,97 @@
         <v>5.4</v>
       </c>
       <c r="T24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U24">
         <v>1.75</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X24">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y24">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Z24">
         <v>17</v>
       </c>
       <c r="AA24">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB24">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD24">
         <v>14.5</v>
       </c>
       <c r="AE24">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF24">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AG24">
         <v>18.5</v>
       </c>
       <c r="AH24">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI24">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AJ24">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK24">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AL24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM24">
         <v>220</v>
       </c>
       <c r="AN24">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AO24">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP24">
         <v>6.4</v>
       </c>
       <c r="AQ24">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR24">
         <v>12.5</v>
       </c>
       <c r="AS24">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT24">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU24">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AV24">
         <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY24">
         <v>13.5</v>
@@ -6561,28 +6561,28 @@
         <v>20</v>
       </c>
       <c r="BA24">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB24">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC24">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BD24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BE24">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BF24">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BG24">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="BH24">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI24">
         <v>2.26</v>
@@ -6591,16 +6591,16 @@
         <v>12</v>
       </c>
       <c r="BK24">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO24">
         <v>5.1</v>
@@ -6609,13 +6609,13 @@
         <v>36</v>
       </c>
       <c r="BQ24">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT24">
         <v>5.3</v>
@@ -6624,22 +6624,22 @@
         <v>4.1</v>
       </c>
       <c r="BV24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW24">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY24">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="s">
         <v>162</v>
@@ -6665,19 +6665,19 @@
         <v>2.42</v>
       </c>
       <c r="G25">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="I25">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J25">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6686,16 +6686,16 @@
         <v>1.08</v>
       </c>
       <c r="N25">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O25">
         <v>1.43</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R25">
         <v>1.17</v>
@@ -6704,16 +6704,16 @@
         <v>3.8</v>
       </c>
       <c r="T25">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U25">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X25">
         <v>12</v>
@@ -6725,10 +6725,10 @@
         <v>26</v>
       </c>
       <c r="AA25">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25">
         <v>7.4</v>
@@ -6737,7 +6737,7 @@
         <v>17</v>
       </c>
       <c r="AE25">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="AF25">
         <v>18</v>
@@ -6749,7 +6749,7 @@
         <v>24</v>
       </c>
       <c r="AI25">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AJ25">
         <v>44</v>
@@ -6761,13 +6761,13 @@
         <v>65</v>
       </c>
       <c r="AM25">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN25">
         <v>38</v>
       </c>
       <c r="AO25">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AP25">
         <v>9</v>
@@ -6779,7 +6779,7 @@
         <v>17</v>
       </c>
       <c r="AS25">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT25">
         <v>7.6</v>
@@ -6791,7 +6791,7 @@
         <v>11</v>
       </c>
       <c r="AW25">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX25">
         <v>11.5</v>
@@ -6800,28 +6800,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ25">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA25">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB25">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BC25">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE25">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF25">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG25">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BH25">
         <v>3.25</v>
@@ -6857,7 +6857,7 @@
         <v>46</v>
       </c>
       <c r="BS25">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT25">
         <v>7.2</v>
@@ -6866,7 +6866,7 @@
         <v>5</v>
       </c>
       <c r="BV25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW25">
         <v>5.2</v>
@@ -6875,13 +6875,13 @@
         <v>55</v>
       </c>
       <c r="BY25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ25">
         <v>46</v>
       </c>
       <c r="CA25">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB25" t="s">
         <v>162</v>
@@ -6907,7 +6907,7 @@
         <v>1.61</v>
       </c>
       <c r="G26">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H26">
         <v>6.2</v>
@@ -6916,7 +6916,7 @@
         <v>7.8</v>
       </c>
       <c r="J26">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K26">
         <v>4.3</v>
@@ -6937,7 +6937,7 @@
         <v>1.9</v>
       </c>
       <c r="Q26">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R26">
         <v>1.35</v>
@@ -6955,7 +6955,7 @@
         <v>1.15</v>
       </c>
       <c r="W26">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X26">
         <v>15</v>
@@ -7003,13 +7003,13 @@
         <v>44</v>
       </c>
       <c r="AM26">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AN26">
         <v>9.800000000000001</v>
       </c>
       <c r="AO26">
-        <v>160</v>
+        <v>530</v>
       </c>
       <c r="AP26">
         <v>12</v>
@@ -7018,7 +7018,7 @@
         <v>18</v>
       </c>
       <c r="AR26">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AS26">
         <v>9.4</v>
@@ -7057,7 +7057,7 @@
         <v>32</v>
       </c>
       <c r="BE26">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF26">
         <v>8.199999999999999</v>
@@ -7182,13 +7182,13 @@
         <v>2.12</v>
       </c>
       <c r="R27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S27">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T27">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="U27">
         <v>1.69</v>
@@ -7212,7 +7212,7 @@
         <v>390</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC27">
         <v>8.800000000000001</v>
@@ -7236,7 +7236,7 @@
         <v>180</v>
       </c>
       <c r="AJ27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK27">
         <v>20</v>
@@ -7260,10 +7260,10 @@
         <v>18</v>
       </c>
       <c r="AR27">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS27">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27">
         <v>5.8</v>
@@ -7275,7 +7275,7 @@
         <v>26</v>
       </c>
       <c r="AW27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX27">
         <v>6.8</v>
@@ -7284,10 +7284,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA27">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
@@ -7299,13 +7299,13 @@
         <v>38</v>
       </c>
       <c r="BE27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF27">
         <v>9.199999999999999</v>
       </c>
       <c r="BG27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH27">
         <v>3.55</v>
@@ -7317,16 +7317,16 @@
         <v>14.5</v>
       </c>
       <c r="BK27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BN27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO27">
         <v>3.1</v>
@@ -7335,37 +7335,37 @@
         <v>12</v>
       </c>
       <c r="BQ27">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR27">
         <v>36</v>
       </c>
       <c r="BS27">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BT27">
         <v>13</v>
       </c>
       <c r="BU27">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV27">
         <v>100</v>
       </c>
       <c r="BW27">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX27">
         <v>110</v>
       </c>
       <c r="BY27">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BZ27">
         <v>27</v>
       </c>
       <c r="CA27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB27" t="s">
         <v>162</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -295,7 +295,7 @@
     <t>2026-08-20</t>
   </si>
   <si>
-    <t>00:00:00</t>
+    <t>00:10:00</t>
   </si>
   <si>
     <t>00:30:00</t>
@@ -502,7 +502,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-19 19:39:32</t>
+    <t>2026-08-19 21:52:20</t>
   </si>
 </sst>
 </file>
@@ -1096,226 +1096,226 @@
         <v>136</v>
       </c>
       <c r="F2">
+        <v>3.45</v>
+      </c>
+      <c r="G2">
+        <v>3.5</v>
+      </c>
+      <c r="H2">
+        <v>2.36</v>
+      </c>
+      <c r="I2">
+        <v>2.4</v>
+      </c>
+      <c r="J2">
+        <v>3.4</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.83</v>
+      </c>
+      <c r="M2">
+        <v>1.09</v>
+      </c>
+      <c r="N2">
+        <v>3.35</v>
+      </c>
+      <c r="O2">
+        <v>1.41</v>
+      </c>
+      <c r="P2">
+        <v>1.76</v>
+      </c>
+      <c r="Q2">
+        <v>2.28</v>
+      </c>
+      <c r="R2">
+        <v>1.3</v>
+      </c>
+      <c r="S2">
         <v>4.2</v>
       </c>
-      <c r="G2">
-        <v>4.4</v>
-      </c>
-      <c r="H2">
-        <v>1.87</v>
-      </c>
-      <c r="I2">
-        <v>1.9</v>
-      </c>
-      <c r="J2">
-        <v>4.1</v>
-      </c>
-      <c r="K2">
-        <v>4.3</v>
-      </c>
-      <c r="L2">
-        <v>1.3</v>
-      </c>
-      <c r="M2">
-        <v>1.04</v>
-      </c>
-      <c r="N2">
-        <v>5.6</v>
-      </c>
-      <c r="O2">
-        <v>1.2</v>
-      </c>
-      <c r="P2">
-        <v>2.56</v>
-      </c>
-      <c r="Q2">
-        <v>1.61</v>
-      </c>
-      <c r="R2">
-        <v>1.63</v>
-      </c>
-      <c r="S2">
-        <v>2.54</v>
-      </c>
       <c r="T2">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X2">
+        <v>11.5</v>
+      </c>
+      <c r="Y2">
+        <v>8.6</v>
+      </c>
+      <c r="Z2">
+        <v>13.5</v>
+      </c>
+      <c r="AA2">
+        <v>32</v>
+      </c>
+      <c r="AB2">
+        <v>11.5</v>
+      </c>
+      <c r="AC2">
+        <v>7.4</v>
+      </c>
+      <c r="AD2">
+        <v>12</v>
+      </c>
+      <c r="AE2">
+        <v>29</v>
+      </c>
+      <c r="AF2">
+        <v>21</v>
+      </c>
+      <c r="AG2">
+        <v>15.5</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>60</v>
+      </c>
+      <c r="AJ2">
+        <v>70</v>
+      </c>
+      <c r="AK2">
+        <v>48</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
+        <v>55</v>
+      </c>
+      <c r="AO2">
+        <v>27</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>12</v>
+      </c>
+      <c r="AS2">
+        <v>29</v>
+      </c>
+      <c r="AT2">
+        <v>10</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>25</v>
+      </c>
+      <c r="AX2">
+        <v>19</v>
+      </c>
+      <c r="AY2">
+        <v>14</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>46</v>
+      </c>
+      <c r="BB2">
+        <v>50</v>
+      </c>
+      <c r="BC2">
+        <v>40</v>
+      </c>
+      <c r="BD2">
+        <v>55</v>
+      </c>
+      <c r="BE2">
+        <v>120</v>
+      </c>
+      <c r="BF2">
+        <v>44</v>
+      </c>
+      <c r="BG2">
         <v>23</v>
       </c>
-      <c r="Y2">
-        <v>12.5</v>
-      </c>
-      <c r="Z2">
+      <c r="BH2">
+        <v>2.18</v>
+      </c>
+      <c r="BI2">
+        <v>2.08</v>
+      </c>
+      <c r="BJ2">
+        <v>16</v>
+      </c>
+      <c r="BK2">
         <v>14</v>
       </c>
-      <c r="AA2">
-        <v>21</v>
-      </c>
-      <c r="AB2">
-        <v>22</v>
-      </c>
-      <c r="AC2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>10</v>
-      </c>
-      <c r="AE2">
-        <v>17</v>
-      </c>
-      <c r="AF2">
+      <c r="BL2">
+        <v>760</v>
+      </c>
+      <c r="BM2">
+        <v>15.5</v>
+      </c>
+      <c r="BN2">
+        <v>6.6</v>
+      </c>
+      <c r="BO2">
+        <v>6</v>
+      </c>
+      <c r="BP2">
+        <v>55</v>
+      </c>
+      <c r="BQ2">
         <v>36</v>
       </c>
-      <c r="AG2">
-        <v>17</v>
-      </c>
-      <c r="AH2">
-        <v>15.5</v>
-      </c>
-      <c r="AI2">
-        <v>26</v>
-      </c>
-      <c r="AJ2">
-        <v>80</v>
-      </c>
-      <c r="AK2">
+      <c r="BR2">
+        <v>140</v>
+      </c>
+      <c r="BS2">
+        <v>55</v>
+      </c>
+      <c r="BT2">
+        <v>5.1</v>
+      </c>
+      <c r="BU2">
+        <v>4.7</v>
+      </c>
+      <c r="BV2">
+        <v>32</v>
+      </c>
+      <c r="BW2">
+        <v>24</v>
+      </c>
+      <c r="BX2">
+        <v>90</v>
+      </c>
+      <c r="BY2">
         <v>44</v>
       </c>
-      <c r="AL2">
+      <c r="BZ2">
+        <v>120</v>
+      </c>
+      <c r="CA2">
         <v>44</v>
-      </c>
-      <c r="AM2">
-        <v>65</v>
-      </c>
-      <c r="AN2">
-        <v>34</v>
-      </c>
-      <c r="AO2">
-        <v>8.6</v>
-      </c>
-      <c r="AP2">
-        <v>21</v>
-      </c>
-      <c r="AQ2">
-        <v>11.5</v>
-      </c>
-      <c r="AR2">
-        <v>13</v>
-      </c>
-      <c r="AS2">
-        <v>19.5</v>
-      </c>
-      <c r="AT2">
-        <v>20</v>
-      </c>
-      <c r="AU2">
-        <v>9</v>
-      </c>
-      <c r="AV2">
-        <v>9.6</v>
-      </c>
-      <c r="AW2">
-        <v>15.5</v>
-      </c>
-      <c r="AX2">
-        <v>32</v>
-      </c>
-      <c r="AY2">
-        <v>15.5</v>
-      </c>
-      <c r="AZ2">
-        <v>14.5</v>
-      </c>
-      <c r="BA2">
-        <v>24</v>
-      </c>
-      <c r="BB2">
-        <v>70</v>
-      </c>
-      <c r="BC2">
-        <v>38</v>
-      </c>
-      <c r="BD2">
-        <v>38</v>
-      </c>
-      <c r="BE2">
-        <v>55</v>
-      </c>
-      <c r="BF2">
-        <v>29</v>
-      </c>
-      <c r="BG2">
-        <v>8</v>
-      </c>
-      <c r="BH2">
-        <v>4.3</v>
-      </c>
-      <c r="BI2">
-        <v>4</v>
-      </c>
-      <c r="BJ2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK2">
-        <v>8</v>
-      </c>
-      <c r="BL2">
-        <v>85</v>
-      </c>
-      <c r="BM2">
-        <v>10</v>
-      </c>
-      <c r="BN2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO2">
-        <v>7</v>
-      </c>
-      <c r="BP2">
-        <v>30</v>
-      </c>
-      <c r="BQ2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR2">
-        <v>36</v>
-      </c>
-      <c r="BS2">
-        <v>8.6</v>
-      </c>
-      <c r="BT2">
-        <v>4.9</v>
-      </c>
-      <c r="BU2">
-        <v>4.6</v>
-      </c>
-      <c r="BV2">
-        <v>14</v>
-      </c>
-      <c r="BW2">
-        <v>11</v>
-      </c>
-      <c r="BX2">
-        <v>25</v>
-      </c>
-      <c r="BY2">
-        <v>17.5</v>
-      </c>
-      <c r="BZ2">
-        <v>16</v>
-      </c>
-      <c r="CA2">
-        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
         <v>162</v>
@@ -1338,226 +1338,226 @@
         <v>137</v>
       </c>
       <c r="F3">
+        <v>2.44</v>
+      </c>
+      <c r="G3">
+        <v>2.5</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>4.2</v>
+      </c>
+      <c r="J3">
+        <v>2.82</v>
+      </c>
+      <c r="K3">
+        <v>2.92</v>
+      </c>
+      <c r="L3">
+        <v>2.06</v>
+      </c>
+      <c r="M3">
+        <v>1.2</v>
+      </c>
+      <c r="N3">
+        <v>2.18</v>
+      </c>
+      <c r="O3">
+        <v>1.81</v>
+      </c>
+      <c r="P3">
+        <v>1.35</v>
+      </c>
+      <c r="Q3">
+        <v>3.7</v>
+      </c>
+      <c r="R3">
+        <v>1.11</v>
+      </c>
+      <c r="S3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="T3">
         <v>2.56</v>
       </c>
-      <c r="G3">
-        <v>2.62</v>
-      </c>
-      <c r="H3">
-        <v>3.5</v>
-      </c>
-      <c r="I3">
-        <v>3.6</v>
-      </c>
-      <c r="J3">
-        <v>2.96</v>
-      </c>
-      <c r="K3">
-        <v>3.05</v>
-      </c>
-      <c r="L3">
-        <v>1.61</v>
-      </c>
-      <c r="M3">
-        <v>1.14</v>
-      </c>
-      <c r="N3">
-        <v>2.66</v>
-      </c>
-      <c r="O3">
-        <v>1.58</v>
-      </c>
-      <c r="P3">
-        <v>1.54</v>
-      </c>
-      <c r="Q3">
-        <v>2.8</v>
-      </c>
-      <c r="R3">
-        <v>1.19</v>
-      </c>
-      <c r="S3">
-        <v>5.9</v>
-      </c>
-      <c r="T3">
-        <v>2.18</v>
-      </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
+        <v>6.4</v>
+      </c>
+      <c r="Y3">
+        <v>9</v>
+      </c>
+      <c r="Z3">
+        <v>28</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>6.2</v>
+      </c>
+      <c r="AC3">
+        <v>7.2</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>13.5</v>
+      </c>
+      <c r="AG3">
+        <v>15.5</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>5.8</v>
+      </c>
+      <c r="AQ3">
+        <v>8</v>
+      </c>
+      <c r="AR3">
+        <v>18</v>
+      </c>
+      <c r="AS3">
+        <v>5</v>
+      </c>
+      <c r="AT3">
+        <v>5.8</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>17.5</v>
+      </c>
+      <c r="AW3">
+        <v>5</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3">
+        <v>5.1</v>
+      </c>
+      <c r="BA3">
+        <v>5</v>
+      </c>
+      <c r="BB3">
+        <v>6.2</v>
+      </c>
+      <c r="BC3">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y3">
-        <v>9.6</v>
-      </c>
-      <c r="Z3">
-        <v>22</v>
-      </c>
-      <c r="AA3">
-        <v>110</v>
-      </c>
-      <c r="AB3">
-        <v>7.8</v>
-      </c>
-      <c r="AC3">
-        <v>6.8</v>
-      </c>
-      <c r="AD3">
-        <v>16</v>
-      </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>15</v>
-      </c>
-      <c r="AG3">
-        <v>13.5</v>
-      </c>
-      <c r="AH3">
-        <v>29</v>
-      </c>
-      <c r="AI3">
-        <v>160</v>
-      </c>
-      <c r="AJ3">
-        <v>42</v>
-      </c>
-      <c r="AK3">
+      <c r="BD3">
+        <v>5</v>
+      </c>
+      <c r="BE3">
+        <v>5</v>
+      </c>
+      <c r="BF3">
         <v>40</v>
       </c>
-      <c r="AL3">
-        <v>130</v>
-      </c>
-      <c r="AM3">
-        <v>210</v>
-      </c>
-      <c r="AN3">
-        <v>44</v>
-      </c>
-      <c r="AO3">
-        <v>85</v>
-      </c>
-      <c r="AP3">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR3">
-        <v>19.5</v>
-      </c>
-      <c r="AS3">
-        <v>55</v>
-      </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
-      <c r="AU3">
+      <c r="BG3">
         <v>6.2</v>
       </c>
-      <c r="AV3">
-        <v>14</v>
-      </c>
-      <c r="AW3">
-        <v>48</v>
-      </c>
-      <c r="AX3">
-        <v>13.5</v>
-      </c>
-      <c r="AY3">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
-      <c r="BA3">
-        <v>15</v>
-      </c>
-      <c r="BB3">
-        <v>34</v>
-      </c>
-      <c r="BC3">
-        <v>34</v>
-      </c>
-      <c r="BD3">
-        <v>46</v>
-      </c>
-      <c r="BE3">
-        <v>15.5</v>
-      </c>
-      <c r="BF3">
-        <v>36</v>
-      </c>
-      <c r="BG3">
+      <c r="BH3">
+        <v>1.9</v>
+      </c>
+      <c r="BI3">
+        <v>1.83</v>
+      </c>
+      <c r="BJ3">
+        <v>970</v>
+      </c>
+      <c r="BK3">
         <v>14.5</v>
       </c>
-      <c r="BH3">
-        <v>2.64</v>
-      </c>
-      <c r="BI3">
-        <v>2.5</v>
-      </c>
-      <c r="BJ3">
-        <v>11.5</v>
-      </c>
-      <c r="BK3">
-        <v>7.2</v>
-      </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
         <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="BS3">
-        <v>2.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3">
+        <v>7.8</v>
+      </c>
+      <c r="BU3">
         <v>6.4</v>
       </c>
-      <c r="BU3">
-        <v>5.5</v>
-      </c>
       <c r="BV3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY3">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>55</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>162</v>
@@ -1580,226 +1580,226 @@
         <v>138</v>
       </c>
       <c r="F4">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="G4">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="J4">
+        <v>4.2</v>
+      </c>
+      <c r="K4">
+        <v>4.4</v>
+      </c>
+      <c r="L4">
+        <v>1.58</v>
+      </c>
+      <c r="M4">
+        <v>1.07</v>
+      </c>
+      <c r="N4">
         <v>3.9</v>
       </c>
-      <c r="K4">
-        <v>3.95</v>
-      </c>
-      <c r="L4">
-        <v>1.43</v>
-      </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>3.8</v>
-      </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="W4">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AA4">
+        <v>410</v>
+      </c>
+      <c r="AB4">
+        <v>7.2</v>
+      </c>
+      <c r="AC4">
+        <v>11</v>
+      </c>
+      <c r="AD4">
+        <v>44</v>
+      </c>
+      <c r="AE4">
         <v>160</v>
       </c>
-      <c r="AB4">
-        <v>7.8</v>
-      </c>
-      <c r="AC4">
-        <v>8.4</v>
-      </c>
-      <c r="AD4">
-        <v>23</v>
-      </c>
-      <c r="AE4">
-        <v>90</v>
-      </c>
       <c r="AF4">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AJ4">
+        <v>13.5</v>
+      </c>
+      <c r="AK4">
         <v>16</v>
       </c>
-      <c r="AK4">
-        <v>18</v>
-      </c>
       <c r="AL4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="AP4">
         <v>13</v>
       </c>
       <c r="AQ4">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AR4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AS4">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AT4">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AW4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BB4">
+        <v>11.5</v>
+      </c>
+      <c r="BC4">
         <v>15</v>
       </c>
-      <c r="BC4">
-        <v>17</v>
-      </c>
       <c r="BD4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BH4">
+        <v>2.8</v>
+      </c>
+      <c r="BI4">
+        <v>2.6</v>
+      </c>
+      <c r="BJ4">
+        <v>14</v>
+      </c>
+      <c r="BK4">
+        <v>13</v>
+      </c>
+      <c r="BL4">
+        <v>380</v>
+      </c>
+      <c r="BM4">
+        <v>180</v>
+      </c>
+      <c r="BN4">
+        <v>3.7</v>
+      </c>
+      <c r="BO4">
         <v>3.4</v>
       </c>
-      <c r="BI4">
-        <v>3.05</v>
-      </c>
-      <c r="BJ4">
+      <c r="BP4">
         <v>11</v>
-      </c>
-      <c r="BK4">
-        <v>8.6</v>
-      </c>
-      <c r="BL4">
-        <v>150</v>
-      </c>
-      <c r="BM4">
-        <v>13</v>
-      </c>
-      <c r="BN4">
-        <v>4.2</v>
-      </c>
-      <c r="BO4">
-        <v>3.8</v>
-      </c>
-      <c r="BP4">
-        <v>12</v>
       </c>
       <c r="BQ4">
         <v>10</v>
       </c>
       <c r="BR4">
+        <v>50</v>
+      </c>
+      <c r="BS4">
         <v>29</v>
       </c>
-      <c r="BS4">
+      <c r="BT4">
+        <v>11</v>
+      </c>
+      <c r="BU4">
         <v>9.6</v>
       </c>
-      <c r="BT4">
-        <v>9.4</v>
-      </c>
-      <c r="BU4">
-        <v>8</v>
-      </c>
       <c r="BV4">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BZ4">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="CA4">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1822,226 +1822,226 @@
         <v>139</v>
       </c>
       <c r="F5">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="G5">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="S5">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="T5">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="Z5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA5">
         <v>120</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AL5">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AM5">
+        <v>140</v>
+      </c>
+      <c r="AN5">
+        <v>13</v>
+      </c>
+      <c r="AO5">
+        <v>70</v>
+      </c>
+      <c r="AP5">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5">
+        <v>14.5</v>
+      </c>
+      <c r="AR5">
+        <v>30</v>
+      </c>
+      <c r="AS5">
         <v>80</v>
       </c>
-      <c r="AN5">
-        <v>7.4</v>
-      </c>
-      <c r="AO5">
-        <v>50</v>
-      </c>
-      <c r="AP5">
-        <v>21</v>
-      </c>
-      <c r="AQ5">
-        <v>20</v>
-      </c>
-      <c r="AR5">
-        <v>36</v>
-      </c>
-      <c r="AS5">
-        <v>40</v>
-      </c>
       <c r="AT5">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
         <v>50</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB5">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="BF5">
+        <v>8.6</v>
+      </c>
+      <c r="BG5">
+        <v>55</v>
+      </c>
+      <c r="BH5">
+        <v>3</v>
+      </c>
+      <c r="BI5">
+        <v>2.72</v>
+      </c>
+      <c r="BJ5">
+        <v>11.5</v>
+      </c>
+      <c r="BK5">
+        <v>10</v>
+      </c>
+      <c r="BL5">
+        <v>230</v>
+      </c>
+      <c r="BM5">
+        <v>11.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.4</v>
+      </c>
+      <c r="BO5">
+        <v>4</v>
+      </c>
+      <c r="BP5">
+        <v>14</v>
+      </c>
+      <c r="BQ5">
+        <v>11.5</v>
+      </c>
+      <c r="BR5">
+        <v>40</v>
+      </c>
+      <c r="BS5">
+        <v>30</v>
+      </c>
+      <c r="BT5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU5">
         <v>6.8</v>
       </c>
-      <c r="BG5">
-        <v>44</v>
-      </c>
-      <c r="BH5">
-        <v>4.3</v>
-      </c>
-      <c r="BI5">
-        <v>3.95</v>
-      </c>
-      <c r="BJ5">
-        <v>9.4</v>
-      </c>
-      <c r="BK5">
-        <v>7.6</v>
-      </c>
-      <c r="BL5">
-        <v>90</v>
-      </c>
-      <c r="BM5">
-        <v>12.5</v>
-      </c>
-      <c r="BN5">
-        <v>4.6</v>
-      </c>
-      <c r="BO5">
-        <v>4.2</v>
-      </c>
-      <c r="BP5">
-        <v>11</v>
-      </c>
-      <c r="BQ5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR5">
-        <v>22</v>
-      </c>
-      <c r="BS5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU5">
-        <v>7.6</v>
-      </c>
       <c r="BV5">
+        <v>50</v>
+      </c>
+      <c r="BW5">
+        <v>34</v>
+      </c>
+      <c r="BX5">
+        <v>70</v>
+      </c>
+      <c r="BY5">
+        <v>46</v>
+      </c>
+      <c r="BZ5">
         <v>40</v>
       </c>
-      <c r="BW5">
-        <v>10.5</v>
-      </c>
-      <c r="BX5">
-        <v>42</v>
-      </c>
-      <c r="BY5">
-        <v>11</v>
-      </c>
-      <c r="BZ5">
-        <v>15</v>
-      </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
         <v>162</v>
@@ -2064,22 +2064,22 @@
         <v>140</v>
       </c>
       <c r="F6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G6">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.51</v>
@@ -2094,64 +2094,64 @@
         <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W6">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="X6">
         <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA6">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AE6">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AJ6">
         <v>17.5</v>
@@ -2160,76 +2160,76 @@
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>790</v>
       </c>
       <c r="AN6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO6">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS6">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AT6">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW6">
         <v>60</v>
       </c>
       <c r="AX6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6">
         <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA6">
         <v>65</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE6">
-        <v>16.5</v>
+        <v>130</v>
       </c>
       <c r="BF6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>16.5</v>
+        <v>110</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2241,7 +2241,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="BN6">
         <v>4.1</v>
@@ -2265,7 +2265,7 @@
         <v>9.6</v>
       </c>
       <c r="BU6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2312,7 +2312,7 @@
         <v>2.1</v>
       </c>
       <c r="H7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I7">
         <v>3.75</v>
@@ -2336,13 +2336,13 @@
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S7">
         <v>2.44</v>
@@ -2351,19 +2351,19 @@
         <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z7">
         <v>32</v>
@@ -2384,7 +2384,7 @@
         <v>36</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2393,13 +2393,13 @@
         <v>14.5</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ7">
         <v>26</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL7">
         <v>26</v>
@@ -2417,16 +2417,16 @@
         <v>22</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU7">
         <v>8.800000000000001</v>
@@ -2435,10 +2435,10 @@
         <v>14</v>
       </c>
       <c r="AW7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2447,7 +2447,7 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB7">
         <v>24</v>
@@ -2465,7 +2465,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH7">
         <v>4.5</v>
@@ -2483,25 +2483,25 @@
         <v>70</v>
       </c>
       <c r="BM7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN7">
         <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR7">
         <v>21</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT7">
         <v>7.4</v>
@@ -2513,13 +2513,13 @@
         <v>24</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX7">
         <v>29</v>
       </c>
       <c r="BY7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
         <v>14.5</v>
@@ -2548,16 +2548,16 @@
         <v>142</v>
       </c>
       <c r="F8">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="H8">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="I8">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J8">
         <v>3.8</v>
@@ -2575,10 +2575,10 @@
         <v>4.8</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
         <v>1.76</v>
@@ -2587,187 +2587,187 @@
         <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="X8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC8">
         <v>8.4</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AE8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH8">
+        <v>15.5</v>
+      </c>
+      <c r="AI8">
+        <v>40</v>
+      </c>
+      <c r="AJ8">
+        <v>32</v>
+      </c>
+      <c r="AK8">
+        <v>23</v>
+      </c>
+      <c r="AL8">
+        <v>32</v>
+      </c>
+      <c r="AM8">
+        <v>70</v>
+      </c>
+      <c r="AN8">
         <v>15</v>
       </c>
-      <c r="AI8">
-        <v>36</v>
-      </c>
-      <c r="AJ8">
-        <v>36</v>
-      </c>
-      <c r="AK8">
-        <v>25</v>
-      </c>
-      <c r="AL8">
-        <v>34</v>
-      </c>
-      <c r="AM8">
-        <v>65</v>
-      </c>
-      <c r="AN8">
-        <v>17.5</v>
-      </c>
       <c r="AO8">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AP8">
         <v>17</v>
       </c>
       <c r="AQ8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU8">
         <v>8</v>
       </c>
       <c r="AV8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AX8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BC8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE8">
         <v>55</v>
       </c>
       <c r="BF8">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BG8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BH8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI8">
         <v>3.65</v>
       </c>
       <c r="BJ8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL8">
         <v>90</v>
       </c>
       <c r="BM8">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BN8">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BO8">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP8">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ8">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BR8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BX8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY8">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
         <v>20</v>
       </c>
       <c r="CA8">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="CB8" t="s">
         <v>162</v>
@@ -2790,85 +2790,85 @@
         <v>143</v>
       </c>
       <c r="F9">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="G9">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="I9">
+        <v>5.3</v>
+      </c>
+      <c r="J9">
+        <v>4.5</v>
+      </c>
+      <c r="K9">
         <v>4.6</v>
       </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
-        <v>4.2</v>
-      </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="R9">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T9">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="X9">
+        <v>22</v>
+      </c>
+      <c r="Y9">
+        <v>23</v>
+      </c>
+      <c r="Z9">
+        <v>46</v>
+      </c>
+      <c r="AA9">
+        <v>110</v>
+      </c>
+      <c r="AB9">
+        <v>11.5</v>
+      </c>
+      <c r="AC9">
+        <v>10.5</v>
+      </c>
+      <c r="AD9">
         <v>19</v>
       </c>
-      <c r="Y9">
-        <v>19</v>
-      </c>
-      <c r="Z9">
-        <v>36</v>
-      </c>
-      <c r="AA9">
-        <v>95</v>
-      </c>
-      <c r="AB9">
-        <v>11</v>
-      </c>
-      <c r="AC9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD9">
-        <v>17.5</v>
-      </c>
       <c r="AE9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
         <v>9.800000000000001</v>
@@ -2880,82 +2880,82 @@
         <v>55</v>
       </c>
       <c r="AJ9">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK9">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM9">
         <v>80</v>
       </c>
       <c r="AN9">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO9">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP9">
+        <v>21</v>
+      </c>
+      <c r="AQ9">
+        <v>21</v>
+      </c>
+      <c r="AR9">
+        <v>40</v>
+      </c>
+      <c r="AS9">
+        <v>48</v>
+      </c>
+      <c r="AT9">
+        <v>10.5</v>
+      </c>
+      <c r="AU9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV9">
         <v>17.5</v>
       </c>
-      <c r="AQ9">
-        <v>17.5</v>
-      </c>
-      <c r="AR9">
-        <v>32</v>
-      </c>
-      <c r="AS9">
-        <v>65</v>
-      </c>
-      <c r="AT9">
-        <v>10</v>
-      </c>
-      <c r="AU9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV9">
-        <v>16</v>
-      </c>
       <c r="AW9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB9">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BD9">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BF9">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BG9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH9">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI9">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
@@ -2964,52 +2964,52 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM9">
         <v>16</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BV9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY9">
         <v>13</v>
       </c>
       <c r="BZ9">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="CA9">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
         <v>162</v>
@@ -3032,22 +3032,22 @@
         <v>144</v>
       </c>
       <c r="F10">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G10">
         <v>2.62</v>
       </c>
       <c r="H10">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I10">
         <v>3.05</v>
       </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.4</v>
@@ -3056,28 +3056,28 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q10">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V10">
         <v>1.48</v>
@@ -3095,7 +3095,7 @@
         <v>21</v>
       </c>
       <c r="AA10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB10">
         <v>11.5</v>
@@ -3107,16 +3107,16 @@
         <v>13.5</v>
       </c>
       <c r="AE10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG10">
         <v>12</v>
       </c>
       <c r="AH10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10">
         <v>42</v>
@@ -3131,13 +3131,13 @@
         <v>38</v>
       </c>
       <c r="AM10">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN10">
         <v>21</v>
       </c>
       <c r="AO10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP10">
         <v>13.5</v>
@@ -3149,13 +3149,13 @@
         <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AT10">
         <v>10</v>
       </c>
       <c r="AU10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10">
         <v>11.5</v>
@@ -3185,13 +3185,13 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>60</v>
+        <v>13.5</v>
       </c>
       <c r="BF10">
         <v>18</v>
       </c>
       <c r="BG10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH10">
         <v>3.55</v>
@@ -3277,7 +3277,7 @@
         <v>2.04</v>
       </c>
       <c r="G11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
         <v>3.5</v>
@@ -3301,7 +3301,7 @@
         <v>7.6</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
         <v>3.2</v>
@@ -3316,13 +3316,13 @@
         <v>2.1</v>
       </c>
       <c r="T11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U11">
         <v>3.1</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
         <v>1.94</v>
@@ -3331,7 +3331,7 @@
         <v>36</v>
       </c>
       <c r="Y11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z11">
         <v>34</v>
@@ -3352,7 +3352,7 @@
         <v>32</v>
       </c>
       <c r="AF11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3367,7 +3367,7 @@
         <v>27</v>
       </c>
       <c r="AK11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL11">
         <v>22</v>
@@ -3379,7 +3379,7 @@
         <v>7.6</v>
       </c>
       <c r="AO11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP11">
         <v>30</v>
@@ -3397,7 +3397,7 @@
         <v>17</v>
       </c>
       <c r="AU11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV11">
         <v>14.5</v>
@@ -3415,7 +3415,7 @@
         <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB11">
         <v>25</v>
@@ -3433,28 +3433,28 @@
         <v>7</v>
       </c>
       <c r="BG11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BI11">
         <v>4.8</v>
       </c>
       <c r="BJ11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL11">
         <v>55</v>
       </c>
       <c r="BM11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BN11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
         <v>5.2</v>
@@ -3463,16 +3463,16 @@
         <v>13</v>
       </c>
       <c r="BQ11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR11">
         <v>19</v>
       </c>
       <c r="BS11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU11">
         <v>6.8</v>
@@ -3481,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX11">
         <v>25</v>
@@ -3490,7 +3490,7 @@
         <v>7</v>
       </c>
       <c r="BZ11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA11">
         <v>8.6</v>
@@ -3516,55 +3516,55 @@
         <v>146</v>
       </c>
       <c r="F12">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
       <c r="I12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
         <v>4.6</v>
       </c>
       <c r="K12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O12">
         <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
         <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T12">
         <v>1.82</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W12">
         <v>2.62</v>
@@ -3573,10 +3573,10 @@
         <v>21</v>
       </c>
       <c r="Y12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA12">
         <v>170</v>
@@ -3594,7 +3594,7 @@
         <v>80</v>
       </c>
       <c r="AF12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -3609,7 +3609,7 @@
         <v>15.5</v>
       </c>
       <c r="AK12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -3618,7 +3618,7 @@
         <v>100</v>
       </c>
       <c r="AN12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO12">
         <v>80</v>
@@ -3630,7 +3630,7 @@
         <v>21</v>
       </c>
       <c r="AR12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS12">
         <v>70</v>
@@ -3639,7 +3639,7 @@
         <v>9.4</v>
       </c>
       <c r="AU12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV12">
         <v>21</v>
@@ -3651,7 +3651,7 @@
         <v>9.6</v>
       </c>
       <c r="AY12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12">
         <v>18.5</v>
@@ -3663,16 +3663,16 @@
         <v>14</v>
       </c>
       <c r="BC12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD12">
         <v>28</v>
       </c>
       <c r="BE12">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG12">
         <v>60</v>
@@ -3705,7 +3705,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ12">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR12">
         <v>23</v>
@@ -3729,7 +3729,7 @@
         <v>55</v>
       </c>
       <c r="BY12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ12">
         <v>15.5</v>
@@ -3770,10 +3770,10 @@
         <v>3.15</v>
       </c>
       <c r="J13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.25</v>
@@ -3797,10 +3797,10 @@
         <v>1.83</v>
       </c>
       <c r="S13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T13">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U13">
         <v>3.1</v>
@@ -3812,7 +3812,7 @@
         <v>1.79</v>
       </c>
       <c r="X13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y13">
         <v>23</v>
@@ -3866,13 +3866,13 @@
         <v>15</v>
       </c>
       <c r="AP13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ13">
         <v>20</v>
       </c>
       <c r="AR13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS13">
         <v>46</v>
@@ -3881,7 +3881,7 @@
         <v>17</v>
       </c>
       <c r="AU13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV13">
         <v>13</v>
@@ -3914,7 +3914,7 @@
         <v>38</v>
       </c>
       <c r="BF13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG13">
         <v>13.5</v>
@@ -3935,10 +3935,10 @@
         <v>60</v>
       </c>
       <c r="BM13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO13">
         <v>5.4</v>
@@ -3953,7 +3953,7 @@
         <v>21</v>
       </c>
       <c r="BS13">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT13">
         <v>6.8</v>
@@ -3965,19 +3965,19 @@
         <v>20</v>
       </c>
       <c r="BW13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
         <v>12.5</v>
       </c>
       <c r="CA13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="s">
         <v>162</v>
@@ -4003,7 +4003,7 @@
         <v>2.38</v>
       </c>
       <c r="G14">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H14">
         <v>2.92</v>
@@ -4024,7 +4024,7 @@
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O14">
         <v>1.29</v>
@@ -4051,7 +4051,7 @@
         <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X14">
         <v>16.5</v>
@@ -4063,7 +4063,7 @@
         <v>23</v>
       </c>
       <c r="AA14">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB14">
         <v>12</v>
@@ -4087,7 +4087,7 @@
         <v>17</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
         <v>70</v>
@@ -4099,7 +4099,7 @@
         <v>65</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN14">
         <v>20</v>
@@ -4177,13 +4177,13 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14">
         <v>5.7</v>
       </c>
       <c r="BO14">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BP14">
         <v>19</v>
@@ -4242,7 +4242,7 @@
         <v>149</v>
       </c>
       <c r="F15">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G15">
         <v>2.56</v>
@@ -4251,10 +4251,10 @@
         <v>2.88</v>
       </c>
       <c r="I15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
         <v>4.2</v>
@@ -4290,7 +4290,7 @@
         <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
         <v>1.64</v>
@@ -4323,7 +4323,7 @@
         <v>19</v>
       </c>
       <c r="AG15">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
         <v>16</v>
@@ -4344,7 +4344,7 @@
         <v>320</v>
       </c>
       <c r="AN15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO15">
         <v>23</v>
@@ -4359,7 +4359,7 @@
         <v>19.5</v>
       </c>
       <c r="AS15">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT15">
         <v>10</v>
@@ -4374,7 +4374,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15">
         <v>8.800000000000001</v>
@@ -4395,7 +4395,7 @@
         <v>14.5</v>
       </c>
       <c r="BE15">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF15">
         <v>10.5</v>
@@ -4526,10 +4526,10 @@
         <v>1.76</v>
       </c>
       <c r="T16">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U16">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
         <v>1.08</v>
@@ -4538,10 +4538,10 @@
         <v>3.25</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y16">
-        <v>70</v>
+        <v>390</v>
       </c>
       <c r="Z16">
         <v>1000</v>
@@ -4556,7 +4556,7 @@
         <v>23</v>
       </c>
       <c r="AD16">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -4568,7 +4568,7 @@
         <v>16.5</v>
       </c>
       <c r="AH16">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AI16">
         <v>1000</v>
@@ -4580,7 +4580,7 @@
         <v>19.5</v>
       </c>
       <c r="AL16">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM16">
         <v>1000</v>
@@ -4592,7 +4592,7 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16">
         <v>4.2</v>
@@ -4610,7 +4610,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AW16">
         <v>4.2</v>
@@ -4628,22 +4628,22 @@
         <v>4.2</v>
       </c>
       <c r="BB16">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="BC16">
-        <v>2.26</v>
+        <v>8.6</v>
       </c>
       <c r="BD16">
         <v>16.5</v>
       </c>
       <c r="BE16">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="BF16">
         <v>2.6</v>
       </c>
       <c r="BG16">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4729,19 +4729,19 @@
         <v>2.34</v>
       </c>
       <c r="G17">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H17">
         <v>2.96</v>
       </c>
       <c r="I17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
         <v>3.7</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>1.28</v>
@@ -4777,7 +4777,7 @@
         <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X17">
         <v>24</v>
@@ -4810,13 +4810,13 @@
         <v>13</v>
       </c>
       <c r="AH17">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
         <v>36</v>
       </c>
       <c r="AJ17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK17">
         <v>26</v>
@@ -4828,7 +4828,7 @@
         <v>70</v>
       </c>
       <c r="AN17">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO17">
         <v>25</v>
@@ -4840,7 +4840,7 @@
         <v>13</v>
       </c>
       <c r="AR17">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS17">
         <v>32</v>
@@ -4974,7 +4974,7 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I18">
         <v>1.27</v>
@@ -5010,10 +5010,10 @@
         <v>2.2</v>
       </c>
       <c r="T18">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U18">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V18">
         <v>4.7</v>
@@ -5037,7 +5037,7 @@
         <v>60</v>
       </c>
       <c r="AC18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD18">
         <v>13</v>
@@ -5052,10 +5052,10 @@
         <v>60</v>
       </c>
       <c r="AH18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ18">
         <v>1000</v>
@@ -5067,7 +5067,7 @@
         <v>190</v>
       </c>
       <c r="AM18">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN18">
         <v>330</v>
@@ -5076,7 +5076,7 @@
         <v>3.9</v>
       </c>
       <c r="AP18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ18">
         <v>9.4</v>
@@ -5085,10 +5085,10 @@
         <v>7.2</v>
       </c>
       <c r="AS18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU18">
         <v>14.5</v>
@@ -5100,31 +5100,31 @@
         <v>11</v>
       </c>
       <c r="AX18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ18">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA18">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BB18">
+        <v>10.5</v>
+      </c>
+      <c r="BC18">
         <v>10</v>
       </c>
-      <c r="BC18">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BD18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF18">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BG18">
         <v>3.35</v>
@@ -5222,7 +5222,7 @@
         <v>6.2</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K19">
         <v>3.65</v>
@@ -5231,25 +5231,25 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
-        <v>2.46</v>
+        <v>1.52</v>
       </c>
       <c r="O19">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P19">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Q19">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T19">
         <v>2.06</v>
@@ -5258,19 +5258,19 @@
         <v>1.71</v>
       </c>
       <c r="V19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W19">
         <v>1.94</v>
       </c>
       <c r="X19">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y19">
         <v>15</v>
       </c>
       <c r="Z19">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA19">
         <v>900</v>
@@ -5285,7 +5285,7 @@
         <v>27</v>
       </c>
       <c r="AE19">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF19">
         <v>11</v>
@@ -5294,7 +5294,7 @@
         <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI19">
         <v>140</v>
@@ -5306,10 +5306,10 @@
         <v>27</v>
       </c>
       <c r="AL19">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>22</v>
@@ -5318,58 +5318,58 @@
         <v>190</v>
       </c>
       <c r="AP19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ19">
+        <v>4.9</v>
+      </c>
+      <c r="AR19">
+        <v>6.4</v>
+      </c>
+      <c r="AS19">
+        <v>7.2</v>
+      </c>
+      <c r="AT19">
+        <v>3.65</v>
+      </c>
+      <c r="AU19">
+        <v>3.95</v>
+      </c>
+      <c r="AV19">
+        <v>5.8</v>
+      </c>
+      <c r="AW19">
+        <v>7</v>
+      </c>
+      <c r="AX19">
+        <v>4.4</v>
+      </c>
+      <c r="AY19">
         <v>4.5</v>
       </c>
-      <c r="AR19">
+      <c r="AZ19">
+        <v>5.8</v>
+      </c>
+      <c r="BA19">
+        <v>7</v>
+      </c>
+      <c r="BB19">
         <v>5.7</v>
       </c>
-      <c r="AS19">
-        <v>6.2</v>
-      </c>
-      <c r="AT19">
-        <v>3.4</v>
-      </c>
-      <c r="AU19">
-        <v>3.65</v>
-      </c>
-      <c r="AV19">
-        <v>5.2</v>
-      </c>
-      <c r="AW19">
-        <v>6</v>
-      </c>
-      <c r="AX19">
-        <v>4</v>
-      </c>
-      <c r="AY19">
-        <v>4.1</v>
-      </c>
-      <c r="AZ19">
-        <v>5.3</v>
-      </c>
-      <c r="BA19">
-        <v>6</v>
-      </c>
-      <c r="BB19">
-        <v>5.1</v>
-      </c>
       <c r="BC19">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD19">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE19">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF19">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG19">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5455,13 +5455,13 @@
         <v>2.48</v>
       </c>
       <c r="G20">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H20">
         <v>3</v>
       </c>
       <c r="I20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J20">
         <v>3.55</v>
@@ -5470,7 +5470,7 @@
         <v>3.65</v>
       </c>
       <c r="L20">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M20">
         <v>1.07</v>
@@ -5482,13 +5482,13 @@
         <v>1.33</v>
       </c>
       <c r="P20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q20">
         <v>2.04</v>
       </c>
       <c r="R20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
         <v>3.5</v>
@@ -5497,34 +5497,34 @@
         <v>1.77</v>
       </c>
       <c r="U20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X20">
         <v>13.5</v>
       </c>
       <c r="Y20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA20">
         <v>55</v>
       </c>
       <c r="AB20">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC20">
         <v>8</v>
       </c>
       <c r="AD20">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE20">
         <v>42</v>
@@ -5533,19 +5533,19 @@
         <v>19</v>
       </c>
       <c r="AG20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI20">
         <v>48</v>
       </c>
       <c r="AJ20">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL20">
         <v>46</v>
@@ -5563,7 +5563,7 @@
         <v>12</v>
       </c>
       <c r="AQ20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR20">
         <v>18.5</v>
@@ -5572,10 +5572,10 @@
         <v>44</v>
       </c>
       <c r="AT20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU20">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV20">
         <v>12</v>
@@ -5587,13 +5587,13 @@
         <v>14.5</v>
       </c>
       <c r="AY20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB20">
         <v>32</v>
@@ -5611,7 +5611,7 @@
         <v>20</v>
       </c>
       <c r="BG20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH20">
         <v>3.75</v>
@@ -5697,7 +5697,7 @@
         <v>2.42</v>
       </c>
       <c r="G21">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H21">
         <v>3.7</v>
@@ -5718,7 +5718,7 @@
         <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O21">
         <v>1.59</v>
@@ -5727,7 +5727,7 @@
         <v>1.53</v>
       </c>
       <c r="Q21">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R21">
         <v>1.18</v>
@@ -5745,13 +5745,13 @@
         <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z21">
         <v>25</v>
@@ -5760,13 +5760,13 @@
         <v>90</v>
       </c>
       <c r="AB21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC21">
         <v>6.8</v>
       </c>
       <c r="AD21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE21">
         <v>65</v>
@@ -5781,7 +5781,7 @@
         <v>26</v>
       </c>
       <c r="AI21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ21">
         <v>36</v>
@@ -5799,22 +5799,22 @@
         <v>38</v>
       </c>
       <c r="AO21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP21">
         <v>7.6</v>
       </c>
       <c r="AQ21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS21">
         <v>75</v>
       </c>
       <c r="AT21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU21">
         <v>6.6</v>
@@ -5838,7 +5838,7 @@
         <v>80</v>
       </c>
       <c r="BB21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC21">
         <v>32</v>
@@ -5948,7 +5948,7 @@
         <v>3.35</v>
       </c>
       <c r="J22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K22">
         <v>3.85</v>
@@ -5963,13 +5963,13 @@
         <v>3.6</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P22">
         <v>1.9</v>
       </c>
       <c r="Q22">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R22">
         <v>1.35</v>
@@ -5978,7 +5978,7 @@
         <v>3.25</v>
       </c>
       <c r="T22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U22">
         <v>2.12</v>
@@ -5993,22 +5993,22 @@
         <v>15.5</v>
       </c>
       <c r="Y22">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z22">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA22">
         <v>55</v>
       </c>
       <c r="AB22">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC22">
         <v>9.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE22">
         <v>38</v>
@@ -6017,7 +6017,7 @@
         <v>19.5</v>
       </c>
       <c r="AG22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH22">
         <v>18</v>
@@ -6035,7 +6035,7 @@
         <v>42</v>
       </c>
       <c r="AM22">
-        <v>300</v>
+        <v>580</v>
       </c>
       <c r="AN22">
         <v>25</v>
@@ -6053,10 +6053,10 @@
         <v>18</v>
       </c>
       <c r="AS22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22">
         <v>6.8</v>
@@ -6077,7 +6077,7 @@
         <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB22">
         <v>14.5</v>
@@ -6086,10 +6086,10 @@
         <v>14.5</v>
       </c>
       <c r="BD22">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BE22">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF22">
         <v>18</v>
@@ -6181,13 +6181,13 @@
         <v>1.58</v>
       </c>
       <c r="G23">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H23">
         <v>7.4</v>
       </c>
       <c r="I23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>3.9</v>
@@ -6205,7 +6205,7 @@
         <v>3.05</v>
       </c>
       <c r="O23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
         <v>1.71</v>
@@ -6214,13 +6214,13 @@
         <v>2.22</v>
       </c>
       <c r="R23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
         <v>4.2</v>
       </c>
       <c r="T23">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U23">
         <v>1.7</v>
@@ -6229,13 +6229,13 @@
         <v>1.14</v>
       </c>
       <c r="W23">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z23">
         <v>70</v>
@@ -6247,7 +6247,7 @@
         <v>6.4</v>
       </c>
       <c r="AC23">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD23">
         <v>32</v>
@@ -6277,7 +6277,7 @@
         <v>55</v>
       </c>
       <c r="AM23">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AN23">
         <v>13</v>
@@ -6295,7 +6295,7 @@
         <v>50</v>
       </c>
       <c r="AS23">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AT23">
         <v>5.9</v>
@@ -6304,10 +6304,10 @@
         <v>8.4</v>
       </c>
       <c r="AV23">
+        <v>11</v>
+      </c>
+      <c r="AW23">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AW23">
-        <v>11.5</v>
       </c>
       <c r="AX23">
         <v>7.2</v>
@@ -6319,7 +6319,7 @@
         <v>25</v>
       </c>
       <c r="BA23">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB23">
         <v>13</v>
@@ -6331,13 +6331,13 @@
         <v>42</v>
       </c>
       <c r="BE23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF23">
         <v>10</v>
       </c>
       <c r="BG23">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6423,13 +6423,13 @@
         <v>3.3</v>
       </c>
       <c r="G24">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H24">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J24">
         <v>2.86</v>
@@ -6462,16 +6462,16 @@
         <v>5.4</v>
       </c>
       <c r="T24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U24">
         <v>1.75</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X24">
         <v>8.6</v>
@@ -6480,7 +6480,7 @@
         <v>7.8</v>
       </c>
       <c r="Z24">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA24">
         <v>42</v>
@@ -6492,7 +6492,7 @@
         <v>7.4</v>
       </c>
       <c r="AD24">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE24">
         <v>40</v>
@@ -6501,16 +6501,16 @@
         <v>24</v>
       </c>
       <c r="AG24">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH24">
         <v>24</v>
       </c>
       <c r="AI24">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AJ24">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="AK24">
         <v>440</v>
@@ -6537,7 +6537,7 @@
         <v>12.5</v>
       </c>
       <c r="AS24">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT24">
         <v>8.4</v>
@@ -6549,7 +6549,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AX24">
         <v>19.5</v>
@@ -6561,22 +6561,22 @@
         <v>20</v>
       </c>
       <c r="BA24">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB24">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC24">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD24">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE24">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG24">
         <v>8.6</v>
@@ -6662,10 +6662,10 @@
         <v>159</v>
       </c>
       <c r="F25">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G25">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H25">
         <v>3.15</v>
@@ -6677,13 +6677,13 @@
         <v>2.8</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N25">
         <v>2.84</v>
@@ -6695,13 +6695,13 @@
         <v>1.61</v>
       </c>
       <c r="Q25">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R25">
         <v>1.17</v>
       </c>
       <c r="S25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T25">
         <v>1.95</v>
@@ -6716,7 +6716,7 @@
         <v>1.58</v>
       </c>
       <c r="X25">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y25">
         <v>12.5</v>
@@ -6725,10 +6725,10 @@
         <v>26</v>
       </c>
       <c r="AA25">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB25">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>7.4</v>
@@ -6737,10 +6737,10 @@
         <v>17</v>
       </c>
       <c r="AE25">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AF25">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG25">
         <v>14</v>
@@ -6749,7 +6749,7 @@
         <v>24</v>
       </c>
       <c r="AI25">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AJ25">
         <v>44</v>
@@ -6761,7 +6761,7 @@
         <v>65</v>
       </c>
       <c r="AM25">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN25">
         <v>38</v>
@@ -6779,7 +6779,7 @@
         <v>17</v>
       </c>
       <c r="AS25">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT25">
         <v>7.6</v>
@@ -6791,19 +6791,19 @@
         <v>11</v>
       </c>
       <c r="AW25">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX25">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY25">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25">
         <v>10.5</v>
       </c>
       <c r="BA25">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB25">
         <v>16</v>
@@ -6812,10 +6812,10 @@
         <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE25">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF25">
         <v>6.2</v>
@@ -6824,64 +6824,64 @@
         <v>8.4</v>
       </c>
       <c r="BH25">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>162</v>
@@ -6910,49 +6910,49 @@
         <v>1.63</v>
       </c>
       <c r="H26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I26">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K26">
         <v>4.3</v>
       </c>
       <c r="L26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O26">
         <v>1.31</v>
       </c>
       <c r="P26">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q26">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S26">
         <v>3.3</v>
       </c>
       <c r="T26">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U26">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V26">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W26">
         <v>2.58</v>
@@ -6967,7 +6967,7 @@
         <v>60</v>
       </c>
       <c r="AA26">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB26">
         <v>8.800000000000001</v>
@@ -6979,40 +6979,40 @@
         <v>27</v>
       </c>
       <c r="AE26">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF26">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH26">
         <v>23</v>
       </c>
       <c r="AI26">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AJ26">
         <v>15.5</v>
       </c>
       <c r="AK26">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL26">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM26">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AN26">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO26">
-        <v>530</v>
+        <v>150</v>
       </c>
       <c r="AP26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ26">
         <v>18</v>
@@ -7021,52 +7021,52 @@
         <v>20</v>
       </c>
       <c r="AS26">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW26">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AX26">
         <v>8</v>
       </c>
       <c r="AY26">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26">
         <v>19</v>
       </c>
       <c r="BA26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC26">
         <v>15.5</v>
       </c>
       <c r="BD26">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG26">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BH26">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI26">
         <v>2.92</v>
@@ -7075,49 +7075,49 @@
         <v>11.5</v>
       </c>
       <c r="BK26">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>2.72</v>
+        <v>13</v>
       </c>
       <c r="BN26">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO26">
         <v>3.2</v>
       </c>
       <c r="BP26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ26">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR26">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS26">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT26">
         <v>11</v>
       </c>
       <c r="BU26">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7146,70 +7146,70 @@
         <v>161</v>
       </c>
       <c r="F27">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="G27">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H27">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I27">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K27">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.07</v>
+      </c>
+      <c r="N27">
+        <v>3.2</v>
+      </c>
+      <c r="O27">
         <v>1.39</v>
       </c>
-      <c r="M27">
-        <v>1.08</v>
-      </c>
-      <c r="N27">
-        <v>3.15</v>
-      </c>
-      <c r="O27">
-        <v>1.38</v>
-      </c>
       <c r="P27">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R27">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S27">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T27">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U27">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="V27">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W27">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="X27">
         <v>13</v>
       </c>
       <c r="Y27">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z27">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA27">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="AB27">
         <v>6.8</v>
@@ -7218,52 +7218,52 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE27">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AF27">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG27">
         <v>11</v>
       </c>
       <c r="AH27">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI27">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK27">
         <v>20</v>
       </c>
       <c r="AL27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM27">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN27">
         <v>12.5</v>
       </c>
       <c r="AO27">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="AP27">
         <v>10.5</v>
       </c>
       <c r="AQ27">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AR27">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS27">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT27">
         <v>5.8</v>
@@ -7272,22 +7272,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV27">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="AW27">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX27">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY27">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA27">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
@@ -7299,13 +7299,13 @@
         <v>38</v>
       </c>
       <c r="BE27">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF27">
         <v>9.199999999999999</v>
       </c>
       <c r="BG27">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH27">
         <v>3.55</v>
@@ -7314,58 +7314,58 @@
         <v>2.66</v>
       </c>
       <c r="BJ27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BN27">
         <v>4.2</v>
       </c>
       <c r="BO27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP27">
         <v>12</v>
       </c>
       <c r="BQ27">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BR27">
         <v>36</v>
       </c>
       <c r="BS27">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BU27">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BW27">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BX27">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BY27">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BZ27">
         <v>27</v>
       </c>
       <c r="CA27">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="CB27" t="s">
         <v>162</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -406,7 +406,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-20 02:18:11</t>
+    <t>2026-08-20 04:31:36</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
         <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H2">
         <v>2.92</v>
@@ -1015,13 +1015,13 @@
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -1030,7 +1030,7 @@
         <v>1.29</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
         <v>1.87</v>
@@ -1039,7 +1039,7 @@
         <v>1.41</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
         <v>1.68</v>
@@ -1051,7 +1051,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X2">
         <v>16.5</v>
@@ -1063,7 +1063,7 @@
         <v>23</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB2">
         <v>12</v>
@@ -1075,7 +1075,7 @@
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AF2">
         <v>17.5</v>
@@ -1090,13 +1090,13 @@
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK2">
         <v>28</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM2">
         <v>580</v>
@@ -1105,31 +1105,31 @@
         <v>20</v>
       </c>
       <c r="AO2">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AP2">
         <v>6.2</v>
       </c>
       <c r="AQ2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
         <v>7</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
         <v>5.4</v>
       </c>
       <c r="AU2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
         <v>6.4</v>
@@ -1138,13 +1138,13 @@
         <v>5.5</v>
       </c>
       <c r="AZ2">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC2">
         <v>7.2</v>
@@ -1159,19 +1159,19 @@
         <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH2">
         <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2">
         <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1183,10 +1183,10 @@
         <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
         <v>6.6</v>
@@ -1201,7 +1201,7 @@
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1216,10 +1216,10 @@
         <v>8</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="s">
         <v>130</v>
@@ -1242,16 +1242,16 @@
         <v>117</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1263,7 +1263,7 @@
         <v>1.34</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
         <v>4.9</v>
@@ -1287,13 +1287,13 @@
         <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
         <v>22</v>
@@ -1302,10 +1302,10 @@
         <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="AB3">
         <v>14.5</v>
@@ -1314,10 +1314,10 @@
         <v>9.4</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AF3">
         <v>18.5</v>
@@ -1329,16 +1329,16 @@
         <v>16</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK3">
         <v>25</v>
       </c>
       <c r="AL3">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM3">
         <v>200</v>
@@ -1347,10 +1347,10 @@
         <v>15.5</v>
       </c>
       <c r="AO3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
         <v>12</v>
@@ -1359,7 +1359,7 @@
         <v>19.5</v>
       </c>
       <c r="AS3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="AT3">
         <v>11.5</v>
@@ -1371,7 +1371,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
         <v>15</v>
@@ -1383,19 +1383,19 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BC3">
         <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
@@ -1413,13 +1413,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
         <v>5.8</v>
@@ -1428,19 +1428,19 @@
         <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
         <v>4.9</v>
@@ -1455,13 +1455,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
         <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="s">
         <v>130</v>
@@ -1487,10 +1487,10 @@
         <v>1.31</v>
       </c>
       <c r="G4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
         <v>10.5</v>
@@ -1505,31 +1505,31 @@
         <v>1.21</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R4">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S4">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="T4">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
         <v>1.1</v>
@@ -1556,7 +1556,7 @@
         <v>17</v>
       </c>
       <c r="AD4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE4">
         <v>130</v>
@@ -1592,7 +1592,7 @@
         <v>110</v>
       </c>
       <c r="AP4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ4">
         <v>40</v>
@@ -1601,7 +1601,7 @@
         <v>9.4</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4">
         <v>13</v>
@@ -1610,7 +1610,7 @@
         <v>14</v>
       </c>
       <c r="AV4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW4">
         <v>65</v>
@@ -1634,7 +1634,7 @@
         <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BE4">
         <v>50</v>
@@ -1655,7 +1655,7 @@
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BL4">
         <v>100</v>
@@ -1664,7 +1664,7 @@
         <v>4.4</v>
       </c>
       <c r="BN4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO4">
         <v>3.45</v>
@@ -1688,10 +1688,10 @@
         <v>3.6</v>
       </c>
       <c r="BV4">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BW4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX4">
         <v>60</v>
@@ -1741,7 +1741,7 @@
         <v>3.7</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
         <v>1.33</v>
@@ -1750,7 +1750,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
         <v>1.24</v>
@@ -1759,19 +1759,19 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U5">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
         <v>1.47</v>
@@ -1810,7 +1810,7 @@
         <v>12</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5">
         <v>40</v>
@@ -1828,13 +1828,13 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
         <v>13</v>
@@ -1867,7 +1867,7 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB5">
         <v>23</v>
@@ -1891,19 +1891,19 @@
         <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5">
         <v>9.199999999999999</v>
       </c>
       <c r="BK5">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN5">
         <v>5.8</v>
@@ -1915,13 +1915,13 @@
         <v>18</v>
       </c>
       <c r="BQ5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR5">
         <v>28</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
         <v>6.6</v>
@@ -1933,16 +1933,16 @@
         <v>23</v>
       </c>
       <c r="BW5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX5">
         <v>32</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA5">
         <v>6</v>
@@ -1974,7 +1974,7 @@
         <v>16</v>
       </c>
       <c r="H6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I6">
         <v>1.29</v>
@@ -1983,34 +1983,34 @@
         <v>6.6</v>
       </c>
       <c r="K6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R6">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
         <v>1.81</v>
@@ -2022,13 +2022,13 @@
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -2040,7 +2040,7 @@
         <v>16.5</v>
       </c>
       <c r="AD6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE6">
         <v>13.5</v>
@@ -2073,10 +2073,10 @@
         <v>320</v>
       </c>
       <c r="AO6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AP6">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6">
         <v>9</v>
@@ -2085,10 +2085,10 @@
         <v>7</v>
       </c>
       <c r="AS6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU6">
         <v>13.5</v>
@@ -2100,94 +2100,94 @@
         <v>11.5</v>
       </c>
       <c r="AX6">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA6">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BD6">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BE6">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BG6">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BH6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI6">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BJ6">
         <v>13</v>
       </c>
       <c r="BK6">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6">
         <v>16</v>
       </c>
       <c r="BO6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BP6">
         <v>120</v>
       </c>
       <c r="BQ6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BR6">
         <v>100</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BU6">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BV6">
         <v>7</v>
       </c>
       <c r="BW6">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BX6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
         <v>130</v>
@@ -2210,79 +2210,79 @@
         <v>121</v>
       </c>
       <c r="F7">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="G7">
         <v>1.98</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
         <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
         <v>2.62</v>
       </c>
       <c r="O7">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q7">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X7">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE7">
         <v>260</v>
@@ -2297,88 +2297,88 @@
         <v>28</v>
       </c>
       <c r="AI7">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
+        <v>22</v>
+      </c>
+      <c r="AO7">
+        <v>600</v>
+      </c>
+      <c r="AP7">
+        <v>7.8</v>
+      </c>
+      <c r="AQ7">
+        <v>11.5</v>
+      </c>
+      <c r="AR7">
+        <v>7.2</v>
+      </c>
+      <c r="AS7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT7">
+        <v>5.5</v>
+      </c>
+      <c r="AU7">
+        <v>6.6</v>
+      </c>
+      <c r="AV7">
+        <v>19</v>
+      </c>
+      <c r="AW7">
+        <v>8</v>
+      </c>
+      <c r="AX7">
+        <v>8.4</v>
+      </c>
+      <c r="AY7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7">
         <v>21</v>
       </c>
-      <c r="AO7">
-        <v>700</v>
-      </c>
-      <c r="AP7">
-        <v>4.3</v>
-      </c>
-      <c r="AQ7">
-        <v>4.9</v>
-      </c>
-      <c r="AR7">
-        <v>6</v>
-      </c>
-      <c r="AS7">
-        <v>6.8</v>
-      </c>
-      <c r="AT7">
-        <v>3.5</v>
-      </c>
-      <c r="AU7">
-        <v>3.9</v>
-      </c>
-      <c r="AV7">
-        <v>5.6</v>
-      </c>
-      <c r="AW7">
-        <v>6.6</v>
-      </c>
-      <c r="AX7">
-        <v>4.2</v>
-      </c>
-      <c r="AY7">
-        <v>4.3</v>
-      </c>
-      <c r="AZ7">
-        <v>5.6</v>
-      </c>
       <c r="BA7">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BC7">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
         <v>1.04</v>
@@ -2390,31 +2390,31 @@
         <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7">
         <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7">
         <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU7">
         <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW7">
         <v>1.04</v>
@@ -2426,7 +2426,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA7">
         <v>1.04</v>
@@ -2455,10 +2455,10 @@
         <v>2.56</v>
       </c>
       <c r="G8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H8">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I8">
         <v>3.05</v>
@@ -2470,7 +2470,7 @@
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2479,25 +2479,25 @@
         <v>3.8</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
         <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
         <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V8">
         <v>1.48</v>
@@ -2512,16 +2512,16 @@
         <v>12</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA8">
         <v>55</v>
       </c>
       <c r="AB8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>13</v>
@@ -2539,19 +2539,19 @@
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK8">
         <v>27</v>
       </c>
       <c r="AL8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2569,7 +2569,7 @@
         <v>18.5</v>
       </c>
       <c r="AS8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT8">
         <v>10</v>
@@ -2599,7 +2599,7 @@
         <v>34</v>
       </c>
       <c r="BC8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD8">
         <v>34</v>
@@ -2608,70 +2608,70 @@
         <v>50</v>
       </c>
       <c r="BF8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BI8">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BN8">
         <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP8">
         <v>23</v>
       </c>
       <c r="BQ8">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS8">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BT8">
         <v>7</v>
       </c>
       <c r="BU8">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW8">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX8">
         <v>42</v>
       </c>
       <c r="BY8">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA8">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="s">
         <v>130</v>
@@ -2706,40 +2706,40 @@
         <v>3.8</v>
       </c>
       <c r="J9">
+        <v>3.05</v>
+      </c>
+      <c r="K9">
         <v>3.1</v>
       </c>
-      <c r="K9">
-        <v>3.15</v>
-      </c>
       <c r="L9">
+        <v>1.59</v>
+      </c>
+      <c r="M9">
+        <v>1.12</v>
+      </c>
+      <c r="N9">
+        <v>2.96</v>
+      </c>
+      <c r="O9">
+        <v>1.5</v>
+      </c>
+      <c r="P9">
         <v>1.63</v>
       </c>
-      <c r="M9">
-        <v>1.13</v>
-      </c>
-      <c r="N9">
-        <v>2.74</v>
-      </c>
-      <c r="O9">
-        <v>1.56</v>
-      </c>
-      <c r="P9">
-        <v>1.57</v>
-      </c>
       <c r="Q9">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="R9">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S9">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="T9">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U9">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V9">
         <v>1.35</v>
@@ -2748,19 +2748,19 @@
         <v>1.69</v>
       </c>
       <c r="X9">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z9">
         <v>24</v>
       </c>
       <c r="AA9">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9">
         <v>6.8</v>
@@ -2772,49 +2772,49 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI9">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ9">
         <v>34</v>
       </c>
       <c r="AK9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM9">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS9">
         <v>70</v>
       </c>
       <c r="AT9">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU9">
         <v>6.6</v>
@@ -2826,94 +2826,94 @@
         <v>50</v>
       </c>
       <c r="AX9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
         <v>11.5</v>
       </c>
       <c r="AZ9">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BB9">
         <v>30</v>
       </c>
       <c r="BC9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BG9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH9">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="BI9">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="BM9">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
         <v>4.9</v>
       </c>
       <c r="BO9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP9">
         <v>21</v>
       </c>
       <c r="BQ9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT9">
         <v>6.8</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
+        <v>30</v>
+      </c>
+      <c r="BX9">
+        <v>65</v>
+      </c>
+      <c r="BY9">
+        <v>14</v>
+      </c>
+      <c r="BZ9">
+        <v>50</v>
+      </c>
+      <c r="CA9">
         <v>13</v>
-      </c>
-      <c r="BX9">
-        <v>70</v>
-      </c>
-      <c r="BY9">
-        <v>15</v>
-      </c>
-      <c r="BZ9">
-        <v>55</v>
-      </c>
-      <c r="CA9">
-        <v>38</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2945,13 +2945,13 @@
         <v>2.9</v>
       </c>
       <c r="I10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
         <v>1.4</v>
@@ -2975,16 +2975,16 @@
         <v>1.36</v>
       </c>
       <c r="S10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
         <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
         <v>1.6</v>
@@ -3035,7 +3035,7 @@
         <v>42</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN10">
         <v>25</v>
@@ -3044,7 +3044,7 @@
         <v>34</v>
       </c>
       <c r="AP10">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10">
         <v>10.5</v>
@@ -3098,64 +3098,64 @@
         <v>6.8</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="s">
         <v>130</v>
@@ -3178,19 +3178,19 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G11">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I11">
         <v>8</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
         <v>4.1</v>
@@ -3202,28 +3202,28 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
         <v>1.28</v>
       </c>
       <c r="S11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U11">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3244,13 +3244,13 @@
         <v>290</v>
       </c>
       <c r="AB11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE11">
         <v>150</v>
@@ -3268,7 +3268,7 @@
         <v>150</v>
       </c>
       <c r="AJ11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK11">
         <v>19.5</v>
@@ -3280,22 +3280,22 @@
         <v>700</v>
       </c>
       <c r="AN11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO11">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP11">
         <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR11">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AS11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AT11">
         <v>5.9</v>
@@ -3307,7 +3307,7 @@
         <v>25</v>
       </c>
       <c r="AW11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AX11">
         <v>7.2</v>
@@ -3319,7 +3319,7 @@
         <v>25</v>
       </c>
       <c r="BA11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BB11">
         <v>13</v>
@@ -3328,76 +3328,76 @@
         <v>17</v>
       </c>
       <c r="BD11">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BE11">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="s">
         <v>130</v>
@@ -3420,22 +3420,22 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G12">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="H12">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="I12">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="J12">
         <v>2.92</v>
       </c>
       <c r="K12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L12">
         <v>1.59</v>
@@ -3444,7 +3444,7 @@
         <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
         <v>1.56</v>
@@ -3453,13 +3453,13 @@
         <v>1.53</v>
       </c>
       <c r="Q12">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T12">
         <v>2.08</v>
@@ -3468,25 +3468,25 @@
         <v>1.75</v>
       </c>
       <c r="V12">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W12">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X12">
         <v>8.6</v>
       </c>
       <c r="Y12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA12">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC12">
         <v>7.4</v>
@@ -3495,10 +3495,10 @@
         <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AF12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG12">
         <v>16.5</v>
@@ -3507,16 +3507,16 @@
         <v>24</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ12">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="AK12">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="AL12">
-        <v>540</v>
+        <v>95</v>
       </c>
       <c r="AM12">
         <v>500</v>
@@ -3525,121 +3525,121 @@
         <v>180</v>
       </c>
       <c r="AO12">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP12">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR12">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="AT12">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU12">
         <v>6</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX12">
+        <v>17.5</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
         <v>19.5</v>
-      </c>
-      <c r="AY12">
-        <v>13.5</v>
-      </c>
-      <c r="AZ12">
-        <v>20</v>
       </c>
       <c r="BA12">
         <v>9</v>
       </c>
       <c r="BB12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD12">
         <v>9.199999999999999</v>
       </c>
       <c r="BE12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12">
         <v>9.800000000000001</v>
       </c>
       <c r="BG12">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BH12">
         <v>2.72</v>
       </c>
       <c r="BI12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12">
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ12">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BU12">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB12" t="s">
         <v>130</v>
@@ -3662,7 +3662,7 @@
         <v>127</v>
       </c>
       <c r="F13">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G13">
         <v>2.62</v>
@@ -3680,19 +3680,19 @@
         <v>3.3</v>
       </c>
       <c r="L13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M13">
         <v>1.11</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O13">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P13">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q13">
         <v>2.44</v>
@@ -3701,7 +3701,7 @@
         <v>1.24</v>
       </c>
       <c r="S13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T13">
         <v>1.99</v>
@@ -3710,7 +3710,7 @@
         <v>1.92</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.61</v>
@@ -3719,10 +3719,10 @@
         <v>10.5</v>
       </c>
       <c r="Y13">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA13">
         <v>160</v>
@@ -3731,7 +3731,7 @@
         <v>9.4</v>
       </c>
       <c r="AC13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD13">
         <v>16.5</v>
@@ -3740,7 +3740,7 @@
         <v>55</v>
       </c>
       <c r="AF13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG13">
         <v>13.5</v>
@@ -3791,7 +3791,7 @@
         <v>11</v>
       </c>
       <c r="AW13">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3803,85 +3803,85 @@
         <v>10.5</v>
       </c>
       <c r="BA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC13">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD13">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE13">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF13">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="BG13">
         <v>42</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB13" t="s">
         <v>130</v>
@@ -3913,7 +3913,7 @@
         <v>6.4</v>
       </c>
       <c r="I14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>4.1</v>
@@ -3943,16 +3943,16 @@
         <v>1.37</v>
       </c>
       <c r="S14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T14">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U14">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W14">
         <v>2.58</v>
@@ -3961,25 +3961,25 @@
         <v>15</v>
       </c>
       <c r="Y14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA14">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE14">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF14">
         <v>9.199999999999999</v>
@@ -3988,13 +3988,13 @@
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI14">
         <v>110</v>
       </c>
       <c r="AJ14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK14">
         <v>18.5</v>
@@ -4009,7 +4009,7 @@
         <v>9.6</v>
       </c>
       <c r="AO14">
-        <v>140</v>
+        <v>530</v>
       </c>
       <c r="AP14">
         <v>12.5</v>
@@ -4021,10 +4021,10 @@
         <v>20</v>
       </c>
       <c r="AS14">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU14">
         <v>7.8</v>
@@ -4033,10 +4033,10 @@
         <v>22</v>
       </c>
       <c r="AW14">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AX14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY14">
         <v>9.4</v>
@@ -4045,10 +4045,10 @@
         <v>20</v>
       </c>
       <c r="BA14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC14">
         <v>15.5</v>
@@ -4057,31 +4057,31 @@
         <v>24</v>
       </c>
       <c r="BE14">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF14">
         <v>8.4</v>
       </c>
       <c r="BG14">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BH14">
         <v>3.6</v>
       </c>
       <c r="BI14">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN14">
         <v>4.1</v>
@@ -4093,31 +4093,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ14">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR14">
         <v>27</v>
       </c>
       <c r="BS14">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>1.59</v>
       </c>
       <c r="G15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H15">
         <v>7.4</v>
@@ -4158,7 +4158,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K15">
         <v>4.2</v>
@@ -4173,7 +4173,7 @@
         <v>3.35</v>
       </c>
       <c r="O15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P15">
         <v>1.8</v>
@@ -4197,7 +4197,7 @@
         <v>1.14</v>
       </c>
       <c r="W15">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="X15">
         <v>13</v>
@@ -4266,7 +4266,7 @@
         <v>9.4</v>
       </c>
       <c r="AT15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU15">
         <v>8.199999999999999</v>
@@ -4296,7 +4296,7 @@
         <v>16</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15">
         <v>9.4</v>
@@ -4314,58 +4314,58 @@
         <v>2.66</v>
       </c>
       <c r="BJ15">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN15">
         <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BP15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ15">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS15">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BT15">
         <v>12</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV15">
         <v>90</v>
       </c>
       <c r="BW15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BX15">
         <v>95</v>
       </c>
       <c r="BY15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BZ15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CA15">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="s">
         <v>130</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -406,7 +406,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-20 04:31:36</t>
+    <t>2026-08-20 06:41:59</t>
   </si>
 </sst>
 </file>
@@ -1009,46 +1009,46 @@
         <v>2.92</v>
       </c>
       <c r="I2">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O2">
         <v>1.29</v>
       </c>
       <c r="P2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2">
         <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U2">
         <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
         <v>1.62</v>
@@ -1114,7 +1114,7 @@
         <v>5.8</v>
       </c>
       <c r="AR2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS2">
         <v>8.4</v>
@@ -1132,16 +1132,16 @@
         <v>7.8</v>
       </c>
       <c r="AX2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY2">
         <v>5.5</v>
       </c>
       <c r="AZ2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB2">
         <v>7.8</v>
@@ -1159,7 +1159,7 @@
         <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH2">
         <v>3.7</v>
@@ -1248,10 +1248,10 @@
         <v>2.58</v>
       </c>
       <c r="H3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1272,7 +1272,7 @@
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
         <v>1.69</v>
@@ -1287,19 +1287,19 @@
         <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
         <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X3">
         <v>22</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3">
         <v>65</v>
@@ -1311,7 +1311,7 @@
         <v>14.5</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
         <v>14</v>
@@ -1344,13 +1344,13 @@
         <v>200</v>
       </c>
       <c r="AN3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
         <v>12</v>
@@ -1359,13 +1359,13 @@
         <v>19.5</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>11.5</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>10.5</v>
@@ -1395,7 +1395,7 @@
         <v>14.5</v>
       </c>
       <c r="BE3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
@@ -1404,28 +1404,28 @@
         <v>17.5</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
         <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>5.8</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
         <v>17.5</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1449,19 +1449,19 @@
         <v>22</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
         <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>130</v>
@@ -1487,7 +1487,7 @@
         <v>1.31</v>
       </c>
       <c r="G4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H4">
         <v>9.199999999999999</v>
@@ -1496,10 +1496,10 @@
         <v>10.5</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L4">
         <v>1.21</v>
@@ -1514,13 +1514,13 @@
         <v>1.12</v>
       </c>
       <c r="P4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q4">
         <v>1.36</v>
       </c>
       <c r="R4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <v>1.9</v>
@@ -1535,7 +1535,7 @@
         <v>1.1</v>
       </c>
       <c r="W4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X4">
         <v>55</v>
@@ -1583,7 +1583,7 @@
         <v>27</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN4">
         <v>3.6</v>
@@ -1592,16 +1592,16 @@
         <v>110</v>
       </c>
       <c r="AP4">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AQ4">
         <v>40</v>
       </c>
       <c r="AR4">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="AS4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
         <v>13</v>
@@ -1613,7 +1613,7 @@
         <v>30</v>
       </c>
       <c r="AW4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1634,13 +1634,13 @@
         <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE4">
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG4">
         <v>50</v>
@@ -1655,22 +1655,22 @@
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BL4">
         <v>100</v>
       </c>
       <c r="BM4">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BN4">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ4">
         <v>5.6</v>
@@ -1679,25 +1679,25 @@
         <v>21</v>
       </c>
       <c r="BS4">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BT4">
         <v>16</v>
       </c>
       <c r="BU4">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BV4">
         <v>65</v>
       </c>
       <c r="BW4">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
         <v>3.7</v>
@@ -1759,19 +1759,19 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
         <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
         <v>1.47</v>
@@ -1834,7 +1834,7 @@
         <v>24</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
         <v>13</v>
@@ -1879,7 +1879,7 @@
         <v>25</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -1968,70 +1968,70 @@
         <v>120</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
+        <v>1.24</v>
+      </c>
+      <c r="I6">
         <v>1.26</v>
       </c>
-      <c r="I6">
-        <v>1.29</v>
-      </c>
       <c r="J6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K6">
+        <v>7.6</v>
+      </c>
+      <c r="L6">
+        <v>1.3</v>
+      </c>
+      <c r="M6">
+        <v>1.04</v>
+      </c>
+      <c r="N6">
+        <v>5.5</v>
+      </c>
+      <c r="O6">
+        <v>1.2</v>
+      </c>
+      <c r="P6">
+        <v>2.52</v>
+      </c>
+      <c r="Q6">
+        <v>1.62</v>
+      </c>
+      <c r="R6">
+        <v>1.6</v>
+      </c>
+      <c r="S6">
+        <v>2.56</v>
+      </c>
+      <c r="T6">
+        <v>2.26</v>
+      </c>
+      <c r="U6">
+        <v>1.72</v>
+      </c>
+      <c r="V6">
+        <v>4.8</v>
+      </c>
+      <c r="W6">
+        <v>1.06</v>
+      </c>
+      <c r="X6">
+        <v>27</v>
+      </c>
+      <c r="Y6">
+        <v>9.6</v>
+      </c>
+      <c r="Z6">
         <v>7.8</v>
       </c>
-      <c r="L6">
-        <v>1.29</v>
-      </c>
-      <c r="M6">
-        <v>1.03</v>
-      </c>
-      <c r="N6">
-        <v>6</v>
-      </c>
-      <c r="O6">
-        <v>1.18</v>
-      </c>
-      <c r="P6">
-        <v>2.62</v>
-      </c>
-      <c r="Q6">
-        <v>1.58</v>
-      </c>
-      <c r="R6">
-        <v>1.66</v>
-      </c>
-      <c r="S6">
-        <v>2.44</v>
-      </c>
-      <c r="T6">
-        <v>2.08</v>
-      </c>
-      <c r="U6">
-        <v>1.81</v>
-      </c>
-      <c r="V6">
-        <v>4.4</v>
-      </c>
-      <c r="W6">
-        <v>1.07</v>
-      </c>
-      <c r="X6">
-        <v>36</v>
-      </c>
-      <c r="Y6">
-        <v>11</v>
-      </c>
-      <c r="Z6">
-        <v>8</v>
-      </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AB6">
         <v>55</v>
@@ -2040,61 +2040,61 @@
         <v>16.5</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AF6">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AG6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="AL6">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AN6">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="AO6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AP6">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6">
         <v>8.4</v>
       </c>
-      <c r="AQ6">
-        <v>9</v>
-      </c>
       <c r="AR6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AU6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
         <v>11.5</v>
@@ -2103,91 +2103,91 @@
         <v>10</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AZ6">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BA6">
+        <v>27</v>
+      </c>
+      <c r="BB6">
+        <v>10.5</v>
+      </c>
+      <c r="BC6">
+        <v>10</v>
+      </c>
+      <c r="BD6">
+        <v>10</v>
+      </c>
+      <c r="BE6">
+        <v>10</v>
+      </c>
+      <c r="BF6">
+        <v>10</v>
+      </c>
+      <c r="BG6">
+        <v>3.85</v>
+      </c>
+      <c r="BH6">
+        <v>4.9</v>
+      </c>
+      <c r="BI6">
+        <v>3.95</v>
+      </c>
+      <c r="BJ6">
+        <v>15.5</v>
+      </c>
+      <c r="BK6">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB6">
-        <v>11</v>
-      </c>
-      <c r="BC6">
-        <v>10.5</v>
-      </c>
-      <c r="BD6">
-        <v>10.5</v>
-      </c>
-      <c r="BE6">
-        <v>10.5</v>
-      </c>
-      <c r="BF6">
-        <v>11</v>
-      </c>
-      <c r="BG6">
-        <v>3.7</v>
-      </c>
-      <c r="BH6">
-        <v>5.2</v>
-      </c>
-      <c r="BI6">
-        <v>4.1</v>
-      </c>
-      <c r="BJ6">
-        <v>13</v>
-      </c>
-      <c r="BK6">
-        <v>10</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BO6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BP6">
+        <v>160</v>
+      </c>
+      <c r="BQ6">
+        <v>9</v>
+      </c>
+      <c r="BR6">
         <v>120</v>
       </c>
-      <c r="BQ6">
-        <v>9.6</v>
-      </c>
-      <c r="BR6">
-        <v>100</v>
-      </c>
       <c r="BS6">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BU6">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BV6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BW6">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BX6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY6">
+        <v>6.8</v>
+      </c>
+      <c r="BZ6">
+        <v>10.5</v>
+      </c>
+      <c r="CA6">
         <v>7.2</v>
-      </c>
-      <c r="BZ6">
-        <v>10</v>
-      </c>
-      <c r="CA6">
-        <v>8</v>
       </c>
       <c r="CB6" t="s">
         <v>130</v>
@@ -2210,22 +2210,22 @@
         <v>121</v>
       </c>
       <c r="F7">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="G7">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
         <v>1.54</v>
@@ -2234,103 +2234,103 @@
         <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="O7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P7">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T7">
+        <v>2.2</v>
+      </c>
+      <c r="U7">
+        <v>1.67</v>
+      </c>
+      <c r="V7">
+        <v>1.16</v>
+      </c>
+      <c r="W7">
         <v>2.16</v>
       </c>
-      <c r="U7">
-        <v>1.68</v>
-      </c>
-      <c r="V7">
-        <v>1.2</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
-      </c>
       <c r="X7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC7">
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE7">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AF7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>500</v>
       </c>
       <c r="AJ7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AK7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL7">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>270</v>
       </c>
       <c r="AP7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7">
         <v>11.5</v>
       </c>
       <c r="AR7">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
@@ -2339,10 +2339,10 @@
         <v>19</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
         <v>9.199999999999999</v>
@@ -2351,85 +2351,85 @@
         <v>21</v>
       </c>
       <c r="BA7">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD7">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE7">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH7">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP7">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV7">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="s">
         <v>130</v>
@@ -2452,19 +2452,19 @@
         <v>122</v>
       </c>
       <c r="F8">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="G8">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="H8">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="I8">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>3.65</v>
@@ -2482,136 +2482,136 @@
         <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q8">
         <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
         <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="X8">
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA8">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS8">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU8">
         <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD8">
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BF8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BG8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BH8">
         <v>3.35</v>
@@ -2623,55 +2623,55 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM8">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BN8">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BR8">
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BT8">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BU8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BW8">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BX8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY8">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA8">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="CB8" t="s">
         <v>130</v>
@@ -2694,25 +2694,25 @@
         <v>123</v>
       </c>
       <c r="F9">
+        <v>2.4</v>
+      </c>
+      <c r="G9">
         <v>2.42</v>
       </c>
-      <c r="G9">
-        <v>2.44</v>
-      </c>
       <c r="H9">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I9">
         <v>3.8</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M9">
         <v>1.12</v>
@@ -2724,10 +2724,10 @@
         <v>1.5</v>
       </c>
       <c r="P9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q9">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R9">
         <v>1.22</v>
@@ -2739,40 +2739,40 @@
         <v>2.08</v>
       </c>
       <c r="U9">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V9">
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y9">
         <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA9">
         <v>80</v>
       </c>
       <c r="AB9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>6.8</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
         <v>12</v>
@@ -2793,7 +2793,7 @@
         <v>60</v>
       </c>
       <c r="AM9">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN9">
         <v>32</v>
@@ -2802,7 +2802,7 @@
         <v>80</v>
       </c>
       <c r="AP9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>7.6</v>
       </c>
       <c r="AU9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
         <v>15</v>
@@ -2826,7 +2826,7 @@
         <v>50</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY9">
         <v>11.5</v>
@@ -2835,7 +2835,7 @@
         <v>20</v>
       </c>
       <c r="BA9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB9">
         <v>30</v>
@@ -2844,10 +2844,10 @@
         <v>28</v>
       </c>
       <c r="BD9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE9">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="BF9">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>2.76</v>
       </c>
       <c r="BI9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9">
         <v>11</v>
@@ -2871,34 +2871,34 @@
         <v>220</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN9">
         <v>4.9</v>
       </c>
       <c r="BO9">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ9">
         <v>17.5</v>
       </c>
       <c r="BR9">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BT9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU9">
         <v>6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW9">
         <v>30</v>
@@ -2907,13 +2907,13 @@
         <v>65</v>
       </c>
       <c r="BY9">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BZ9">
         <v>50</v>
       </c>
       <c r="CA9">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="CB9" t="s">
         <v>130</v>
@@ -2936,7 +2936,7 @@
         <v>124</v>
       </c>
       <c r="F10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G10">
         <v>2.66</v>
@@ -2951,7 +2951,7 @@
         <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
         <v>1.4</v>
@@ -2966,7 +2966,7 @@
         <v>1.31</v>
       </c>
       <c r="P10">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q10">
         <v>1.94</v>
@@ -3008,10 +3008,10 @@
         <v>8.4</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF10">
         <v>17.5</v>
@@ -3020,10 +3020,10 @@
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI10">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AJ10">
         <v>38</v>
@@ -3032,16 +3032,16 @@
         <v>29</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM10">
         <v>200</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP10">
         <v>12.5</v>
@@ -3053,19 +3053,19 @@
         <v>18</v>
       </c>
       <c r="AS10">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV10">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="AX10">
         <v>14</v>
@@ -3077,25 +3077,25 @@
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BB10">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC10">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BD10">
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="BF10">
         <v>18</v>
       </c>
       <c r="BG10">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BH10">
         <v>3.55</v>
@@ -3178,16 +3178,16 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>3.95</v>
@@ -3202,7 +3202,7 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
         <v>1.4</v>
@@ -3211,22 +3211,22 @@
         <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R11">
         <v>1.28</v>
       </c>
       <c r="S11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T11">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W11">
         <v>2.6</v>
@@ -3235,52 +3235,52 @@
         <v>12</v>
       </c>
       <c r="Y11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z11">
         <v>65</v>
       </c>
       <c r="AA11">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AB11">
         <v>6.8</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL11">
         <v>50</v>
       </c>
       <c r="AM11">
-        <v>700</v>
+        <v>210</v>
       </c>
       <c r="AN11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO11">
         <v>230</v>
@@ -3289,16 +3289,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AS11">
         <v>13.5</v>
       </c>
       <c r="AT11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU11">
         <v>8.4</v>
@@ -3310,10 +3310,10 @@
         <v>13.5</v>
       </c>
       <c r="AX11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
         <v>25</v>
@@ -3328,34 +3328,34 @@
         <v>17</v>
       </c>
       <c r="BD11">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE11">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF11">
         <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI11">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11">
         <v>13</v>
       </c>
       <c r="BK11">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN11">
         <v>3.95</v>
@@ -3367,37 +3367,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ11">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR11">
         <v>34</v>
       </c>
       <c r="BS11">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU11">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>26</v>
       </c>
       <c r="CA11">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="s">
         <v>130</v>
@@ -3420,22 +3420,22 @@
         <v>126</v>
       </c>
       <c r="F12">
+        <v>2.88</v>
+      </c>
+      <c r="G12">
         <v>3.15</v>
       </c>
-      <c r="G12">
-        <v>3.55</v>
-      </c>
       <c r="H12">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="I12">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L12">
         <v>1.59</v>
@@ -3453,7 +3453,7 @@
         <v>1.53</v>
       </c>
       <c r="Q12">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R12">
         <v>1.18</v>
@@ -3462,76 +3462,76 @@
         <v>5.6</v>
       </c>
       <c r="T12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
         <v>1.75</v>
       </c>
       <c r="V12">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y12">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AB12">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC12">
         <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE12">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AF12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG12">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ12">
-        <v>420</v>
+        <v>170</v>
       </c>
       <c r="AK12">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AL12">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AM12">
         <v>500</v>
       </c>
       <c r="AN12">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AO12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP12">
         <v>7</v>
       </c>
       <c r="AQ12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR12">
         <v>13.5</v>
@@ -3540,10 +3540,10 @@
         <v>38</v>
       </c>
       <c r="AT12">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV12">
         <v>11</v>
@@ -3552,25 +3552,25 @@
         <v>34</v>
       </c>
       <c r="AX12">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ12">
         <v>19.5</v>
       </c>
       <c r="BA12">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BB12">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BC12">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BD12">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE12">
         <v>9.800000000000001</v>
@@ -3591,55 +3591,55 @@
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO12">
         <v>4.8</v>
       </c>
       <c r="BP12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ12">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT12">
         <v>5.6</v>
       </c>
       <c r="BU12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV12">
         <v>26</v>
       </c>
       <c r="BW12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX12">
         <v>50</v>
       </c>
       <c r="BY12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB12" t="s">
         <v>130</v>
@@ -3665,13 +3665,13 @@
         <v>2.52</v>
       </c>
       <c r="G13">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H13">
         <v>3.25</v>
       </c>
       <c r="I13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J13">
         <v>3.1</v>
@@ -3689,7 +3689,7 @@
         <v>3.05</v>
       </c>
       <c r="O13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P13">
         <v>1.66</v>
@@ -3698,13 +3698,13 @@
         <v>2.44</v>
       </c>
       <c r="R13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S13">
         <v>4.8</v>
       </c>
       <c r="T13">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U13">
         <v>1.92</v>
@@ -3716,7 +3716,7 @@
         <v>1.61</v>
       </c>
       <c r="X13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10.5</v>
@@ -3776,7 +3776,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS13">
         <v>23</v>
@@ -3788,10 +3788,10 @@
         <v>6.4</v>
       </c>
       <c r="AV13">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3800,88 +3800,88 @@
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
+        <v>7.6</v>
+      </c>
+      <c r="BC13">
         <v>7.4</v>
-      </c>
-      <c r="BC13">
-        <v>7.2</v>
       </c>
       <c r="BD13">
         <v>8</v>
       </c>
       <c r="BE13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG13">
         <v>42</v>
       </c>
       <c r="BH13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI13">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ13">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK13">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="BN13">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BO13">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP13">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS13">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BT13">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU13">
+        <v>4.9</v>
+      </c>
+      <c r="BV13">
+        <v>34</v>
+      </c>
+      <c r="BW13">
+        <v>5.2</v>
+      </c>
+      <c r="BX13">
+        <v>55</v>
+      </c>
+      <c r="BY13">
         <v>5.5</v>
       </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>7.6</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>8.4</v>
-      </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA13">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="s">
         <v>130</v>
@@ -3904,127 +3904,127 @@
         <v>128</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G14">
         <v>1.63</v>
       </c>
       <c r="H14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
+        <v>3.95</v>
+      </c>
+      <c r="K14">
         <v>4.1</v>
       </c>
-      <c r="K14">
-        <v>4.3</v>
-      </c>
       <c r="L14">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
+        <v>3.5</v>
+      </c>
+      <c r="O14">
+        <v>1.37</v>
+      </c>
+      <c r="P14">
+        <v>1.82</v>
+      </c>
+      <c r="Q14">
+        <v>2.1</v>
+      </c>
+      <c r="R14">
+        <v>1.31</v>
+      </c>
+      <c r="S14">
         <v>3.85</v>
       </c>
-      <c r="O14">
-        <v>1.31</v>
-      </c>
-      <c r="P14">
-        <v>1.98</v>
-      </c>
-      <c r="Q14">
-        <v>1.93</v>
-      </c>
-      <c r="R14">
-        <v>1.37</v>
-      </c>
-      <c r="S14">
-        <v>3.35</v>
-      </c>
       <c r="T14">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="V14">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W14">
         <v>2.58</v>
       </c>
       <c r="X14">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA14">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AB14">
+        <v>7.8</v>
+      </c>
+      <c r="AC14">
         <v>9</v>
       </c>
-      <c r="AC14">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AD14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE14">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="AF14">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG14">
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI14">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK14">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM14">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AN14">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AO14">
-        <v>530</v>
+        <v>200</v>
       </c>
       <c r="AP14">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14">
         <v>18</v>
       </c>
       <c r="AR14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AS14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT14">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
         <v>7.8</v>
@@ -4033,10 +4033,10 @@
         <v>22</v>
       </c>
       <c r="AW14">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="AX14">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY14">
         <v>9.4</v>
@@ -4045,34 +4045,34 @@
         <v>20</v>
       </c>
       <c r="BA14">
+        <v>14</v>
+      </c>
+      <c r="BB14">
         <v>13</v>
       </c>
-      <c r="BB14">
-        <v>13.5</v>
-      </c>
       <c r="BC14">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD14">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="BE14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF14">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH14">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI14">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK14">
         <v>6.2</v>
@@ -4081,43 +4081,43 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN14">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO14">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BP14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BS14">
         <v>9.199999999999999</v>
       </c>
       <c r="BT14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4170,28 +4170,28 @@
         <v>1.09</v>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P15">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T15">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U15">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V15">
         <v>1.14</v>
@@ -4254,7 +4254,7 @@
         <v>270</v>
       </c>
       <c r="AP15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ15">
         <v>16.5</v>
@@ -4266,7 +4266,7 @@
         <v>9.4</v>
       </c>
       <c r="AT15">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU15">
         <v>8.199999999999999</v>
@@ -4308,7 +4308,7 @@
         <v>9.4</v>
       </c>
       <c r="BH15">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI15">
         <v>2.66</v>
@@ -4323,10 +4323,10 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BO15">
         <v>3.4</v>
@@ -4341,31 +4341,31 @@
         <v>34</v>
       </c>
       <c r="BS15">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU15">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV15">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BW15">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15">
         <v>95</v>
       </c>
       <c r="BY15">
+        <v>8.4</v>
+      </c>
+      <c r="BZ15">
+        <v>29</v>
+      </c>
+      <c r="CA15">
         <v>7</v>
-      </c>
-      <c r="BZ15">
-        <v>25</v>
-      </c>
-      <c r="CA15">
-        <v>5.8</v>
       </c>
       <c r="CB15" t="s">
         <v>130</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="136">
   <si>
     <t>League</t>
   </si>
@@ -310,6 +310,9 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>21:10:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -349,6 +352,12 @@
     <t>Real Santander</t>
   </si>
   <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
+    <t>San Antonio FC</t>
+  </si>
+  <si>
     <t>LDU</t>
   </si>
   <si>
@@ -391,6 +400,12 @@
     <t>Barranquilla</t>
   </si>
   <si>
+    <t>El Nacional</t>
+  </si>
+  <si>
+    <t>Club Nueve de Octubre</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
@@ -406,7 +421,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-20 06:41:59</t>
+    <t>2026-08-20 08:58:19</t>
   </si>
 </sst>
 </file>
@@ -738,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -994,28 +1009,28 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H2">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I2">
         <v>3.2</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -1024,58 +1039,58 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB2">
         <v>12</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AF2">
         <v>17.5</v>
@@ -1090,139 +1105,139 @@
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AK2">
         <v>28</v>
       </c>
       <c r="AL2">
+        <v>40</v>
+      </c>
+      <c r="AM2">
         <v>85</v>
       </c>
-      <c r="AM2">
-        <v>580</v>
-      </c>
       <c r="AN2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="AP2">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX2">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY2">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="BF2">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI2">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
         <v>9.6</v>
       </c>
       <c r="BK2">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="BN2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
         <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>2.56</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA2">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1236,28 +1251,28 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.34</v>
@@ -1266,100 +1281,100 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R3">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z3">
+        <v>36</v>
+      </c>
+      <c r="AA3">
         <v>65</v>
       </c>
-      <c r="AA3">
-        <v>280</v>
-      </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>16</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AK3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AO3">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS3">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="AT3">
         <v>11.5</v>
@@ -1368,103 +1383,103 @@
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="BB3">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BC3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BD3">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BE3">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
+        <v>7.4</v>
+      </c>
+      <c r="BU3">
+        <v>6</v>
+      </c>
+      <c r="BV3">
+        <v>26</v>
+      </c>
+      <c r="BW3">
+        <v>7.4</v>
+      </c>
+      <c r="BX3">
+        <v>34</v>
+      </c>
+      <c r="BY3">
+        <v>7.8</v>
+      </c>
+      <c r="BZ3">
+        <v>18.5</v>
+      </c>
+      <c r="CA3">
         <v>6.6</v>
       </c>
-      <c r="BU3">
-        <v>4.9</v>
-      </c>
-      <c r="BV3">
-        <v>22</v>
-      </c>
-      <c r="BW3">
-        <v>7.6</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>8.4</v>
-      </c>
-      <c r="BZ3">
-        <v>19.5</v>
-      </c>
-      <c r="CA3">
-        <v>7.2</v>
-      </c>
       <c r="CB3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1478,19 +1493,19 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G4">
         <v>1.35</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>10.5</v>
@@ -1499,7 +1514,7 @@
         <v>6.2</v>
       </c>
       <c r="K4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L4">
         <v>1.21</v>
@@ -1508,7 +1523,7 @@
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O4">
         <v>1.12</v>
@@ -1520,16 +1535,16 @@
         <v>1.36</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S4">
         <v>1.9</v>
       </c>
       <c r="T4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
         <v>1.1</v>
@@ -1538,7 +1553,7 @@
         <v>3.75</v>
       </c>
       <c r="X4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y4">
         <v>60</v>
@@ -1547,7 +1562,7 @@
         <v>120</v>
       </c>
       <c r="AA4">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB4">
         <v>16</v>
@@ -1571,13 +1586,13 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AJ4">
         <v>13</v>
       </c>
       <c r="AK4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL4">
         <v>27</v>
@@ -1601,7 +1616,7 @@
         <v>34</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT4">
         <v>13</v>
@@ -1610,13 +1625,13 @@
         <v>14</v>
       </c>
       <c r="AV4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW4">
         <v>70</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1625,16 +1640,16 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC4">
         <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE4">
         <v>50</v>
@@ -1649,28 +1664,28 @@
         <v>6.8</v>
       </c>
       <c r="BI4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ4">
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BL4">
         <v>100</v>
       </c>
       <c r="BM4">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ4">
         <v>5.6</v>
@@ -1679,25 +1694,25 @@
         <v>21</v>
       </c>
       <c r="BS4">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BT4">
         <v>16</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BV4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW4">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1706,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1720,31 +1735,31 @@
         <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1756,31 +1771,31 @@
         <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T5">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y5">
         <v>16.5</v>
@@ -1789,13 +1804,13 @@
         <v>25</v>
       </c>
       <c r="AA5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB5">
         <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD5">
         <v>14</v>
@@ -1807,7 +1822,7 @@
         <v>18</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
         <v>16</v>
@@ -1819,31 +1834,31 @@
         <v>34</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO5">
         <v>24</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
         <v>13</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
@@ -1852,7 +1867,7 @@
         <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
         <v>23</v>
@@ -1861,7 +1876,7 @@
         <v>14.5</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>13</v>
@@ -1879,31 +1894,31 @@
         <v>25</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG5">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BH5">
         <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL5">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BM5">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
         <v>5.8</v>
@@ -1915,13 +1930,13 @@
         <v>18</v>
       </c>
       <c r="BQ5">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR5">
         <v>28</v>
       </c>
       <c r="BS5">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BT5">
         <v>6.6</v>
@@ -1930,25 +1945,25 @@
         <v>5.4</v>
       </c>
       <c r="BV5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BW5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX5">
         <v>32</v>
       </c>
       <c r="BY5">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1962,19 +1977,19 @@
         <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="H6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I6">
         <v>1.26</v>
@@ -1983,16 +1998,16 @@
         <v>6.8</v>
       </c>
       <c r="K6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
         <v>1.2</v>
@@ -2004,16 +2019,16 @@
         <v>1.62</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S6">
         <v>2.56</v>
       </c>
       <c r="T6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U6">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V6">
         <v>4.8</v>
@@ -2022,7 +2037,7 @@
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y6">
         <v>9.6</v>
@@ -2034,22 +2049,22 @@
         <v>9.4</v>
       </c>
       <c r="AB6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AC6">
         <v>16.5</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AF6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AG6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AH6">
         <v>44</v>
@@ -2070,10 +2085,10 @@
         <v>260</v>
       </c>
       <c r="AN6">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AO6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AP6">
         <v>12.5</v>
@@ -2094,13 +2109,13 @@
         <v>14</v>
       </c>
       <c r="AV6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6">
         <v>30</v>
@@ -2112,70 +2127,70 @@
         <v>27</v>
       </c>
       <c r="BB6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC6">
         <v>10</v>
       </c>
       <c r="BD6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG6">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI6">
         <v>3.95</v>
       </c>
       <c r="BJ6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BK6">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BO6">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BP6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BQ6">
         <v>9</v>
       </c>
       <c r="BR6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BS6">
         <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BU6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BW6">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BX6">
         <v>25</v>
@@ -2184,13 +2199,13 @@
         <v>6.8</v>
       </c>
       <c r="BZ6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CA6">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2204,70 +2219,70 @@
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G7">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M7">
         <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T7">
         <v>2.2</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z7">
         <v>55</v>
@@ -2279,10 +2294,10 @@
         <v>6.6</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AE7">
         <v>500</v>
@@ -2300,7 +2315,7 @@
         <v>500</v>
       </c>
       <c r="AJ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK7">
         <v>25</v>
@@ -2312,127 +2327,127 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO7">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AP7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR7">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT7">
         <v>5.3</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AW7">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BA7">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BB7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD7">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG7">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7">
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
         <v>5.9</v>
       </c>
       <c r="BR7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2446,13 +2461,13 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G8">
         <v>2.74</v>
@@ -2461,13 +2476,13 @@
         <v>2.8</v>
       </c>
       <c r="I8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J8">
+        <v>3.5</v>
+      </c>
+      <c r="K8">
         <v>3.6</v>
-      </c>
-      <c r="K8">
-        <v>3.65</v>
       </c>
       <c r="L8">
         <v>1.42</v>
@@ -2476,10 +2491,10 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
         <v>1.96</v>
@@ -2488,7 +2503,7 @@
         <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S8">
         <v>3.6</v>
@@ -2506,13 +2521,13 @@
         <v>1.57</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y8">
         <v>11.5</v>
       </c>
       <c r="Z8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA8">
         <v>44</v>
@@ -2524,16 +2539,16 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF8">
         <v>18</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
@@ -2548,25 +2563,25 @@
         <v>29</v>
       </c>
       <c r="AL8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS8">
         <v>38</v>
@@ -2581,7 +2596,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX8">
         <v>16.5</v>
@@ -2590,22 +2605,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA8">
         <v>40</v>
       </c>
       <c r="BB8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC8">
         <v>26</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF8">
         <v>23</v>
@@ -2626,10 +2641,10 @@
         <v>6</v>
       </c>
       <c r="BL8">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
         <v>5.8</v>
@@ -2638,7 +2653,7 @@
         <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BQ8">
         <v>8</v>
@@ -2647,34 +2662,34 @@
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8">
         <v>5.8</v>
       </c>
       <c r="BU8">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV8">
         <v>22</v>
       </c>
       <c r="BW8">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX8">
         <v>40</v>
       </c>
       <c r="BY8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
         <v>28</v>
       </c>
       <c r="CA8">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2688,70 +2703,70 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F9">
+        <v>2.38</v>
+      </c>
+      <c r="G9">
         <v>2.4</v>
       </c>
-      <c r="G9">
-        <v>2.42</v>
-      </c>
       <c r="H9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M9">
         <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P9">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q9">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R9">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U9">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V9">
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9">
         <v>23</v>
@@ -2766,46 +2781,46 @@
         <v>6.8</v>
       </c>
       <c r="AD9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
         <v>22</v>
       </c>
       <c r="AI9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM9">
         <v>160</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR9">
         <v>21</v>
@@ -2817,10 +2832,10 @@
         <v>7.6</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW9">
         <v>50</v>
@@ -2829,13 +2844,13 @@
         <v>12</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
         <v>20</v>
       </c>
       <c r="BA9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB9">
         <v>30</v>
@@ -2844,22 +2859,22 @@
         <v>28</v>
       </c>
       <c r="BD9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE9">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BF9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BG9">
         <v>65</v>
       </c>
       <c r="BH9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9">
         <v>11</v>
@@ -2868,28 +2883,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BL9">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BM9">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN9">
         <v>4.9</v>
       </c>
       <c r="BO9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BR9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS9">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BT9">
         <v>6.6</v>
@@ -2907,16 +2922,16 @@
         <v>65</v>
       </c>
       <c r="BY9">
+        <v>17</v>
+      </c>
+      <c r="BZ9">
+        <v>48</v>
+      </c>
+      <c r="CA9">
         <v>15.5</v>
       </c>
-      <c r="BZ9">
-        <v>50</v>
-      </c>
-      <c r="CA9">
-        <v>14.5</v>
-      </c>
       <c r="CB9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2930,19 +2945,19 @@
         <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F10">
         <v>2.44</v>
       </c>
       <c r="G10">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H10">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I10">
         <v>3.25</v>
@@ -2951,7 +2966,7 @@
         <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
         <v>1.4</v>
@@ -2972,7 +2987,7 @@
         <v>1.94</v>
       </c>
       <c r="R10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S10">
         <v>3.4</v>
@@ -2987,7 +3002,7 @@
         <v>1.45</v>
       </c>
       <c r="W10">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X10">
         <v>15</v>
@@ -3011,7 +3026,7 @@
         <v>14</v>
       </c>
       <c r="AE10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF10">
         <v>17.5</v>
@@ -3041,7 +3056,7 @@
         <v>23</v>
       </c>
       <c r="AO10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP10">
         <v>12.5</v>
@@ -3077,7 +3092,7 @@
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB10">
         <v>25</v>
@@ -3086,7 +3101,7 @@
         <v>21</v>
       </c>
       <c r="BD10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE10">
         <v>60</v>
@@ -3098,25 +3113,25 @@
         <v>19.5</v>
       </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO10">
         <v>4.3</v>
@@ -3125,13 +3140,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
         <v>34</v>
       </c>
       <c r="BS10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT10">
         <v>6.6</v>
@@ -3140,272 +3155,272 @@
         <v>4.9</v>
       </c>
       <c r="BV10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX10">
         <v>38</v>
       </c>
       <c r="BY10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
         <v>28</v>
       </c>
       <c r="CA10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F11">
+        <v>1.33</v>
+      </c>
+      <c r="G11">
+        <v>1.43</v>
+      </c>
+      <c r="H11">
+        <v>7.6</v>
+      </c>
+      <c r="I11">
+        <v>13</v>
+      </c>
+      <c r="J11">
+        <v>4.4</v>
+      </c>
+      <c r="K11">
+        <v>6.4</v>
+      </c>
+      <c r="L11">
+        <v>1.3</v>
+      </c>
+      <c r="M11">
+        <v>1.03</v>
+      </c>
+      <c r="N11">
+        <v>4.7</v>
+      </c>
+      <c r="O11">
+        <v>1.21</v>
+      </c>
+      <c r="P11">
+        <v>2.18</v>
+      </c>
+      <c r="Q11">
         <v>1.61</v>
       </c>
-      <c r="G11">
-        <v>1.62</v>
-      </c>
-      <c r="H11">
-        <v>7.2</v>
-      </c>
-      <c r="I11">
-        <v>7.8</v>
-      </c>
-      <c r="J11">
+      <c r="R11">
+        <v>1.5</v>
+      </c>
+      <c r="S11">
+        <v>2.44</v>
+      </c>
+      <c r="T11">
+        <v>1.94</v>
+      </c>
+      <c r="U11">
+        <v>1.82</v>
+      </c>
+      <c r="V11">
+        <v>1.08</v>
+      </c>
+      <c r="W11">
+        <v>3.3</v>
+      </c>
+      <c r="X11">
+        <v>27</v>
+      </c>
+      <c r="Y11">
+        <v>40</v>
+      </c>
+      <c r="Z11">
+        <v>110</v>
+      </c>
+      <c r="AA11">
+        <v>420</v>
+      </c>
+      <c r="AB11">
+        <v>11</v>
+      </c>
+      <c r="AC11">
+        <v>15</v>
+      </c>
+      <c r="AD11">
+        <v>44</v>
+      </c>
+      <c r="AE11">
+        <v>190</v>
+      </c>
+      <c r="AF11">
+        <v>10</v>
+      </c>
+      <c r="AG11">
+        <v>12.5</v>
+      </c>
+      <c r="AH11">
+        <v>32</v>
+      </c>
+      <c r="AI11">
+        <v>150</v>
+      </c>
+      <c r="AJ11">
+        <v>13</v>
+      </c>
+      <c r="AK11">
+        <v>17</v>
+      </c>
+      <c r="AL11">
+        <v>42</v>
+      </c>
+      <c r="AM11">
+        <v>170</v>
+      </c>
+      <c r="AN11">
+        <v>6.2</v>
+      </c>
+      <c r="AO11">
+        <v>240</v>
+      </c>
+      <c r="AP11">
+        <v>4.3</v>
+      </c>
+      <c r="AQ11">
+        <v>4.6</v>
+      </c>
+      <c r="AR11">
+        <v>4.9</v>
+      </c>
+      <c r="AS11">
+        <v>5.1</v>
+      </c>
+      <c r="AT11">
+        <v>3.5</v>
+      </c>
+      <c r="AU11">
+        <v>3.85</v>
+      </c>
+      <c r="AV11">
+        <v>4.6</v>
+      </c>
+      <c r="AW11">
+        <v>5</v>
+      </c>
+      <c r="AX11">
+        <v>3.4</v>
+      </c>
+      <c r="AY11">
+        <v>3.65</v>
+      </c>
+      <c r="AZ11">
+        <v>4.4</v>
+      </c>
+      <c r="BA11">
+        <v>5</v>
+      </c>
+      <c r="BB11">
+        <v>3.7</v>
+      </c>
+      <c r="BC11">
         <v>3.95</v>
       </c>
-      <c r="K11">
-        <v>4.1</v>
-      </c>
-      <c r="L11">
-        <v>1.48</v>
-      </c>
-      <c r="M11">
-        <v>1.09</v>
-      </c>
-      <c r="N11">
-        <v>3.3</v>
-      </c>
-      <c r="O11">
-        <v>1.4</v>
-      </c>
-      <c r="P11">
-        <v>1.77</v>
-      </c>
-      <c r="Q11">
-        <v>2.22</v>
-      </c>
-      <c r="R11">
-        <v>1.28</v>
-      </c>
-      <c r="S11">
-        <v>4.3</v>
-      </c>
-      <c r="T11">
-        <v>2.16</v>
-      </c>
-      <c r="U11">
-        <v>1.79</v>
-      </c>
-      <c r="V11">
-        <v>1.15</v>
-      </c>
-      <c r="W11">
-        <v>2.6</v>
-      </c>
-      <c r="X11">
-        <v>12</v>
-      </c>
-      <c r="Y11">
-        <v>19.5</v>
-      </c>
-      <c r="Z11">
-        <v>65</v>
-      </c>
-      <c r="AA11">
-        <v>270</v>
-      </c>
-      <c r="AB11">
-        <v>6.8</v>
-      </c>
-      <c r="AC11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>29</v>
-      </c>
-      <c r="AE11">
-        <v>170</v>
-      </c>
-      <c r="AF11">
-        <v>8.6</v>
-      </c>
-      <c r="AG11">
-        <v>10.5</v>
-      </c>
-      <c r="AH11">
-        <v>28</v>
-      </c>
-      <c r="AI11">
-        <v>140</v>
-      </c>
-      <c r="AJ11">
-        <v>15</v>
-      </c>
-      <c r="AK11">
-        <v>20</v>
-      </c>
-      <c r="AL11">
-        <v>50</v>
-      </c>
-      <c r="AM11">
-        <v>210</v>
-      </c>
-      <c r="AN11">
+      <c r="BD11">
+        <v>4.6</v>
+      </c>
+      <c r="BE11">
+        <v>5</v>
+      </c>
+      <c r="BF11">
+        <v>2.82</v>
+      </c>
+      <c r="BG11">
+        <v>5</v>
+      </c>
+      <c r="BH11">
+        <v>4.4</v>
+      </c>
+      <c r="BI11">
+        <v>2.96</v>
+      </c>
+      <c r="BJ11">
         <v>12.5</v>
       </c>
-      <c r="AO11">
-        <v>230</v>
-      </c>
-      <c r="AP11">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11">
-        <v>9.4</v>
-      </c>
-      <c r="AR11">
-        <v>48</v>
-      </c>
-      <c r="AS11">
-        <v>13.5</v>
-      </c>
-      <c r="AT11">
-        <v>6.2</v>
-      </c>
-      <c r="AU11">
-        <v>8.4</v>
-      </c>
-      <c r="AV11">
-        <v>25</v>
-      </c>
-      <c r="AW11">
-        <v>13.5</v>
-      </c>
-      <c r="AX11">
-        <v>7.6</v>
-      </c>
-      <c r="AY11">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11">
-        <v>25</v>
-      </c>
-      <c r="BA11">
-        <v>13.5</v>
-      </c>
-      <c r="BB11">
-        <v>13</v>
-      </c>
-      <c r="BC11">
-        <v>17</v>
-      </c>
-      <c r="BD11">
-        <v>13.5</v>
-      </c>
-      <c r="BE11">
-        <v>16.5</v>
-      </c>
-      <c r="BF11">
-        <v>10.5</v>
-      </c>
-      <c r="BG11">
-        <v>17</v>
-      </c>
-      <c r="BH11">
-        <v>3.2</v>
-      </c>
-      <c r="BI11">
-        <v>2.54</v>
-      </c>
-      <c r="BJ11">
-        <v>13</v>
-      </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11</v>
+        <v>2.78</v>
       </c>
       <c r="BN11">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO11">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="BP11">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BQ11">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BR11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BS11">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BT11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BZ11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="CA11">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>90</v>
@@ -3414,240 +3429,240 @@
         <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F12">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H12">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J12">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="K12">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L12">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="M12">
         <v>1.13</v>
       </c>
       <c r="N12">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O12">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="P12">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="Q12">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="X12">
         <v>8.800000000000001</v>
       </c>
       <c r="Y12">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD12">
         <v>15</v>
       </c>
       <c r="AE12">
+        <v>60</v>
+      </c>
+      <c r="AF12">
+        <v>24</v>
+      </c>
+      <c r="AG12">
+        <v>16</v>
+      </c>
+      <c r="AH12">
+        <v>34</v>
+      </c>
+      <c r="AI12">
         <v>100</v>
       </c>
-      <c r="AF12">
-        <v>19</v>
-      </c>
-      <c r="AG12">
-        <v>15</v>
-      </c>
-      <c r="AH12">
-        <v>25</v>
-      </c>
-      <c r="AI12">
+      <c r="AJ12">
+        <v>85</v>
+      </c>
+      <c r="AK12">
+        <v>70</v>
+      </c>
+      <c r="AL12">
+        <v>110</v>
+      </c>
+      <c r="AM12">
+        <v>290</v>
+      </c>
+      <c r="AN12">
+        <v>100</v>
+      </c>
+      <c r="AO12">
         <v>80</v>
       </c>
-      <c r="AJ12">
-        <v>170</v>
-      </c>
-      <c r="AK12">
-        <v>130</v>
-      </c>
-      <c r="AL12">
-        <v>210</v>
-      </c>
-      <c r="AM12">
-        <v>500</v>
-      </c>
-      <c r="AN12">
-        <v>65</v>
-      </c>
-      <c r="AO12">
-        <v>60</v>
-      </c>
       <c r="AP12">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ12">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS12">
+        <v>6</v>
+      </c>
+      <c r="AT12">
+        <v>6.2</v>
+      </c>
+      <c r="AU12">
+        <v>6</v>
+      </c>
+      <c r="AV12">
+        <v>10.5</v>
+      </c>
+      <c r="AW12">
         <v>38</v>
       </c>
-      <c r="AT12">
-        <v>7.2</v>
-      </c>
-      <c r="AU12">
+      <c r="AX12">
+        <v>14</v>
+      </c>
+      <c r="AY12">
+        <v>11</v>
+      </c>
+      <c r="AZ12">
+        <v>5.3</v>
+      </c>
+      <c r="BA12">
         <v>6.2</v>
       </c>
-      <c r="AV12">
-        <v>11</v>
-      </c>
-      <c r="AW12">
-        <v>34</v>
-      </c>
-      <c r="AX12">
-        <v>15.5</v>
-      </c>
-      <c r="AY12">
-        <v>12</v>
-      </c>
-      <c r="AZ12">
-        <v>19.5</v>
-      </c>
-      <c r="BA12">
-        <v>30</v>
-      </c>
       <c r="BB12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BC12">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="BD12">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="BE12">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BF12">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="BH12">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="BI12">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12">
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BN12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO12">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BT12">
         <v>5.6</v>
       </c>
       <c r="BU12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BX12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CB12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>90</v>
@@ -3656,235 +3671,235 @@
         <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F13">
-        <v>2.52</v>
+        <v>1.62</v>
       </c>
       <c r="G13">
-        <v>2.64</v>
+        <v>1.64</v>
       </c>
       <c r="H13">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="K13">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="M13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P13">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T13">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y13">
+        <v>19</v>
+      </c>
+      <c r="Z13">
+        <v>65</v>
+      </c>
+      <c r="AA13">
+        <v>270</v>
+      </c>
+      <c r="AB13">
+        <v>6.8</v>
+      </c>
+      <c r="AC13">
+        <v>9</v>
+      </c>
+      <c r="AD13">
+        <v>29</v>
+      </c>
+      <c r="AE13">
+        <v>160</v>
+      </c>
+      <c r="AF13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG13">
         <v>10.5</v>
       </c>
-      <c r="Z13">
-        <v>24</v>
-      </c>
-      <c r="AA13">
+      <c r="AH13">
+        <v>28</v>
+      </c>
+      <c r="AI13">
         <v>160</v>
       </c>
-      <c r="AB13">
-        <v>9.4</v>
-      </c>
-      <c r="AC13">
-        <v>7.2</v>
-      </c>
-      <c r="AD13">
-        <v>16.5</v>
-      </c>
-      <c r="AE13">
+      <c r="AJ13">
+        <v>16</v>
+      </c>
+      <c r="AK13">
+        <v>21</v>
+      </c>
+      <c r="AL13">
         <v>55</v>
-      </c>
-      <c r="AF13">
-        <v>16.5</v>
-      </c>
-      <c r="AG13">
-        <v>13.5</v>
-      </c>
-      <c r="AH13">
-        <v>21</v>
-      </c>
-      <c r="AI13">
-        <v>75</v>
-      </c>
-      <c r="AJ13">
-        <v>42</v>
-      </c>
-      <c r="AK13">
-        <v>36</v>
-      </c>
-      <c r="AL13">
-        <v>60</v>
       </c>
       <c r="AM13">
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="AO13">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AP13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="AS13">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AT13">
+        <v>6</v>
+      </c>
+      <c r="AU13">
+        <v>8.4</v>
+      </c>
+      <c r="AV13">
+        <v>25</v>
+      </c>
+      <c r="AW13">
+        <v>75</v>
+      </c>
+      <c r="AX13">
         <v>7.6</v>
       </c>
-      <c r="AU13">
-        <v>6.4</v>
-      </c>
-      <c r="AV13">
+      <c r="AY13">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13">
+        <v>25</v>
+      </c>
+      <c r="BA13">
+        <v>75</v>
+      </c>
+      <c r="BB13">
+        <v>13.5</v>
+      </c>
+      <c r="BC13">
+        <v>17</v>
+      </c>
+      <c r="BD13">
+        <v>34</v>
+      </c>
+      <c r="BE13">
+        <v>16</v>
+      </c>
+      <c r="BF13">
+        <v>10.5</v>
+      </c>
+      <c r="BG13">
+        <v>100</v>
+      </c>
+      <c r="BH13">
+        <v>3.05</v>
+      </c>
+      <c r="BI13">
+        <v>2.78</v>
+      </c>
+      <c r="BJ13">
         <v>12.5</v>
       </c>
-      <c r="AW13">
-        <v>7.8</v>
-      </c>
-      <c r="AX13">
-        <v>13.5</v>
-      </c>
-      <c r="AY13">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13">
-        <v>13</v>
-      </c>
-      <c r="BA13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB13">
-        <v>7.6</v>
-      </c>
-      <c r="BC13">
-        <v>7.4</v>
-      </c>
-      <c r="BD13">
-        <v>8</v>
-      </c>
-      <c r="BE13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF13">
-        <v>7.4</v>
-      </c>
-      <c r="BG13">
-        <v>42</v>
-      </c>
-      <c r="BH13">
-        <v>3.2</v>
-      </c>
-      <c r="BI13">
-        <v>2.44</v>
-      </c>
-      <c r="BJ13">
-        <v>12</v>
-      </c>
       <c r="BK13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="BN13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO13">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BQ13">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR13">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BS13">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BT13">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BU13">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="BX13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ13">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="CA13">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3895,238 +3910,238 @@
         <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F14">
-        <v>1.61</v>
+        <v>2.92</v>
       </c>
       <c r="G14">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="H14">
-        <v>6.8</v>
+        <v>2.74</v>
       </c>
       <c r="I14">
-        <v>7.6</v>
+        <v>2.98</v>
       </c>
       <c r="J14">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="K14">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L14">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N14">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="O14">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="P14">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="R14">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="S14">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="T14">
         <v>2.1</v>
       </c>
       <c r="U14">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V14">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>2.58</v>
+        <v>1.47</v>
       </c>
       <c r="X14">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y14">
-        <v>19.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14">
-        <v>65</v>
+        <v>18.5</v>
       </c>
       <c r="AA14">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AB14">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AE14">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AF14">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH14">
         <v>25</v>
       </c>
       <c r="AI14">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AJ14">
+        <v>75</v>
+      </c>
+      <c r="AK14">
+        <v>46</v>
+      </c>
+      <c r="AL14">
+        <v>100</v>
+      </c>
+      <c r="AM14">
+        <v>500</v>
+      </c>
+      <c r="AN14">
+        <v>100</v>
+      </c>
+      <c r="AO14">
+        <v>600</v>
+      </c>
+      <c r="AP14">
+        <v>7.2</v>
+      </c>
+      <c r="AQ14">
+        <v>7.2</v>
+      </c>
+      <c r="AR14">
         <v>15</v>
       </c>
-      <c r="AK14">
-        <v>19.5</v>
-      </c>
-      <c r="AL14">
-        <v>48</v>
-      </c>
-      <c r="AM14">
-        <v>190</v>
-      </c>
-      <c r="AN14">
-        <v>11.5</v>
-      </c>
-      <c r="AO14">
-        <v>200</v>
-      </c>
-      <c r="AP14">
-        <v>10.5</v>
-      </c>
-      <c r="AQ14">
-        <v>18</v>
-      </c>
-      <c r="AR14">
-        <v>32</v>
-      </c>
       <c r="AS14">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU14">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AW14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AX14">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AY14">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AZ14">
         <v>20</v>
       </c>
       <c r="BA14">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="BB14">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BC14">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BD14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BE14">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="BF14">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BG14">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="BH14">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="BI14">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="BJ14">
         <v>12</v>
       </c>
       <c r="BK14">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN14">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="BO14">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BP14">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BQ14">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BR14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT14">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="BU14">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV14">
+        <v>27</v>
+      </c>
+      <c r="BW14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX14">
+        <v>55</v>
+      </c>
+      <c r="BY14">
+        <v>9.6</v>
+      </c>
+      <c r="BZ14">
         <v>1000</v>
       </c>
-      <c r="BW14">
-        <v>11</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>11</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
       <c r="CA14">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB14" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4137,238 +4152,722 @@
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F15">
+        <v>2.6</v>
+      </c>
+      <c r="G15">
+        <v>2.68</v>
+      </c>
+      <c r="H15">
+        <v>3.2</v>
+      </c>
+      <c r="I15">
+        <v>3.3</v>
+      </c>
+      <c r="J15">
+        <v>3.15</v>
+      </c>
+      <c r="K15">
+        <v>3.25</v>
+      </c>
+      <c r="L15">
+        <v>1.52</v>
+      </c>
+      <c r="M15">
+        <v>1.11</v>
+      </c>
+      <c r="N15">
+        <v>3.05</v>
+      </c>
+      <c r="O15">
+        <v>1.46</v>
+      </c>
+      <c r="P15">
+        <v>1.67</v>
+      </c>
+      <c r="Q15">
+        <v>2.44</v>
+      </c>
+      <c r="R15">
+        <v>1.24</v>
+      </c>
+      <c r="S15">
+        <v>4.8</v>
+      </c>
+      <c r="T15">
+        <v>1.97</v>
+      </c>
+      <c r="U15">
+        <v>1.94</v>
+      </c>
+      <c r="V15">
+        <v>1.43</v>
+      </c>
+      <c r="W15">
         <v>1.59</v>
       </c>
-      <c r="G15">
-        <v>1.62</v>
-      </c>
-      <c r="H15">
-        <v>7.4</v>
-      </c>
-      <c r="I15">
+      <c r="X15">
+        <v>10</v>
+      </c>
+      <c r="Y15">
+        <v>10.5</v>
+      </c>
+      <c r="Z15">
+        <v>24</v>
+      </c>
+      <c r="AA15">
+        <v>75</v>
+      </c>
+      <c r="AB15">
+        <v>9.4</v>
+      </c>
+      <c r="AC15">
+        <v>7.2</v>
+      </c>
+      <c r="AD15">
+        <v>16.5</v>
+      </c>
+      <c r="AE15">
+        <v>55</v>
+      </c>
+      <c r="AF15">
+        <v>16.5</v>
+      </c>
+      <c r="AG15">
+        <v>13</v>
+      </c>
+      <c r="AH15">
+        <v>21</v>
+      </c>
+      <c r="AI15">
+        <v>75</v>
+      </c>
+      <c r="AJ15">
+        <v>42</v>
+      </c>
+      <c r="AK15">
+        <v>36</v>
+      </c>
+      <c r="AL15">
+        <v>150</v>
+      </c>
+      <c r="AM15">
+        <v>580</v>
+      </c>
+      <c r="AN15">
+        <v>36</v>
+      </c>
+      <c r="AO15">
+        <v>65</v>
+      </c>
+      <c r="AP15">
+        <v>9</v>
+      </c>
+      <c r="AQ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>11</v>
+      </c>
+      <c r="AS15">
+        <v>23</v>
+      </c>
+      <c r="AT15">
+        <v>7.8</v>
+      </c>
+      <c r="AU15">
+        <v>6.4</v>
+      </c>
+      <c r="AV15">
+        <v>12.5</v>
+      </c>
+      <c r="AW15">
         <v>8.199999999999999</v>
       </c>
-      <c r="J15">
-        <v>3.95</v>
-      </c>
-      <c r="K15">
-        <v>4.2</v>
-      </c>
-      <c r="L15">
-        <v>1.47</v>
-      </c>
-      <c r="M15">
-        <v>1.09</v>
-      </c>
-      <c r="N15">
-        <v>3.3</v>
-      </c>
-      <c r="O15">
-        <v>1.41</v>
-      </c>
-      <c r="P15">
-        <v>1.75</v>
-      </c>
-      <c r="Q15">
-        <v>2.24</v>
-      </c>
-      <c r="R15">
-        <v>1.28</v>
-      </c>
-      <c r="S15">
-        <v>4.3</v>
-      </c>
-      <c r="T15">
-        <v>2.22</v>
-      </c>
-      <c r="U15">
-        <v>1.73</v>
-      </c>
-      <c r="V15">
-        <v>1.14</v>
-      </c>
-      <c r="W15">
-        <v>2.6</v>
-      </c>
-      <c r="X15">
-        <v>13</v>
-      </c>
-      <c r="Y15">
-        <v>21</v>
-      </c>
-      <c r="Z15">
-        <v>75</v>
-      </c>
-      <c r="AA15">
-        <v>320</v>
-      </c>
-      <c r="AB15">
-        <v>6.8</v>
-      </c>
-      <c r="AC15">
-        <v>9.4</v>
-      </c>
-      <c r="AD15">
-        <v>32</v>
-      </c>
-      <c r="AE15">
-        <v>160</v>
-      </c>
-      <c r="AF15">
+      <c r="AX15">
+        <v>13.5</v>
+      </c>
+      <c r="AY15">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15">
+        <v>17.5</v>
+      </c>
+      <c r="BA15">
+        <v>8.6</v>
+      </c>
+      <c r="BB15">
+        <v>16</v>
+      </c>
+      <c r="BC15">
+        <v>14.5</v>
+      </c>
+      <c r="BD15">
+        <v>8.4</v>
+      </c>
+      <c r="BE15">
         <v>8.800000000000001</v>
       </c>
-      <c r="AG15">
-        <v>11</v>
-      </c>
-      <c r="AH15">
-        <v>29</v>
-      </c>
-      <c r="AI15">
-        <v>160</v>
-      </c>
-      <c r="AJ15">
-        <v>15.5</v>
-      </c>
-      <c r="AK15">
-        <v>20</v>
-      </c>
-      <c r="AL15">
-        <v>55</v>
-      </c>
-      <c r="AM15">
-        <v>230</v>
-      </c>
-      <c r="AN15">
-        <v>12.5</v>
-      </c>
-      <c r="AO15">
-        <v>270</v>
-      </c>
-      <c r="AP15">
-        <v>10</v>
-      </c>
-      <c r="AQ15">
-        <v>16.5</v>
-      </c>
-      <c r="AR15">
-        <v>8.6</v>
-      </c>
-      <c r="AS15">
-        <v>9.4</v>
-      </c>
-      <c r="AT15">
-        <v>5.7</v>
-      </c>
-      <c r="AU15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15">
-        <v>24</v>
-      </c>
-      <c r="AW15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX15">
-        <v>7.2</v>
-      </c>
-      <c r="AY15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15">
-        <v>7.2</v>
-      </c>
-      <c r="BA15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB15">
-        <v>11.5</v>
-      </c>
-      <c r="BC15">
-        <v>16</v>
-      </c>
-      <c r="BD15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE15">
-        <v>9.4</v>
-      </c>
       <c r="BF15">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG15">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH15">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BI15">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK15">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
+        <v>5.9</v>
+      </c>
+      <c r="BN15">
+        <v>6</v>
+      </c>
+      <c r="BO15">
+        <v>4.2</v>
+      </c>
+      <c r="BP15">
+        <v>25</v>
+      </c>
+      <c r="BQ15">
+        <v>4.9</v>
+      </c>
+      <c r="BR15">
+        <v>46</v>
+      </c>
+      <c r="BS15">
+        <v>5.4</v>
+      </c>
+      <c r="BT15">
+        <v>7</v>
+      </c>
+      <c r="BU15">
+        <v>4.9</v>
+      </c>
+      <c r="BV15">
+        <v>34</v>
+      </c>
+      <c r="BW15">
+        <v>5.1</v>
+      </c>
+      <c r="BX15">
+        <v>55</v>
+      </c>
+      <c r="BY15">
+        <v>5.5</v>
+      </c>
+      <c r="BZ15">
+        <v>46</v>
+      </c>
+      <c r="CA15">
+        <v>5.4</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16">
+        <v>1.59</v>
+      </c>
+      <c r="G16">
+        <v>1.62</v>
+      </c>
+      <c r="H16">
+        <v>6.8</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16">
+        <v>4.1</v>
+      </c>
+      <c r="K16">
+        <v>4.4</v>
+      </c>
+      <c r="L16">
+        <v>1.4</v>
+      </c>
+      <c r="M16">
+        <v>1.07</v>
+      </c>
+      <c r="N16">
+        <v>3.9</v>
+      </c>
+      <c r="O16">
+        <v>1.31</v>
+      </c>
+      <c r="P16">
+        <v>2</v>
+      </c>
+      <c r="Q16">
+        <v>1.94</v>
+      </c>
+      <c r="R16">
+        <v>1.38</v>
+      </c>
+      <c r="S16">
+        <v>3.35</v>
+      </c>
+      <c r="T16">
+        <v>2.02</v>
+      </c>
+      <c r="U16">
+        <v>1.86</v>
+      </c>
+      <c r="V16">
+        <v>1.15</v>
+      </c>
+      <c r="W16">
+        <v>2.6</v>
+      </c>
+      <c r="X16">
+        <v>14.5</v>
+      </c>
+      <c r="Y16">
+        <v>23</v>
+      </c>
+      <c r="Z16">
+        <v>65</v>
+      </c>
+      <c r="AA16">
+        <v>230</v>
+      </c>
+      <c r="AB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16">
+        <v>9.4</v>
+      </c>
+      <c r="AD16">
+        <v>27</v>
+      </c>
+      <c r="AE16">
+        <v>110</v>
+      </c>
+      <c r="AF16">
         <v>8.800000000000001</v>
       </c>
-      <c r="BN15">
+      <c r="AG16">
+        <v>11</v>
+      </c>
+      <c r="AH16">
+        <v>24</v>
+      </c>
+      <c r="AI16">
+        <v>110</v>
+      </c>
+      <c r="AJ16">
+        <v>14.5</v>
+      </c>
+      <c r="AK16">
+        <v>17.5</v>
+      </c>
+      <c r="AL16">
+        <v>40</v>
+      </c>
+      <c r="AM16">
+        <v>150</v>
+      </c>
+      <c r="AN16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO16">
+        <v>130</v>
+      </c>
+      <c r="AP16">
+        <v>13</v>
+      </c>
+      <c r="AQ16">
+        <v>20</v>
+      </c>
+      <c r="AR16">
+        <v>32</v>
+      </c>
+      <c r="AS16">
+        <v>15</v>
+      </c>
+      <c r="AT16">
+        <v>7.2</v>
+      </c>
+      <c r="AU16">
+        <v>8.4</v>
+      </c>
+      <c r="AV16">
+        <v>23</v>
+      </c>
+      <c r="AW16">
+        <v>14</v>
+      </c>
+      <c r="AX16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY16">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16">
+        <v>21</v>
+      </c>
+      <c r="BA16">
+        <v>14</v>
+      </c>
+      <c r="BB16">
+        <v>13</v>
+      </c>
+      <c r="BC16">
+        <v>15.5</v>
+      </c>
+      <c r="BD16">
+        <v>32</v>
+      </c>
+      <c r="BE16">
+        <v>14.5</v>
+      </c>
+      <c r="BF16">
+        <v>8.4</v>
+      </c>
+      <c r="BG16">
+        <v>14.5</v>
+      </c>
+      <c r="BH16">
+        <v>3.55</v>
+      </c>
+      <c r="BI16">
+        <v>2.92</v>
+      </c>
+      <c r="BJ16">
+        <v>11.5</v>
+      </c>
+      <c r="BK16">
+        <v>6.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>14</v>
+      </c>
+      <c r="BN16">
+        <v>3.95</v>
+      </c>
+      <c r="BO16">
+        <v>3.25</v>
+      </c>
+      <c r="BP16">
+        <v>10</v>
+      </c>
+      <c r="BQ16">
+        <v>7.6</v>
+      </c>
+      <c r="BR16">
+        <v>27</v>
+      </c>
+      <c r="BS16">
+        <v>9.6</v>
+      </c>
+      <c r="BT16">
+        <v>11</v>
+      </c>
+      <c r="BU16">
+        <v>6.4</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>12.5</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>12.5</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17">
+        <v>1.6</v>
+      </c>
+      <c r="G17">
+        <v>1.63</v>
+      </c>
+      <c r="H17">
+        <v>7.2</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17">
         <v>4</v>
       </c>
-      <c r="BO15">
-        <v>3.4</v>
-      </c>
-      <c r="BP15">
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>1.47</v>
+      </c>
+      <c r="M17">
+        <v>1.09</v>
+      </c>
+      <c r="N17">
+        <v>3.3</v>
+      </c>
+      <c r="O17">
+        <v>1.4</v>
+      </c>
+      <c r="P17">
+        <v>1.76</v>
+      </c>
+      <c r="Q17">
+        <v>2.22</v>
+      </c>
+      <c r="R17">
+        <v>1.28</v>
+      </c>
+      <c r="S17">
+        <v>4.3</v>
+      </c>
+      <c r="T17">
+        <v>2.18</v>
+      </c>
+      <c r="U17">
+        <v>1.75</v>
+      </c>
+      <c r="V17">
+        <v>1.15</v>
+      </c>
+      <c r="W17">
+        <v>2.58</v>
+      </c>
+      <c r="X17">
+        <v>13</v>
+      </c>
+      <c r="Y17">
+        <v>23</v>
+      </c>
+      <c r="Z17">
+        <v>75</v>
+      </c>
+      <c r="AA17">
+        <v>310</v>
+      </c>
+      <c r="AB17">
+        <v>6.8</v>
+      </c>
+      <c r="AC17">
+        <v>9.4</v>
+      </c>
+      <c r="AD17">
+        <v>32</v>
+      </c>
+      <c r="AE17">
+        <v>160</v>
+      </c>
+      <c r="AF17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG17">
         <v>11</v>
       </c>
-      <c r="BQ15">
+      <c r="AH17">
+        <v>28</v>
+      </c>
+      <c r="AI17">
+        <v>150</v>
+      </c>
+      <c r="AJ17">
+        <v>15.5</v>
+      </c>
+      <c r="AK17">
+        <v>23</v>
+      </c>
+      <c r="AL17">
+        <v>55</v>
+      </c>
+      <c r="AM17">
+        <v>220</v>
+      </c>
+      <c r="AN17">
+        <v>12.5</v>
+      </c>
+      <c r="AO17">
+        <v>260</v>
+      </c>
+      <c r="AP17">
+        <v>10</v>
+      </c>
+      <c r="AQ17">
+        <v>17.5</v>
+      </c>
+      <c r="AR17">
+        <v>8</v>
+      </c>
+      <c r="AS17">
+        <v>8.6</v>
+      </c>
+      <c r="AT17">
+        <v>5.8</v>
+      </c>
+      <c r="AU17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV17">
+        <v>24</v>
+      </c>
+      <c r="AW17">
         <v>8.4</v>
       </c>
-      <c r="BR15">
-        <v>34</v>
-      </c>
-      <c r="BS15">
-        <v>7.2</v>
-      </c>
-      <c r="BT15">
-        <v>11</v>
-      </c>
-      <c r="BU15">
-        <v>5</v>
-      </c>
-      <c r="BV15">
+      <c r="AX17">
+        <v>7.6</v>
+      </c>
+      <c r="AY17">
+        <v>9</v>
+      </c>
+      <c r="AZ17">
+        <v>7</v>
+      </c>
+      <c r="BA17">
+        <v>8.4</v>
+      </c>
+      <c r="BB17">
+        <v>13</v>
+      </c>
+      <c r="BC17">
+        <v>17</v>
+      </c>
+      <c r="BD17">
+        <v>7.6</v>
+      </c>
+      <c r="BE17">
+        <v>8.6</v>
+      </c>
+      <c r="BF17">
+        <v>10</v>
+      </c>
+      <c r="BG17">
+        <v>8.6</v>
+      </c>
+      <c r="BH17">
+        <v>3.55</v>
+      </c>
+      <c r="BI17">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17">
+        <v>12.5</v>
+      </c>
+      <c r="BK17">
+        <v>4.4</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>6.6</v>
+      </c>
+      <c r="BN17">
+        <v>4.4</v>
+      </c>
+      <c r="BO17">
+        <v>3.15</v>
+      </c>
+      <c r="BP17">
+        <v>11.5</v>
+      </c>
+      <c r="BQ17">
+        <v>8.4</v>
+      </c>
+      <c r="BR17">
+        <v>32</v>
+      </c>
+      <c r="BS17">
+        <v>5.6</v>
+      </c>
+      <c r="BT17">
+        <v>12</v>
+      </c>
+      <c r="BU17">
+        <v>8.4</v>
+      </c>
+      <c r="BV17">
         <v>80</v>
       </c>
-      <c r="BW15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX15">
+      <c r="BW17">
+        <v>6.2</v>
+      </c>
+      <c r="BX17">
         <v>95</v>
       </c>
-      <c r="BY15">
-        <v>8.4</v>
-      </c>
-      <c r="BZ15">
-        <v>29</v>
-      </c>
-      <c r="CA15">
-        <v>7</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>130</v>
+      <c r="BY17">
+        <v>6.2</v>
+      </c>
+      <c r="BZ17">
+        <v>28</v>
+      </c>
+      <c r="CA17">
+        <v>5.4</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-20.xlsx
@@ -421,7 +421,7 @@
     <t>America MG</t>
   </si>
   <si>
-    <t>2026-08-20 08:58:19</t>
+    <t>2026-08-20 11:18:52</t>
   </si>
 </sst>
 </file>
@@ -1015,226 +1015,226 @@
         <v>119</v>
       </c>
       <c r="F2">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>820</v>
       </c>
       <c r="H2">
-        <v>2.96</v>
+        <v>1.21</v>
       </c>
       <c r="I2">
-        <v>3.2</v>
+        <v>920</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>1.12</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>1.19</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>1.1</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="R2">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>100</v>
       </c>
       <c r="T2">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
+        <v>1.26</v>
+      </c>
+      <c r="AD2">
+        <v>26</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>810</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.09</v>
+      </c>
+      <c r="AQ2">
+        <v>5.8</v>
+      </c>
+      <c r="AR2">
+        <v>1.09</v>
+      </c>
+      <c r="AS2">
+        <v>1.09</v>
+      </c>
+      <c r="AT2">
+        <v>5.8</v>
+      </c>
+      <c r="AU2">
+        <v>1.23</v>
+      </c>
+      <c r="AV2">
+        <v>8.4</v>
+      </c>
+      <c r="AW2">
+        <v>8.4</v>
+      </c>
+      <c r="AX2">
+        <v>1.09</v>
+      </c>
+      <c r="AY2">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2">
+        <v>7.8</v>
+      </c>
+      <c r="BA2">
+        <v>7.8</v>
+      </c>
+      <c r="BB2">
+        <v>1.09</v>
+      </c>
+      <c r="BC2">
+        <v>8.4</v>
+      </c>
+      <c r="BD2">
+        <v>8.4</v>
+      </c>
+      <c r="BE2">
+        <v>7.8</v>
+      </c>
+      <c r="BF2">
+        <v>7.8</v>
+      </c>
+      <c r="BG2">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD2">
-        <v>13.5</v>
-      </c>
-      <c r="AE2">
-        <v>34</v>
-      </c>
-      <c r="AF2">
-        <v>17.5</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
-      </c>
-      <c r="AH2">
-        <v>17</v>
-      </c>
-      <c r="AI2">
-        <v>100</v>
-      </c>
-      <c r="AJ2">
-        <v>38</v>
-      </c>
-      <c r="AK2">
-        <v>28</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>85</v>
-      </c>
-      <c r="AN2">
-        <v>22</v>
-      </c>
-      <c r="AO2">
-        <v>30</v>
-      </c>
-      <c r="AP2">
-        <v>13</v>
-      </c>
-      <c r="AQ2">
-        <v>11.5</v>
-      </c>
-      <c r="AR2">
-        <v>18</v>
-      </c>
-      <c r="AS2">
-        <v>22</v>
-      </c>
-      <c r="AT2">
-        <v>10.5</v>
-      </c>
-      <c r="AU2">
-        <v>8</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>10.5</v>
-      </c>
-      <c r="AX2">
-        <v>14.5</v>
-      </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>26</v>
-      </c>
-      <c r="BB2">
-        <v>30</v>
-      </c>
-      <c r="BC2">
-        <v>22</v>
-      </c>
-      <c r="BD2">
-        <v>32</v>
-      </c>
-      <c r="BE2">
-        <v>70</v>
-      </c>
-      <c r="BF2">
-        <v>17.5</v>
-      </c>
-      <c r="BG2">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH2">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>135</v>
@@ -1257,31 +1257,31 @@
         <v>120</v>
       </c>
       <c r="F3">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="G3">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
         <v>1.22</v>
@@ -1290,193 +1290,193 @@
         <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="X3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB3">
         <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
+        <v>16.5</v>
+      </c>
+      <c r="AE3">
+        <v>65</v>
+      </c>
+      <c r="AF3">
         <v>15.5</v>
       </c>
-      <c r="AE3">
-        <v>44</v>
-      </c>
-      <c r="AF3">
-        <v>16.5</v>
-      </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>16</v>
       </c>
       <c r="AI3">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
         <v>38</v>
       </c>
       <c r="AM3">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AP3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AS3">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB3">
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BF3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BG3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3">
         <v>9.199999999999999</v>
       </c>
       <c r="BK3">
-        <v>4.8</v>
+        <v>2.34</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
+        <v>3</v>
+      </c>
+      <c r="BN3">
+        <v>5.2</v>
+      </c>
+      <c r="BO3">
+        <v>3.9</v>
+      </c>
+      <c r="BP3">
+        <v>13.5</v>
+      </c>
+      <c r="BQ3">
         <v>9.199999999999999</v>
       </c>
-      <c r="BN3">
-        <v>5.5</v>
-      </c>
-      <c r="BO3">
-        <v>4.5</v>
-      </c>
-      <c r="BP3">
-        <v>15</v>
-      </c>
-      <c r="BQ3">
-        <v>6</v>
-      </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>2.76</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
         <v>6</v>
       </c>
       <c r="BV3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW3">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY3">
-        <v>7.8</v>
+        <v>2.88</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>135</v>
@@ -1499,220 +1499,220 @@
         <v>121</v>
       </c>
       <c r="F4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H4">
         <v>9.4</v>
       </c>
       <c r="I4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J4">
         <v>6.2</v>
       </c>
       <c r="K4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M4">
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="O4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q4">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="R4">
         <v>2.02</v>
       </c>
       <c r="S4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U4">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="V4">
         <v>1.1</v>
       </c>
       <c r="W4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="X4">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="Y4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z4">
         <v>120</v>
       </c>
       <c r="AA4">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AB4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AD4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AE4">
+        <v>200</v>
+      </c>
+      <c r="AF4">
+        <v>11.5</v>
+      </c>
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4">
+        <v>29</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>12.5</v>
+      </c>
+      <c r="AK4">
+        <v>14.5</v>
+      </c>
+      <c r="AL4">
+        <v>29</v>
+      </c>
+      <c r="AM4">
+        <v>110</v>
+      </c>
+      <c r="AN4">
+        <v>3.7</v>
+      </c>
+      <c r="AO4">
         <v>130</v>
       </c>
-      <c r="AF4">
-        <v>12.5</v>
-      </c>
-      <c r="AG4">
+      <c r="AP4">
+        <v>19.5</v>
+      </c>
+      <c r="AQ4">
+        <v>23</v>
+      </c>
+      <c r="AR4">
+        <v>32</v>
+      </c>
+      <c r="AS4">
+        <v>7.8</v>
+      </c>
+      <c r="AT4">
+        <v>11.5</v>
+      </c>
+      <c r="AU4">
+        <v>13.5</v>
+      </c>
+      <c r="AV4">
+        <v>30</v>
+      </c>
+      <c r="AW4">
+        <v>8</v>
+      </c>
+      <c r="AX4">
+        <v>9.6</v>
+      </c>
+      <c r="AY4">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4">
         <v>12</v>
       </c>
-      <c r="AH4">
-        <v>24</v>
-      </c>
-      <c r="AI4">
-        <v>230</v>
-      </c>
-      <c r="AJ4">
-        <v>13</v>
-      </c>
-      <c r="AK4">
-        <v>16</v>
-      </c>
-      <c r="AL4">
-        <v>27</v>
-      </c>
-      <c r="AM4">
-        <v>90</v>
-      </c>
-      <c r="AN4">
-        <v>3.6</v>
-      </c>
-      <c r="AO4">
-        <v>110</v>
-      </c>
-      <c r="AP4">
-        <v>29</v>
-      </c>
-      <c r="AQ4">
-        <v>40</v>
-      </c>
-      <c r="AR4">
-        <v>34</v>
-      </c>
-      <c r="AS4">
-        <v>10</v>
-      </c>
-      <c r="AT4">
-        <v>13</v>
-      </c>
-      <c r="AU4">
-        <v>14</v>
-      </c>
-      <c r="AV4">
-        <v>29</v>
-      </c>
-      <c r="AW4">
-        <v>70</v>
-      </c>
-      <c r="AX4">
+      <c r="BA4">
+        <v>7.6</v>
+      </c>
+      <c r="BB4">
         <v>10.5</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>20</v>
-      </c>
-      <c r="BA4">
-        <v>44</v>
-      </c>
-      <c r="BB4">
-        <v>11</v>
       </c>
       <c r="BC4">
         <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BF4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BG4">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>6.8</v>
       </c>
       <c r="BI4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="BL4">
         <v>100</v>
       </c>
       <c r="BM4">
+        <v>5.4</v>
+      </c>
+      <c r="BN4">
+        <v>5.2</v>
+      </c>
+      <c r="BO4">
+        <v>3.45</v>
+      </c>
+      <c r="BP4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ4">
+        <v>6</v>
+      </c>
+      <c r="BR4">
+        <v>20</v>
+      </c>
+      <c r="BS4">
         <v>4.4</v>
       </c>
-      <c r="BN4">
+      <c r="BT4">
+        <v>14</v>
+      </c>
+      <c r="BU4">
+        <v>4</v>
+      </c>
+      <c r="BV4">
+        <v>80</v>
+      </c>
+      <c r="BW4">
         <v>5.3</v>
       </c>
-      <c r="BO4">
-        <v>3.55</v>
-      </c>
-      <c r="BP4">
-        <v>9</v>
-      </c>
-      <c r="BQ4">
-        <v>5.6</v>
-      </c>
-      <c r="BR4">
-        <v>21</v>
-      </c>
-      <c r="BS4">
-        <v>3.8</v>
-      </c>
-      <c r="BT4">
-        <v>16</v>
-      </c>
-      <c r="BU4">
-        <v>3.6</v>
-      </c>
-      <c r="BV4">
-        <v>75</v>
-      </c>
-      <c r="BW4">
-        <v>4.3</v>
-      </c>
       <c r="BX4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>122</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="I5">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
         <v>3.65</v>
@@ -1759,208 +1759,208 @@
         <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="X5">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y5">
         <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>16</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>75</v>
       </c>
       <c r="AN5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AP5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AQ5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AT5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AX5">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BO5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS5">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BT5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY5">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
         <v>22</v>
       </c>
       <c r="CA5">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="s">
         <v>135</v>
@@ -1983,13 +1983,13 @@
         <v>123</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="G6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I6">
         <v>1.26</v>
@@ -1998,37 +1998,37 @@
         <v>6.8</v>
       </c>
       <c r="K6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T6">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U6">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="V6">
         <v>4.8</v>
@@ -2037,22 +2037,22 @@
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA6">
         <v>9.4</v>
       </c>
       <c r="AB6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD6">
         <v>11.5</v>
@@ -2061,52 +2061,52 @@
         <v>14.5</v>
       </c>
       <c r="AF6">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AG6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AH6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AI6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AL6">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AM6">
         <v>260</v>
       </c>
       <c r="AN6">
-        <v>460</v>
+        <v>540</v>
       </c>
       <c r="AO6">
         <v>4.5</v>
       </c>
       <c r="AP6">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AQ6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS6">
         <v>8.199999999999999</v>
       </c>
       <c r="AT6">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AU6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV6">
         <v>10</v>
@@ -2115,70 +2115,70 @@
         <v>12</v>
       </c>
       <c r="AX6">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AZ6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA6">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BB6">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BE6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BM6">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BO6">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BP6">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BQ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6">
         <v>130</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT6">
         <v>3.65</v>
@@ -2190,19 +2190,19 @@
         <v>7</v>
       </c>
       <c r="BW6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BX6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY6">
         <v>6.8</v>
       </c>
       <c r="BZ6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CB6" t="s">
         <v>135</v>
@@ -2225,52 +2225,52 @@
         <v>124</v>
       </c>
       <c r="F7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G7">
         <v>1.84</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I7">
         <v>7.2</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
         <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M7">
         <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O7">
         <v>1.48</v>
       </c>
       <c r="P7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q7">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
         <v>1.21</v>
       </c>
       <c r="S7">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
         <v>1.18</v>
@@ -2282,7 +2282,7 @@
         <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z7">
         <v>55</v>
@@ -2294,10 +2294,10 @@
         <v>6.6</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE7">
         <v>500</v>
@@ -2315,7 +2315,7 @@
         <v>500</v>
       </c>
       <c r="AJ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK7">
         <v>25</v>
@@ -2327,22 +2327,22 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO7">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AP7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT7">
         <v>5.3</v>
@@ -2351,13 +2351,13 @@
         <v>7</v>
       </c>
       <c r="AV7">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AW7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
         <v>9</v>
@@ -2366,37 +2366,37 @@
         <v>11</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB7">
+        <v>16.5</v>
+      </c>
+      <c r="BC7">
+        <v>20</v>
+      </c>
+      <c r="BD7">
+        <v>7</v>
+      </c>
+      <c r="BE7">
+        <v>7.8</v>
+      </c>
+      <c r="BF7">
         <v>15.5</v>
       </c>
-      <c r="BC7">
-        <v>19.5</v>
-      </c>
-      <c r="BD7">
-        <v>6.8</v>
-      </c>
-      <c r="BE7">
-        <v>7.4</v>
-      </c>
-      <c r="BF7">
-        <v>14</v>
-      </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH7">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI7">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7">
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2411,13 +2411,13 @@
         <v>3.15</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS7">
         <v>8.4</v>
@@ -2426,16 +2426,16 @@
         <v>10</v>
       </c>
       <c r="BU7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW7">
         <v>9.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY7">
         <v>9.6</v>
@@ -2467,22 +2467,22 @@
         <v>125</v>
       </c>
       <c r="F8">
+        <v>2.84</v>
+      </c>
+      <c r="G8">
+        <v>2.92</v>
+      </c>
+      <c r="H8">
+        <v>2.66</v>
+      </c>
+      <c r="I8">
         <v>2.72</v>
-      </c>
-      <c r="G8">
-        <v>2.74</v>
-      </c>
-      <c r="H8">
-        <v>2.8</v>
-      </c>
-      <c r="I8">
-        <v>2.84</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
         <v>1.42</v>
@@ -2503,34 +2503,34 @@
         <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T8">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
         <v>2.2</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
         <v>14</v>
       </c>
       <c r="Y8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB8">
         <v>11.5</v>
@@ -2539,52 +2539,52 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE8">
         <v>30</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI8">
         <v>44</v>
       </c>
       <c r="AJ8">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN8">
         <v>27</v>
       </c>
       <c r="AO8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP8">
         <v>13</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR8">
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
@@ -2596,37 +2596,37 @@
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
         <v>16</v>
       </c>
       <c r="BA8">
+        <v>38</v>
+      </c>
+      <c r="BB8">
         <v>40</v>
       </c>
-      <c r="BB8">
-        <v>36</v>
-      </c>
       <c r="BC8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD8">
         <v>38</v>
       </c>
       <c r="BE8">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF8">
+        <v>25</v>
+      </c>
+      <c r="BG8">
         <v>23</v>
-      </c>
-      <c r="BG8">
-        <v>24</v>
       </c>
       <c r="BH8">
         <v>3.35</v>
@@ -2638,55 +2638,55 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="BN8">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BO8">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP8">
         <v>26</v>
       </c>
       <c r="BQ8">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BR8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BT8">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW8">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX8">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BZ8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="s">
         <v>135</v>
@@ -2709,25 +2709,25 @@
         <v>126</v>
       </c>
       <c r="F9">
+        <v>2.36</v>
+      </c>
+      <c r="G9">
         <v>2.38</v>
       </c>
-      <c r="G9">
-        <v>2.4</v>
-      </c>
       <c r="H9">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I9">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M9">
         <v>1.12</v>
@@ -2739,46 +2739,46 @@
         <v>1.48</v>
       </c>
       <c r="P9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q9">
         <v>2.52</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S9">
         <v>5</v>
       </c>
       <c r="T9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U9">
         <v>1.91</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.72</v>
       </c>
       <c r="X9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB9">
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD9">
         <v>16</v>
@@ -2808,7 +2808,7 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN9">
         <v>30</v>
@@ -2817,7 +2817,7 @@
         <v>75</v>
       </c>
       <c r="AP9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
@@ -2853,7 +2853,7 @@
         <v>70</v>
       </c>
       <c r="BB9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC9">
         <v>28</v>
@@ -2886,7 +2886,7 @@
         <v>210</v>
       </c>
       <c r="BM9">
-        <v>18.5</v>
+        <v>150</v>
       </c>
       <c r="BN9">
         <v>4.9</v>
@@ -2895,19 +2895,19 @@
         <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BR9">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BT9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU9">
         <v>6</v>
@@ -2916,19 +2916,19 @@
         <v>40</v>
       </c>
       <c r="BW9">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BX9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BZ9">
         <v>48</v>
       </c>
       <c r="CA9">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CB9" t="s">
         <v>135</v>
@@ -2951,13 +2951,13 @@
         <v>127</v>
       </c>
       <c r="F10">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G10">
         <v>2.62</v>
       </c>
       <c r="H10">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I10">
         <v>3.25</v>
@@ -2966,7 +2966,7 @@
         <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
         <v>1.4</v>
@@ -2975,25 +2975,25 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q10">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S10">
         <v>3.4</v>
       </c>
       <c r="T10">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U10">
         <v>2.2</v>
@@ -3026,10 +3026,10 @@
         <v>14</v>
       </c>
       <c r="AE10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -3050,13 +3050,13 @@
         <v>40</v>
       </c>
       <c r="AM10">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN10">
         <v>23</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP10">
         <v>12.5</v>
@@ -3077,25 +3077,25 @@
         <v>7</v>
       </c>
       <c r="AV10">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AX10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
         <v>10</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA10">
         <v>30</v>
       </c>
       <c r="BB10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC10">
         <v>21</v>
@@ -3104,73 +3104,73 @@
         <v>27</v>
       </c>
       <c r="BE10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF10">
         <v>18</v>
       </c>
       <c r="BG10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BJ10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
         <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU10">
         <v>4.9</v>
       </c>
       <c r="BV10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="s">
         <v>135</v>
@@ -3193,19 +3193,19 @@
         <v>128</v>
       </c>
       <c r="F11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G11">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H11">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
         <v>6.4</v>
@@ -3226,13 +3226,13 @@
         <v>2.18</v>
       </c>
       <c r="Q11">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R11">
         <v>1.5</v>
       </c>
       <c r="S11">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
         <v>1.94</v>
@@ -3241,16 +3241,16 @@
         <v>1.82</v>
       </c>
       <c r="V11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W11">
         <v>3.3</v>
       </c>
       <c r="X11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y11">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z11">
         <v>110</v>
@@ -3262,97 +3262,97 @@
         <v>11</v>
       </c>
       <c r="AC11">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD11">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AE11">
         <v>190</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI11">
         <v>150</v>
       </c>
       <c r="AJ11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL11">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM11">
         <v>170</v>
       </c>
       <c r="AN11">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AO11">
         <v>240</v>
       </c>
       <c r="AP11">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11">
+        <v>6.2</v>
+      </c>
+      <c r="AR11">
+        <v>7</v>
+      </c>
+      <c r="AS11">
+        <v>7.4</v>
+      </c>
+      <c r="AT11">
+        <v>4.4</v>
+      </c>
+      <c r="AU11">
+        <v>4.8</v>
+      </c>
+      <c r="AV11">
+        <v>6.2</v>
+      </c>
+      <c r="AW11">
+        <v>7.2</v>
+      </c>
+      <c r="AX11">
+        <v>4.1</v>
+      </c>
+      <c r="AY11">
+        <v>4.5</v>
+      </c>
+      <c r="AZ11">
+        <v>6</v>
+      </c>
+      <c r="BA11">
+        <v>7.2</v>
+      </c>
+      <c r="BB11">
         <v>4.6</v>
       </c>
-      <c r="AR11">
-        <v>4.9</v>
-      </c>
-      <c r="AS11">
-        <v>5.1</v>
-      </c>
-      <c r="AT11">
-        <v>3.5</v>
-      </c>
-      <c r="AU11">
-        <v>3.85</v>
-      </c>
-      <c r="AV11">
-        <v>4.6</v>
-      </c>
-      <c r="AW11">
+      <c r="BC11">
         <v>5</v>
       </c>
-      <c r="AX11">
-        <v>3.4</v>
-      </c>
-      <c r="AY11">
-        <v>3.65</v>
-      </c>
-      <c r="AZ11">
-        <v>4.4</v>
-      </c>
-      <c r="BA11">
-        <v>5</v>
-      </c>
-      <c r="BB11">
-        <v>3.7</v>
-      </c>
-      <c r="BC11">
-        <v>3.95</v>
-      </c>
       <c r="BD11">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE11">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BF11">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="BG11">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BH11">
         <v>4.4</v>
@@ -3450,10 +3450,10 @@
         <v>2.78</v>
       </c>
       <c r="K12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L12">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M12">
         <v>1.13</v>
@@ -3465,16 +3465,16 @@
         <v>1.63</v>
       </c>
       <c r="P12">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
         <v>2.2</v>
@@ -3486,19 +3486,19 @@
         <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X12">
         <v>8.800000000000001</v>
       </c>
       <c r="Y12">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA12">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB12">
         <v>8.6</v>
@@ -3513,67 +3513,67 @@
         <v>60</v>
       </c>
       <c r="AF12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG12">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AJ12">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL12">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AM12">
         <v>290</v>
       </c>
       <c r="AN12">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AO12">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP12">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR12">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS12">
         <v>6</v>
       </c>
       <c r="AT12">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="AU12">
+        <v>3.45</v>
+      </c>
+      <c r="AV12">
+        <v>4.6</v>
+      </c>
+      <c r="AW12">
         <v>6</v>
       </c>
-      <c r="AV12">
-        <v>10.5</v>
-      </c>
-      <c r="AW12">
-        <v>38</v>
-      </c>
       <c r="AX12">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="AZ12">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA12">
         <v>6.2</v>
@@ -3588,73 +3588,73 @@
         <v>6.2</v>
       </c>
       <c r="BE12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG12">
         <v>6</v>
       </c>
       <c r="BH12">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BI12">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BJ12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK12">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>16.5</v>
+        <v>2.12</v>
       </c>
       <c r="BN12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO12">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BT12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU12">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>11</v>
+        <v>1.99</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>14</v>
+        <v>2.06</v>
       </c>
       <c r="CB12" t="s">
         <v>135</v>
@@ -3677,13 +3677,13 @@
         <v>130</v>
       </c>
       <c r="F13">
+        <v>1.6</v>
+      </c>
+      <c r="G13">
         <v>1.62</v>
       </c>
-      <c r="G13">
-        <v>1.64</v>
-      </c>
       <c r="H13">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I13">
         <v>7.8</v>
@@ -3692,43 +3692,43 @@
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q13">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U13">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W13">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X13">
         <v>11.5</v>
@@ -3746,55 +3746,55 @@
         <v>6.8</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD13">
         <v>29</v>
       </c>
       <c r="AE13">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF13">
         <v>8.199999999999999</v>
       </c>
       <c r="AG13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH13">
         <v>28</v>
       </c>
       <c r="AI13">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO13">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AP13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR13">
         <v>48</v>
       </c>
       <c r="AS13">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT13">
         <v>6</v>
@@ -3806,7 +3806,7 @@
         <v>25</v>
       </c>
       <c r="AW13">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AX13">
         <v>7.6</v>
@@ -3815,10 +3815,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA13">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB13">
         <v>13.5</v>
@@ -3827,37 +3827,37 @@
         <v>17</v>
       </c>
       <c r="BD13">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE13">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="BF13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG13">
         <v>100</v>
       </c>
       <c r="BH13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI13">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>3.15</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BO13">
         <v>3.55</v>
@@ -3866,16 +3866,16 @@
         <v>11</v>
       </c>
       <c r="BQ13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR13">
         <v>34</v>
       </c>
       <c r="BS13">
+        <v>10</v>
+      </c>
+      <c r="BT13">
         <v>11</v>
-      </c>
-      <c r="BT13">
-        <v>10.5</v>
       </c>
       <c r="BU13">
         <v>6.2</v>
@@ -3884,19 +3884,19 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BZ13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA13">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="s">
         <v>135</v>
@@ -3919,19 +3919,19 @@
         <v>131</v>
       </c>
       <c r="F14">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G14">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H14">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
         <v>2.98</v>
-      </c>
-      <c r="J14">
-        <v>2.96</v>
       </c>
       <c r="K14">
         <v>3.3</v>
@@ -3940,31 +3940,31 @@
         <v>1.59</v>
       </c>
       <c r="M14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N14">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O14">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P14">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T14">
         <v>2.1</v>
       </c>
       <c r="U14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V14">
         <v>1.51</v>
@@ -3973,7 +3973,7 @@
         <v>1.47</v>
       </c>
       <c r="X14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8.800000000000001</v>
@@ -4003,13 +4003,13 @@
         <v>15</v>
       </c>
       <c r="AH14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AJ14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AK14">
         <v>46</v>
@@ -4021,22 +4021,22 @@
         <v>500</v>
       </c>
       <c r="AN14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AO14">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR14">
         <v>15</v>
       </c>
       <c r="AS14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AT14">
         <v>7</v>
@@ -4051,7 +4051,7 @@
         <v>36</v>
       </c>
       <c r="AX14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY14">
         <v>12</v>
@@ -4066,7 +4066,7 @@
         <v>38</v>
       </c>
       <c r="BC14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD14">
         <v>48</v>
@@ -4078,19 +4078,19 @@
         <v>46</v>
       </c>
       <c r="BG14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH14">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI14">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4105,7 +4105,7 @@
         <v>4.7</v>
       </c>
       <c r="BP14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ14">
         <v>8.6</v>
@@ -4114,10 +4114,10 @@
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT14">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU14">
         <v>4.4</v>
@@ -4129,7 +4129,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
         <v>9.6</v>
@@ -4138,7 +4138,7 @@
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB14" t="s">
         <v>135</v>
@@ -4161,16 +4161,16 @@
         <v>132</v>
       </c>
       <c r="F15">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G15">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H15">
         <v>3.2</v>
       </c>
       <c r="I15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J15">
         <v>3.15</v>
@@ -4179,40 +4179,40 @@
         <v>3.25</v>
       </c>
       <c r="L15">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M15">
         <v>1.11</v>
       </c>
       <c r="N15">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q15">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R15">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T15">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U15">
         <v>1.94</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -4221,43 +4221,43 @@
         <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA15">
         <v>75</v>
       </c>
       <c r="AB15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>7.2</v>
       </c>
       <c r="AD15">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE15">
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AI15">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ15">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AK15">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AL15">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM15">
         <v>580</v>
@@ -4269,19 +4269,19 @@
         <v>65</v>
       </c>
       <c r="AP15">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ15">
         <v>9.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AS15">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AT15">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU15">
         <v>6.4</v>
@@ -4290,7 +4290,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX15">
         <v>13.5</v>
@@ -4302,43 +4302,43 @@
         <v>17.5</v>
       </c>
       <c r="BA15">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BB15">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BC15">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BD15">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BE15">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF15">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BG15">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BH15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI15">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ15">
         <v>12</v>
       </c>
       <c r="BK15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN15">
         <v>6</v>
@@ -4350,13 +4350,13 @@
         <v>25</v>
       </c>
       <c r="BQ15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR15">
         <v>46</v>
       </c>
       <c r="BS15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT15">
         <v>7</v>
@@ -4368,19 +4368,19 @@
         <v>34</v>
       </c>
       <c r="BW15">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BX15">
         <v>55</v>
       </c>
       <c r="BY15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ15">
         <v>46</v>
       </c>
       <c r="CA15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB15" t="s">
         <v>135</v>
@@ -4403,85 +4403,85 @@
         <v>133</v>
       </c>
       <c r="F16">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="G16">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L16">
+        <v>1.39</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>3.95</v>
+      </c>
+      <c r="O16">
+        <v>1.3</v>
+      </c>
+      <c r="P16">
+        <v>2.02</v>
+      </c>
+      <c r="Q16">
+        <v>1.9</v>
+      </c>
+      <c r="R16">
         <v>1.4</v>
       </c>
-      <c r="M16">
-        <v>1.07</v>
-      </c>
-      <c r="N16">
-        <v>3.9</v>
-      </c>
-      <c r="O16">
-        <v>1.31</v>
-      </c>
-      <c r="P16">
-        <v>2</v>
-      </c>
-      <c r="Q16">
-        <v>1.94</v>
-      </c>
-      <c r="R16">
-        <v>1.38</v>
-      </c>
       <c r="S16">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
         <v>2.02</v>
       </c>
       <c r="U16">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V16">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W16">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="X16">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z16">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA16">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AB16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC16">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE16">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AF16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG16">
         <v>11</v>
@@ -4490,52 +4490,52 @@
         <v>24</v>
       </c>
       <c r="AI16">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL16">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM16">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AN16">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO16">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ16">
         <v>20</v>
       </c>
       <c r="AR16">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AS16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU16">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW16">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AX16">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY16">
         <v>9.4</v>
@@ -4544,79 +4544,79 @@
         <v>21</v>
       </c>
       <c r="BA16">
+        <v>65</v>
+      </c>
+      <c r="BB16">
+        <v>11.5</v>
+      </c>
+      <c r="BC16">
+        <v>14.5</v>
+      </c>
+      <c r="BD16">
+        <v>34</v>
+      </c>
+      <c r="BE16">
+        <v>36</v>
+      </c>
+      <c r="BF16">
+        <v>7.6</v>
+      </c>
+      <c r="BG16">
         <v>14</v>
       </c>
-      <c r="BB16">
-        <v>13</v>
-      </c>
-      <c r="BC16">
-        <v>15.5</v>
-      </c>
-      <c r="BD16">
-        <v>32</v>
-      </c>
-      <c r="BE16">
-        <v>14.5</v>
-      </c>
-      <c r="BF16">
-        <v>8.4</v>
-      </c>
-      <c r="BG16">
-        <v>14.5</v>
-      </c>
       <c r="BH16">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI16">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ16">
         <v>11.5</v>
       </c>
       <c r="BK16">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BN16">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO16">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ16">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR16">
         <v>27</v>
       </c>
       <c r="BS16">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT16">
         <v>11</v>
       </c>
       <c r="BU16">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4654,7 +4654,7 @@
         <v>7.2</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4669,19 +4669,19 @@
         <v>1.09</v>
       </c>
       <c r="N17">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O17">
         <v>1.4</v>
       </c>
       <c r="P17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q17">
         <v>2.22</v>
       </c>
       <c r="R17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S17">
         <v>4.3</v>
@@ -4702,7 +4702,7 @@
         <v>13</v>
       </c>
       <c r="Y17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z17">
         <v>75</v>
@@ -4738,7 +4738,7 @@
         <v>15.5</v>
       </c>
       <c r="AK17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL17">
         <v>55</v>
@@ -4747,25 +4747,25 @@
         <v>220</v>
       </c>
       <c r="AN17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO17">
         <v>260</v>
       </c>
       <c r="AP17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS17">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT17">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU17">
         <v>8.199999999999999</v>
@@ -4774,7 +4774,7 @@
         <v>24</v>
       </c>
       <c r="AW17">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX17">
         <v>7.6</v>
@@ -4783,10 +4783,10 @@
         <v>9</v>
       </c>
       <c r="AZ17">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BA17">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB17">
         <v>13</v>
@@ -4795,76 +4795,76 @@
         <v>17</v>
       </c>
       <c r="BD17">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BE17">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF17">
         <v>10</v>
       </c>
       <c r="BG17">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH17">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI17">
         <v>2.64</v>
       </c>
       <c r="BJ17">
+        <v>14</v>
+      </c>
+      <c r="BK17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL17">
+        <v>240</v>
+      </c>
+      <c r="BM17">
+        <v>7.8</v>
+      </c>
+      <c r="BN17">
+        <v>4</v>
+      </c>
+      <c r="BO17">
+        <v>3.4</v>
+      </c>
+      <c r="BP17">
         <v>12.5</v>
       </c>
-      <c r="BK17">
-        <v>4.4</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>6.6</v>
-      </c>
-      <c r="BN17">
-        <v>4.4</v>
-      </c>
-      <c r="BO17">
-        <v>3.15</v>
-      </c>
-      <c r="BP17">
-        <v>11.5</v>
-      </c>
       <c r="BQ17">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR17">
         <v>32</v>
       </c>
       <c r="BS17">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU17">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
         <v>80</v>
       </c>
       <c r="BW17">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BX17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY17">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA17">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="CB17" t="s">
         <v>135</v>
